--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6D82F8-FC16-490D-B138-11FDCC07FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CEA9A0-2808-4C59-BD81-62BD32235626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1425" windowWidth="33090" windowHeight="18225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【テストターゲット名】_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体" sheetId="26" r:id="rId4"/>
-    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
+    <sheet name="【リクエストID】_クラス単体テスト" sheetId="25" r:id="rId3"/>
+    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="26" r:id="rId4"/>
+    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$450</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$312</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$450</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$450</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$312</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$450</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$Q$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="852">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -9259,10 +9259,6 @@
     <rPh sb="8" eb="9">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>リクエストID：XXX</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -13259,8 +13255,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7953375" y="285750"/>
-          <a:ext cx="1400175" cy="590550"/>
+          <a:off x="7905750" y="285750"/>
+          <a:ext cx="1390650" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -14787,8 +14783,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15497175" y="1647825"/>
-          <a:ext cx="4914900" cy="2733675"/>
+          <a:off x="15462250" y="1616075"/>
+          <a:ext cx="4899025" cy="2670175"/>
           <a:chOff x="16335375" y="4752975"/>
           <a:chExt cx="4914900" cy="2733675"/>
         </a:xfrm>
@@ -16408,9 +16404,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -16448,9 +16444,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -16483,26 +16479,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -16535,26 +16514,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16732,9 +16694,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K513"/>
-  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="6.58203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="6.625" style="3"/>
+    <col min="1" max="16384" width="6.58203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.5" customHeight="1">
@@ -16820,18 +16782,18 @@
       <c r="G31" s="10"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="6:11" ht="18.75">
+    <row r="32" spans="6:11" ht="19">
       <c r="F32" s="7"/>
       <c r="G32" s="10"/>
       <c r="H32" s="7"/>
       <c r="J32" s="11"/>
     </row>
-    <row r="33" spans="6:10" ht="18.75">
+    <row r="33" spans="6:10" ht="19">
       <c r="F33" s="7"/>
       <c r="H33" s="7"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="6:10" ht="18.75">
+    <row r="34" spans="6:10" ht="19">
       <c r="F34" s="7"/>
       <c r="H34" s="7"/>
       <c r="J34" s="11"/>
@@ -17334,9 +17296,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="11"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="24"/>
+    <col min="1" max="16384" width="3.58203125" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
@@ -18564,7 +18526,7 @@
       <c r="AH33" s="289"/>
       <c r="AI33" s="290"/>
     </row>
-    <row r="34" spans="1:35" ht="14.25">
+    <row r="34" spans="1:35" ht="14">
       <c r="K34" s="25"/>
     </row>
   </sheetData>
@@ -18763,18 +18725,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R312"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="31" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="30" customWidth="1"/>
-    <col min="6" max="6" width="40.625" style="30" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="30" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="30" customWidth="1"/>
-    <col min="10" max="11" width="25.625" style="30" customWidth="1"/>
+    <col min="1" max="2" width="8.58203125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="31" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="30" customWidth="1"/>
+    <col min="6" max="6" width="40.58203125" style="30" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="30" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="30" customWidth="1"/>
+    <col min="10" max="11" width="25.58203125" style="30" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="30" customWidth="1"/>
-    <col min="14" max="18" width="8.625" style="30" customWidth="1"/>
+    <col min="13" max="13" width="12.58203125" style="30" customWidth="1"/>
+    <col min="14" max="18" width="8.58203125" style="30" customWidth="1"/>
     <col min="19" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
@@ -18820,7 +18782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
       <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="33"/>
@@ -18897,7 +18859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -18926,7 +18888,7 @@
         <v>106</v>
       </c>
       <c r="G11" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H11" s="129"/>
       <c r="I11" s="129"/>
@@ -18940,7 +18902,7 @@
       <c r="Q11" s="136"/>
       <c r="R11" s="115"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -18963,7 +18925,7 @@
         <v>108</v>
       </c>
       <c r="G12" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H12" s="80"/>
       <c r="I12" s="80"/>
@@ -18977,7 +18939,7 @@
       <c r="Q12" s="82"/>
       <c r="R12" s="84"/>
     </row>
-    <row r="13" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="13" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A13" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -19002,7 +18964,7 @@
         <v>111</v>
       </c>
       <c r="G13" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H13" s="80"/>
       <c r="I13" s="80"/>
@@ -19016,7 +18978,7 @@
       <c r="Q13" s="83"/>
       <c r="R13" s="82"/>
     </row>
-    <row r="14" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="14" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A14" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -19037,7 +18999,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H14" s="80"/>
       <c r="I14" s="80"/>
@@ -19051,7 +19013,7 @@
       <c r="Q14" s="83"/>
       <c r="R14" s="82"/>
     </row>
-    <row r="15" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="15" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A15" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -19072,7 +19034,7 @@
         <v>113</v>
       </c>
       <c r="G15" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H15" s="80"/>
       <c r="I15" s="88"/>
@@ -19086,7 +19048,7 @@
       <c r="Q15" s="83"/>
       <c r="R15" s="82"/>
     </row>
-    <row r="16" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="16" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A16" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -19107,7 +19069,7 @@
         <v>114</v>
       </c>
       <c r="G16" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H16" s="80"/>
       <c r="I16" s="88"/>
@@ -19121,7 +19083,7 @@
       <c r="Q16" s="82"/>
       <c r="R16" s="84"/>
     </row>
-    <row r="17" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="17" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A17" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -19142,7 +19104,7 @@
         <v>115</v>
       </c>
       <c r="G17" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H17" s="80"/>
       <c r="I17" s="88"/>
@@ -19156,7 +19118,7 @@
       <c r="Q17" s="82"/>
       <c r="R17" s="84"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -19181,7 +19143,7 @@
         <v>118</v>
       </c>
       <c r="G18" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H18" s="80"/>
       <c r="I18" s="80"/>
@@ -19195,7 +19157,7 @@
       <c r="Q18" s="82"/>
       <c r="R18" s="84"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -19216,7 +19178,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H19" s="80"/>
       <c r="I19" s="80"/>
@@ -19230,7 +19192,7 @@
       <c r="Q19" s="82"/>
       <c r="R19" s="84"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -19251,7 +19213,7 @@
         <v>120</v>
       </c>
       <c r="G20" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H20" s="80"/>
       <c r="I20" s="88"/>
@@ -19265,7 +19227,7 @@
       <c r="Q20" s="82"/>
       <c r="R20" s="84"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -19288,7 +19250,7 @@
         <v>122</v>
       </c>
       <c r="G21" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H21" s="80"/>
       <c r="I21" s="80"/>
@@ -19302,7 +19264,7 @@
       <c r="Q21" s="82"/>
       <c r="R21" s="84"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -19323,7 +19285,7 @@
         <v>123</v>
       </c>
       <c r="G22" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H22" s="80"/>
       <c r="I22" s="80"/>
@@ -19337,7 +19299,7 @@
       <c r="Q22" s="82"/>
       <c r="R22" s="84"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -19358,7 +19320,7 @@
         <v>124</v>
       </c>
       <c r="G23" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H23" s="80"/>
       <c r="I23" s="80"/>
@@ -19372,7 +19334,7 @@
       <c r="Q23" s="82"/>
       <c r="R23" s="84"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -19393,7 +19355,7 @@
         <v>125</v>
       </c>
       <c r="G24" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H24" s="80"/>
       <c r="I24" s="80"/>
@@ -19407,7 +19369,7 @@
       <c r="Q24" s="82"/>
       <c r="R24" s="84"/>
     </row>
-    <row r="25" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="25" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A25" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -19432,7 +19394,7 @@
         <v>127</v>
       </c>
       <c r="G25" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H25" s="80"/>
       <c r="I25" s="80"/>
@@ -19446,7 +19408,7 @@
       <c r="Q25" s="83"/>
       <c r="R25" s="82"/>
     </row>
-    <row r="26" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="26" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A26" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E26),
@@ -19467,7 +19429,7 @@
         <v>128</v>
       </c>
       <c r="G26" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H26" s="80"/>
       <c r="I26" s="80"/>
@@ -19481,7 +19443,7 @@
       <c r="Q26" s="83"/>
       <c r="R26" s="82"/>
     </row>
-    <row r="27" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="27" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A27" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -19506,7 +19468,7 @@
         <v>131</v>
       </c>
       <c r="G27" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H27" s="80"/>
       <c r="I27" s="80"/>
@@ -19520,7 +19482,7 @@
       <c r="Q27" s="83"/>
       <c r="R27" s="82"/>
     </row>
-    <row r="28" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="28" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A28" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -19541,7 +19503,7 @@
         <v>132</v>
       </c>
       <c r="G28" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H28" s="80"/>
       <c r="I28" s="80"/>
@@ -19555,7 +19517,7 @@
       <c r="Q28" s="83"/>
       <c r="R28" s="82"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -19578,7 +19540,7 @@
         <v>134</v>
       </c>
       <c r="G29" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H29" s="80"/>
       <c r="I29" s="80"/>
@@ -19592,7 +19554,7 @@
       <c r="Q29" s="84"/>
       <c r="R29" s="84"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -19613,7 +19575,7 @@
         <v>135</v>
       </c>
       <c r="G30" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H30" s="80"/>
       <c r="I30" s="80"/>
@@ -19627,7 +19589,7 @@
       <c r="Q30" s="84"/>
       <c r="R30" s="84"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -19648,7 +19610,7 @@
         <v>136</v>
       </c>
       <c r="G31" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H31" s="80"/>
       <c r="I31" s="80"/>
@@ -19662,7 +19624,7 @@
       <c r="Q31" s="84"/>
       <c r="R31" s="84"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -19683,7 +19645,7 @@
         <v>137</v>
       </c>
       <c r="G32" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H32" s="80"/>
       <c r="I32" s="80"/>
@@ -19697,7 +19659,7 @@
       <c r="Q32" s="84"/>
       <c r="R32" s="84"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -19720,7 +19682,7 @@
         <v>139</v>
       </c>
       <c r="G33" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H33" s="80"/>
       <c r="I33" s="88"/>
@@ -19734,7 +19696,7 @@
       <c r="Q33" s="84"/>
       <c r="R33" s="84"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -19755,7 +19717,7 @@
         <v>140</v>
       </c>
       <c r="G34" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H34" s="80"/>
       <c r="I34" s="88"/>
@@ -19769,7 +19731,7 @@
       <c r="Q34" s="84"/>
       <c r="R34" s="84"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -19792,7 +19754,7 @@
         <v>142</v>
       </c>
       <c r="G35" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H35" s="88"/>
       <c r="I35" s="88"/>
@@ -19806,7 +19768,7 @@
       <c r="Q35" s="84"/>
       <c r="R35" s="84"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -19833,7 +19795,7 @@
         <v>144</v>
       </c>
       <c r="G36" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H36" s="87"/>
       <c r="I36" s="87"/>
@@ -19847,7 +19809,7 @@
       <c r="Q36" s="115"/>
       <c r="R36" s="115"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -19868,7 +19830,7 @@
         <v>145</v>
       </c>
       <c r="G37" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H37" s="87"/>
       <c r="I37" s="87"/>
@@ -19882,7 +19844,7 @@
       <c r="Q37" s="115"/>
       <c r="R37" s="115"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -19903,7 +19865,7 @@
         <v>146</v>
       </c>
       <c r="G38" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H38" s="87"/>
       <c r="I38" s="129"/>
@@ -19917,7 +19879,7 @@
       <c r="Q38" s="115"/>
       <c r="R38" s="115"/>
     </row>
-    <row r="39" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="39" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A39" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -19938,7 +19900,7 @@
         <v>147</v>
       </c>
       <c r="G39" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H39" s="87"/>
       <c r="I39" s="129"/>
@@ -19952,7 +19914,7 @@
       <c r="Q39" s="136"/>
       <c r="R39" s="115"/>
     </row>
-    <row r="40" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="40" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A40" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -19977,7 +19939,7 @@
         <v>149</v>
       </c>
       <c r="G40" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H40" s="87"/>
       <c r="I40" s="87"/>
@@ -19991,7 +19953,7 @@
       <c r="Q40" s="136"/>
       <c r="R40" s="115"/>
     </row>
-    <row r="41" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="41" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A41" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A41" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E41),
@@ -20012,7 +19974,7 @@
         <v>150</v>
       </c>
       <c r="G41" s="87" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H41" s="87"/>
       <c r="I41" s="87"/>
@@ -20026,7 +19988,7 @@
       <c r="Q41" s="136"/>
       <c r="R41" s="115"/>
     </row>
-    <row r="42" spans="1:18" s="37" customFormat="1" ht="45">
+    <row r="42" spans="1:18" s="37" customFormat="1" ht="44">
       <c r="A42" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -20062,10 +20024,10 @@
         <v>29</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="K42" s="167" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L42" s="168" t="s">
         <v>524</v>
@@ -20079,7 +20041,7 @@
       <c r="Q42" s="171"/>
       <c r="R42" s="169"/>
     </row>
-    <row r="43" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="43" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A43" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -20107,7 +20069,7 @@
         <v>29</v>
       </c>
       <c r="J43" s="39" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="K43" s="167" t="s">
         <v>744</v>
@@ -20124,7 +20086,7 @@
       <c r="Q43" s="171"/>
       <c r="R43" s="169"/>
     </row>
-    <row r="44" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="44" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A44" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -20159,7 +20121,7 @@
       <c r="Q44" s="82"/>
       <c r="R44" s="84"/>
     </row>
-    <row r="45" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="45" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A45" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -20196,7 +20158,7 @@
       <c r="Q45" s="82"/>
       <c r="R45" s="84"/>
     </row>
-    <row r="46" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="46" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A46" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -20231,7 +20193,7 @@
       <c r="Q46" s="82"/>
       <c r="R46" s="84"/>
     </row>
-    <row r="47" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="47" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A47" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -20266,7 +20228,7 @@
       <c r="Q47" s="82"/>
       <c r="R47" s="84"/>
     </row>
-    <row r="48" spans="1:18" s="37" customFormat="1" ht="45">
+    <row r="48" spans="1:18" s="37" customFormat="1" ht="44">
       <c r="A48" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -20296,10 +20258,10 @@
         <v>29</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="K48" s="167" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L48" s="168" t="s">
         <v>524</v>
@@ -20313,7 +20275,7 @@
       <c r="Q48" s="171"/>
       <c r="R48" s="169"/>
     </row>
-    <row r="49" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="49" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A49" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -20341,7 +20303,7 @@
         <v>29</v>
       </c>
       <c r="J49" s="39" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="K49" s="167" t="s">
         <v>744</v>
@@ -20358,7 +20320,7 @@
       <c r="Q49" s="171"/>
       <c r="R49" s="169"/>
     </row>
-    <row r="50" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="50" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A50" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -20395,7 +20357,7 @@
       <c r="Q50" s="82"/>
       <c r="R50" s="84"/>
     </row>
-    <row r="51" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="51" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A51" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -20430,7 +20392,7 @@
       <c r="Q51" s="82"/>
       <c r="R51" s="84"/>
     </row>
-    <row r="52" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="52" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A52" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -20465,7 +20427,7 @@
       <c r="Q52" s="82"/>
       <c r="R52" s="84"/>
     </row>
-    <row r="53" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="53" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A53" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -20500,7 +20462,7 @@
       <c r="Q53" s="82"/>
       <c r="R53" s="84"/>
     </row>
-    <row r="54" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="54" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A54" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -20535,7 +20497,7 @@
       <c r="Q54" s="82"/>
       <c r="R54" s="84"/>
     </row>
-    <row r="55" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="55" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A55" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -20570,7 +20532,7 @@
       <c r="Q55" s="82"/>
       <c r="R55" s="84"/>
     </row>
-    <row r="56" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="56" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A56" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -20607,7 +20569,7 @@
       <c r="Q56" s="82"/>
       <c r="R56" s="84"/>
     </row>
-    <row r="57" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="57" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A57" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -20644,7 +20606,7 @@
       <c r="Q57" s="82"/>
       <c r="R57" s="84"/>
     </row>
-    <row r="58" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="58" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A58" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -20681,7 +20643,7 @@
       <c r="Q58" s="82"/>
       <c r="R58" s="84"/>
     </row>
-    <row r="59" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="59" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A59" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -20720,7 +20682,7 @@
       <c r="Q59" s="136"/>
       <c r="R59" s="115"/>
     </row>
-    <row r="60" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="60" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A60" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -20748,10 +20710,10 @@
         <v>741</v>
       </c>
       <c r="J60" s="141" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K60" s="167" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L60" s="97" t="s">
         <v>524</v>
@@ -20765,7 +20727,7 @@
       <c r="Q60" s="101"/>
       <c r="R60" s="98"/>
     </row>
-    <row r="61" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="61" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A61" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -20800,7 +20762,7 @@
       <c r="Q61" s="136"/>
       <c r="R61" s="115"/>
     </row>
-    <row r="62" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="62" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A62" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -20835,7 +20797,7 @@
       <c r="Q62" s="136"/>
       <c r="R62" s="115"/>
     </row>
-    <row r="63" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="63" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A63" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -20870,7 +20832,7 @@
       <c r="Q63" s="136"/>
       <c r="R63" s="115"/>
     </row>
-    <row r="64" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="64" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A64" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -20907,7 +20869,7 @@
       <c r="Q64" s="136"/>
       <c r="R64" s="115"/>
     </row>
-    <row r="65" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="65" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A65" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -20942,7 +20904,7 @@
       <c r="Q65" s="136"/>
       <c r="R65" s="115"/>
     </row>
-    <row r="66" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="66" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A66" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -20977,7 +20939,7 @@
       <c r="Q66" s="136"/>
       <c r="R66" s="115"/>
     </row>
-    <row r="67" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="67" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A67" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -21012,7 +20974,7 @@
       <c r="Q67" s="136"/>
       <c r="R67" s="115"/>
     </row>
-    <row r="68" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="68" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A68" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -21047,7 +21009,7 @@
       <c r="Q68" s="136"/>
       <c r="R68" s="115"/>
     </row>
-    <row r="69" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="69" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A69" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -21082,7 +21044,7 @@
       <c r="Q69" s="136"/>
       <c r="R69" s="115"/>
     </row>
-    <row r="70" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="70" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A70" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -21117,7 +21079,7 @@
       <c r="Q70" s="136"/>
       <c r="R70" s="115"/>
     </row>
-    <row r="71" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="71" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A71" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -21152,7 +21114,7 @@
       <c r="Q71" s="265"/>
       <c r="R71" s="182"/>
     </row>
-    <row r="72" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="72" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A72" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -21182,10 +21144,10 @@
         <v>742</v>
       </c>
       <c r="J72" s="102" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K72" s="102" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L72" s="102" t="s">
         <v>644</v>
@@ -21199,7 +21161,7 @@
       <c r="Q72" s="102"/>
       <c r="R72" s="102"/>
     </row>
-    <row r="73" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="73" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A73" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A73" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E73),
@@ -21225,10 +21187,10 @@
         <v>742</v>
       </c>
       <c r="J73" s="102" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K73" s="102" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L73" s="102" t="s">
         <v>644</v>
@@ -21242,7 +21204,7 @@
       <c r="Q73" s="102"/>
       <c r="R73" s="102"/>
     </row>
-    <row r="74" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="74" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A74" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A74" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E74),
@@ -21268,10 +21230,10 @@
         <v>742</v>
       </c>
       <c r="J74" s="102" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K74" s="102" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L74" s="102" t="s">
         <v>644</v>
@@ -21285,7 +21247,7 @@
       <c r="Q74" s="102"/>
       <c r="R74" s="102"/>
     </row>
-    <row r="75" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="75" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A75" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A75" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E75),
@@ -21311,10 +21273,10 @@
         <v>742</v>
       </c>
       <c r="J75" s="102" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="K75" s="102" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L75" s="102" t="s">
         <v>644</v>
@@ -21328,7 +21290,7 @@
       <c r="Q75" s="102"/>
       <c r="R75" s="102"/>
     </row>
-    <row r="76" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="76" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A76" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A76" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E76),
@@ -21354,10 +21316,10 @@
         <v>742</v>
       </c>
       <c r="J76" s="102" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K76" s="102" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L76" s="102" t="s">
         <v>644</v>
@@ -21371,7 +21333,7 @@
       <c r="Q76" s="102"/>
       <c r="R76" s="102"/>
     </row>
-    <row r="77" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="77" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A77" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -21397,10 +21359,10 @@
         <v>742</v>
       </c>
       <c r="J77" s="102" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K77" s="102" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L77" s="102" t="s">
         <v>644</v>
@@ -21414,7 +21376,7 @@
       <c r="Q77" s="102"/>
       <c r="R77" s="102"/>
     </row>
-    <row r="78" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="78" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A78" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -21440,10 +21402,10 @@
         <v>742</v>
       </c>
       <c r="J78" s="102" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K78" s="102" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L78" s="102" t="s">
         <v>644</v>
@@ -21457,7 +21419,7 @@
       <c r="Q78" s="102"/>
       <c r="R78" s="102"/>
     </row>
-    <row r="79" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="79" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A79" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -21483,10 +21445,10 @@
         <v>742</v>
       </c>
       <c r="J79" s="102" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K79" s="102" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L79" s="102" t="s">
         <v>644</v>
@@ -21500,7 +21462,7 @@
       <c r="Q79" s="102"/>
       <c r="R79" s="102"/>
     </row>
-    <row r="80" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="80" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A80" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A80" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E80),
@@ -21526,10 +21488,10 @@
         <v>742</v>
       </c>
       <c r="J80" s="102" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K80" s="102" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L80" s="102" t="s">
         <v>644</v>
@@ -21543,7 +21505,7 @@
       <c r="Q80" s="102"/>
       <c r="R80" s="102"/>
     </row>
-    <row r="81" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="81" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A81" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -21570,13 +21532,13 @@
         <v>522</v>
       </c>
       <c r="I81" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J81" s="102" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K81" s="102" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L81" s="102" t="s">
         <v>644</v>
@@ -21590,7 +21552,7 @@
       <c r="Q81" s="102"/>
       <c r="R81" s="102"/>
     </row>
-    <row r="82" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="82" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A82" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -21613,13 +21575,13 @@
         <v>522</v>
       </c>
       <c r="I82" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J82" s="102" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K82" s="102" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L82" s="102" t="s">
         <v>644</v>
@@ -21633,7 +21595,7 @@
       <c r="Q82" s="102"/>
       <c r="R82" s="102"/>
     </row>
-    <row r="83" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="83" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A83" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -21656,13 +21618,13 @@
         <v>522</v>
       </c>
       <c r="I83" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J83" s="102" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K83" s="102" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L83" s="102" t="s">
         <v>644</v>
@@ -21676,7 +21638,7 @@
       <c r="Q83" s="102"/>
       <c r="R83" s="102"/>
     </row>
-    <row r="84" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="84" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A84" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -21699,13 +21661,13 @@
         <v>522</v>
       </c>
       <c r="I84" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J84" s="102" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K84" s="102" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L84" s="102" t="s">
         <v>644</v>
@@ -21719,7 +21681,7 @@
       <c r="Q84" s="102"/>
       <c r="R84" s="102"/>
     </row>
-    <row r="85" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="85" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A85" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -21742,13 +21704,13 @@
         <v>522</v>
       </c>
       <c r="I85" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J85" s="102" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K85" s="102" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L85" s="102" t="s">
         <v>644</v>
@@ -21762,7 +21724,7 @@
       <c r="Q85" s="102"/>
       <c r="R85" s="102"/>
     </row>
-    <row r="86" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="86" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A86" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A86" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E86),
@@ -21785,13 +21747,13 @@
         <v>522</v>
       </c>
       <c r="I86" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J86" s="102" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K86" s="102" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L86" s="102" t="s">
         <v>644</v>
@@ -21805,7 +21767,7 @@
       <c r="Q86" s="102"/>
       <c r="R86" s="102"/>
     </row>
-    <row r="87" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="87" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A87" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -21828,13 +21790,13 @@
         <v>522</v>
       </c>
       <c r="I87" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J87" s="102" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="K87" s="102" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L87" s="102" t="s">
         <v>644</v>
@@ -21848,7 +21810,7 @@
       <c r="Q87" s="102"/>
       <c r="R87" s="102"/>
     </row>
-    <row r="88" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="88" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A88" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -21871,13 +21833,13 @@
         <v>522</v>
       </c>
       <c r="I88" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J88" s="102" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K88" s="102" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L88" s="102" t="s">
         <v>644</v>
@@ -21891,7 +21853,7 @@
       <c r="Q88" s="102"/>
       <c r="R88" s="102"/>
     </row>
-    <row r="89" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="89" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A89" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A89" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E89),
@@ -21914,13 +21876,13 @@
         <v>522</v>
       </c>
       <c r="I89" s="64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J89" s="102" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K89" s="102" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L89" s="102" t="s">
         <v>644</v>
@@ -21934,7 +21896,7 @@
       <c r="Q89" s="102"/>
       <c r="R89" s="102"/>
     </row>
-    <row r="90" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="90" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A90" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A90" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E90),
@@ -22041,7 +22003,7 @@
       <c r="Q92" s="115"/>
       <c r="R92" s="115"/>
     </row>
-    <row r="93" spans="1:18" ht="22.5">
+    <row r="93" spans="1:18" ht="22">
       <c r="A93" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -22076,7 +22038,7 @@
       <c r="Q93" s="115"/>
       <c r="R93" s="115"/>
     </row>
-    <row r="94" spans="1:18" ht="22.5">
+    <row r="94" spans="1:18" ht="22">
       <c r="A94" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -22117,7 +22079,7 @@
       <c r="Q94" s="84"/>
       <c r="R94" s="84"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -22189,7 +22151,7 @@
       <c r="Q96" s="84"/>
       <c r="R96" s="84"/>
     </row>
-    <row r="97" spans="1:18" ht="33.75">
+    <row r="97" spans="1:18" ht="33">
       <c r="A97" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -22226,7 +22188,7 @@
       <c r="Q97" s="84"/>
       <c r="R97" s="84"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -22261,7 +22223,7 @@
       <c r="Q98" s="84"/>
       <c r="R98" s="84"/>
     </row>
-    <row r="99" spans="1:18" ht="22.5">
+    <row r="99" spans="1:18" ht="22">
       <c r="A99" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -22298,7 +22260,7 @@
       <c r="Q99" s="84"/>
       <c r="R99" s="84"/>
     </row>
-    <row r="100" spans="1:18" ht="22.5">
+    <row r="100" spans="1:18" ht="22">
       <c r="A100" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -22335,7 +22297,7 @@
       <c r="Q100" s="84"/>
       <c r="R100" s="84"/>
     </row>
-    <row r="101" spans="1:18" ht="56.25">
+    <row r="101" spans="1:18" ht="55">
       <c r="A101" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A101" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E101),
@@ -22369,10 +22331,10 @@
         <v>742</v>
       </c>
       <c r="J101" s="39" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K101" s="169" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L101" s="168" t="s">
         <v>60</v>
@@ -22386,7 +22348,7 @@
       <c r="Q101" s="169"/>
       <c r="R101" s="169"/>
     </row>
-    <row r="102" spans="1:18" ht="56.25">
+    <row r="102" spans="1:18" ht="55">
       <c r="A102" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -22416,10 +22378,10 @@
         <v>742</v>
       </c>
       <c r="J102" s="39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K102" s="169" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L102" s="168" t="s">
         <v>60</v>
@@ -22433,7 +22395,7 @@
       <c r="Q102" s="169"/>
       <c r="R102" s="169"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -22470,7 +22432,7 @@
       <c r="Q103" s="115"/>
       <c r="R103" s="115"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -22504,10 +22466,10 @@
         <v>742</v>
       </c>
       <c r="J104" s="39" t="s">
+        <v>788</v>
+      </c>
+      <c r="K104" s="169" t="s">
         <v>789</v>
-      </c>
-      <c r="K104" s="169" t="s">
-        <v>790</v>
       </c>
       <c r="L104" s="168" t="s">
         <v>60</v>
@@ -22521,7 +22483,7 @@
       <c r="Q104" s="169"/>
       <c r="R104" s="169"/>
     </row>
-    <row r="105" spans="1:18" ht="45">
+    <row r="105" spans="1:18" ht="44">
       <c r="A105" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -22547,10 +22509,10 @@
         <v>742</v>
       </c>
       <c r="J105" s="39" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K105" s="169" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L105" s="168" t="s">
         <v>60</v>
@@ -22564,7 +22526,7 @@
       <c r="Q105" s="169"/>
       <c r="R105" s="169"/>
     </row>
-    <row r="106" spans="1:18" ht="33.75">
+    <row r="106" spans="1:18" ht="33">
       <c r="A106" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -22599,7 +22561,7 @@
       <c r="Q106" s="115"/>
       <c r="R106" s="115"/>
     </row>
-    <row r="107" spans="1:18" ht="56.25">
+    <row r="107" spans="1:18" ht="55">
       <c r="A107" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A107" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E107),
@@ -22629,10 +22591,10 @@
         <v>742</v>
       </c>
       <c r="J107" s="39" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K107" s="169" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L107" s="168" t="s">
         <v>60</v>
@@ -22646,7 +22608,7 @@
       <c r="Q107" s="169"/>
       <c r="R107" s="169"/>
     </row>
-    <row r="108" spans="1:18" ht="33.75">
+    <row r="108" spans="1:18" ht="33">
       <c r="A108" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -22683,7 +22645,7 @@
       <c r="Q108" s="115"/>
       <c r="R108" s="115"/>
     </row>
-    <row r="109" spans="1:18" ht="33.75">
+    <row r="109" spans="1:18" ht="33">
       <c r="A109" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -22718,7 +22680,7 @@
       <c r="Q109" s="115"/>
       <c r="R109" s="115"/>
     </row>
-    <row r="110" spans="1:18" ht="33.75">
+    <row r="110" spans="1:18" ht="33">
       <c r="A110" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A110" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E110),
@@ -22755,7 +22717,7 @@
       <c r="Q110" s="115"/>
       <c r="R110" s="115"/>
     </row>
-    <row r="111" spans="1:18" ht="22.5">
+    <row r="111" spans="1:18" ht="22">
       <c r="A111" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -22796,7 +22758,7 @@
       <c r="Q111" s="115"/>
       <c r="R111" s="115"/>
     </row>
-    <row r="112" spans="1:18" ht="33.75">
+    <row r="112" spans="1:18" ht="33">
       <c r="A112" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -22866,7 +22828,7 @@
       <c r="Q113" s="115"/>
       <c r="R113" s="115"/>
     </row>
-    <row r="114" spans="1:18" ht="33.75">
+    <row r="114" spans="1:18" ht="33">
       <c r="A114" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -22901,7 +22863,7 @@
       <c r="Q114" s="115"/>
       <c r="R114" s="115"/>
     </row>
-    <row r="115" spans="1:18" ht="33.75">
+    <row r="115" spans="1:18" ht="33">
       <c r="A115" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -22936,7 +22898,7 @@
       <c r="Q115" s="115"/>
       <c r="R115" s="115"/>
     </row>
-    <row r="116" spans="1:18" ht="56.25">
+    <row r="116" spans="1:18" ht="55">
       <c r="A116" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -22966,10 +22928,10 @@
         <v>742</v>
       </c>
       <c r="J116" s="39" t="s">
+        <v>792</v>
+      </c>
+      <c r="K116" s="169" t="s">
         <v>793</v>
-      </c>
-      <c r="K116" s="169" t="s">
-        <v>794</v>
       </c>
       <c r="L116" s="168" t="s">
         <v>524</v>
@@ -22983,7 +22945,7 @@
       <c r="Q116" s="169"/>
       <c r="R116" s="169"/>
     </row>
-    <row r="117" spans="1:18" ht="33.75">
+    <row r="117" spans="1:18" ht="33">
       <c r="A117" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -23018,7 +22980,7 @@
       <c r="Q117" s="115"/>
       <c r="R117" s="115"/>
     </row>
-    <row r="118" spans="1:18" ht="56.25">
+    <row r="118" spans="1:18" ht="55">
       <c r="A118" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -23046,10 +23008,10 @@
         <v>742</v>
       </c>
       <c r="J118" s="39" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="K118" s="169" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L118" s="168" t="s">
         <v>524</v>
@@ -23063,7 +23025,7 @@
       <c r="Q118" s="169"/>
       <c r="R118" s="169"/>
     </row>
-    <row r="119" spans="1:18" ht="33.75">
+    <row r="119" spans="1:18" ht="33">
       <c r="A119" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -23098,7 +23060,7 @@
       <c r="Q119" s="115"/>
       <c r="R119" s="115"/>
     </row>
-    <row r="120" spans="1:18" ht="33.75">
+    <row r="120" spans="1:18" ht="33">
       <c r="A120" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -23133,7 +23095,7 @@
       <c r="Q120" s="182"/>
       <c r="R120" s="182"/>
     </row>
-    <row r="121" spans="1:18" ht="33.75">
+    <row r="121" spans="1:18" ht="33">
       <c r="A121" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -23170,7 +23132,7 @@
       <c r="Q121" s="115"/>
       <c r="R121" s="115"/>
     </row>
-    <row r="122" spans="1:18" ht="33.75">
+    <row r="122" spans="1:18" ht="33">
       <c r="A122" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -23289,7 +23251,7 @@
       <c r="Q124" s="84"/>
       <c r="R124" s="84"/>
     </row>
-    <row r="125" spans="1:18" ht="22.5">
+    <row r="125" spans="1:18" ht="22">
       <c r="A125" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -23330,7 +23292,7 @@
       <c r="Q125" s="84"/>
       <c r="R125" s="84"/>
     </row>
-    <row r="126" spans="1:18" ht="22.5">
+    <row r="126" spans="1:18" ht="22">
       <c r="A126" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -23406,7 +23368,7 @@
       <c r="Q127" s="84"/>
       <c r="R127" s="84"/>
     </row>
-    <row r="128" spans="1:18" ht="22.5">
+    <row r="128" spans="1:18" ht="22">
       <c r="A128" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -23449,7 +23411,7 @@
       <c r="Q128" s="115"/>
       <c r="R128" s="115"/>
     </row>
-    <row r="129" spans="1:18" ht="22.5">
+    <row r="129" spans="1:18" ht="22">
       <c r="A129" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -23486,7 +23448,7 @@
       <c r="Q129" s="115"/>
       <c r="R129" s="115"/>
     </row>
-    <row r="130" spans="1:18" ht="22.5">
+    <row r="130" spans="1:18" ht="22">
       <c r="A130" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -23521,7 +23483,7 @@
       <c r="Q130" s="115"/>
       <c r="R130" s="115"/>
     </row>
-    <row r="131" spans="1:18" ht="22.5">
+    <row r="131" spans="1:18" ht="22">
       <c r="A131" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -23556,7 +23518,7 @@
       <c r="Q131" s="115"/>
       <c r="R131" s="115"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -23593,7 +23555,7 @@
       <c r="Q132" s="115"/>
       <c r="R132" s="115"/>
     </row>
-    <row r="133" spans="1:18" ht="22.5">
+    <row r="133" spans="1:18" ht="22">
       <c r="A133" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -23628,7 +23590,7 @@
       <c r="Q133" s="115"/>
       <c r="R133" s="115"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -23663,7 +23625,7 @@
       <c r="Q134" s="115"/>
       <c r="R134" s="115"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -23698,7 +23660,7 @@
       <c r="Q135" s="115"/>
       <c r="R135" s="115"/>
     </row>
-    <row r="136" spans="1:18" ht="33.75">
+    <row r="136" spans="1:18" ht="33">
       <c r="A136" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -23733,7 +23695,7 @@
       <c r="Q136" s="115"/>
       <c r="R136" s="115"/>
     </row>
-    <row r="137" spans="1:18" ht="33.75">
+    <row r="137" spans="1:18" ht="33">
       <c r="A137" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -23770,7 +23732,7 @@
       <c r="Q137" s="115"/>
       <c r="R137" s="115"/>
     </row>
-    <row r="138" spans="1:18" ht="33.75">
+    <row r="138" spans="1:18" ht="33">
       <c r="A138" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -23805,7 +23767,7 @@
       <c r="Q138" s="115"/>
       <c r="R138" s="115"/>
     </row>
-    <row r="139" spans="1:18" ht="45">
+    <row r="139" spans="1:18" ht="44">
       <c r="A139" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -23840,7 +23802,7 @@
       <c r="Q139" s="115"/>
       <c r="R139" s="115"/>
     </row>
-    <row r="140" spans="1:18" ht="45">
+    <row r="140" spans="1:18" ht="44">
       <c r="A140" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -23875,7 +23837,7 @@
       <c r="Q140" s="115"/>
       <c r="R140" s="115"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -23910,7 +23872,7 @@
       <c r="Q141" s="115"/>
       <c r="R141" s="115"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -23947,7 +23909,7 @@
       <c r="Q142" s="115"/>
       <c r="R142" s="115"/>
     </row>
-    <row r="143" spans="1:18" ht="33.75">
+    <row r="143" spans="1:18" ht="33">
       <c r="A143" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -23986,7 +23948,7 @@
       <c r="Q143" s="115"/>
       <c r="R143" s="115"/>
     </row>
-    <row r="144" spans="1:18" ht="33.75">
+    <row r="144" spans="1:18" ht="33">
       <c r="A144" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -24027,7 +23989,7 @@
       <c r="Q144" s="115"/>
       <c r="R144" s="115"/>
     </row>
-    <row r="145" spans="1:18" ht="22.5">
+    <row r="145" spans="1:18" ht="22">
       <c r="A145" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -24064,7 +24026,7 @@
       <c r="Q145" s="115"/>
       <c r="R145" s="115"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -24099,7 +24061,7 @@
       <c r="Q146" s="115"/>
       <c r="R146" s="115"/>
     </row>
-    <row r="147" spans="1:18" ht="45">
+    <row r="147" spans="1:18" ht="44">
       <c r="A147" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -24134,7 +24096,7 @@
       <c r="Q147" s="115"/>
       <c r="R147" s="115"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -24177,7 +24139,7 @@
       <c r="Q148" s="115"/>
       <c r="R148" s="115"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -24214,7 +24176,7 @@
       <c r="Q149" s="115"/>
       <c r="R149" s="115"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -24249,7 +24211,7 @@
       <c r="Q150" s="115"/>
       <c r="R150" s="115"/>
     </row>
-    <row r="151" spans="1:18" ht="22.5">
+    <row r="151" spans="1:18" ht="22">
       <c r="A151" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -24284,7 +24246,7 @@
       <c r="Q151" s="115"/>
       <c r="R151" s="115"/>
     </row>
-    <row r="152" spans="1:18" ht="22.5">
+    <row r="152" spans="1:18" ht="22">
       <c r="A152" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -24321,7 +24283,7 @@
       <c r="Q152" s="115"/>
       <c r="R152" s="115"/>
     </row>
-    <row r="153" spans="1:18" ht="33.75">
+    <row r="153" spans="1:18" ht="33">
       <c r="A153" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -24356,7 +24318,7 @@
       <c r="Q153" s="115"/>
       <c r="R153" s="115"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -24395,7 +24357,7 @@
       <c r="Q154" s="115"/>
       <c r="R154" s="115"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -24436,7 +24398,7 @@
       <c r="Q155" s="115"/>
       <c r="R155" s="115"/>
     </row>
-    <row r="156" spans="1:18" ht="33.75">
+    <row r="156" spans="1:18" ht="33">
       <c r="A156" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -24473,7 +24435,7 @@
       <c r="Q156" s="115"/>
       <c r="R156" s="115"/>
     </row>
-    <row r="157" spans="1:18" ht="33.75">
+    <row r="157" spans="1:18" ht="33">
       <c r="A157" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -24510,7 +24472,7 @@
       <c r="Q157" s="115"/>
       <c r="R157" s="115"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -24547,7 +24509,7 @@
       <c r="Q158" s="115"/>
       <c r="R158" s="115"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -24584,7 +24546,7 @@
       <c r="Q159" s="115"/>
       <c r="R159" s="115"/>
     </row>
-    <row r="160" spans="1:18" ht="22.5">
+    <row r="160" spans="1:18" ht="22">
       <c r="A160" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -24621,7 +24583,7 @@
       <c r="Q160" s="115"/>
       <c r="R160" s="115"/>
     </row>
-    <row r="161" spans="1:18" ht="22.5">
+    <row r="161" spans="1:18" ht="22">
       <c r="A161" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -24656,7 +24618,7 @@
       <c r="Q161" s="115"/>
       <c r="R161" s="115"/>
     </row>
-    <row r="162" spans="1:18" ht="22.5">
+    <row r="162" spans="1:18" ht="22">
       <c r="A162" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A162" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E162),
@@ -24691,7 +24653,7 @@
       <c r="Q162" s="115"/>
       <c r="R162" s="115"/>
     </row>
-    <row r="163" spans="1:18" ht="22.5">
+    <row r="163" spans="1:18" ht="22">
       <c r="A163" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A163" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E163),
@@ -24726,7 +24688,7 @@
       <c r="Q163" s="115"/>
       <c r="R163" s="115"/>
     </row>
-    <row r="164" spans="1:18" ht="22.5">
+    <row r="164" spans="1:18" ht="22">
       <c r="A164" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -24761,7 +24723,7 @@
       <c r="Q164" s="115"/>
       <c r="R164" s="115"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -24796,7 +24758,7 @@
       <c r="Q165" s="115"/>
       <c r="R165" s="115"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -24835,7 +24797,7 @@
       <c r="Q166" s="115"/>
       <c r="R166" s="115"/>
     </row>
-    <row r="167" spans="1:18" ht="22.5">
+    <row r="167" spans="1:18" ht="22">
       <c r="A167" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -24870,7 +24832,7 @@
       <c r="Q167" s="115"/>
       <c r="R167" s="115"/>
     </row>
-    <row r="168" spans="1:18" ht="33.75">
+    <row r="168" spans="1:18" ht="33">
       <c r="A168" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -24907,7 +24869,7 @@
       <c r="Q168" s="115"/>
       <c r="R168" s="115"/>
     </row>
-    <row r="169" spans="1:18" ht="33.75">
+    <row r="169" spans="1:18" ht="33">
       <c r="A169" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -24942,7 +24904,7 @@
       <c r="Q169" s="115"/>
       <c r="R169" s="115"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -24977,7 +24939,7 @@
       <c r="Q170" s="115"/>
       <c r="R170" s="115"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -25012,7 +24974,7 @@
       <c r="Q171" s="115"/>
       <c r="R171" s="115"/>
     </row>
-    <row r="172" spans="1:18" ht="33.75">
+    <row r="172" spans="1:18" ht="33">
       <c r="A172" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -25047,7 +25009,7 @@
       <c r="Q172" s="115"/>
       <c r="R172" s="115"/>
     </row>
-    <row r="173" spans="1:18" ht="22.5">
+    <row r="173" spans="1:18" ht="22">
       <c r="A173" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -25082,7 +25044,7 @@
       <c r="Q173" s="115"/>
       <c r="R173" s="115"/>
     </row>
-    <row r="174" spans="1:18" ht="22.5">
+    <row r="174" spans="1:18" ht="22">
       <c r="A174" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -25117,7 +25079,7 @@
       <c r="Q174" s="115"/>
       <c r="R174" s="115"/>
     </row>
-    <row r="175" spans="1:18" ht="33.75">
+    <row r="175" spans="1:18" ht="33">
       <c r="A175" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -25152,7 +25114,7 @@
       <c r="Q175" s="115"/>
       <c r="R175" s="115"/>
     </row>
-    <row r="176" spans="1:18" ht="33.75">
+    <row r="176" spans="1:18" ht="33">
       <c r="A176" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -25187,7 +25149,7 @@
       <c r="Q176" s="115"/>
       <c r="R176" s="115"/>
     </row>
-    <row r="177" spans="1:18" ht="33.75">
+    <row r="177" spans="1:18" ht="33">
       <c r="A177" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -25222,7 +25184,7 @@
       <c r="Q177" s="115"/>
       <c r="R177" s="115"/>
     </row>
-    <row r="178" spans="1:18" ht="33.75">
+    <row r="178" spans="1:18" ht="33">
       <c r="A178" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -25329,7 +25291,7 @@
       <c r="Q180" s="115"/>
       <c r="R180" s="115"/>
     </row>
-    <row r="181" spans="1:18" ht="22.5">
+    <row r="181" spans="1:18" ht="22">
       <c r="A181" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -25364,7 +25326,7 @@
       <c r="Q181" s="115"/>
       <c r="R181" s="115"/>
     </row>
-    <row r="182" spans="1:18" ht="22.5">
+    <row r="182" spans="1:18" ht="22">
       <c r="A182" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A182" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E182),
@@ -25399,7 +25361,7 @@
       <c r="Q182" s="115"/>
       <c r="R182" s="115"/>
     </row>
-    <row r="183" spans="1:18" ht="22.5">
+    <row r="183" spans="1:18" ht="22">
       <c r="A183" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -25434,7 +25396,7 @@
       <c r="Q183" s="115"/>
       <c r="R183" s="115"/>
     </row>
-    <row r="184" spans="1:18" ht="33.75">
+    <row r="184" spans="1:18" ht="33">
       <c r="A184" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -25469,7 +25431,7 @@
       <c r="Q184" s="115"/>
       <c r="R184" s="115"/>
     </row>
-    <row r="185" spans="1:18" ht="22.5">
+    <row r="185" spans="1:18" ht="22">
       <c r="A185" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -25504,7 +25466,7 @@
       <c r="Q185" s="115"/>
       <c r="R185" s="115"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -25541,7 +25503,7 @@
       <c r="Q186" s="115"/>
       <c r="R186" s="115"/>
     </row>
-    <row r="187" spans="1:18" ht="33.75">
+    <row r="187" spans="1:18" ht="33">
       <c r="A187" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -25576,7 +25538,7 @@
       <c r="Q187" s="115"/>
       <c r="R187" s="115"/>
     </row>
-    <row r="188" spans="1:18" ht="33.75">
+    <row r="188" spans="1:18" ht="33">
       <c r="A188" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -25611,7 +25573,7 @@
       <c r="Q188" s="115"/>
       <c r="R188" s="115"/>
     </row>
-    <row r="189" spans="1:18" ht="45">
+    <row r="189" spans="1:18" ht="44">
       <c r="A189" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -25646,7 +25608,7 @@
       <c r="Q189" s="115"/>
       <c r="R189" s="115"/>
     </row>
-    <row r="190" spans="1:18" ht="45">
+    <row r="190" spans="1:18" ht="44">
       <c r="A190" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -25681,7 +25643,7 @@
       <c r="Q190" s="115"/>
       <c r="R190" s="115"/>
     </row>
-    <row r="191" spans="1:18" ht="33.75">
+    <row r="191" spans="1:18" ht="33">
       <c r="A191" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -25716,7 +25678,7 @@
       <c r="Q191" s="115"/>
       <c r="R191" s="115"/>
     </row>
-    <row r="192" spans="1:18" ht="45">
+    <row r="192" spans="1:18" ht="44">
       <c r="A192" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -25751,7 +25713,7 @@
       <c r="Q192" s="115"/>
       <c r="R192" s="115"/>
     </row>
-    <row r="193" spans="1:18" ht="45">
+    <row r="193" spans="1:18" ht="44">
       <c r="A193" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -25786,7 +25748,7 @@
       <c r="Q193" s="115"/>
       <c r="R193" s="115"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -25821,7 +25783,7 @@
       <c r="Q194" s="115"/>
       <c r="R194" s="115"/>
     </row>
-    <row r="195" spans="1:18" ht="33.75">
+    <row r="195" spans="1:18" ht="33">
       <c r="A195" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -25858,7 +25820,7 @@
       <c r="Q195" s="115"/>
       <c r="R195" s="115"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -25895,7 +25857,7 @@
       <c r="Q196" s="115"/>
       <c r="R196" s="115"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -25938,7 +25900,7 @@
       <c r="Q197" s="84"/>
       <c r="R197" s="84"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -26016,7 +25978,7 @@
       <c r="Q199" s="84"/>
       <c r="R199" s="84"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -26059,7 +26021,7 @@
       <c r="Q200" s="84"/>
       <c r="R200" s="84"/>
     </row>
-    <row r="201" spans="1:18" ht="22.5">
+    <row r="201" spans="1:18" ht="22">
       <c r="A201" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -26096,7 +26058,7 @@
       <c r="Q201" s="84"/>
       <c r="R201" s="84"/>
     </row>
-    <row r="202" spans="1:18" ht="22.5">
+    <row r="202" spans="1:18" ht="22">
       <c r="A202" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -26131,7 +26093,7 @@
       <c r="Q202" s="84"/>
       <c r="R202" s="84"/>
     </row>
-    <row r="203" spans="1:18" ht="22.5">
+    <row r="203" spans="1:18" ht="22">
       <c r="A203" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -26168,7 +26130,7 @@
       <c r="Q203" s="84"/>
       <c r="R203" s="84"/>
     </row>
-    <row r="204" spans="1:18" ht="22.5">
+    <row r="204" spans="1:18" ht="22">
       <c r="A204" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -26203,7 +26165,7 @@
       <c r="Q204" s="84"/>
       <c r="R204" s="84"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -26242,7 +26204,7 @@
       <c r="Q205" s="84"/>
       <c r="R205" s="84"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -26283,7 +26245,7 @@
       <c r="Q206" s="84"/>
       <c r="R206" s="84"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -26318,7 +26280,7 @@
       <c r="Q207" s="84"/>
       <c r="R207" s="84"/>
     </row>
-    <row r="208" spans="1:18" ht="22.5">
+    <row r="208" spans="1:18" ht="22">
       <c r="A208" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -26353,7 +26315,7 @@
       <c r="Q208" s="84"/>
       <c r="R208" s="84"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -26388,7 +26350,7 @@
       <c r="Q209" s="84"/>
       <c r="R209" s="84"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -26423,7 +26385,7 @@
       <c r="Q210" s="84"/>
       <c r="R210" s="84"/>
     </row>
-    <row r="211" spans="1:18" ht="22.5">
+    <row r="211" spans="1:18" ht="22">
       <c r="A211" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -26458,7 +26420,7 @@
       <c r="Q211" s="84"/>
       <c r="R211" s="84"/>
     </row>
-    <row r="212" spans="1:18" ht="22.5">
+    <row r="212" spans="1:18" ht="22">
       <c r="A212" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -26493,7 +26455,7 @@
       <c r="Q212" s="84"/>
       <c r="R212" s="84"/>
     </row>
-    <row r="213" spans="1:18" ht="22.5">
+    <row r="213" spans="1:18" ht="22">
       <c r="A213" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A213" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E213),
@@ -26530,7 +26492,7 @@
       <c r="Q213" s="84"/>
       <c r="R213" s="84"/>
     </row>
-    <row r="214" spans="1:18" ht="22.5">
+    <row r="214" spans="1:18" ht="22">
       <c r="A214" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -26569,7 +26531,7 @@
       <c r="Q214" s="84"/>
       <c r="R214" s="84"/>
     </row>
-    <row r="215" spans="1:18" ht="22.5">
+    <row r="215" spans="1:18" ht="22">
       <c r="A215" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -26639,7 +26601,7 @@
       <c r="Q216" s="84"/>
       <c r="R216" s="84"/>
     </row>
-    <row r="217" spans="1:18" ht="22.5">
+    <row r="217" spans="1:18" ht="22">
       <c r="A217" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -26674,7 +26636,7 @@
       <c r="Q217" s="84"/>
       <c r="R217" s="84"/>
     </row>
-    <row r="218" spans="1:18" ht="33.75">
+    <row r="218" spans="1:18" ht="33">
       <c r="A218" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -26709,7 +26671,7 @@
       <c r="Q218" s="84"/>
       <c r="R218" s="84"/>
     </row>
-    <row r="219" spans="1:18" ht="33.75">
+    <row r="219" spans="1:18" ht="33">
       <c r="A219" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -26744,7 +26706,7 @@
       <c r="Q219" s="84"/>
       <c r="R219" s="84"/>
     </row>
-    <row r="220" spans="1:18" ht="45">
+    <row r="220" spans="1:18" ht="44">
       <c r="A220" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -26779,7 +26741,7 @@
       <c r="Q220" s="84"/>
       <c r="R220" s="84"/>
     </row>
-    <row r="221" spans="1:18" ht="33.75">
+    <row r="221" spans="1:18" ht="33">
       <c r="A221" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -26814,7 +26776,7 @@
       <c r="Q221" s="84"/>
       <c r="R221" s="84"/>
     </row>
-    <row r="222" spans="1:18" ht="33.75">
+    <row r="222" spans="1:18" ht="33">
       <c r="A222" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -26849,7 +26811,7 @@
       <c r="Q222" s="84"/>
       <c r="R222" s="84"/>
     </row>
-    <row r="223" spans="1:18" ht="22.5">
+    <row r="223" spans="1:18" ht="22">
       <c r="A223" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -26884,7 +26846,7 @@
       <c r="Q223" s="84"/>
       <c r="R223" s="84"/>
     </row>
-    <row r="224" spans="1:18" ht="22.5">
+    <row r="224" spans="1:18" ht="22">
       <c r="A224" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -26919,7 +26881,7 @@
       <c r="Q224" s="84"/>
       <c r="R224" s="84"/>
     </row>
-    <row r="225" spans="1:18" ht="33.75">
+    <row r="225" spans="1:18" ht="33">
       <c r="A225" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -26954,7 +26916,7 @@
       <c r="Q225" s="84"/>
       <c r="R225" s="84"/>
     </row>
-    <row r="226" spans="1:18" ht="22.5">
+    <row r="226" spans="1:18" ht="22">
       <c r="A226" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -26989,7 +26951,7 @@
       <c r="Q226" s="84"/>
       <c r="R226" s="84"/>
     </row>
-    <row r="227" spans="1:18" ht="22.5">
+    <row r="227" spans="1:18" ht="22">
       <c r="A227" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -27028,7 +26990,7 @@
       <c r="Q227" s="84"/>
       <c r="R227" s="84"/>
     </row>
-    <row r="228" spans="1:18" ht="22.5">
+    <row r="228" spans="1:18" ht="22">
       <c r="A228" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -27063,7 +27025,7 @@
       <c r="Q228" s="84"/>
       <c r="R228" s="84"/>
     </row>
-    <row r="229" spans="1:18" ht="22.5">
+    <row r="229" spans="1:18" ht="22">
       <c r="A229" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -27133,7 +27095,7 @@
       <c r="Q230" s="84"/>
       <c r="R230" s="84"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -27168,7 +27130,7 @@
       <c r="Q231" s="84"/>
       <c r="R231" s="84"/>
     </row>
-    <row r="232" spans="1:18" ht="45">
+    <row r="232" spans="1:18" ht="44">
       <c r="A232" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -27203,7 +27165,7 @@
       <c r="Q232" s="84"/>
       <c r="R232" s="84"/>
     </row>
-    <row r="233" spans="1:18" ht="33.75">
+    <row r="233" spans="1:18" ht="33">
       <c r="A233" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -27238,7 +27200,7 @@
       <c r="Q233" s="84"/>
       <c r="R233" s="84"/>
     </row>
-    <row r="234" spans="1:18" ht="33.75">
+    <row r="234" spans="1:18" ht="33">
       <c r="A234" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -27273,7 +27235,7 @@
       <c r="Q234" s="84"/>
       <c r="R234" s="84"/>
     </row>
-    <row r="235" spans="1:18" ht="45">
+    <row r="235" spans="1:18" ht="44">
       <c r="A235" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -27308,7 +27270,7 @@
       <c r="Q235" s="84"/>
       <c r="R235" s="84"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -27343,7 +27305,7 @@
       <c r="Q236" s="84"/>
       <c r="R236" s="84"/>
     </row>
-    <row r="237" spans="1:18" ht="33.75">
+    <row r="237" spans="1:18" ht="33">
       <c r="A237" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -27378,7 +27340,7 @@
       <c r="Q237" s="84"/>
       <c r="R237" s="84"/>
     </row>
-    <row r="238" spans="1:18" ht="22.5">
+    <row r="238" spans="1:18" ht="22">
       <c r="A238" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -27413,7 +27375,7 @@
       <c r="Q238" s="84"/>
       <c r="R238" s="84"/>
     </row>
-    <row r="239" spans="1:18" ht="22.5">
+    <row r="239" spans="1:18" ht="22">
       <c r="A239" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -27448,7 +27410,7 @@
       <c r="Q239" s="84"/>
       <c r="R239" s="84"/>
     </row>
-    <row r="240" spans="1:18" ht="33.75">
+    <row r="240" spans="1:18" ht="33">
       <c r="A240" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -27483,7 +27445,7 @@
       <c r="Q240" s="84"/>
       <c r="R240" s="84"/>
     </row>
-    <row r="241" spans="1:18" ht="22.5">
+    <row r="241" spans="1:18" ht="22">
       <c r="A241" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -27518,7 +27480,7 @@
       <c r="Q241" s="84"/>
       <c r="R241" s="84"/>
     </row>
-    <row r="242" spans="1:18" ht="45">
+    <row r="242" spans="1:18" ht="44">
       <c r="A242" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -27555,7 +27517,7 @@
       <c r="Q242" s="84"/>
       <c r="R242" s="84"/>
     </row>
-    <row r="243" spans="1:18" ht="45">
+    <row r="243" spans="1:18" ht="44">
       <c r="A243" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -27590,7 +27552,7 @@
       <c r="Q243" s="84"/>
       <c r="R243" s="84"/>
     </row>
-    <row r="244" spans="1:18" ht="33.75">
+    <row r="244" spans="1:18" ht="33">
       <c r="A244" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -27625,7 +27587,7 @@
       <c r="Q244" s="84"/>
       <c r="R244" s="84"/>
     </row>
-    <row r="245" spans="1:18" ht="33.75">
+    <row r="245" spans="1:18" ht="33">
       <c r="A245" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -27662,7 +27624,7 @@
       <c r="Q245" s="84"/>
       <c r="R245" s="84"/>
     </row>
-    <row r="246" spans="1:18" ht="22.5">
+    <row r="246" spans="1:18" ht="22">
       <c r="A246" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -27699,7 +27661,7 @@
       <c r="Q246" s="84"/>
       <c r="R246" s="84"/>
     </row>
-    <row r="247" spans="1:18" ht="22.5">
+    <row r="247" spans="1:18" ht="22">
       <c r="A247" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -27742,7 +27704,7 @@
       <c r="Q247" s="84"/>
       <c r="R247" s="84"/>
     </row>
-    <row r="248" spans="1:18" ht="22.5">
+    <row r="248" spans="1:18" ht="22">
       <c r="A248" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -27779,7 +27741,7 @@
       <c r="Q248" s="84"/>
       <c r="R248" s="84"/>
     </row>
-    <row r="249" spans="1:18" ht="22.5">
+    <row r="249" spans="1:18" ht="22">
       <c r="A249" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -27814,7 +27776,7 @@
       <c r="Q249" s="84"/>
       <c r="R249" s="84"/>
     </row>
-    <row r="250" spans="1:18" ht="22.5">
+    <row r="250" spans="1:18" ht="22">
       <c r="A250" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -27849,7 +27811,7 @@
       <c r="Q250" s="84"/>
       <c r="R250" s="84"/>
     </row>
-    <row r="251" spans="1:18" ht="22.5">
+    <row r="251" spans="1:18" ht="22">
       <c r="A251" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -27884,7 +27846,7 @@
       <c r="Q251" s="84"/>
       <c r="R251" s="84"/>
     </row>
-    <row r="252" spans="1:18" ht="33.75">
+    <row r="252" spans="1:18" ht="33">
       <c r="A252" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -27919,7 +27881,7 @@
       <c r="Q252" s="84"/>
       <c r="R252" s="84"/>
     </row>
-    <row r="253" spans="1:18" ht="33.75">
+    <row r="253" spans="1:18" ht="33">
       <c r="A253" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -27956,7 +27918,7 @@
       <c r="Q253" s="84"/>
       <c r="R253" s="84"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -27991,7 +27953,7 @@
       <c r="Q254" s="84"/>
       <c r="R254" s="84"/>
     </row>
-    <row r="255" spans="1:18" ht="45">
+    <row r="255" spans="1:18" ht="44">
       <c r="A255" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -28026,7 +27988,7 @@
       <c r="Q255" s="84"/>
       <c r="R255" s="84"/>
     </row>
-    <row r="256" spans="1:18" ht="45">
+    <row r="256" spans="1:18" ht="44">
       <c r="A256" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -28061,7 +28023,7 @@
       <c r="Q256" s="84"/>
       <c r="R256" s="84"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -28096,7 +28058,7 @@
       <c r="Q257" s="84"/>
       <c r="R257" s="84"/>
     </row>
-    <row r="258" spans="1:18" ht="33.75">
+    <row r="258" spans="1:18" ht="33">
       <c r="A258" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -28133,7 +28095,7 @@
       <c r="Q258" s="84"/>
       <c r="R258" s="84"/>
     </row>
-    <row r="259" spans="1:18" ht="33.75">
+    <row r="259" spans="1:18" ht="33">
       <c r="A259" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -28174,7 +28136,7 @@
       <c r="Q259" s="84"/>
       <c r="R259" s="84"/>
     </row>
-    <row r="260" spans="1:18" ht="22.5">
+    <row r="260" spans="1:18" ht="22">
       <c r="A260" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -28217,7 +28179,7 @@
       <c r="Q260" s="84"/>
       <c r="R260" s="84"/>
     </row>
-    <row r="261" spans="1:18" ht="22.5">
+    <row r="261" spans="1:18" ht="22">
       <c r="A261" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -28252,7 +28214,7 @@
       <c r="Q261" s="84"/>
       <c r="R261" s="84"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -28291,7 +28253,7 @@
       <c r="Q262" s="84"/>
       <c r="R262" s="84"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -28326,7 +28288,7 @@
       <c r="Q263" s="84"/>
       <c r="R263" s="84"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -28367,7 +28329,7 @@
       <c r="Q264" s="84"/>
       <c r="R264" s="84"/>
     </row>
-    <row r="265" spans="1:18" ht="33.75">
+    <row r="265" spans="1:18" ht="33">
       <c r="A265" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A265" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E265),
@@ -28404,7 +28366,7 @@
       <c r="Q265" s="84"/>
       <c r="R265" s="84"/>
     </row>
-    <row r="266" spans="1:18" ht="33.75">
+    <row r="266" spans="1:18" ht="33">
       <c r="A266" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -28441,7 +28403,7 @@
       <c r="Q266" s="84"/>
       <c r="R266" s="84"/>
     </row>
-    <row r="267" spans="1:18" ht="33.75">
+    <row r="267" spans="1:18" ht="33">
       <c r="A267" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -28478,7 +28440,7 @@
       <c r="Q267" s="84"/>
       <c r="R267" s="84"/>
     </row>
-    <row r="268" spans="1:18" ht="22.5">
+    <row r="268" spans="1:18" ht="22">
       <c r="A268" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -28517,7 +28479,7 @@
       <c r="Q268" s="84"/>
       <c r="R268" s="84"/>
     </row>
-    <row r="269" spans="1:18" ht="22.5">
+    <row r="269" spans="1:18" ht="22">
       <c r="A269" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -28552,7 +28514,7 @@
       <c r="Q269" s="84"/>
       <c r="R269" s="84"/>
     </row>
-    <row r="270" spans="1:18" ht="33.75">
+    <row r="270" spans="1:18" ht="33">
       <c r="A270" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -28589,7 +28551,7 @@
       <c r="Q270" s="84"/>
       <c r="R270" s="84"/>
     </row>
-    <row r="271" spans="1:18" ht="33.75">
+    <row r="271" spans="1:18" ht="33">
       <c r="A271" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -28624,7 +28586,7 @@
       <c r="Q271" s="84"/>
       <c r="R271" s="84"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -28659,7 +28621,7 @@
       <c r="Q272" s="84"/>
       <c r="R272" s="84"/>
     </row>
-    <row r="273" spans="1:18" ht="33.75">
+    <row r="273" spans="1:18" ht="33">
       <c r="A273" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -28694,7 +28656,7 @@
       <c r="Q273" s="84"/>
       <c r="R273" s="84"/>
     </row>
-    <row r="274" spans="1:18" ht="33.75">
+    <row r="274" spans="1:18" ht="33">
       <c r="A274" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -28729,7 +28691,7 @@
       <c r="Q274" s="84"/>
       <c r="R274" s="84"/>
     </row>
-    <row r="275" spans="1:18" ht="22.5">
+    <row r="275" spans="1:18" ht="22">
       <c r="A275" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -28764,7 +28726,7 @@
       <c r="Q275" s="84"/>
       <c r="R275" s="84"/>
     </row>
-    <row r="276" spans="1:18" ht="22.5">
+    <row r="276" spans="1:18" ht="22">
       <c r="A276" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -28799,7 +28761,7 @@
       <c r="Q276" s="84"/>
       <c r="R276" s="84"/>
     </row>
-    <row r="277" spans="1:18" ht="33.75">
+    <row r="277" spans="1:18" ht="33">
       <c r="A277" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -28834,7 +28796,7 @@
       <c r="Q277" s="84"/>
       <c r="R277" s="84"/>
     </row>
-    <row r="278" spans="1:18" ht="33.75">
+    <row r="278" spans="1:18" ht="33">
       <c r="A278" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -28869,7 +28831,7 @@
       <c r="Q278" s="84"/>
       <c r="R278" s="84"/>
     </row>
-    <row r="279" spans="1:18" ht="33.75">
+    <row r="279" spans="1:18" ht="33">
       <c r="A279" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -28904,7 +28866,7 @@
       <c r="Q279" s="84"/>
       <c r="R279" s="84"/>
     </row>
-    <row r="280" spans="1:18" ht="33.75">
+    <row r="280" spans="1:18" ht="33">
       <c r="A280" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -29011,7 +28973,7 @@
       <c r="Q282" s="84"/>
       <c r="R282" s="84"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -29046,7 +29008,7 @@
       <c r="Q283" s="84"/>
       <c r="R283" s="84"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -29081,7 +29043,7 @@
       <c r="Q284" s="84"/>
       <c r="R284" s="84"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -29116,7 +29078,7 @@
       <c r="Q285" s="84"/>
       <c r="R285" s="84"/>
     </row>
-    <row r="286" spans="1:18" ht="33.75">
+    <row r="286" spans="1:18" ht="33">
       <c r="A286" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -29151,7 +29113,7 @@
       <c r="Q286" s="84"/>
       <c r="R286" s="84"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -29188,7 +29150,7 @@
       <c r="Q287" s="84"/>
       <c r="R287" s="84"/>
     </row>
-    <row r="288" spans="1:18" ht="33.75">
+    <row r="288" spans="1:18" ht="33">
       <c r="A288" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -29223,7 +29185,7 @@
       <c r="Q288" s="84"/>
       <c r="R288" s="84"/>
     </row>
-    <row r="289" spans="1:18" ht="45">
+    <row r="289" spans="1:18" ht="44">
       <c r="A289" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -29258,7 +29220,7 @@
       <c r="Q289" s="84"/>
       <c r="R289" s="84"/>
     </row>
-    <row r="290" spans="1:18" ht="45">
+    <row r="290" spans="1:18" ht="44">
       <c r="A290" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -29293,7 +29255,7 @@
       <c r="Q290" s="84"/>
       <c r="R290" s="84"/>
     </row>
-    <row r="291" spans="1:18" ht="22.5">
+    <row r="291" spans="1:18" ht="22">
       <c r="A291" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -29328,7 +29290,7 @@
       <c r="Q291" s="84"/>
       <c r="R291" s="84"/>
     </row>
-    <row r="292" spans="1:18" ht="45">
+    <row r="292" spans="1:18" ht="44">
       <c r="A292" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -29363,7 +29325,7 @@
       <c r="Q292" s="84"/>
       <c r="R292" s="84"/>
     </row>
-    <row r="293" spans="1:18" ht="45">
+    <row r="293" spans="1:18" ht="44">
       <c r="A293" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -29398,7 +29360,7 @@
       <c r="Q293" s="84"/>
       <c r="R293" s="84"/>
     </row>
-    <row r="294" spans="1:18" ht="22.5">
+    <row r="294" spans="1:18" ht="22">
       <c r="A294" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -29433,7 +29395,7 @@
       <c r="Q294" s="84"/>
       <c r="R294" s="84"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -29470,7 +29432,7 @@
       <c r="Q295" s="84"/>
       <c r="R295" s="84"/>
     </row>
-    <row r="296" spans="1:18" ht="22.5">
+    <row r="296" spans="1:18" ht="22">
       <c r="A296" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -29513,7 +29475,7 @@
       <c r="Q296" s="115"/>
       <c r="R296" s="115"/>
     </row>
-    <row r="297" spans="1:18" ht="22.5">
+    <row r="297" spans="1:18" ht="22">
       <c r="A297" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -29548,7 +29510,7 @@
       <c r="Q297" s="115"/>
       <c r="R297" s="115"/>
     </row>
-    <row r="298" spans="1:18" ht="22.5">
+    <row r="298" spans="1:18" ht="22">
       <c r="A298" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -29583,7 +29545,7 @@
       <c r="Q298" s="115"/>
       <c r="R298" s="115"/>
     </row>
-    <row r="299" spans="1:18" ht="22.5">
+    <row r="299" spans="1:18" ht="22">
       <c r="A299" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -29618,7 +29580,7 @@
       <c r="Q299" s="115"/>
       <c r="R299" s="115"/>
     </row>
-    <row r="300" spans="1:18" ht="22.5">
+    <row r="300" spans="1:18" ht="22">
       <c r="A300" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -29659,7 +29621,7 @@
       <c r="Q300" s="115"/>
       <c r="R300" s="115"/>
     </row>
-    <row r="301" spans="1:18" ht="22.5">
+    <row r="301" spans="1:18" ht="22">
       <c r="A301" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -29696,7 +29658,7 @@
       <c r="Q301" s="115"/>
       <c r="R301" s="115"/>
     </row>
-    <row r="302" spans="1:18" ht="22.5">
+    <row r="302" spans="1:18" ht="22">
       <c r="A302" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -29733,7 +29695,7 @@
       <c r="Q302" s="115"/>
       <c r="R302" s="115"/>
     </row>
-    <row r="303" spans="1:18" ht="22.5">
+    <row r="303" spans="1:18" ht="22">
       <c r="A303" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -29770,7 +29732,7 @@
       <c r="Q303" s="115"/>
       <c r="R303" s="115"/>
     </row>
-    <row r="304" spans="1:18" ht="22.5">
+    <row r="304" spans="1:18" ht="22">
       <c r="A304" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A304" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E304),
@@ -29809,7 +29771,7 @@
       <c r="Q304" s="115"/>
       <c r="R304" s="115"/>
     </row>
-    <row r="305" spans="1:18" ht="22.5">
+    <row r="305" spans="1:18" ht="22">
       <c r="A305" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A305" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E305),
@@ -29844,7 +29806,7 @@
       <c r="Q305" s="115"/>
       <c r="R305" s="115"/>
     </row>
-    <row r="306" spans="1:18" ht="33.75">
+    <row r="306" spans="1:18" ht="33">
       <c r="A306" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A306" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E306),
@@ -29879,7 +29841,7 @@
       <c r="Q306" s="115"/>
       <c r="R306" s="115"/>
     </row>
-    <row r="307" spans="1:18" ht="33.75">
+    <row r="307" spans="1:18" ht="33">
       <c r="A307" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A307" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E307),
@@ -29914,7 +29876,7 @@
       <c r="Q307" s="115"/>
       <c r="R307" s="115"/>
     </row>
-    <row r="308" spans="1:18" ht="33.75">
+    <row r="308" spans="1:18" ht="33">
       <c r="A308" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A308" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E308),
@@ -29949,7 +29911,7 @@
       <c r="Q308" s="115"/>
       <c r="R308" s="115"/>
     </row>
-    <row r="309" spans="1:18" ht="33.75">
+    <row r="309" spans="1:18" ht="33">
       <c r="A309" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A309" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E309),
@@ -29984,7 +29946,7 @@
       <c r="Q309" s="115"/>
       <c r="R309" s="115"/>
     </row>
-    <row r="310" spans="1:18" ht="33.75">
+    <row r="310" spans="1:18" ht="33">
       <c r="A310" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A310" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E310),
@@ -30019,7 +29981,7 @@
       <c r="Q310" s="115"/>
       <c r="R310" s="115"/>
     </row>
-    <row r="311" spans="1:18" ht="22.5">
+    <row r="311" spans="1:18" ht="22">
       <c r="A311" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A311" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E311),
@@ -30054,7 +30016,7 @@
       <c r="Q311" s="115"/>
       <c r="R311" s="115"/>
     </row>
-    <row r="312" spans="1:18" ht="22.5">
+    <row r="312" spans="1:18" ht="22">
       <c r="A312" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A312" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E312),
@@ -30127,17 +30089,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R450"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="3" width="8.625" style="30" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="40.375" style="31" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="124" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="30" customWidth="1"/>
-    <col min="10" max="10" width="29.375" style="30" customWidth="1"/>
-    <col min="11" max="11" width="27.375" style="30" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="30" customWidth="1"/>
-    <col min="13" max="18" width="8.625" style="30" customWidth="1"/>
+    <col min="1" max="3" width="8.58203125" style="30" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="31" customWidth="1"/>
+    <col min="6" max="6" width="40.33203125" style="31" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="124" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="30" customWidth="1"/>
+    <col min="10" max="10" width="29.33203125" style="30" customWidth="1"/>
+    <col min="11" max="11" width="27.33203125" style="30" customWidth="1"/>
+    <col min="12" max="12" width="15.58203125" style="30" customWidth="1"/>
+    <col min="13" max="18" width="8.58203125" style="30" customWidth="1"/>
     <col min="19" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
@@ -30183,10 +30145,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
-      <c r="A8" s="32" t="s">
-        <v>752</v>
-      </c>
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
+      <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
       <c r="D8" s="33"/>
@@ -30262,7 +30222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -30305,7 +30265,7 @@
       <c r="Q11" s="126"/>
       <c r="R11" s="128"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -30342,7 +30302,7 @@
       <c r="Q12" s="126"/>
       <c r="R12" s="128"/>
     </row>
-    <row r="13" spans="1:18" ht="33.75">
+    <row r="13" spans="1:18" ht="33">
       <c r="A13" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -30381,7 +30341,7 @@
       <c r="Q13" s="126"/>
       <c r="R13" s="128"/>
     </row>
-    <row r="14" spans="1:18" ht="22.5">
+    <row r="14" spans="1:18" ht="22">
       <c r="A14" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -30416,7 +30376,7 @@
       <c r="Q14" s="126"/>
       <c r="R14" s="128"/>
     </row>
-    <row r="15" spans="1:18" ht="22.5">
+    <row r="15" spans="1:18" ht="22">
       <c r="A15" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -30451,7 +30411,7 @@
       <c r="Q15" s="126"/>
       <c r="R15" s="128"/>
     </row>
-    <row r="16" spans="1:18" ht="22.5">
+    <row r="16" spans="1:18" ht="22">
       <c r="A16" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -30486,7 +30446,7 @@
       <c r="Q16" s="126"/>
       <c r="R16" s="128"/>
     </row>
-    <row r="17" spans="1:18" ht="33.75">
+    <row r="17" spans="1:18" ht="33">
       <c r="A17" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -30521,7 +30481,7 @@
       <c r="Q17" s="126"/>
       <c r="R17" s="128"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -30560,7 +30520,7 @@
       <c r="Q18" s="126"/>
       <c r="R18" s="128"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -30595,7 +30555,7 @@
       <c r="Q19" s="126"/>
       <c r="R19" s="128"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -30630,7 +30590,7 @@
       <c r="Q20" s="126"/>
       <c r="R20" s="128"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -30667,7 +30627,7 @@
       <c r="Q21" s="126"/>
       <c r="R21" s="128"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -30702,7 +30662,7 @@
       <c r="Q22" s="126"/>
       <c r="R22" s="128"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -30737,7 +30697,7 @@
       <c r="Q23" s="126"/>
       <c r="R23" s="128"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -30772,7 +30732,7 @@
       <c r="Q24" s="126"/>
       <c r="R24" s="128"/>
     </row>
-    <row r="25" spans="1:18" ht="22.5">
+    <row r="25" spans="1:18" ht="22">
       <c r="A25" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -30846,7 +30806,7 @@
       <c r="Q26" s="126"/>
       <c r="R26" s="128"/>
     </row>
-    <row r="27" spans="1:18" ht="33.75">
+    <row r="27" spans="1:18" ht="33">
       <c r="A27" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -30885,7 +30845,7 @@
       <c r="Q27" s="126"/>
       <c r="R27" s="128"/>
     </row>
-    <row r="28" spans="1:18" ht="22.5">
+    <row r="28" spans="1:18" ht="22">
       <c r="A28" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -30920,7 +30880,7 @@
       <c r="Q28" s="126"/>
       <c r="R28" s="128"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -30957,7 +30917,7 @@
       <c r="Q29" s="126"/>
       <c r="R29" s="128"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -30992,7 +30952,7 @@
       <c r="Q30" s="126"/>
       <c r="R30" s="128"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -31027,7 +30987,7 @@
       <c r="Q31" s="126"/>
       <c r="R31" s="128"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -31062,7 +31022,7 @@
       <c r="Q32" s="126"/>
       <c r="R32" s="128"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -31099,7 +31059,7 @@
       <c r="Q33" s="126"/>
       <c r="R33" s="128"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -31134,7 +31094,7 @@
       <c r="Q34" s="126"/>
       <c r="R34" s="128"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -31171,7 +31131,7 @@
       <c r="Q35" s="126"/>
       <c r="R35" s="128"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -31212,7 +31172,7 @@
       <c r="Q36" s="126"/>
       <c r="R36" s="128"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -31247,7 +31207,7 @@
       <c r="Q37" s="126"/>
       <c r="R37" s="128"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -31282,7 +31242,7 @@
       <c r="Q38" s="126"/>
       <c r="R38" s="128"/>
     </row>
-    <row r="39" spans="1:18" ht="22.5">
+    <row r="39" spans="1:18" ht="22">
       <c r="A39" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -31317,7 +31277,7 @@
       <c r="Q39" s="126"/>
       <c r="R39" s="128"/>
     </row>
-    <row r="40" spans="1:18" ht="33.75">
+    <row r="40" spans="1:18" ht="33">
       <c r="A40" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -31391,7 +31351,7 @@
       <c r="Q41" s="126"/>
       <c r="R41" s="128"/>
     </row>
-    <row r="42" spans="1:18" ht="22.5">
+    <row r="42" spans="1:18" ht="22">
       <c r="A42" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -31434,7 +31394,7 @@
       <c r="Q42" s="126"/>
       <c r="R42" s="128"/>
     </row>
-    <row r="43" spans="1:18" ht="22.5">
+    <row r="43" spans="1:18" ht="22">
       <c r="A43" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -31469,7 +31429,7 @@
       <c r="Q43" s="126"/>
       <c r="R43" s="128"/>
     </row>
-    <row r="44" spans="1:18" ht="33.75">
+    <row r="44" spans="1:18" ht="33">
       <c r="A44" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -31504,7 +31464,7 @@
       <c r="Q44" s="126"/>
       <c r="R44" s="128"/>
     </row>
-    <row r="45" spans="1:18" ht="22.5">
+    <row r="45" spans="1:18" ht="22">
       <c r="A45" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -31541,7 +31501,7 @@
       <c r="Q45" s="126"/>
       <c r="R45" s="128"/>
     </row>
-    <row r="46" spans="1:18" ht="22.5">
+    <row r="46" spans="1:18" ht="22">
       <c r="A46" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -31576,7 +31536,7 @@
       <c r="Q46" s="126"/>
       <c r="R46" s="128"/>
     </row>
-    <row r="47" spans="1:18" ht="33.75">
+    <row r="47" spans="1:18" ht="33">
       <c r="A47" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -31611,7 +31571,7 @@
       <c r="Q47" s="126"/>
       <c r="R47" s="128"/>
     </row>
-    <row r="48" spans="1:18" ht="22.5">
+    <row r="48" spans="1:18" ht="22">
       <c r="A48" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -31648,7 +31608,7 @@
       <c r="Q48" s="126"/>
       <c r="R48" s="128"/>
     </row>
-    <row r="49" spans="1:18" ht="22.5">
+    <row r="49" spans="1:18" ht="22">
       <c r="A49" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -31683,7 +31643,7 @@
       <c r="Q49" s="126"/>
       <c r="R49" s="128"/>
     </row>
-    <row r="50" spans="1:18" ht="22.5">
+    <row r="50" spans="1:18" ht="22">
       <c r="A50" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -31720,7 +31680,7 @@
       <c r="Q50" s="126"/>
       <c r="R50" s="128"/>
     </row>
-    <row r="51" spans="1:18" ht="22.5">
+    <row r="51" spans="1:18" ht="22">
       <c r="A51" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -31755,7 +31715,7 @@
       <c r="Q51" s="126"/>
       <c r="R51" s="128"/>
     </row>
-    <row r="52" spans="1:18" ht="22.5">
+    <row r="52" spans="1:18" ht="22">
       <c r="A52" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -31790,7 +31750,7 @@
       <c r="Q52" s="126"/>
       <c r="R52" s="128"/>
     </row>
-    <row r="53" spans="1:18" ht="22.5">
+    <row r="53" spans="1:18" ht="22">
       <c r="A53" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -31825,7 +31785,7 @@
       <c r="Q53" s="126"/>
       <c r="R53" s="128"/>
     </row>
-    <row r="54" spans="1:18" ht="22.5">
+    <row r="54" spans="1:18" ht="22">
       <c r="A54" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -31860,7 +31820,7 @@
       <c r="Q54" s="126"/>
       <c r="R54" s="128"/>
     </row>
-    <row r="55" spans="1:18" ht="22.5">
+    <row r="55" spans="1:18" ht="22">
       <c r="A55" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -31895,7 +31855,7 @@
       <c r="Q55" s="126"/>
       <c r="R55" s="128"/>
     </row>
-    <row r="56" spans="1:18" ht="33.75">
+    <row r="56" spans="1:18" ht="33">
       <c r="A56" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -31932,7 +31892,7 @@
       <c r="Q56" s="126"/>
       <c r="R56" s="128"/>
     </row>
-    <row r="57" spans="1:18" ht="22.5">
+    <row r="57" spans="1:18" ht="22">
       <c r="A57" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -31969,7 +31929,7 @@
       <c r="Q57" s="126"/>
       <c r="R57" s="128"/>
     </row>
-    <row r="58" spans="1:18" ht="22.5">
+    <row r="58" spans="1:18" ht="22">
       <c r="A58" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -32006,7 +31966,7 @@
       <c r="Q58" s="126"/>
       <c r="R58" s="128"/>
     </row>
-    <row r="59" spans="1:18" ht="22.5">
+    <row r="59" spans="1:18" ht="22">
       <c r="A59" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -32045,7 +32005,7 @@
       <c r="Q59" s="126"/>
       <c r="R59" s="128"/>
     </row>
-    <row r="60" spans="1:18" ht="22.5">
+    <row r="60" spans="1:18" ht="22">
       <c r="A60" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -32080,7 +32040,7 @@
       <c r="Q60" s="126"/>
       <c r="R60" s="128"/>
     </row>
-    <row r="61" spans="1:18" ht="22.5">
+    <row r="61" spans="1:18" ht="22">
       <c r="A61" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -32115,7 +32075,7 @@
       <c r="Q61" s="126"/>
       <c r="R61" s="128"/>
     </row>
-    <row r="62" spans="1:18" ht="22.5">
+    <row r="62" spans="1:18" ht="22">
       <c r="A62" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -32150,7 +32110,7 @@
       <c r="Q62" s="126"/>
       <c r="R62" s="128"/>
     </row>
-    <row r="63" spans="1:18" ht="22.5">
+    <row r="63" spans="1:18" ht="22">
       <c r="A63" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -32185,7 +32145,7 @@
       <c r="Q63" s="126"/>
       <c r="R63" s="128"/>
     </row>
-    <row r="64" spans="1:18" ht="33.75">
+    <row r="64" spans="1:18" ht="33">
       <c r="A64" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -32222,7 +32182,7 @@
       <c r="Q64" s="126"/>
       <c r="R64" s="128"/>
     </row>
-    <row r="65" spans="1:18" ht="33.75">
+    <row r="65" spans="1:18" ht="33">
       <c r="A65" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -32257,7 +32217,7 @@
       <c r="Q65" s="126"/>
       <c r="R65" s="128"/>
     </row>
-    <row r="66" spans="1:18" ht="33.75">
+    <row r="66" spans="1:18" ht="33">
       <c r="A66" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -32292,7 +32252,7 @@
       <c r="Q66" s="126"/>
       <c r="R66" s="128"/>
     </row>
-    <row r="67" spans="1:18" ht="33.75">
+    <row r="67" spans="1:18" ht="33">
       <c r="A67" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -32327,7 +32287,7 @@
       <c r="Q67" s="126"/>
       <c r="R67" s="128"/>
     </row>
-    <row r="68" spans="1:18" ht="33.75">
+    <row r="68" spans="1:18" ht="33">
       <c r="A68" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -32362,7 +32322,7 @@
       <c r="Q68" s="126"/>
       <c r="R68" s="128"/>
     </row>
-    <row r="69" spans="1:18" ht="22.5">
+    <row r="69" spans="1:18" ht="22">
       <c r="A69" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -32397,7 +32357,7 @@
       <c r="Q69" s="126"/>
       <c r="R69" s="128"/>
     </row>
-    <row r="70" spans="1:18" ht="22.5">
+    <row r="70" spans="1:18" ht="22">
       <c r="A70" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -32432,7 +32392,7 @@
       <c r="Q70" s="126"/>
       <c r="R70" s="128"/>
     </row>
-    <row r="71" spans="1:18" ht="33.75">
+    <row r="71" spans="1:18" ht="33">
       <c r="A71" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -32467,7 +32427,7 @@
       <c r="Q71" s="126"/>
       <c r="R71" s="128"/>
     </row>
-    <row r="72" spans="1:18" ht="22.5">
+    <row r="72" spans="1:18" ht="22">
       <c r="A72" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -32646,7 +32606,7 @@
       <c r="Q76" s="126"/>
       <c r="R76" s="128"/>
     </row>
-    <row r="77" spans="1:18" ht="22.5">
+    <row r="77" spans="1:18" ht="22">
       <c r="A77" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -32681,7 +32641,7 @@
       <c r="Q77" s="126"/>
       <c r="R77" s="128"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -32722,7 +32682,7 @@
       <c r="Q78" s="126"/>
       <c r="R78" s="128"/>
     </row>
-    <row r="79" spans="1:18" ht="33.75">
+    <row r="79" spans="1:18" ht="33">
       <c r="A79" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -32794,7 +32754,7 @@
       <c r="Q80" s="126"/>
       <c r="R80" s="128"/>
     </row>
-    <row r="81" spans="1:18" ht="33.75">
+    <row r="81" spans="1:18" ht="33">
       <c r="A81" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -32831,7 +32791,7 @@
       <c r="Q81" s="126"/>
       <c r="R81" s="128"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -32866,7 +32826,7 @@
       <c r="Q82" s="126"/>
       <c r="R82" s="128"/>
     </row>
-    <row r="83" spans="1:18" ht="22.5">
+    <row r="83" spans="1:18" ht="22">
       <c r="A83" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -32903,7 +32863,7 @@
       <c r="Q83" s="126"/>
       <c r="R83" s="128"/>
     </row>
-    <row r="84" spans="1:18" ht="22.5">
+    <row r="84" spans="1:18" ht="22">
       <c r="A84" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -32940,7 +32900,7 @@
       <c r="Q84" s="126"/>
       <c r="R84" s="128"/>
     </row>
-    <row r="85" spans="1:18" ht="22.5">
+    <row r="85" spans="1:18" ht="22">
       <c r="A85" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -33018,7 +32978,7 @@
       <c r="Q86" s="126"/>
       <c r="R86" s="128"/>
     </row>
-    <row r="87" spans="1:18" ht="33.75">
+    <row r="87" spans="1:18" ht="33">
       <c r="A87" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -33055,7 +33015,7 @@
       <c r="Q87" s="126"/>
       <c r="R87" s="128"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -33096,7 +33056,7 @@
       <c r="Q88" s="126"/>
       <c r="R88" s="128"/>
     </row>
-    <row r="89" spans="1:18" ht="33.75">
+    <row r="89" spans="1:18" ht="33">
       <c r="A89" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A89" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E89),
@@ -33168,7 +33128,7 @@
       <c r="Q90" s="126"/>
       <c r="R90" s="128"/>
     </row>
-    <row r="91" spans="1:18" ht="33.75">
+    <row r="91" spans="1:18" ht="33">
       <c r="A91" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -33205,7 +33165,7 @@
       <c r="Q91" s="126"/>
       <c r="R91" s="128"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -33240,7 +33200,7 @@
       <c r="Q92" s="126"/>
       <c r="R92" s="128"/>
     </row>
-    <row r="93" spans="1:18" ht="33.75">
+    <row r="93" spans="1:18" ht="33">
       <c r="A93" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -33277,7 +33237,7 @@
       <c r="Q93" s="126"/>
       <c r="R93" s="128"/>
     </row>
-    <row r="94" spans="1:18" ht="22.5">
+    <row r="94" spans="1:18" ht="22">
       <c r="A94" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -33318,7 +33278,7 @@
       <c r="Q94" s="126"/>
       <c r="R94" s="128"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -33388,7 +33348,7 @@
       <c r="Q96" s="126"/>
       <c r="R96" s="128"/>
     </row>
-    <row r="97" spans="1:18" ht="33.75">
+    <row r="97" spans="1:18" ht="33">
       <c r="A97" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -33423,7 +33383,7 @@
       <c r="Q97" s="126"/>
       <c r="R97" s="128"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -33458,7 +33418,7 @@
       <c r="Q98" s="126"/>
       <c r="R98" s="128"/>
     </row>
-    <row r="99" spans="1:18" ht="22.5">
+    <row r="99" spans="1:18" ht="22">
       <c r="A99" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -33495,7 +33455,7 @@
       <c r="Q99" s="126"/>
       <c r="R99" s="128"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -33565,7 +33525,7 @@
       <c r="Q101" s="126"/>
       <c r="R101" s="128"/>
     </row>
-    <row r="102" spans="1:18" ht="33.75">
+    <row r="102" spans="1:18" ht="33">
       <c r="A102" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -33600,7 +33560,7 @@
       <c r="Q102" s="126"/>
       <c r="R102" s="128"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -33635,7 +33595,7 @@
       <c r="Q103" s="126"/>
       <c r="R103" s="128"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -33672,7 +33632,7 @@
       <c r="Q104" s="126"/>
       <c r="R104" s="128"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -33791,7 +33751,7 @@
       <c r="Q107" s="126"/>
       <c r="R107" s="128"/>
     </row>
-    <row r="108" spans="1:18" ht="22.5">
+    <row r="108" spans="1:18" ht="22">
       <c r="A108" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -33832,7 +33792,7 @@
       <c r="Q108" s="126"/>
       <c r="R108" s="128"/>
     </row>
-    <row r="109" spans="1:18" ht="22.5">
+    <row r="109" spans="1:18" ht="22">
       <c r="A109" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -33908,7 +33868,7 @@
       <c r="Q110" s="126"/>
       <c r="R110" s="128"/>
     </row>
-    <row r="111" spans="1:18" ht="22.5">
+    <row r="111" spans="1:18" ht="22">
       <c r="A111" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -33951,7 +33911,7 @@
       <c r="Q111" s="126"/>
       <c r="R111" s="128"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -33988,7 +33948,7 @@
       <c r="Q112" s="126"/>
       <c r="R112" s="128"/>
     </row>
-    <row r="113" spans="1:18" ht="22.5">
+    <row r="113" spans="1:18" ht="22">
       <c r="A113" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -34023,7 +33983,7 @@
       <c r="Q113" s="126"/>
       <c r="R113" s="128"/>
     </row>
-    <row r="114" spans="1:18" ht="22.5">
+    <row r="114" spans="1:18" ht="22">
       <c r="A114" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -34058,7 +34018,7 @@
       <c r="Q114" s="126"/>
       <c r="R114" s="128"/>
     </row>
-    <row r="115" spans="1:18" ht="22.5">
+    <row r="115" spans="1:18" ht="22">
       <c r="A115" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -34095,7 +34055,7 @@
       <c r="Q115" s="126"/>
       <c r="R115" s="128"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -34130,7 +34090,7 @@
       <c r="Q116" s="126"/>
       <c r="R116" s="128"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -34165,7 +34125,7 @@
       <c r="Q117" s="126"/>
       <c r="R117" s="128"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -34200,7 +34160,7 @@
       <c r="Q118" s="126"/>
       <c r="R118" s="128"/>
     </row>
-    <row r="119" spans="1:18" ht="33.75">
+    <row r="119" spans="1:18" ht="33">
       <c r="A119" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -34235,7 +34195,7 @@
       <c r="Q119" s="126"/>
       <c r="R119" s="128"/>
     </row>
-    <row r="120" spans="1:18" ht="33.75">
+    <row r="120" spans="1:18" ht="33">
       <c r="A120" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -34272,7 +34232,7 @@
       <c r="Q120" s="126"/>
       <c r="R120" s="128"/>
     </row>
-    <row r="121" spans="1:18" ht="33.75">
+    <row r="121" spans="1:18" ht="33">
       <c r="A121" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -34307,7 +34267,7 @@
       <c r="Q121" s="126"/>
       <c r="R121" s="128"/>
     </row>
-    <row r="122" spans="1:18" ht="45">
+    <row r="122" spans="1:18" ht="44">
       <c r="A122" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -34342,7 +34302,7 @@
       <c r="Q122" s="126"/>
       <c r="R122" s="128"/>
     </row>
-    <row r="123" spans="1:18" ht="45">
+    <row r="123" spans="1:18" ht="44">
       <c r="A123" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -34377,7 +34337,7 @@
       <c r="Q123" s="126"/>
       <c r="R123" s="128"/>
     </row>
-    <row r="124" spans="1:18" ht="33.75">
+    <row r="124" spans="1:18" ht="33">
       <c r="A124" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -34412,7 +34372,7 @@
       <c r="Q124" s="126"/>
       <c r="R124" s="128"/>
     </row>
-    <row r="125" spans="1:18" ht="33.75">
+    <row r="125" spans="1:18" ht="33">
       <c r="A125" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -34449,7 +34409,7 @@
       <c r="Q125" s="126"/>
       <c r="R125" s="128"/>
     </row>
-    <row r="126" spans="1:18" ht="33.75">
+    <row r="126" spans="1:18" ht="33">
       <c r="A126" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -34488,7 +34448,7 @@
       <c r="Q126" s="126"/>
       <c r="R126" s="128"/>
     </row>
-    <row r="127" spans="1:18" ht="33.75">
+    <row r="127" spans="1:18" ht="33">
       <c r="A127" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -34529,7 +34489,7 @@
       <c r="Q127" s="126"/>
       <c r="R127" s="128"/>
     </row>
-    <row r="128" spans="1:18" ht="22.5">
+    <row r="128" spans="1:18" ht="22">
       <c r="A128" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -34566,7 +34526,7 @@
       <c r="Q128" s="126"/>
       <c r="R128" s="128"/>
     </row>
-    <row r="129" spans="1:18" ht="22.5">
+    <row r="129" spans="1:18" ht="22">
       <c r="A129" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -34601,7 +34561,7 @@
       <c r="Q129" s="126"/>
       <c r="R129" s="128"/>
     </row>
-    <row r="130" spans="1:18" ht="45">
+    <row r="130" spans="1:18" ht="44">
       <c r="A130" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -34636,7 +34596,7 @@
       <c r="Q130" s="126"/>
       <c r="R130" s="128"/>
     </row>
-    <row r="131" spans="1:18" ht="22.5">
+    <row r="131" spans="1:18" ht="22">
       <c r="A131" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -34679,7 +34639,7 @@
       <c r="Q131" s="126"/>
       <c r="R131" s="128"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -34716,7 +34676,7 @@
       <c r="Q132" s="126"/>
       <c r="R132" s="128"/>
     </row>
-    <row r="133" spans="1:18" ht="22.5">
+    <row r="133" spans="1:18" ht="22">
       <c r="A133" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -34751,7 +34711,7 @@
       <c r="Q133" s="126"/>
       <c r="R133" s="128"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -34786,7 +34746,7 @@
       <c r="Q134" s="126"/>
       <c r="R134" s="128"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -34823,7 +34783,7 @@
       <c r="Q135" s="126"/>
       <c r="R135" s="128"/>
     </row>
-    <row r="136" spans="1:18" ht="33.75">
+    <row r="136" spans="1:18" ht="33">
       <c r="A136" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -34858,7 +34818,7 @@
       <c r="Q136" s="126"/>
       <c r="R136" s="128"/>
     </row>
-    <row r="137" spans="1:18" ht="33.75">
+    <row r="137" spans="1:18" ht="33">
       <c r="A137" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -34897,7 +34857,7 @@
       <c r="Q137" s="126"/>
       <c r="R137" s="128"/>
     </row>
-    <row r="138" spans="1:18" ht="33.75">
+    <row r="138" spans="1:18" ht="33">
       <c r="A138" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -34938,7 +34898,7 @@
       <c r="Q138" s="126"/>
       <c r="R138" s="128"/>
     </row>
-    <row r="139" spans="1:18" ht="33.75">
+    <row r="139" spans="1:18" ht="33">
       <c r="A139" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -34975,7 +34935,7 @@
       <c r="Q139" s="126"/>
       <c r="R139" s="128"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -35012,7 +34972,7 @@
       <c r="Q140" s="126"/>
       <c r="R140" s="128"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -35049,7 +35009,7 @@
       <c r="Q141" s="126"/>
       <c r="R141" s="128"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -35086,7 +35046,7 @@
       <c r="Q142" s="126"/>
       <c r="R142" s="128"/>
     </row>
-    <row r="143" spans="1:18" ht="22.5">
+    <row r="143" spans="1:18" ht="22">
       <c r="A143" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -35123,7 +35083,7 @@
       <c r="Q143" s="126"/>
       <c r="R143" s="128"/>
     </row>
-    <row r="144" spans="1:18" ht="22.5">
+    <row r="144" spans="1:18" ht="22">
       <c r="A144" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -35158,7 +35118,7 @@
       <c r="Q144" s="126"/>
       <c r="R144" s="128"/>
     </row>
-    <row r="145" spans="1:18" ht="22.5">
+    <row r="145" spans="1:18" ht="22">
       <c r="A145" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -35193,7 +35153,7 @@
       <c r="Q145" s="126"/>
       <c r="R145" s="128"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -35228,7 +35188,7 @@
       <c r="Q146" s="126"/>
       <c r="R146" s="128"/>
     </row>
-    <row r="147" spans="1:18" ht="22.5">
+    <row r="147" spans="1:18" ht="22">
       <c r="A147" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -35263,7 +35223,7 @@
       <c r="Q147" s="126"/>
       <c r="R147" s="128"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -35298,7 +35258,7 @@
       <c r="Q148" s="126"/>
       <c r="R148" s="128"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -35337,7 +35297,7 @@
       <c r="Q149" s="126"/>
       <c r="R149" s="128"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -35372,7 +35332,7 @@
       <c r="Q150" s="126"/>
       <c r="R150" s="128"/>
     </row>
-    <row r="151" spans="1:18" ht="33.75">
+    <row r="151" spans="1:18" ht="33">
       <c r="A151" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -35409,7 +35369,7 @@
       <c r="Q151" s="126"/>
       <c r="R151" s="128"/>
     </row>
-    <row r="152" spans="1:18" ht="33.75">
+    <row r="152" spans="1:18" ht="33">
       <c r="A152" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -35444,7 +35404,7 @@
       <c r="Q152" s="126"/>
       <c r="R152" s="128"/>
     </row>
-    <row r="153" spans="1:18" ht="33.75">
+    <row r="153" spans="1:18" ht="33">
       <c r="A153" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -35479,7 +35439,7 @@
       <c r="Q153" s="126"/>
       <c r="R153" s="128"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -35514,7 +35474,7 @@
       <c r="Q154" s="126"/>
       <c r="R154" s="128"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -35549,7 +35509,7 @@
       <c r="Q155" s="126"/>
       <c r="R155" s="128"/>
     </row>
-    <row r="156" spans="1:18" ht="22.5">
+    <row r="156" spans="1:18" ht="22">
       <c r="A156" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -35584,7 +35544,7 @@
       <c r="Q156" s="126"/>
       <c r="R156" s="128"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -35619,7 +35579,7 @@
       <c r="Q157" s="126"/>
       <c r="R157" s="128"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -35654,7 +35614,7 @@
       <c r="Q158" s="126"/>
       <c r="R158" s="128"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -35689,7 +35649,7 @@
       <c r="Q159" s="126"/>
       <c r="R159" s="128"/>
     </row>
-    <row r="160" spans="1:18" ht="33.75">
+    <row r="160" spans="1:18" ht="33">
       <c r="A160" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -35724,7 +35684,7 @@
       <c r="Q160" s="126"/>
       <c r="R160" s="128"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -35831,7 +35791,7 @@
       <c r="Q163" s="126"/>
       <c r="R163" s="128"/>
     </row>
-    <row r="164" spans="1:18" ht="22.5">
+    <row r="164" spans="1:18" ht="22">
       <c r="A164" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -35866,7 +35826,7 @@
       <c r="Q164" s="126"/>
       <c r="R164" s="128"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -35901,7 +35861,7 @@
       <c r="Q165" s="126"/>
       <c r="R165" s="128"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -35936,7 +35896,7 @@
       <c r="Q166" s="126"/>
       <c r="R166" s="128"/>
     </row>
-    <row r="167" spans="1:18" ht="33.75">
+    <row r="167" spans="1:18" ht="33">
       <c r="A167" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -35971,7 +35931,7 @@
       <c r="Q167" s="126"/>
       <c r="R167" s="128"/>
     </row>
-    <row r="168" spans="1:18" ht="22.5">
+    <row r="168" spans="1:18" ht="22">
       <c r="A168" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -36006,7 +35966,7 @@
       <c r="Q168" s="126"/>
       <c r="R168" s="128"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -36043,7 +36003,7 @@
       <c r="Q169" s="126"/>
       <c r="R169" s="128"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -36078,7 +36038,7 @@
       <c r="Q170" s="126"/>
       <c r="R170" s="128"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -36113,7 +36073,7 @@
       <c r="Q171" s="126"/>
       <c r="R171" s="128"/>
     </row>
-    <row r="172" spans="1:18" ht="45">
+    <row r="172" spans="1:18" ht="44">
       <c r="A172" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -36148,7 +36108,7 @@
       <c r="Q172" s="126"/>
       <c r="R172" s="128"/>
     </row>
-    <row r="173" spans="1:18" ht="45">
+    <row r="173" spans="1:18" ht="44">
       <c r="A173" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -36183,7 +36143,7 @@
       <c r="Q173" s="126"/>
       <c r="R173" s="128"/>
     </row>
-    <row r="174" spans="1:18" ht="33.75">
+    <row r="174" spans="1:18" ht="33">
       <c r="A174" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -36218,7 +36178,7 @@
       <c r="Q174" s="126"/>
       <c r="R174" s="128"/>
     </row>
-    <row r="175" spans="1:18" ht="45">
+    <row r="175" spans="1:18" ht="44">
       <c r="A175" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -36253,7 +36213,7 @@
       <c r="Q175" s="126"/>
       <c r="R175" s="128"/>
     </row>
-    <row r="176" spans="1:18" ht="45">
+    <row r="176" spans="1:18" ht="44">
       <c r="A176" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -36288,7 +36248,7 @@
       <c r="Q176" s="126"/>
       <c r="R176" s="128"/>
     </row>
-    <row r="177" spans="1:18" ht="22.5">
+    <row r="177" spans="1:18" ht="22">
       <c r="A177" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -36323,7 +36283,7 @@
       <c r="Q177" s="126"/>
       <c r="R177" s="128"/>
     </row>
-    <row r="178" spans="1:18" ht="33.75">
+    <row r="178" spans="1:18" ht="33">
       <c r="A178" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -36360,7 +36320,7 @@
       <c r="Q178" s="126"/>
       <c r="R178" s="128"/>
     </row>
-    <row r="179" spans="1:18" ht="22.5">
+    <row r="179" spans="1:18" ht="22">
       <c r="A179" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -36397,7 +36357,7 @@
       <c r="Q179" s="126"/>
       <c r="R179" s="128"/>
     </row>
-    <row r="180" spans="1:18" ht="22.5">
+    <row r="180" spans="1:18" ht="22">
       <c r="A180" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -36440,7 +36400,7 @@
       <c r="Q180" s="126"/>
       <c r="R180" s="128"/>
     </row>
-    <row r="181" spans="1:18" ht="22.5">
+    <row r="181" spans="1:18" ht="22">
       <c r="A181" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -36518,7 +36478,7 @@
       <c r="Q182" s="126"/>
       <c r="R182" s="128"/>
     </row>
-    <row r="183" spans="1:18" ht="22.5">
+    <row r="183" spans="1:18" ht="22">
       <c r="A183" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -36561,7 +36521,7 @@
       <c r="Q183" s="126"/>
       <c r="R183" s="128"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -36598,7 +36558,7 @@
       <c r="Q184" s="126"/>
       <c r="R184" s="128"/>
     </row>
-    <row r="185" spans="1:18" ht="22.5">
+    <row r="185" spans="1:18" ht="22">
       <c r="A185" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -36633,7 +36593,7 @@
       <c r="Q185" s="126"/>
       <c r="R185" s="128"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -36670,7 +36630,7 @@
       <c r="Q186" s="126"/>
       <c r="R186" s="128"/>
     </row>
-    <row r="187" spans="1:18" ht="22.5">
+    <row r="187" spans="1:18" ht="22">
       <c r="A187" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -36705,7 +36665,7 @@
       <c r="Q187" s="126"/>
       <c r="R187" s="128"/>
     </row>
-    <row r="188" spans="1:18" ht="33.75">
+    <row r="188" spans="1:18" ht="33">
       <c r="A188" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -36744,7 +36704,7 @@
       <c r="Q188" s="126"/>
       <c r="R188" s="128"/>
     </row>
-    <row r="189" spans="1:18" ht="22.5">
+    <row r="189" spans="1:18" ht="22">
       <c r="A189" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -36785,7 +36745,7 @@
       <c r="Q189" s="126"/>
       <c r="R189" s="128"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -36820,7 +36780,7 @@
       <c r="Q190" s="126"/>
       <c r="R190" s="128"/>
     </row>
-    <row r="191" spans="1:18" ht="22.5">
+    <row r="191" spans="1:18" ht="22">
       <c r="A191" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -36855,7 +36815,7 @@
       <c r="Q191" s="126"/>
       <c r="R191" s="128"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -36890,7 +36850,7 @@
       <c r="Q192" s="126"/>
       <c r="R192" s="128"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -36925,7 +36885,7 @@
       <c r="Q193" s="126"/>
       <c r="R193" s="128"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -36960,7 +36920,7 @@
       <c r="Q194" s="126"/>
       <c r="R194" s="128"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -36995,7 +36955,7 @@
       <c r="Q195" s="126"/>
       <c r="R195" s="128"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -37032,7 +36992,7 @@
       <c r="Q196" s="126"/>
       <c r="R196" s="128"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -37071,7 +37031,7 @@
       <c r="Q197" s="126"/>
       <c r="R197" s="128"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -37141,7 +37101,7 @@
       <c r="Q199" s="126"/>
       <c r="R199" s="128"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -37176,7 +37136,7 @@
       <c r="Q200" s="126"/>
       <c r="R200" s="128"/>
     </row>
-    <row r="201" spans="1:18" ht="33.75">
+    <row r="201" spans="1:18" ht="33">
       <c r="A201" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -37211,7 +37171,7 @@
       <c r="Q201" s="126"/>
       <c r="R201" s="128"/>
     </row>
-    <row r="202" spans="1:18" ht="33.75">
+    <row r="202" spans="1:18" ht="33">
       <c r="A202" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -37246,7 +37206,7 @@
       <c r="Q202" s="126"/>
       <c r="R202" s="128"/>
     </row>
-    <row r="203" spans="1:18" ht="45">
+    <row r="203" spans="1:18" ht="44">
       <c r="A203" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -37281,7 +37241,7 @@
       <c r="Q203" s="126"/>
       <c r="R203" s="128"/>
     </row>
-    <row r="204" spans="1:18" ht="33.75">
+    <row r="204" spans="1:18" ht="33">
       <c r="A204" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -37316,7 +37276,7 @@
       <c r="Q204" s="126"/>
       <c r="R204" s="128"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -37351,7 +37311,7 @@
       <c r="Q205" s="126"/>
       <c r="R205" s="128"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -37386,7 +37346,7 @@
       <c r="Q206" s="126"/>
       <c r="R206" s="128"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -37421,7 +37381,7 @@
       <c r="Q207" s="126"/>
       <c r="R207" s="128"/>
     </row>
-    <row r="208" spans="1:18" ht="33.75">
+    <row r="208" spans="1:18" ht="33">
       <c r="A208" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -37456,7 +37416,7 @@
       <c r="Q208" s="126"/>
       <c r="R208" s="128"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -37491,7 +37451,7 @@
       <c r="Q209" s="126"/>
       <c r="R209" s="128"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -37530,7 +37490,7 @@
       <c r="Q210" s="126"/>
       <c r="R210" s="128"/>
     </row>
-    <row r="211" spans="1:18" ht="22.5">
+    <row r="211" spans="1:18" ht="22">
       <c r="A211" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -37565,7 +37525,7 @@
       <c r="Q211" s="126"/>
       <c r="R211" s="128"/>
     </row>
-    <row r="212" spans="1:18" ht="22.5">
+    <row r="212" spans="1:18" ht="22">
       <c r="A212" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -37635,7 +37595,7 @@
       <c r="Q213" s="126"/>
       <c r="R213" s="128"/>
     </row>
-    <row r="214" spans="1:18" ht="22.5">
+    <row r="214" spans="1:18" ht="22">
       <c r="A214" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -37670,7 +37630,7 @@
       <c r="Q214" s="126"/>
       <c r="R214" s="128"/>
     </row>
-    <row r="215" spans="1:18" ht="45">
+    <row r="215" spans="1:18" ht="44">
       <c r="A215" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -37705,7 +37665,7 @@
       <c r="Q215" s="126"/>
       <c r="R215" s="128"/>
     </row>
-    <row r="216" spans="1:18" ht="33.75">
+    <row r="216" spans="1:18" ht="33">
       <c r="A216" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -37740,7 +37700,7 @@
       <c r="Q216" s="126"/>
       <c r="R216" s="128"/>
     </row>
-    <row r="217" spans="1:18" ht="33.75">
+    <row r="217" spans="1:18" ht="33">
       <c r="A217" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -37775,7 +37735,7 @@
       <c r="Q217" s="126"/>
       <c r="R217" s="128"/>
     </row>
-    <row r="218" spans="1:18" ht="45">
+    <row r="218" spans="1:18" ht="44">
       <c r="A218" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -37810,7 +37770,7 @@
       <c r="Q218" s="126"/>
       <c r="R218" s="128"/>
     </row>
-    <row r="219" spans="1:18" ht="33.75">
+    <row r="219" spans="1:18" ht="33">
       <c r="A219" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -37845,7 +37805,7 @@
       <c r="Q219" s="126"/>
       <c r="R219" s="128"/>
     </row>
-    <row r="220" spans="1:18" ht="33.75">
+    <row r="220" spans="1:18" ht="33">
       <c r="A220" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -37880,7 +37840,7 @@
       <c r="Q220" s="126"/>
       <c r="R220" s="128"/>
     </row>
-    <row r="221" spans="1:18" ht="22.5">
+    <row r="221" spans="1:18" ht="22">
       <c r="A221" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -37915,7 +37875,7 @@
       <c r="Q221" s="126"/>
       <c r="R221" s="128"/>
     </row>
-    <row r="222" spans="1:18" ht="22.5">
+    <row r="222" spans="1:18" ht="22">
       <c r="A222" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -37950,7 +37910,7 @@
       <c r="Q222" s="126"/>
       <c r="R222" s="128"/>
     </row>
-    <row r="223" spans="1:18" ht="33.75">
+    <row r="223" spans="1:18" ht="33">
       <c r="A223" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -37985,7 +37945,7 @@
       <c r="Q223" s="126"/>
       <c r="R223" s="128"/>
     </row>
-    <row r="224" spans="1:18" ht="22.5">
+    <row r="224" spans="1:18" ht="22">
       <c r="A224" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -38020,7 +37980,7 @@
       <c r="Q224" s="126"/>
       <c r="R224" s="128"/>
     </row>
-    <row r="225" spans="1:18" ht="45">
+    <row r="225" spans="1:18" ht="44">
       <c r="A225" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -38057,7 +38017,7 @@
       <c r="Q225" s="126"/>
       <c r="R225" s="128"/>
     </row>
-    <row r="226" spans="1:18" ht="45">
+    <row r="226" spans="1:18" ht="44">
       <c r="A226" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -38092,7 +38052,7 @@
       <c r="Q226" s="126"/>
       <c r="R226" s="128"/>
     </row>
-    <row r="227" spans="1:18" ht="33.75">
+    <row r="227" spans="1:18" ht="33">
       <c r="A227" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -38127,7 +38087,7 @@
       <c r="Q227" s="126"/>
       <c r="R227" s="128"/>
     </row>
-    <row r="228" spans="1:18" ht="33.75">
+    <row r="228" spans="1:18" ht="33">
       <c r="A228" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -38164,7 +38124,7 @@
       <c r="Q228" s="126"/>
       <c r="R228" s="128"/>
     </row>
-    <row r="229" spans="1:18" ht="22.5">
+    <row r="229" spans="1:18" ht="22">
       <c r="A229" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -38201,7 +38161,7 @@
       <c r="Q229" s="126"/>
       <c r="R229" s="128"/>
     </row>
-    <row r="230" spans="1:18" ht="22.5">
+    <row r="230" spans="1:18" ht="22">
       <c r="A230" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -38244,7 +38204,7 @@
       <c r="Q230" s="126"/>
       <c r="R230" s="128"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -38281,7 +38241,7 @@
       <c r="Q231" s="126"/>
       <c r="R231" s="128"/>
     </row>
-    <row r="232" spans="1:18" ht="22.5">
+    <row r="232" spans="1:18" ht="22">
       <c r="A232" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -38316,7 +38276,7 @@
       <c r="Q232" s="126"/>
       <c r="R232" s="128"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -38351,7 +38311,7 @@
       <c r="Q233" s="126"/>
       <c r="R233" s="128"/>
     </row>
-    <row r="234" spans="1:18" ht="22.5">
+    <row r="234" spans="1:18" ht="22">
       <c r="A234" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -38386,7 +38346,7 @@
       <c r="Q234" s="126"/>
       <c r="R234" s="128"/>
     </row>
-    <row r="235" spans="1:18" ht="33.75">
+    <row r="235" spans="1:18" ht="33">
       <c r="A235" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -38421,7 +38381,7 @@
       <c r="Q235" s="126"/>
       <c r="R235" s="128"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -38458,7 +38418,7 @@
       <c r="Q236" s="126"/>
       <c r="R236" s="128"/>
     </row>
-    <row r="237" spans="1:18" ht="33.75">
+    <row r="237" spans="1:18" ht="33">
       <c r="A237" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -38493,7 +38453,7 @@
       <c r="Q237" s="126"/>
       <c r="R237" s="128"/>
     </row>
-    <row r="238" spans="1:18" ht="45">
+    <row r="238" spans="1:18" ht="44">
       <c r="A238" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -38528,7 +38488,7 @@
       <c r="Q238" s="126"/>
       <c r="R238" s="128"/>
     </row>
-    <row r="239" spans="1:18" ht="45">
+    <row r="239" spans="1:18" ht="44">
       <c r="A239" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -38563,7 +38523,7 @@
       <c r="Q239" s="126"/>
       <c r="R239" s="128"/>
     </row>
-    <row r="240" spans="1:18" ht="33.75">
+    <row r="240" spans="1:18" ht="33">
       <c r="A240" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -38598,7 +38558,7 @@
       <c r="Q240" s="126"/>
       <c r="R240" s="128"/>
     </row>
-    <row r="241" spans="1:18" ht="33.75">
+    <row r="241" spans="1:18" ht="33">
       <c r="A241" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -38635,7 +38595,7 @@
       <c r="Q241" s="126"/>
       <c r="R241" s="128"/>
     </row>
-    <row r="242" spans="1:18" ht="33.75">
+    <row r="242" spans="1:18" ht="33">
       <c r="A242" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -38676,7 +38636,7 @@
       <c r="Q242" s="126"/>
       <c r="R242" s="128"/>
     </row>
-    <row r="243" spans="1:18" ht="22.5">
+    <row r="243" spans="1:18" ht="22">
       <c r="A243" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -38719,7 +38679,7 @@
       <c r="Q243" s="126"/>
       <c r="R243" s="128"/>
     </row>
-    <row r="244" spans="1:18" ht="22.5">
+    <row r="244" spans="1:18" ht="22">
       <c r="A244" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -38754,7 +38714,7 @@
       <c r="Q244" s="126"/>
       <c r="R244" s="128"/>
     </row>
-    <row r="245" spans="1:18" ht="33.75">
+    <row r="245" spans="1:18" ht="33">
       <c r="A245" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -38793,7 +38753,7 @@
       <c r="Q245" s="126"/>
       <c r="R245" s="128"/>
     </row>
-    <row r="246" spans="1:18" ht="33.75">
+    <row r="246" spans="1:18" ht="33">
       <c r="A246" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -38828,7 +38788,7 @@
       <c r="Q246" s="126"/>
       <c r="R246" s="128"/>
     </row>
-    <row r="247" spans="1:18" ht="33.75">
+    <row r="247" spans="1:18" ht="33">
       <c r="A247" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -38869,7 +38829,7 @@
       <c r="Q247" s="126"/>
       <c r="R247" s="128"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -38906,7 +38866,7 @@
       <c r="Q248" s="126"/>
       <c r="R248" s="128"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -38943,7 +38903,7 @@
       <c r="Q249" s="126"/>
       <c r="R249" s="128"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -38980,7 +38940,7 @@
       <c r="Q250" s="126"/>
       <c r="R250" s="128"/>
     </row>
-    <row r="251" spans="1:18" ht="22.5">
+    <row r="251" spans="1:18" ht="22">
       <c r="A251" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -39019,7 +38979,7 @@
       <c r="Q251" s="126"/>
       <c r="R251" s="128"/>
     </row>
-    <row r="252" spans="1:18" ht="22.5">
+    <row r="252" spans="1:18" ht="22">
       <c r="A252" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -39054,7 +39014,7 @@
       <c r="Q252" s="126"/>
       <c r="R252" s="128"/>
     </row>
-    <row r="253" spans="1:18" ht="33.75">
+    <row r="253" spans="1:18" ht="33">
       <c r="A253" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -39091,7 +39051,7 @@
       <c r="Q253" s="126"/>
       <c r="R253" s="128"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -39126,7 +39086,7 @@
       <c r="Q254" s="126"/>
       <c r="R254" s="128"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -39161,7 +39121,7 @@
       <c r="Q255" s="126"/>
       <c r="R255" s="128"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -39196,7 +39156,7 @@
       <c r="Q256" s="126"/>
       <c r="R256" s="128"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -39231,7 +39191,7 @@
       <c r="Q257" s="126"/>
       <c r="R257" s="128"/>
     </row>
-    <row r="258" spans="1:18" ht="22.5">
+    <row r="258" spans="1:18" ht="22">
       <c r="A258" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -39266,7 +39226,7 @@
       <c r="Q258" s="126"/>
       <c r="R258" s="128"/>
     </row>
-    <row r="259" spans="1:18" ht="22.5">
+    <row r="259" spans="1:18" ht="22">
       <c r="A259" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -39301,7 +39261,7 @@
       <c r="Q259" s="126"/>
       <c r="R259" s="128"/>
     </row>
-    <row r="260" spans="1:18" ht="33.75">
+    <row r="260" spans="1:18" ht="33">
       <c r="A260" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -39336,7 +39296,7 @@
       <c r="Q260" s="126"/>
       <c r="R260" s="128"/>
     </row>
-    <row r="261" spans="1:18" ht="33.75">
+    <row r="261" spans="1:18" ht="33">
       <c r="A261" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -39371,7 +39331,7 @@
       <c r="Q261" s="126"/>
       <c r="R261" s="128"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -39406,7 +39366,7 @@
       <c r="Q262" s="126"/>
       <c r="R262" s="128"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -39513,7 +39473,7 @@
       <c r="Q265" s="126"/>
       <c r="R265" s="128"/>
     </row>
-    <row r="266" spans="1:18" ht="22.5">
+    <row r="266" spans="1:18" ht="22">
       <c r="A266" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -39548,7 +39508,7 @@
       <c r="Q266" s="126"/>
       <c r="R266" s="128"/>
     </row>
-    <row r="267" spans="1:18" ht="22.5">
+    <row r="267" spans="1:18" ht="22">
       <c r="A267" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -39583,7 +39543,7 @@
       <c r="Q267" s="126"/>
       <c r="R267" s="128"/>
     </row>
-    <row r="268" spans="1:18" ht="22.5">
+    <row r="268" spans="1:18" ht="22">
       <c r="A268" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -39618,7 +39578,7 @@
       <c r="Q268" s="126"/>
       <c r="R268" s="128"/>
     </row>
-    <row r="269" spans="1:18" ht="33.75">
+    <row r="269" spans="1:18" ht="33">
       <c r="A269" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -39653,7 +39613,7 @@
       <c r="Q269" s="126"/>
       <c r="R269" s="128"/>
     </row>
-    <row r="270" spans="1:18" ht="22.5">
+    <row r="270" spans="1:18" ht="22">
       <c r="A270" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -39690,7 +39650,7 @@
       <c r="Q270" s="126"/>
       <c r="R270" s="128"/>
     </row>
-    <row r="271" spans="1:18" ht="33.75">
+    <row r="271" spans="1:18" ht="33">
       <c r="A271" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -39725,7 +39685,7 @@
       <c r="Q271" s="126"/>
       <c r="R271" s="128"/>
     </row>
-    <row r="272" spans="1:18" ht="45">
+    <row r="272" spans="1:18" ht="44">
       <c r="A272" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -39760,7 +39720,7 @@
       <c r="Q272" s="126"/>
       <c r="R272" s="128"/>
     </row>
-    <row r="273" spans="1:18" ht="45">
+    <row r="273" spans="1:18" ht="44">
       <c r="A273" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -39795,7 +39755,7 @@
       <c r="Q273" s="126"/>
       <c r="R273" s="128"/>
     </row>
-    <row r="274" spans="1:18" ht="22.5">
+    <row r="274" spans="1:18" ht="22">
       <c r="A274" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -39830,7 +39790,7 @@
       <c r="Q274" s="126"/>
       <c r="R274" s="128"/>
     </row>
-    <row r="275" spans="1:18" ht="45">
+    <row r="275" spans="1:18" ht="44">
       <c r="A275" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -39865,7 +39825,7 @@
       <c r="Q275" s="126"/>
       <c r="R275" s="128"/>
     </row>
-    <row r="276" spans="1:18" ht="45">
+    <row r="276" spans="1:18" ht="44">
       <c r="A276" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -39900,7 +39860,7 @@
       <c r="Q276" s="126"/>
       <c r="R276" s="128"/>
     </row>
-    <row r="277" spans="1:18" ht="22.5">
+    <row r="277" spans="1:18" ht="22">
       <c r="A277" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -39935,7 +39895,7 @@
       <c r="Q277" s="126"/>
       <c r="R277" s="128"/>
     </row>
-    <row r="278" spans="1:18" ht="22.5">
+    <row r="278" spans="1:18" ht="22">
       <c r="A278" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -39972,7 +39932,7 @@
       <c r="Q278" s="126"/>
       <c r="R278" s="128"/>
     </row>
-    <row r="279" spans="1:18" ht="22.5">
+    <row r="279" spans="1:18" ht="22">
       <c r="A279" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -40015,7 +39975,7 @@
       <c r="Q279" s="126"/>
       <c r="R279" s="128"/>
     </row>
-    <row r="280" spans="1:18" ht="22.5">
+    <row r="280" spans="1:18" ht="22">
       <c r="A280" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -40050,7 +40010,7 @@
       <c r="Q280" s="126"/>
       <c r="R280" s="128"/>
     </row>
-    <row r="281" spans="1:18" ht="22.5">
+    <row r="281" spans="1:18" ht="22">
       <c r="A281" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -40085,7 +40045,7 @@
       <c r="Q281" s="126"/>
       <c r="R281" s="128"/>
     </row>
-    <row r="282" spans="1:18" ht="22.5">
+    <row r="282" spans="1:18" ht="22">
       <c r="A282" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -40120,7 +40080,7 @@
       <c r="Q282" s="126"/>
       <c r="R282" s="128"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -40161,7 +40121,7 @@
       <c r="Q283" s="126"/>
       <c r="R283" s="128"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -40198,7 +40158,7 @@
       <c r="Q284" s="126"/>
       <c r="R284" s="128"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -40235,7 +40195,7 @@
       <c r="Q285" s="126"/>
       <c r="R285" s="128"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -40272,7 +40232,7 @@
       <c r="Q286" s="126"/>
       <c r="R286" s="128"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -40311,7 +40271,7 @@
       <c r="Q287" s="126"/>
       <c r="R287" s="128"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -40346,7 +40306,7 @@
       <c r="Q288" s="126"/>
       <c r="R288" s="128"/>
     </row>
-    <row r="289" spans="1:18" ht="33.75">
+    <row r="289" spans="1:18" ht="33">
       <c r="A289" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -40381,7 +40341,7 @@
       <c r="Q289" s="126"/>
       <c r="R289" s="128"/>
     </row>
-    <row r="290" spans="1:18" ht="33.75">
+    <row r="290" spans="1:18" ht="33">
       <c r="A290" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -40416,7 +40376,7 @@
       <c r="Q290" s="126"/>
       <c r="R290" s="128"/>
     </row>
-    <row r="291" spans="1:18" ht="33.75">
+    <row r="291" spans="1:18" ht="33">
       <c r="A291" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -40451,7 +40411,7 @@
       <c r="Q291" s="126"/>
       <c r="R291" s="128"/>
     </row>
-    <row r="292" spans="1:18" ht="33.75">
+    <row r="292" spans="1:18" ht="33">
       <c r="A292" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -40486,7 +40446,7 @@
       <c r="Q292" s="126"/>
       <c r="R292" s="128"/>
     </row>
-    <row r="293" spans="1:18" ht="33.75">
+    <row r="293" spans="1:18" ht="33">
       <c r="A293" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -40521,7 +40481,7 @@
       <c r="Q293" s="126"/>
       <c r="R293" s="128"/>
     </row>
-    <row r="294" spans="1:18" ht="22.5">
+    <row r="294" spans="1:18" ht="22">
       <c r="A294" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -40556,7 +40516,7 @@
       <c r="Q294" s="126"/>
       <c r="R294" s="128"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -40591,7 +40551,7 @@
       <c r="Q295" s="126"/>
       <c r="R295" s="128"/>
     </row>
-    <row r="296" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="296" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A296" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -40669,7 +40629,7 @@
       <c r="Q297" s="131"/>
       <c r="R297" s="131"/>
     </row>
-    <row r="298" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="298" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A298" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -40714,7 +40674,7 @@
       <c r="Q298" s="102"/>
       <c r="R298" s="102"/>
     </row>
-    <row r="299" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="299" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A299" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -40759,7 +40719,7 @@
       <c r="Q299" s="102"/>
       <c r="R299" s="102"/>
     </row>
-    <row r="300" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="300" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A300" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -40804,7 +40764,7 @@
       <c r="Q300" s="102"/>
       <c r="R300" s="102"/>
     </row>
-    <row r="301" spans="1:18" ht="22.5">
+    <row r="301" spans="1:18" ht="22">
       <c r="A301" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -40849,7 +40809,7 @@
       <c r="Q301" s="98"/>
       <c r="R301" s="98"/>
     </row>
-    <row r="302" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="302" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A302" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -40877,13 +40837,13 @@
         <v>648</v>
       </c>
       <c r="J302" s="166" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K302" s="167" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L302" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M302" s="98"/>
       <c r="N302" s="169"/>
@@ -40892,7 +40852,7 @@
       <c r="Q302" s="167"/>
       <c r="R302" s="167"/>
     </row>
-    <row r="303" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="303" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A303" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -40920,13 +40880,13 @@
         <v>648</v>
       </c>
       <c r="J303" s="166" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K303" s="167" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L303" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M303" s="98"/>
       <c r="N303" s="169"/>
@@ -40935,7 +40895,7 @@
       <c r="Q303" s="167"/>
       <c r="R303" s="167"/>
     </row>
-    <row r="304" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="304" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A304" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A304" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E304),
@@ -40980,7 +40940,7 @@
       <c r="Q304" s="102"/>
       <c r="R304" s="102"/>
     </row>
-    <row r="305" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="305" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A305" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A305" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E305),
@@ -41025,7 +40985,7 @@
       <c r="Q305" s="102"/>
       <c r="R305" s="102"/>
     </row>
-    <row r="306" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="306" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A306" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A306" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E306),
@@ -41070,7 +41030,7 @@
       <c r="Q306" s="102"/>
       <c r="R306" s="102"/>
     </row>
-    <row r="307" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="307" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A307" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A307" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E307),
@@ -41115,7 +41075,7 @@
       <c r="Q307" s="102"/>
       <c r="R307" s="102"/>
     </row>
-    <row r="308" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="308" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A308" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A308" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E308),
@@ -41160,7 +41120,7 @@
       <c r="Q308" s="102"/>
       <c r="R308" s="102"/>
     </row>
-    <row r="309" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="309" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A309" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A309" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E309),
@@ -41205,7 +41165,7 @@
       <c r="Q309" s="102"/>
       <c r="R309" s="102"/>
     </row>
-    <row r="310" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="310" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A310" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A310" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E310),
@@ -41248,7 +41208,7 @@
       <c r="Q310" s="102"/>
       <c r="R310" s="102"/>
     </row>
-    <row r="311" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="311" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A311" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A311" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E311),
@@ -41291,7 +41251,7 @@
       <c r="Q311" s="102"/>
       <c r="R311" s="102"/>
     </row>
-    <row r="312" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="312" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A312" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A312" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E312),
@@ -41334,7 +41294,7 @@
       <c r="Q312" s="102"/>
       <c r="R312" s="102"/>
     </row>
-    <row r="313" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="313" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A313" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A313" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E313),
@@ -41377,7 +41337,7 @@
       <c r="Q313" s="102"/>
       <c r="R313" s="102"/>
     </row>
-    <row r="314" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="314" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A314" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A314" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E314),
@@ -41420,7 +41380,7 @@
       <c r="Q314" s="102"/>
       <c r="R314" s="102"/>
     </row>
-    <row r="315" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="315" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A315" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A315" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E315),
@@ -41463,7 +41423,7 @@
       <c r="Q315" s="102"/>
       <c r="R315" s="102"/>
     </row>
-    <row r="316" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="316" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A316" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A316" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E316),
@@ -41506,7 +41466,7 @@
       <c r="Q316" s="102"/>
       <c r="R316" s="102"/>
     </row>
-    <row r="317" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="317" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A317" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A317" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E317),
@@ -41549,7 +41509,7 @@
       <c r="Q317" s="102"/>
       <c r="R317" s="102"/>
     </row>
-    <row r="318" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="318" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A318" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A318" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E318),
@@ -41592,7 +41552,7 @@
       <c r="Q318" s="102"/>
       <c r="R318" s="102"/>
     </row>
-    <row r="319" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="319" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A319" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A319" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E319),
@@ -41637,7 +41597,7 @@
       <c r="Q319" s="102"/>
       <c r="R319" s="102"/>
     </row>
-    <row r="320" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="320" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A320" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A320" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E320),
@@ -41674,7 +41634,7 @@
       <c r="Q320" s="131"/>
       <c r="R320" s="131"/>
     </row>
-    <row r="321" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="321" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A321" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A321" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E321),
@@ -41719,7 +41679,7 @@
       <c r="Q321" s="102"/>
       <c r="R321" s="102"/>
     </row>
-    <row r="322" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="322" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A322" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A322" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E322),
@@ -41762,7 +41722,7 @@
       <c r="Q322" s="102"/>
       <c r="R322" s="102"/>
     </row>
-    <row r="323" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="323" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A323" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A323" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E323),
@@ -41805,7 +41765,7 @@
       <c r="Q323" s="102"/>
       <c r="R323" s="102"/>
     </row>
-    <row r="324" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="324" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A324" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A324" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E324),
@@ -41848,7 +41808,7 @@
       <c r="Q324" s="102"/>
       <c r="R324" s="102"/>
     </row>
-    <row r="325" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="325" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A325" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A325" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E325),
@@ -41891,7 +41851,7 @@
       <c r="Q325" s="102"/>
       <c r="R325" s="102"/>
     </row>
-    <row r="326" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="326" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A326" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A326" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E326),
@@ -41934,7 +41894,7 @@
       <c r="Q326" s="102"/>
       <c r="R326" s="102"/>
     </row>
-    <row r="327" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="327" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A327" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A327" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E327),
@@ -41977,7 +41937,7 @@
       <c r="Q327" s="102"/>
       <c r="R327" s="102"/>
     </row>
-    <row r="328" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="328" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A328" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A328" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E328),
@@ -42020,7 +41980,7 @@
       <c r="Q328" s="102"/>
       <c r="R328" s="102"/>
     </row>
-    <row r="329" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="329" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A329" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A329" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E329),
@@ -42063,7 +42023,7 @@
       <c r="Q329" s="102"/>
       <c r="R329" s="102"/>
     </row>
-    <row r="330" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="330" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A330" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A330" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E330),
@@ -42106,7 +42066,7 @@
       <c r="Q330" s="102"/>
       <c r="R330" s="102"/>
     </row>
-    <row r="331" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="331" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A331" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A331" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E331),
@@ -42151,7 +42111,7 @@
       <c r="Q331" s="102"/>
       <c r="R331" s="102"/>
     </row>
-    <row r="332" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="332" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A332" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A332" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E332),
@@ -42194,7 +42154,7 @@
       <c r="Q332" s="102"/>
       <c r="R332" s="102"/>
     </row>
-    <row r="333" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="333" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A333" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A333" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E333),
@@ -42237,7 +42197,7 @@
       <c r="Q333" s="102"/>
       <c r="R333" s="102"/>
     </row>
-    <row r="334" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="334" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A334" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A334" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E334),
@@ -42280,7 +42240,7 @@
       <c r="Q334" s="102"/>
       <c r="R334" s="102"/>
     </row>
-    <row r="335" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="335" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A335" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A335" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E335),
@@ -42323,7 +42283,7 @@
       <c r="Q335" s="102"/>
       <c r="R335" s="102"/>
     </row>
-    <row r="336" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="336" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A336" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A336" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E336),
@@ -42366,7 +42326,7 @@
       <c r="Q336" s="102"/>
       <c r="R336" s="102"/>
     </row>
-    <row r="337" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="337" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A337" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A337" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E337),
@@ -42409,7 +42369,7 @@
       <c r="Q337" s="102"/>
       <c r="R337" s="102"/>
     </row>
-    <row r="338" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="338" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A338" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A338" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E338),
@@ -42452,7 +42412,7 @@
       <c r="Q338" s="102"/>
       <c r="R338" s="102"/>
     </row>
-    <row r="339" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="339" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A339" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A339" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E339),
@@ -42495,7 +42455,7 @@
       <c r="Q339" s="102"/>
       <c r="R339" s="102"/>
     </row>
-    <row r="340" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="340" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A340" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A340" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E340),
@@ -42538,7 +42498,7 @@
       <c r="Q340" s="102"/>
       <c r="R340" s="102"/>
     </row>
-    <row r="341" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="341" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A341" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A341" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E341),
@@ -42583,7 +42543,7 @@
       <c r="Q341" s="102"/>
       <c r="R341" s="102"/>
     </row>
-    <row r="342" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="342" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A342" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A342" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E342),
@@ -42626,7 +42586,7 @@
       <c r="Q342" s="102"/>
       <c r="R342" s="102"/>
     </row>
-    <row r="343" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="343" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A343" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A343" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E343),
@@ -42669,7 +42629,7 @@
       <c r="Q343" s="102"/>
       <c r="R343" s="102"/>
     </row>
-    <row r="344" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="344" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A344" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A344" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E344),
@@ -42712,7 +42672,7 @@
       <c r="Q344" s="102"/>
       <c r="R344" s="102"/>
     </row>
-    <row r="345" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="345" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A345" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A345" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E345),
@@ -42755,7 +42715,7 @@
       <c r="Q345" s="102"/>
       <c r="R345" s="102"/>
     </row>
-    <row r="346" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="346" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A346" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A346" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E346),
@@ -42798,7 +42758,7 @@
       <c r="Q346" s="102"/>
       <c r="R346" s="102"/>
     </row>
-    <row r="347" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="347" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A347" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A347" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E347),
@@ -42841,7 +42801,7 @@
       <c r="Q347" s="102"/>
       <c r="R347" s="102"/>
     </row>
-    <row r="348" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="348" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A348" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A348" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E348),
@@ -42884,7 +42844,7 @@
       <c r="Q348" s="102"/>
       <c r="R348" s="102"/>
     </row>
-    <row r="349" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="349" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A349" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A349" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E349),
@@ -42927,7 +42887,7 @@
       <c r="Q349" s="102"/>
       <c r="R349" s="102"/>
     </row>
-    <row r="350" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="350" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A350" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A350" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E350),
@@ -42970,7 +42930,7 @@
       <c r="Q350" s="102"/>
       <c r="R350" s="102"/>
     </row>
-    <row r="351" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="351" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A351" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A351" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E351),
@@ -43005,7 +42965,7 @@
       <c r="Q351" s="131"/>
       <c r="R351" s="131"/>
     </row>
-    <row r="352" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="352" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A352" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A352" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E352),
@@ -43040,7 +43000,7 @@
       <c r="Q352" s="131"/>
       <c r="R352" s="131"/>
     </row>
-    <row r="353" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="353" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A353" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A353" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E353),
@@ -43077,7 +43037,7 @@
       <c r="Q353" s="131"/>
       <c r="R353" s="131"/>
     </row>
-    <row r="354" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="354" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A354" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A354" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E354),
@@ -43112,7 +43072,7 @@
       <c r="Q354" s="131"/>
       <c r="R354" s="131"/>
     </row>
-    <row r="355" spans="1:18" ht="22.5">
+    <row r="355" spans="1:18" ht="22">
       <c r="A355" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A355" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E355),
@@ -43149,7 +43109,7 @@
       <c r="Q355" s="126"/>
       <c r="R355" s="126"/>
     </row>
-    <row r="356" spans="1:18" ht="22.5">
+    <row r="356" spans="1:18" ht="22">
       <c r="A356" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A356" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E356),
@@ -43184,7 +43144,7 @@
       <c r="Q356" s="126"/>
       <c r="R356" s="126"/>
     </row>
-    <row r="357" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="357" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A357" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A357" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E357),
@@ -43221,7 +43181,7 @@
       <c r="Q357" s="131"/>
       <c r="R357" s="131"/>
     </row>
-    <row r="358" spans="1:18" s="37" customFormat="1" ht="67.5">
+    <row r="358" spans="1:18" s="37" customFormat="1" ht="66">
       <c r="A358" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A358" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E358),
@@ -43253,10 +43213,10 @@
         <v>693</v>
       </c>
       <c r="J358" s="96" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K358" s="102" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L358" s="167" t="s">
         <v>645</v>
@@ -43270,7 +43230,7 @@
       <c r="Q358" s="167"/>
       <c r="R358" s="167"/>
     </row>
-    <row r="359" spans="1:18" s="37" customFormat="1" ht="67.5">
+    <row r="359" spans="1:18" s="37" customFormat="1" ht="66">
       <c r="A359" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A359" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E359),
@@ -43296,10 +43256,10 @@
         <v>693</v>
       </c>
       <c r="J359" s="96" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K359" s="102" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L359" s="167" t="s">
         <v>645</v>
@@ -43313,7 +43273,7 @@
       <c r="Q359" s="167"/>
       <c r="R359" s="167"/>
     </row>
-    <row r="360" spans="1:18" ht="22.5">
+    <row r="360" spans="1:18" ht="22">
       <c r="A360" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A360" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E360),
@@ -43348,7 +43308,7 @@
       <c r="Q360" s="128"/>
       <c r="R360" s="128"/>
     </row>
-    <row r="361" spans="1:18" ht="67.5">
+    <row r="361" spans="1:18" ht="66">
       <c r="A361" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A361" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E361),
@@ -43376,10 +43336,10 @@
         <v>693</v>
       </c>
       <c r="J361" s="96" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="K361" s="97" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L361" s="97" t="s">
         <v>645</v>
@@ -43393,7 +43353,7 @@
       <c r="Q361" s="97"/>
       <c r="R361" s="97"/>
     </row>
-    <row r="362" spans="1:18" ht="45">
+    <row r="362" spans="1:18" ht="44">
       <c r="A362" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A362" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E362),
@@ -43428,7 +43388,7 @@
       <c r="Q362" s="128"/>
       <c r="R362" s="128"/>
     </row>
-    <row r="363" spans="1:18" ht="33.75">
+    <row r="363" spans="1:18" ht="33">
       <c r="A363" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A363" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E363),
@@ -43463,7 +43423,7 @@
       <c r="Q363" s="128"/>
       <c r="R363" s="128"/>
     </row>
-    <row r="364" spans="1:18" ht="45">
+    <row r="364" spans="1:18" ht="44">
       <c r="A364" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A364" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E364),
@@ -43498,7 +43458,7 @@
       <c r="Q364" s="128"/>
       <c r="R364" s="128"/>
     </row>
-    <row r="365" spans="1:18" ht="33.75">
+    <row r="365" spans="1:18" ht="33">
       <c r="A365" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A365" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E365),
@@ -43533,7 +43493,7 @@
       <c r="Q365" s="128"/>
       <c r="R365" s="128"/>
     </row>
-    <row r="366" spans="1:18" ht="45">
+    <row r="366" spans="1:18" ht="44">
       <c r="A366" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A366" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E366),
@@ -43568,7 +43528,7 @@
       <c r="Q366" s="128"/>
       <c r="R366" s="128"/>
     </row>
-    <row r="367" spans="1:18" ht="45">
+    <row r="367" spans="1:18" ht="44">
       <c r="A367" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A367" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E367),
@@ -43596,13 +43556,13 @@
         <v>695</v>
       </c>
       <c r="J367" s="243" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K367" s="97" t="s">
         <v>696</v>
       </c>
       <c r="L367" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M367" s="169"/>
       <c r="N367" s="169"/>
@@ -43611,7 +43571,7 @@
       <c r="Q367" s="168"/>
       <c r="R367" s="168"/>
     </row>
-    <row r="368" spans="1:18" ht="22.5">
+    <row r="368" spans="1:18" ht="22">
       <c r="A368" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A368" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E368),
@@ -43648,7 +43608,7 @@
       <c r="Q368" s="128"/>
       <c r="R368" s="128"/>
     </row>
-    <row r="369" spans="1:18" ht="22.5">
+    <row r="369" spans="1:18" ht="22">
       <c r="A369" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A369" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E369),
@@ -43678,13 +43638,13 @@
         <v>697</v>
       </c>
       <c r="J369" s="96" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K369" s="98" t="s">
         <v>698</v>
       </c>
       <c r="L369" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M369" s="98"/>
       <c r="N369" s="169"/>
@@ -43693,7 +43653,7 @@
       <c r="Q369" s="168"/>
       <c r="R369" s="168"/>
     </row>
-    <row r="370" spans="1:18" ht="22.5">
+    <row r="370" spans="1:18" ht="22">
       <c r="A370" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A370" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E370),
@@ -43742,7 +43702,7 @@
       <c r="Q370" s="168"/>
       <c r="R370" s="168"/>
     </row>
-    <row r="371" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="371" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A371" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A371" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E371),
@@ -43785,7 +43745,7 @@
       <c r="Q371" s="102"/>
       <c r="R371" s="102"/>
     </row>
-    <row r="372" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="372" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A372" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A372" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E372),
@@ -43828,7 +43788,7 @@
       <c r="Q372" s="102"/>
       <c r="R372" s="102"/>
     </row>
-    <row r="373" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="373" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A373" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A373" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E373),
@@ -43871,7 +43831,7 @@
       <c r="Q373" s="102"/>
       <c r="R373" s="102"/>
     </row>
-    <row r="374" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="374" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A374" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A374" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E374),
@@ -43914,7 +43874,7 @@
       <c r="Q374" s="102"/>
       <c r="R374" s="102"/>
     </row>
-    <row r="375" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="375" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A375" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A375" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E375),
@@ -43957,7 +43917,7 @@
       <c r="Q375" s="102"/>
       <c r="R375" s="102"/>
     </row>
-    <row r="376" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="376" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A376" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A376" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E376),
@@ -44000,7 +43960,7 @@
       <c r="Q376" s="102"/>
       <c r="R376" s="102"/>
     </row>
-    <row r="377" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="377" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A377" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A377" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E377),
@@ -44043,7 +44003,7 @@
       <c r="Q377" s="102"/>
       <c r="R377" s="102"/>
     </row>
-    <row r="378" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="378" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A378" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A378" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E378),
@@ -44086,7 +44046,7 @@
       <c r="Q378" s="102"/>
       <c r="R378" s="102"/>
     </row>
-    <row r="379" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="379" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A379" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A379" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E379),
@@ -44129,7 +44089,7 @@
       <c r="Q379" s="102"/>
       <c r="R379" s="102"/>
     </row>
-    <row r="380" spans="1:18" ht="22.5">
+    <row r="380" spans="1:18" ht="22">
       <c r="A380" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A380" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E380),
@@ -44166,7 +44126,7 @@
       <c r="Q380" s="128"/>
       <c r="R380" s="128"/>
     </row>
-    <row r="381" spans="1:18" ht="33.75">
+    <row r="381" spans="1:18" ht="33">
       <c r="A381" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A381" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E381),
@@ -44211,7 +44171,7 @@
       <c r="Q381" s="168"/>
       <c r="R381" s="168"/>
     </row>
-    <row r="382" spans="1:18" ht="33.75">
+    <row r="382" spans="1:18" ht="33">
       <c r="A382" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A382" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E382),
@@ -44239,10 +44199,10 @@
         <v>710</v>
       </c>
       <c r="J382" s="167" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K382" s="167" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="L382" s="102" t="s">
         <v>644</v>
@@ -44256,7 +44216,7 @@
       <c r="Q382" s="168"/>
       <c r="R382" s="168"/>
     </row>
-    <row r="383" spans="1:18" ht="33.75">
+    <row r="383" spans="1:18" ht="33">
       <c r="A383" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A383" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E383),
@@ -44284,10 +44244,10 @@
         <v>710</v>
       </c>
       <c r="J383" s="167" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K383" s="167" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L383" s="102" t="s">
         <v>644</v>
@@ -44340,7 +44300,7 @@
       <c r="Q384" s="128"/>
       <c r="R384" s="128"/>
     </row>
-    <row r="385" spans="1:18" ht="22.5">
+    <row r="385" spans="1:18" ht="22">
       <c r="A385" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A385" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E385),
@@ -44375,7 +44335,7 @@
       <c r="Q385" s="128"/>
       <c r="R385" s="128"/>
     </row>
-    <row r="386" spans="1:18" ht="22.5">
+    <row r="386" spans="1:18" ht="22">
       <c r="A386" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A386" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E386),
@@ -44459,7 +44419,7 @@
       <c r="Q387" s="97"/>
       <c r="R387" s="97"/>
     </row>
-    <row r="388" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="388" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A388" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A388" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E388),
@@ -44502,7 +44462,7 @@
       <c r="Q388" s="102"/>
       <c r="R388" s="102"/>
     </row>
-    <row r="389" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="389" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A389" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A389" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E389),
@@ -44545,7 +44505,7 @@
       <c r="Q389" s="102"/>
       <c r="R389" s="102"/>
     </row>
-    <row r="390" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="390" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A390" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A390" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E390),
@@ -44588,7 +44548,7 @@
       <c r="Q390" s="102"/>
       <c r="R390" s="102"/>
     </row>
-    <row r="391" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="391" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A391" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A391" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E391),
@@ -44631,7 +44591,7 @@
       <c r="Q391" s="102"/>
       <c r="R391" s="102"/>
     </row>
-    <row r="392" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="392" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A392" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A392" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E392),
@@ -44674,7 +44634,7 @@
       <c r="Q392" s="102"/>
       <c r="R392" s="102"/>
     </row>
-    <row r="393" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="393" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A393" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A393" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E393),
@@ -44717,7 +44677,7 @@
       <c r="Q393" s="102"/>
       <c r="R393" s="102"/>
     </row>
-    <row r="394" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="394" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A394" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A394" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E394),
@@ -44760,7 +44720,7 @@
       <c r="Q394" s="102"/>
       <c r="R394" s="102"/>
     </row>
-    <row r="395" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="395" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A395" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A395" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E395),
@@ -44803,7 +44763,7 @@
       <c r="Q395" s="102"/>
       <c r="R395" s="102"/>
     </row>
-    <row r="396" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="396" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A396" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A396" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E396),
@@ -44846,7 +44806,7 @@
       <c r="Q396" s="102"/>
       <c r="R396" s="102"/>
     </row>
-    <row r="397" spans="1:18" ht="22.5">
+    <row r="397" spans="1:18" ht="22">
       <c r="A397" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A397" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E397),
@@ -44874,7 +44834,7 @@
         <v>735</v>
       </c>
       <c r="J397" s="96" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K397" s="97" t="s">
         <v>640</v>
@@ -44891,7 +44851,7 @@
       <c r="Q397" s="97"/>
       <c r="R397" s="97"/>
     </row>
-    <row r="398" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="398" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A398" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A398" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E398),
@@ -44917,7 +44877,7 @@
         <v>735</v>
       </c>
       <c r="J398" s="96" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K398" s="97" t="s">
         <v>640</v>
@@ -44934,7 +44894,7 @@
       <c r="Q398" s="102"/>
       <c r="R398" s="102"/>
     </row>
-    <row r="399" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="399" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A399" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A399" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E399),
@@ -44960,7 +44920,7 @@
         <v>735</v>
       </c>
       <c r="J399" s="96" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K399" s="97" t="s">
         <v>640</v>
@@ -44977,7 +44937,7 @@
       <c r="Q399" s="102"/>
       <c r="R399" s="102"/>
     </row>
-    <row r="400" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="400" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A400" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A400" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E400),
@@ -45003,7 +44963,7 @@
         <v>735</v>
       </c>
       <c r="J400" s="96" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="K400" s="97" t="s">
         <v>640</v>
@@ -45020,7 +44980,7 @@
       <c r="Q400" s="102"/>
       <c r="R400" s="102"/>
     </row>
-    <row r="401" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="401" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A401" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A401" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E401),
@@ -45046,7 +45006,7 @@
         <v>735</v>
       </c>
       <c r="J401" s="96" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K401" s="97" t="s">
         <v>640</v>
@@ -45063,7 +45023,7 @@
       <c r="Q401" s="102"/>
       <c r="R401" s="102"/>
     </row>
-    <row r="402" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="402" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A402" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A402" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E402),
@@ -45089,7 +45049,7 @@
         <v>735</v>
       </c>
       <c r="J402" s="96" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K402" s="97" t="s">
         <v>640</v>
@@ -45106,7 +45066,7 @@
       <c r="Q402" s="102"/>
       <c r="R402" s="102"/>
     </row>
-    <row r="403" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="403" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A403" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A403" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E403),
@@ -45132,7 +45092,7 @@
         <v>735</v>
       </c>
       <c r="J403" s="96" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="K403" s="97" t="s">
         <v>640</v>
@@ -45149,7 +45109,7 @@
       <c r="Q403" s="102"/>
       <c r="R403" s="102"/>
     </row>
-    <row r="404" spans="1:18" ht="33.75">
+    <row r="404" spans="1:18" ht="33">
       <c r="A404" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A404" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E404),
@@ -45177,7 +45137,7 @@
         <v>735</v>
       </c>
       <c r="J404" s="96" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K404" s="56" t="s">
         <v>641</v>
@@ -45194,7 +45154,7 @@
       <c r="Q404" s="97"/>
       <c r="R404" s="97"/>
     </row>
-    <row r="405" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="405" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A405" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A405" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E405),
@@ -45220,7 +45180,7 @@
         <v>735</v>
       </c>
       <c r="J405" s="96" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K405" s="56" t="s">
         <v>641</v>
@@ -45237,7 +45197,7 @@
       <c r="Q405" s="102"/>
       <c r="R405" s="102"/>
     </row>
-    <row r="406" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="406" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A406" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A406" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E406),
@@ -45263,7 +45223,7 @@
         <v>735</v>
       </c>
       <c r="J406" s="96" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K406" s="56" t="s">
         <v>641</v>
@@ -45280,7 +45240,7 @@
       <c r="Q406" s="102"/>
       <c r="R406" s="102"/>
     </row>
-    <row r="407" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="407" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A407" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A407" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E407),
@@ -45306,7 +45266,7 @@
         <v>735</v>
       </c>
       <c r="J407" s="96" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K407" s="56" t="s">
         <v>641</v>
@@ -45323,7 +45283,7 @@
       <c r="Q407" s="102"/>
       <c r="R407" s="102"/>
     </row>
-    <row r="408" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="408" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A408" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A408" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E408),
@@ -45349,7 +45309,7 @@
         <v>735</v>
       </c>
       <c r="J408" s="96" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K408" s="56" t="s">
         <v>641</v>
@@ -45366,7 +45326,7 @@
       <c r="Q408" s="102"/>
       <c r="R408" s="102"/>
     </row>
-    <row r="409" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="409" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A409" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A409" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E409),
@@ -45392,7 +45352,7 @@
         <v>735</v>
       </c>
       <c r="J409" s="96" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="K409" s="56" t="s">
         <v>641</v>
@@ -45409,7 +45369,7 @@
       <c r="Q409" s="102"/>
       <c r="R409" s="102"/>
     </row>
-    <row r="410" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="410" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A410" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A410" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E410),
@@ -45435,7 +45395,7 @@
         <v>735</v>
       </c>
       <c r="J410" s="96" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="K410" s="56" t="s">
         <v>641</v>
@@ -45452,7 +45412,7 @@
       <c r="Q410" s="102"/>
       <c r="R410" s="102"/>
     </row>
-    <row r="411" spans="1:18" ht="22.5">
+    <row r="411" spans="1:18" ht="22">
       <c r="A411" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A411" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E411),
@@ -45487,7 +45447,7 @@
       <c r="Q411" s="128"/>
       <c r="R411" s="128"/>
     </row>
-    <row r="412" spans="1:18" ht="22.5">
+    <row r="412" spans="1:18" ht="22">
       <c r="A412" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A412" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E412),
@@ -45522,7 +45482,7 @@
       <c r="Q412" s="128"/>
       <c r="R412" s="128"/>
     </row>
-    <row r="413" spans="1:18" ht="33.75">
+    <row r="413" spans="1:18" ht="33">
       <c r="A413" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A413" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E413),
@@ -45557,7 +45517,7 @@
       <c r="Q413" s="128"/>
       <c r="R413" s="128"/>
     </row>
-    <row r="414" spans="1:18" ht="22.5">
+    <row r="414" spans="1:18" ht="22">
       <c r="A414" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A414" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E414),
@@ -45592,7 +45552,7 @@
       <c r="Q414" s="128"/>
       <c r="R414" s="128"/>
     </row>
-    <row r="415" spans="1:18" ht="22.5">
+    <row r="415" spans="1:18" ht="22">
       <c r="A415" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A415" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E415),
@@ -45627,7 +45587,7 @@
       <c r="Q415" s="128"/>
       <c r="R415" s="128"/>
     </row>
-    <row r="416" spans="1:18" ht="22.5">
+    <row r="416" spans="1:18" ht="22">
       <c r="A416" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A416" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E416),
@@ -45662,7 +45622,7 @@
       <c r="Q416" s="128"/>
       <c r="R416" s="128"/>
     </row>
-    <row r="417" spans="1:18" ht="22.5">
+    <row r="417" spans="1:18" ht="22">
       <c r="A417" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A417" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E417),
@@ -45697,7 +45657,7 @@
       <c r="Q417" s="128"/>
       <c r="R417" s="128"/>
     </row>
-    <row r="418" spans="1:18" ht="33.75">
+    <row r="418" spans="1:18" ht="33">
       <c r="A418" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A418" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E418),
@@ -45725,10 +45685,10 @@
         <v>29</v>
       </c>
       <c r="J418" s="56" t="s">
+        <v>823</v>
+      </c>
+      <c r="K418" s="56" t="s">
         <v>824</v>
-      </c>
-      <c r="K418" s="56" t="s">
-        <v>825</v>
       </c>
       <c r="L418" s="102" t="s">
         <v>644</v>
@@ -45742,7 +45702,7 @@
       <c r="Q418" s="97"/>
       <c r="R418" s="97"/>
     </row>
-    <row r="419" spans="1:18" ht="22.5">
+    <row r="419" spans="1:18" ht="22">
       <c r="A419" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A419" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E419),
@@ -45777,7 +45737,7 @@
       <c r="Q419" s="128"/>
       <c r="R419" s="128"/>
     </row>
-    <row r="420" spans="1:18" ht="22.5">
+    <row r="420" spans="1:18" ht="22">
       <c r="A420" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A420" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E420),
@@ -45812,7 +45772,7 @@
       <c r="Q420" s="128"/>
       <c r="R420" s="128"/>
     </row>
-    <row r="421" spans="1:18" ht="22.5">
+    <row r="421" spans="1:18" ht="22">
       <c r="A421" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A421" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E421),
@@ -45847,7 +45807,7 @@
       <c r="Q421" s="128"/>
       <c r="R421" s="128"/>
     </row>
-    <row r="422" spans="1:18" ht="22.5">
+    <row r="422" spans="1:18" ht="22">
       <c r="A422" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A422" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E422),
@@ -45894,7 +45854,7 @@
       <c r="Q422" s="97"/>
       <c r="R422" s="97"/>
     </row>
-    <row r="423" spans="1:18" ht="33.75">
+    <row r="423" spans="1:18" ht="33">
       <c r="A423" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A423" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E423),
@@ -45929,7 +45889,7 @@
       <c r="Q423" s="128"/>
       <c r="R423" s="128"/>
     </row>
-    <row r="424" spans="1:18" ht="33.75">
+    <row r="424" spans="1:18" ht="33">
       <c r="A424" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A424" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E424),
@@ -45964,7 +45924,7 @@
       <c r="Q424" s="128"/>
       <c r="R424" s="128"/>
     </row>
-    <row r="425" spans="1:18" ht="33.75">
+    <row r="425" spans="1:18" ht="33">
       <c r="A425" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A425" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E425),
@@ -45999,7 +45959,7 @@
       <c r="Q425" s="128"/>
       <c r="R425" s="128"/>
     </row>
-    <row r="426" spans="1:18" ht="22.5">
+    <row r="426" spans="1:18" ht="22">
       <c r="A426" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A426" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E426),
@@ -46034,7 +45994,7 @@
       <c r="Q426" s="128"/>
       <c r="R426" s="128"/>
     </row>
-    <row r="427" spans="1:18" ht="22.5">
+    <row r="427" spans="1:18" ht="22">
       <c r="A427" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A427" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E427),
@@ -46069,7 +46029,7 @@
       <c r="Q427" s="128"/>
       <c r="R427" s="128"/>
     </row>
-    <row r="428" spans="1:18" ht="22.5">
+    <row r="428" spans="1:18" ht="22">
       <c r="A428" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A428" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E428),
@@ -46104,7 +46064,7 @@
       <c r="Q428" s="128"/>
       <c r="R428" s="128"/>
     </row>
-    <row r="429" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="429" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A429" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A429" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E429),
@@ -46147,7 +46107,7 @@
       <c r="Q429" s="227"/>
       <c r="R429" s="227"/>
     </row>
-    <row r="430" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="430" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A430" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A430" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E430),
@@ -46182,7 +46142,7 @@
       <c r="Q430" s="202"/>
       <c r="R430" s="202"/>
     </row>
-    <row r="431" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="431" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A431" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A431" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E431),
@@ -46217,7 +46177,7 @@
       <c r="Q431" s="202"/>
       <c r="R431" s="202"/>
     </row>
-    <row r="432" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="432" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A432" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A432" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E432),
@@ -46252,7 +46212,7 @@
       <c r="Q432" s="202"/>
       <c r="R432" s="202"/>
     </row>
-    <row r="433" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="433" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A433" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A433" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E433),
@@ -46361,7 +46321,7 @@
       <c r="Q435" s="202"/>
       <c r="R435" s="202"/>
     </row>
-    <row r="436" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="436" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A436" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A436" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E436),
@@ -46396,7 +46356,7 @@
       <c r="Q436" s="202"/>
       <c r="R436" s="202"/>
     </row>
-    <row r="437" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="437" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A437" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A437" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E437),
@@ -46466,7 +46426,7 @@
       <c r="Q438" s="202"/>
       <c r="R438" s="202"/>
     </row>
-    <row r="439" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="439" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A439" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A439" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E439),
@@ -46500,7 +46460,7 @@
         <v>724</v>
       </c>
       <c r="J439" s="96" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K439" s="203" t="s">
         <v>725</v>
@@ -46517,7 +46477,7 @@
       <c r="Q439" s="205"/>
       <c r="R439" s="205"/>
     </row>
-    <row r="440" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="440" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A440" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A440" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E440),
@@ -46552,7 +46512,7 @@
       <c r="Q440" s="209"/>
       <c r="R440" s="209"/>
     </row>
-    <row r="441" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="441" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A441" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A441" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E441),
@@ -46580,10 +46540,10 @@
         <v>728</v>
       </c>
       <c r="J441" s="96" t="s">
+        <v>833</v>
+      </c>
+      <c r="K441" s="98" t="s">
         <v>834</v>
-      </c>
-      <c r="K441" s="98" t="s">
-        <v>835</v>
       </c>
       <c r="L441" s="102" t="s">
         <v>644</v>
@@ -46632,7 +46592,7 @@
       <c r="Q442" s="209"/>
       <c r="R442" s="209"/>
     </row>
-    <row r="443" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="443" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A443" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A443" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E443),
@@ -46667,7 +46627,7 @@
       <c r="Q443" s="209"/>
       <c r="R443" s="209"/>
     </row>
-    <row r="444" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="444" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A444" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A444" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E444),
@@ -46695,7 +46655,7 @@
         <v>726</v>
       </c>
       <c r="J444" s="166" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K444" s="203" t="s">
         <v>725</v>
@@ -46712,7 +46672,7 @@
       <c r="Q444" s="251"/>
       <c r="R444" s="251"/>
     </row>
-    <row r="445" spans="1:18" s="37" customFormat="1" ht="33.75">
+    <row r="445" spans="1:18" s="37" customFormat="1" ht="33">
       <c r="A445" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A445" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E445),
@@ -46744,13 +46704,13 @@
         <v>729</v>
       </c>
       <c r="J445" s="248" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K445" s="252" t="s">
         <v>730</v>
       </c>
       <c r="L445" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M445" s="204"/>
       <c r="N445" s="205"/>
@@ -46759,7 +46719,7 @@
       <c r="Q445" s="205"/>
       <c r="R445" s="205"/>
     </row>
-    <row r="446" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="446" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A446" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A446" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E446),
@@ -46791,10 +46751,10 @@
         <v>731</v>
       </c>
       <c r="J446" s="96" t="s">
+        <v>828</v>
+      </c>
+      <c r="K446" s="98" t="s">
         <v>829</v>
-      </c>
-      <c r="K446" s="98" t="s">
-        <v>830</v>
       </c>
       <c r="L446" s="102" t="s">
         <v>644</v>
@@ -46808,7 +46768,7 @@
       <c r="Q446" s="205"/>
       <c r="R446" s="205"/>
     </row>
-    <row r="447" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="447" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A447" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A447" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E447),
@@ -46834,10 +46794,10 @@
         <v>731</v>
       </c>
       <c r="J447" s="96" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K447" s="98" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="L447" s="167" t="s">
         <v>645</v>
@@ -46851,7 +46811,7 @@
       <c r="Q447" s="210"/>
       <c r="R447" s="210"/>
     </row>
-    <row r="448" spans="1:18" s="37" customFormat="1" ht="22.5">
+    <row r="448" spans="1:18" s="37" customFormat="1" ht="22">
       <c r="A448" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A448" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E448),
@@ -46883,13 +46843,13 @@
         <v>740</v>
       </c>
       <c r="J448" s="96" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K448" s="263" t="s">
         <v>739</v>
       </c>
       <c r="L448" s="212" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M448" s="261"/>
       <c r="N448" s="262"/>
@@ -46898,7 +46858,7 @@
       <c r="Q448" s="262"/>
       <c r="R448" s="262"/>
     </row>
-    <row r="449" spans="1:18" ht="22.5">
+    <row r="449" spans="1:18" ht="22">
       <c r="A449" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A449" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E449),
@@ -46941,7 +46901,7 @@
       <c r="Q449" s="128"/>
       <c r="R449" s="128"/>
     </row>
-    <row r="450" spans="1:18" ht="22.5">
+    <row r="450" spans="1:18" ht="22">
       <c r="A450" s="77" t="str" cm="1">
         <f t="array" aca="1" ref="A450" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E450),
@@ -47022,18 +46982,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q551"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="30" customWidth="1"/>
-    <col min="2" max="3" width="10.625" style="30" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="31" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.125" style="124" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="16.375" style="30" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" style="30" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="15.58203125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.08203125" style="124" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="16.33203125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="30" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="31" style="30" customWidth="1"/>
     <col min="11" max="11" width="17.25" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="8.625" style="30" customWidth="1"/>
+    <col min="12" max="15" width="8.58203125" style="30" customWidth="1"/>
     <col min="16" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
@@ -47076,7 +47036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="12" thickBot="1">
+    <row r="8" spans="1:17" ht="11.5" thickBot="1">
       <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -47096,7 +47056,7 @@
       <c r="Q8" s="32"/>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" thickTop="1"/>
-    <row r="10" spans="1:17" s="37" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="10" spans="1:17" s="37" customFormat="1" ht="10" customHeight="1">
       <c r="A10" s="34" t="s">
         <v>88</v>
       </c>
@@ -47149,7 +47109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="37" customFormat="1" ht="56.25">
+    <row r="11" spans="1:17" s="37" customFormat="1" ht="55">
       <c r="A11" s="40" t="s">
         <v>50</v>
       </c>
@@ -47171,10 +47131,10 @@
         <v>748</v>
       </c>
       <c r="I11" s="41" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K11" s="45"/>
       <c r="L11" s="46"/>
@@ -47184,9 +47144,9 @@
       <c r="P11" s="46"/>
       <c r="Q11" s="46"/>
     </row>
-    <row r="12" spans="1:17" s="37" customFormat="1" ht="90">
+    <row r="12" spans="1:17" s="37" customFormat="1" ht="88">
       <c r="A12" s="40" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="47"/>
@@ -47196,7 +47156,7 @@
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
       <c r="I12" s="49" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J12" s="49" t="s">
         <v>55</v>
@@ -47209,7 +47169,7 @@
       <c r="P12" s="46"/>
       <c r="Q12" s="46"/>
     </row>
-    <row r="13" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="13" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A13" s="52" t="s">
         <v>21</v>
       </c>
@@ -47227,7 +47187,7 @@
         <v>737</v>
       </c>
       <c r="I13" s="56" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="J13" s="56" t="s">
         <v>52</v>
@@ -47240,9 +47200,9 @@
       <c r="P13" s="58"/>
       <c r="Q13" s="58"/>
     </row>
-    <row r="14" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="14" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A14" s="52" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B14" s="53"/>
       <c r="C14" s="53"/>
@@ -47252,7 +47212,7 @@
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
       <c r="I14" s="56" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="J14" s="56" t="s">
         <v>53</v>
@@ -47290,7 +47250,7 @@
       <c r="P15" s="256"/>
       <c r="Q15" s="256"/>
     </row>
-    <row r="16" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="16" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A16" s="52" t="s">
         <v>31</v>
       </c>
@@ -47308,7 +47268,7 @@
         <v>737</v>
       </c>
       <c r="I16" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J16" s="56" t="s">
         <v>54</v>
@@ -47321,7 +47281,7 @@
       <c r="P16" s="58"/>
       <c r="Q16" s="58"/>
     </row>
-    <row r="17" spans="1:17" s="37" customFormat="1" ht="67.5">
+    <row r="17" spans="1:17" s="37" customFormat="1" ht="66">
       <c r="A17" s="52" t="s">
         <v>32</v>
       </c>
@@ -47341,10 +47301,10 @@
         <v>737</v>
       </c>
       <c r="I17" s="64" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K17" s="57"/>
       <c r="L17" s="58"/>
@@ -47379,9 +47339,9 @@
       <c r="P18" s="256"/>
       <c r="Q18" s="256"/>
     </row>
-    <row r="19" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="19" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A19" s="52" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
@@ -47397,7 +47357,7 @@
         <v>737</v>
       </c>
       <c r="I19" s="56" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="J19" s="56" t="s">
         <v>56</v>
@@ -47410,9 +47370,9 @@
       <c r="P19" s="58"/>
       <c r="Q19" s="58"/>
     </row>
-    <row r="20" spans="1:17" s="37" customFormat="1" ht="33.75">
+    <row r="20" spans="1:17" s="37" customFormat="1" ht="33">
       <c r="A20" s="52" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
@@ -47422,7 +47382,7 @@
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
       <c r="I20" s="56" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="J20" s="56" t="s">
         <v>57</v>
@@ -47437,7 +47397,7 @@
     </row>
     <row r="21" spans="1:17" s="37" customFormat="1">
       <c r="A21" s="52" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -47460,7 +47420,7 @@
       <c r="P21" s="256"/>
       <c r="Q21" s="256"/>
     </row>
-    <row r="22" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="22" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A22" s="52" t="s">
         <v>33</v>
       </c>
@@ -47487,7 +47447,7 @@
       <c r="P22" s="256"/>
       <c r="Q22" s="256"/>
     </row>
-    <row r="23" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="23" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A23" s="66" t="s">
         <v>34</v>
       </c>
@@ -47507,7 +47467,7 @@
         <v>737</v>
       </c>
       <c r="I23" s="56" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J23" s="56" t="s">
         <v>58</v>
@@ -47520,9 +47480,9 @@
       <c r="P23" s="68"/>
       <c r="Q23" s="68"/>
     </row>
-    <row r="24" spans="1:17" s="37" customFormat="1" ht="22.5">
+    <row r="24" spans="1:17" s="37" customFormat="1" ht="22">
       <c r="A24" s="66" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B24" s="65"/>
       <c r="C24" s="65"/>
@@ -47532,7 +47492,7 @@
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
       <c r="I24" s="56" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="J24" s="56" t="s">
         <v>59</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CEA9A0-2808-4C59-BD81-62BD32235626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725F3364-EEEF-45CD-BC74-30D6DC9DA24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【リクエストID】_クラス単体テスト" sheetId="25" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="26" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
+    <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
+    <sheet name="RWxxxxxxxx_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$450</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$312</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$450</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RWxxxxxxxx_リクエスト単体!$A$10:$R$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">RWxxxxxxxx_リクエスト単体!$A$1:$R$450</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$312</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">RWxxxxxxxx_リクエスト単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="853">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -11367,6 +11367,10 @@
   </si>
   <si>
     <t>7-1-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：RWxxxxxxxx</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -12916,108 +12920,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -13124,6 +13026,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -17302,57 +17306,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="322" t="s">
+      <c r="A1" s="288" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="323"/>
-      <c r="C1" s="323"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="325" t="s">
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="290"/>
+      <c r="E1" s="291" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
-      <c r="K1" s="326"/>
-      <c r="L1" s="326"/>
-      <c r="M1" s="326"/>
-      <c r="N1" s="327"/>
-      <c r="O1" s="331" t="s">
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="N1" s="293"/>
+      <c r="O1" s="297" t="s">
         <v>67</v>
       </c>
-      <c r="P1" s="332"/>
-      <c r="Q1" s="332"/>
-      <c r="R1" s="333"/>
-      <c r="S1" s="340" t="s">
+      <c r="P1" s="298"/>
+      <c r="Q1" s="298"/>
+      <c r="R1" s="299"/>
+      <c r="S1" s="306" t="s">
         <v>82</v>
       </c>
-      <c r="T1" s="341"/>
-      <c r="U1" s="341"/>
-      <c r="V1" s="341"/>
-      <c r="W1" s="341"/>
-      <c r="X1" s="341"/>
-      <c r="Y1" s="341"/>
-      <c r="Z1" s="342"/>
-      <c r="AA1" s="322" t="s">
+      <c r="T1" s="307"/>
+      <c r="U1" s="307"/>
+      <c r="V1" s="307"/>
+      <c r="W1" s="307"/>
+      <c r="X1" s="307"/>
+      <c r="Y1" s="307"/>
+      <c r="Z1" s="308"/>
+      <c r="AA1" s="288" t="s">
         <v>68</v>
       </c>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="349" t="str">
+      <c r="AB1" s="290"/>
+      <c r="AC1" s="315" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="350"/>
-      <c r="AE1" s="350"/>
-      <c r="AF1" s="351"/>
-      <c r="AG1" s="316">
+      <c r="AD1" s="316"/>
+      <c r="AE1" s="316"/>
+      <c r="AF1" s="317"/>
+      <c r="AG1" s="282">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="317"/>
-      <c r="AI1" s="318"/>
+      <c r="AH1" s="283"/>
+      <c r="AI1" s="284"/>
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
       <c r="AL1" s="13"/>
@@ -17360,53 +17364,53 @@
       <c r="AN1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="322" t="s">
+      <c r="A2" s="288" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="323"/>
-      <c r="C2" s="323"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="325" t="s">
+      <c r="B2" s="289"/>
+      <c r="C2" s="289"/>
+      <c r="D2" s="290"/>
+      <c r="E2" s="291" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="326"/>
-      <c r="G2" s="326"/>
-      <c r="H2" s="326"/>
-      <c r="I2" s="326"/>
-      <c r="J2" s="326"/>
-      <c r="K2" s="326"/>
-      <c r="L2" s="326"/>
-      <c r="M2" s="326"/>
-      <c r="N2" s="327"/>
-      <c r="O2" s="334"/>
-      <c r="P2" s="335"/>
-      <c r="Q2" s="335"/>
-      <c r="R2" s="336"/>
-      <c r="S2" s="343"/>
-      <c r="T2" s="344"/>
-      <c r="U2" s="344"/>
-      <c r="V2" s="344"/>
-      <c r="W2" s="344"/>
-      <c r="X2" s="344"/>
-      <c r="Y2" s="344"/>
-      <c r="Z2" s="345"/>
-      <c r="AA2" s="322" t="s">
+      <c r="F2" s="292"/>
+      <c r="G2" s="292"/>
+      <c r="H2" s="292"/>
+      <c r="I2" s="292"/>
+      <c r="J2" s="292"/>
+      <c r="K2" s="292"/>
+      <c r="L2" s="292"/>
+      <c r="M2" s="292"/>
+      <c r="N2" s="293"/>
+      <c r="O2" s="300"/>
+      <c r="P2" s="301"/>
+      <c r="Q2" s="301"/>
+      <c r="R2" s="302"/>
+      <c r="S2" s="309"/>
+      <c r="T2" s="310"/>
+      <c r="U2" s="310"/>
+      <c r="V2" s="310"/>
+      <c r="W2" s="310"/>
+      <c r="X2" s="310"/>
+      <c r="Y2" s="310"/>
+      <c r="Z2" s="311"/>
+      <c r="AA2" s="288" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" s="324"/>
-      <c r="AC2" s="328" t="str">
+      <c r="AB2" s="290"/>
+      <c r="AC2" s="294" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="329"/>
-      <c r="AE2" s="329"/>
-      <c r="AF2" s="330"/>
-      <c r="AG2" s="316">
+      <c r="AD2" s="295"/>
+      <c r="AE2" s="295"/>
+      <c r="AF2" s="296"/>
+      <c r="AG2" s="282">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="317"/>
-      <c r="AI2" s="318"/>
+      <c r="AH2" s="283"/>
+      <c r="AI2" s="284"/>
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
       <c r="AL2" s="13"/>
@@ -17414,45 +17418,45 @@
       <c r="AN2" s="13"/>
     </row>
     <row r="3" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="322" t="s">
+      <c r="A3" s="288" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="323"/>
-      <c r="C3" s="323"/>
-      <c r="D3" s="324"/>
-      <c r="E3" s="325" t="s">
+      <c r="B3" s="289"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="291" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="326"/>
-      <c r="G3" s="326"/>
-      <c r="H3" s="326"/>
-      <c r="I3" s="326"/>
-      <c r="J3" s="326"/>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="327"/>
-      <c r="O3" s="337"/>
-      <c r="P3" s="338"/>
-      <c r="Q3" s="338"/>
-      <c r="R3" s="339"/>
-      <c r="S3" s="346"/>
-      <c r="T3" s="347"/>
-      <c r="U3" s="347"/>
-      <c r="V3" s="347"/>
-      <c r="W3" s="347"/>
-      <c r="X3" s="347"/>
-      <c r="Y3" s="347"/>
-      <c r="Z3" s="348"/>
-      <c r="AA3" s="322"/>
-      <c r="AB3" s="324"/>
-      <c r="AC3" s="349"/>
-      <c r="AD3" s="350"/>
-      <c r="AE3" s="350"/>
-      <c r="AF3" s="351"/>
-      <c r="AG3" s="316"/>
-      <c r="AH3" s="317"/>
-      <c r="AI3" s="318"/>
+      <c r="F3" s="292"/>
+      <c r="G3" s="292"/>
+      <c r="H3" s="292"/>
+      <c r="I3" s="292"/>
+      <c r="J3" s="292"/>
+      <c r="K3" s="292"/>
+      <c r="L3" s="292"/>
+      <c r="M3" s="292"/>
+      <c r="N3" s="293"/>
+      <c r="O3" s="303"/>
+      <c r="P3" s="304"/>
+      <c r="Q3" s="304"/>
+      <c r="R3" s="305"/>
+      <c r="S3" s="312"/>
+      <c r="T3" s="313"/>
+      <c r="U3" s="313"/>
+      <c r="V3" s="313"/>
+      <c r="W3" s="313"/>
+      <c r="X3" s="313"/>
+      <c r="Y3" s="313"/>
+      <c r="Z3" s="314"/>
+      <c r="AA3" s="288"/>
+      <c r="AB3" s="290"/>
+      <c r="AC3" s="315"/>
+      <c r="AD3" s="316"/>
+      <c r="AE3" s="316"/>
+      <c r="AF3" s="317"/>
+      <c r="AG3" s="282"/>
+      <c r="AH3" s="283"/>
+      <c r="AI3" s="284"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
@@ -17489,97 +17493,97 @@
       <c r="A7" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="319" t="s">
+      <c r="B7" s="285" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="320"/>
-      <c r="D7" s="319" t="s">
+      <c r="C7" s="286"/>
+      <c r="D7" s="285" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="321"/>
-      <c r="F7" s="320"/>
-      <c r="G7" s="319" t="s">
+      <c r="E7" s="287"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="285" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="321"/>
-      <c r="I7" s="320"/>
-      <c r="J7" s="319" t="s">
+      <c r="H7" s="287"/>
+      <c r="I7" s="286"/>
+      <c r="J7" s="285" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="321"/>
-      <c r="L7" s="321"/>
-      <c r="M7" s="321"/>
-      <c r="N7" s="321"/>
-      <c r="O7" s="321"/>
-      <c r="P7" s="320"/>
-      <c r="Q7" s="319" t="s">
+      <c r="K7" s="287"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
+      <c r="N7" s="287"/>
+      <c r="O7" s="287"/>
+      <c r="P7" s="286"/>
+      <c r="Q7" s="285" t="s">
         <v>77</v>
       </c>
-      <c r="R7" s="321"/>
-      <c r="S7" s="321"/>
-      <c r="T7" s="321"/>
-      <c r="U7" s="321"/>
-      <c r="V7" s="321"/>
-      <c r="W7" s="321"/>
-      <c r="X7" s="321"/>
-      <c r="Y7" s="321"/>
-      <c r="Z7" s="321"/>
-      <c r="AA7" s="321"/>
-      <c r="AB7" s="321"/>
-      <c r="AC7" s="321"/>
-      <c r="AD7" s="321"/>
-      <c r="AE7" s="320"/>
-      <c r="AF7" s="319" t="s">
+      <c r="R7" s="287"/>
+      <c r="S7" s="287"/>
+      <c r="T7" s="287"/>
+      <c r="U7" s="287"/>
+      <c r="V7" s="287"/>
+      <c r="W7" s="287"/>
+      <c r="X7" s="287"/>
+      <c r="Y7" s="287"/>
+      <c r="Z7" s="287"/>
+      <c r="AA7" s="287"/>
+      <c r="AB7" s="287"/>
+      <c r="AC7" s="287"/>
+      <c r="AD7" s="287"/>
+      <c r="AE7" s="286"/>
+      <c r="AF7" s="285" t="s">
         <v>78</v>
       </c>
-      <c r="AG7" s="321"/>
-      <c r="AH7" s="321"/>
-      <c r="AI7" s="320"/>
+      <c r="AG7" s="287"/>
+      <c r="AH7" s="287"/>
+      <c r="AI7" s="286"/>
     </row>
     <row r="8" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="26">
         <v>1</v>
       </c>
-      <c r="B8" s="307" t="s">
+      <c r="B8" s="330" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="308"/>
-      <c r="D8" s="309">
+      <c r="C8" s="331"/>
+      <c r="D8" s="332">
         <v>43336</v>
       </c>
-      <c r="E8" s="310"/>
-      <c r="F8" s="311"/>
-      <c r="G8" s="307" t="s">
+      <c r="E8" s="333"/>
+      <c r="F8" s="334"/>
+      <c r="G8" s="330" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="312"/>
-      <c r="I8" s="308"/>
-      <c r="J8" s="313" t="s">
+      <c r="H8" s="335"/>
+      <c r="I8" s="331"/>
+      <c r="J8" s="336" t="s">
         <v>85</v>
       </c>
-      <c r="K8" s="314"/>
-      <c r="L8" s="314"/>
-      <c r="M8" s="314"/>
-      <c r="N8" s="314"/>
-      <c r="O8" s="314"/>
-      <c r="P8" s="315"/>
-      <c r="Q8" s="313" t="s">
+      <c r="K8" s="337"/>
+      <c r="L8" s="337"/>
+      <c r="M8" s="337"/>
+      <c r="N8" s="337"/>
+      <c r="O8" s="337"/>
+      <c r="P8" s="338"/>
+      <c r="Q8" s="336" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="314"/>
-      <c r="S8" s="314"/>
-      <c r="T8" s="314"/>
-      <c r="U8" s="314"/>
-      <c r="V8" s="314"/>
-      <c r="W8" s="314"/>
-      <c r="X8" s="314"/>
-      <c r="Y8" s="314"/>
-      <c r="Z8" s="314"/>
-      <c r="AA8" s="314"/>
-      <c r="AB8" s="314"/>
-      <c r="AC8" s="314"/>
-      <c r="AD8" s="314"/>
-      <c r="AE8" s="315"/>
+      <c r="R8" s="337"/>
+      <c r="S8" s="337"/>
+      <c r="T8" s="337"/>
+      <c r="U8" s="337"/>
+      <c r="V8" s="337"/>
+      <c r="W8" s="337"/>
+      <c r="X8" s="337"/>
+      <c r="Y8" s="337"/>
+      <c r="Z8" s="337"/>
+      <c r="AA8" s="337"/>
+      <c r="AB8" s="337"/>
+      <c r="AC8" s="337"/>
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="338"/>
       <c r="AF8" s="27" t="s">
         <v>87</v>
       </c>
@@ -17591,946 +17595,1101 @@
       <c r="A9" s="26">
         <v>2</v>
       </c>
-      <c r="B9" s="295" t="s">
+      <c r="B9" s="318" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="296"/>
-      <c r="D9" s="297">
+      <c r="C9" s="319"/>
+      <c r="D9" s="320">
         <v>44852</v>
       </c>
-      <c r="E9" s="298"/>
-      <c r="F9" s="299"/>
-      <c r="G9" s="297" t="s">
+      <c r="E9" s="321"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="320" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="300"/>
-      <c r="I9" s="296"/>
-      <c r="J9" s="301" t="s">
+      <c r="H9" s="323"/>
+      <c r="I9" s="319"/>
+      <c r="J9" s="324" t="s">
         <v>749</v>
       </c>
-      <c r="K9" s="302"/>
-      <c r="L9" s="302"/>
-      <c r="M9" s="302"/>
-      <c r="N9" s="302"/>
-      <c r="O9" s="302"/>
-      <c r="P9" s="303"/>
-      <c r="Q9" s="301" t="s">
+      <c r="K9" s="325"/>
+      <c r="L9" s="325"/>
+      <c r="M9" s="325"/>
+      <c r="N9" s="325"/>
+      <c r="O9" s="325"/>
+      <c r="P9" s="326"/>
+      <c r="Q9" s="324" t="s">
         <v>750</v>
       </c>
-      <c r="R9" s="304"/>
-      <c r="S9" s="304"/>
-      <c r="T9" s="304"/>
-      <c r="U9" s="304"/>
-      <c r="V9" s="304"/>
-      <c r="W9" s="304"/>
-      <c r="X9" s="304"/>
-      <c r="Y9" s="304"/>
-      <c r="Z9" s="304"/>
-      <c r="AA9" s="304"/>
-      <c r="AB9" s="304"/>
-      <c r="AC9" s="304"/>
-      <c r="AD9" s="304"/>
-      <c r="AE9" s="305"/>
-      <c r="AF9" s="306" t="s">
+      <c r="R9" s="327"/>
+      <c r="S9" s="327"/>
+      <c r="T9" s="327"/>
+      <c r="U9" s="327"/>
+      <c r="V9" s="327"/>
+      <c r="W9" s="327"/>
+      <c r="X9" s="327"/>
+      <c r="Y9" s="327"/>
+      <c r="Z9" s="327"/>
+      <c r="AA9" s="327"/>
+      <c r="AB9" s="327"/>
+      <c r="AC9" s="327"/>
+      <c r="AD9" s="327"/>
+      <c r="AE9" s="328"/>
+      <c r="AF9" s="329" t="s">
         <v>87</v>
       </c>
-      <c r="AG9" s="302"/>
-      <c r="AH9" s="302"/>
-      <c r="AI9" s="303"/>
+      <c r="AG9" s="325"/>
+      <c r="AH9" s="325"/>
+      <c r="AI9" s="326"/>
     </row>
     <row r="10" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="282"/>
-      <c r="C10" s="283"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="285"/>
-      <c r="F10" s="286"/>
-      <c r="G10" s="282"/>
-      <c r="H10" s="287"/>
-      <c r="I10" s="283"/>
-      <c r="J10" s="288"/>
-      <c r="K10" s="289"/>
-      <c r="L10" s="289"/>
-      <c r="M10" s="289"/>
-      <c r="N10" s="289"/>
-      <c r="O10" s="289"/>
-      <c r="P10" s="290"/>
-      <c r="Q10" s="291"/>
-      <c r="R10" s="292"/>
-      <c r="S10" s="292"/>
-      <c r="T10" s="292"/>
-      <c r="U10" s="292"/>
-      <c r="V10" s="292"/>
-      <c r="W10" s="292"/>
-      <c r="X10" s="292"/>
-      <c r="Y10" s="292"/>
-      <c r="Z10" s="292"/>
-      <c r="AA10" s="292"/>
-      <c r="AB10" s="292"/>
-      <c r="AC10" s="292"/>
-      <c r="AD10" s="292"/>
-      <c r="AE10" s="293"/>
-      <c r="AF10" s="288"/>
-      <c r="AG10" s="289"/>
-      <c r="AH10" s="289"/>
-      <c r="AI10" s="290"/>
+      <c r="B10" s="339"/>
+      <c r="C10" s="340"/>
+      <c r="D10" s="341"/>
+      <c r="E10" s="342"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="339"/>
+      <c r="H10" s="344"/>
+      <c r="I10" s="340"/>
+      <c r="J10" s="345"/>
+      <c r="K10" s="346"/>
+      <c r="L10" s="346"/>
+      <c r="M10" s="346"/>
+      <c r="N10" s="346"/>
+      <c r="O10" s="346"/>
+      <c r="P10" s="347"/>
+      <c r="Q10" s="348"/>
+      <c r="R10" s="349"/>
+      <c r="S10" s="349"/>
+      <c r="T10" s="349"/>
+      <c r="U10" s="349"/>
+      <c r="V10" s="349"/>
+      <c r="W10" s="349"/>
+      <c r="X10" s="349"/>
+      <c r="Y10" s="349"/>
+      <c r="Z10" s="349"/>
+      <c r="AA10" s="349"/>
+      <c r="AB10" s="349"/>
+      <c r="AC10" s="349"/>
+      <c r="AD10" s="349"/>
+      <c r="AE10" s="350"/>
+      <c r="AF10" s="345"/>
+      <c r="AG10" s="346"/>
+      <c r="AH10" s="346"/>
+      <c r="AI10" s="347"/>
     </row>
     <row r="11" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="23"/>
-      <c r="B11" s="282"/>
-      <c r="C11" s="283"/>
-      <c r="D11" s="284"/>
-      <c r="E11" s="285"/>
-      <c r="F11" s="286"/>
-      <c r="G11" s="282"/>
-      <c r="H11" s="287"/>
-      <c r="I11" s="283"/>
-      <c r="J11" s="288"/>
-      <c r="K11" s="289"/>
-      <c r="L11" s="289"/>
-      <c r="M11" s="289"/>
-      <c r="N11" s="289"/>
-      <c r="O11" s="289"/>
-      <c r="P11" s="290"/>
-      <c r="Q11" s="291"/>
-      <c r="R11" s="292"/>
-      <c r="S11" s="292"/>
-      <c r="T11" s="292"/>
-      <c r="U11" s="292"/>
-      <c r="V11" s="292"/>
-      <c r="W11" s="292"/>
-      <c r="X11" s="292"/>
-      <c r="Y11" s="292"/>
-      <c r="Z11" s="292"/>
-      <c r="AA11" s="292"/>
-      <c r="AB11" s="292"/>
-      <c r="AC11" s="292"/>
-      <c r="AD11" s="292"/>
-      <c r="AE11" s="293"/>
-      <c r="AF11" s="288"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="289"/>
-      <c r="AI11" s="290"/>
+      <c r="B11" s="339"/>
+      <c r="C11" s="340"/>
+      <c r="D11" s="341"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="343"/>
+      <c r="G11" s="339"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="340"/>
+      <c r="J11" s="345"/>
+      <c r="K11" s="346"/>
+      <c r="L11" s="346"/>
+      <c r="M11" s="346"/>
+      <c r="N11" s="346"/>
+      <c r="O11" s="346"/>
+      <c r="P11" s="347"/>
+      <c r="Q11" s="348"/>
+      <c r="R11" s="349"/>
+      <c r="S11" s="349"/>
+      <c r="T11" s="349"/>
+      <c r="U11" s="349"/>
+      <c r="V11" s="349"/>
+      <c r="W11" s="349"/>
+      <c r="X11" s="349"/>
+      <c r="Y11" s="349"/>
+      <c r="Z11" s="349"/>
+      <c r="AA11" s="349"/>
+      <c r="AB11" s="349"/>
+      <c r="AC11" s="349"/>
+      <c r="AD11" s="349"/>
+      <c r="AE11" s="350"/>
+      <c r="AF11" s="345"/>
+      <c r="AG11" s="346"/>
+      <c r="AH11" s="346"/>
+      <c r="AI11" s="347"/>
     </row>
     <row r="12" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="23"/>
-      <c r="B12" s="282"/>
-      <c r="C12" s="283"/>
-      <c r="D12" s="284"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="286"/>
-      <c r="G12" s="282"/>
-      <c r="H12" s="287"/>
-      <c r="I12" s="283"/>
-      <c r="J12" s="288"/>
-      <c r="K12" s="289"/>
-      <c r="L12" s="289"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
-      <c r="O12" s="289"/>
-      <c r="P12" s="290"/>
-      <c r="Q12" s="291"/>
-      <c r="R12" s="292"/>
-      <c r="S12" s="292"/>
-      <c r="T12" s="292"/>
-      <c r="U12" s="292"/>
-      <c r="V12" s="292"/>
-      <c r="W12" s="292"/>
-      <c r="X12" s="292"/>
-      <c r="Y12" s="292"/>
-      <c r="Z12" s="292"/>
-      <c r="AA12" s="292"/>
-      <c r="AB12" s="292"/>
-      <c r="AC12" s="292"/>
-      <c r="AD12" s="292"/>
-      <c r="AE12" s="293"/>
-      <c r="AF12" s="288"/>
-      <c r="AG12" s="289"/>
-      <c r="AH12" s="289"/>
-      <c r="AI12" s="290"/>
+      <c r="B12" s="339"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="343"/>
+      <c r="G12" s="339"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="340"/>
+      <c r="J12" s="345"/>
+      <c r="K12" s="346"/>
+      <c r="L12" s="346"/>
+      <c r="M12" s="346"/>
+      <c r="N12" s="346"/>
+      <c r="O12" s="346"/>
+      <c r="P12" s="347"/>
+      <c r="Q12" s="348"/>
+      <c r="R12" s="349"/>
+      <c r="S12" s="349"/>
+      <c r="T12" s="349"/>
+      <c r="U12" s="349"/>
+      <c r="V12" s="349"/>
+      <c r="W12" s="349"/>
+      <c r="X12" s="349"/>
+      <c r="Y12" s="349"/>
+      <c r="Z12" s="349"/>
+      <c r="AA12" s="349"/>
+      <c r="AB12" s="349"/>
+      <c r="AC12" s="349"/>
+      <c r="AD12" s="349"/>
+      <c r="AE12" s="350"/>
+      <c r="AF12" s="345"/>
+      <c r="AG12" s="346"/>
+      <c r="AH12" s="346"/>
+      <c r="AI12" s="347"/>
     </row>
     <row r="13" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="23"/>
-      <c r="B13" s="282"/>
-      <c r="C13" s="283"/>
-      <c r="D13" s="284"/>
-      <c r="E13" s="285"/>
-      <c r="F13" s="286"/>
-      <c r="G13" s="282"/>
-      <c r="H13" s="287"/>
-      <c r="I13" s="283"/>
-      <c r="J13" s="288"/>
-      <c r="K13" s="289"/>
-      <c r="L13" s="289"/>
-      <c r="M13" s="289"/>
-      <c r="N13" s="289"/>
-      <c r="O13" s="289"/>
-      <c r="P13" s="290"/>
-      <c r="Q13" s="291"/>
-      <c r="R13" s="292"/>
-      <c r="S13" s="292"/>
-      <c r="T13" s="292"/>
-      <c r="U13" s="292"/>
-      <c r="V13" s="292"/>
-      <c r="W13" s="292"/>
-      <c r="X13" s="292"/>
-      <c r="Y13" s="292"/>
-      <c r="Z13" s="292"/>
-      <c r="AA13" s="292"/>
-      <c r="AB13" s="292"/>
-      <c r="AC13" s="292"/>
-      <c r="AD13" s="292"/>
-      <c r="AE13" s="293"/>
-      <c r="AF13" s="288"/>
-      <c r="AG13" s="289"/>
-      <c r="AH13" s="289"/>
-      <c r="AI13" s="290"/>
+      <c r="B13" s="339"/>
+      <c r="C13" s="340"/>
+      <c r="D13" s="341"/>
+      <c r="E13" s="342"/>
+      <c r="F13" s="343"/>
+      <c r="G13" s="339"/>
+      <c r="H13" s="344"/>
+      <c r="I13" s="340"/>
+      <c r="J13" s="345"/>
+      <c r="K13" s="346"/>
+      <c r="L13" s="346"/>
+      <c r="M13" s="346"/>
+      <c r="N13" s="346"/>
+      <c r="O13" s="346"/>
+      <c r="P13" s="347"/>
+      <c r="Q13" s="348"/>
+      <c r="R13" s="349"/>
+      <c r="S13" s="349"/>
+      <c r="T13" s="349"/>
+      <c r="U13" s="349"/>
+      <c r="V13" s="349"/>
+      <c r="W13" s="349"/>
+      <c r="X13" s="349"/>
+      <c r="Y13" s="349"/>
+      <c r="Z13" s="349"/>
+      <c r="AA13" s="349"/>
+      <c r="AB13" s="349"/>
+      <c r="AC13" s="349"/>
+      <c r="AD13" s="349"/>
+      <c r="AE13" s="350"/>
+      <c r="AF13" s="345"/>
+      <c r="AG13" s="346"/>
+      <c r="AH13" s="346"/>
+      <c r="AI13" s="347"/>
     </row>
     <row r="14" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="23"/>
-      <c r="B14" s="282"/>
-      <c r="C14" s="283"/>
-      <c r="D14" s="284"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="286"/>
-      <c r="G14" s="282"/>
-      <c r="H14" s="287"/>
-      <c r="I14" s="283"/>
-      <c r="J14" s="288"/>
-      <c r="K14" s="289"/>
-      <c r="L14" s="289"/>
-      <c r="M14" s="289"/>
-      <c r="N14" s="289"/>
-      <c r="O14" s="289"/>
-      <c r="P14" s="290"/>
-      <c r="Q14" s="291"/>
-      <c r="R14" s="292"/>
-      <c r="S14" s="292"/>
-      <c r="T14" s="292"/>
-      <c r="U14" s="292"/>
-      <c r="V14" s="292"/>
-      <c r="W14" s="292"/>
-      <c r="X14" s="292"/>
-      <c r="Y14" s="292"/>
-      <c r="Z14" s="292"/>
-      <c r="AA14" s="292"/>
-      <c r="AB14" s="292"/>
-      <c r="AC14" s="292"/>
-      <c r="AD14" s="292"/>
-      <c r="AE14" s="293"/>
-      <c r="AF14" s="288"/>
-      <c r="AG14" s="289"/>
-      <c r="AH14" s="289"/>
-      <c r="AI14" s="290"/>
+      <c r="B14" s="339"/>
+      <c r="C14" s="340"/>
+      <c r="D14" s="341"/>
+      <c r="E14" s="342"/>
+      <c r="F14" s="343"/>
+      <c r="G14" s="339"/>
+      <c r="H14" s="344"/>
+      <c r="I14" s="340"/>
+      <c r="J14" s="345"/>
+      <c r="K14" s="346"/>
+      <c r="L14" s="346"/>
+      <c r="M14" s="346"/>
+      <c r="N14" s="346"/>
+      <c r="O14" s="346"/>
+      <c r="P14" s="347"/>
+      <c r="Q14" s="348"/>
+      <c r="R14" s="349"/>
+      <c r="S14" s="349"/>
+      <c r="T14" s="349"/>
+      <c r="U14" s="349"/>
+      <c r="V14" s="349"/>
+      <c r="W14" s="349"/>
+      <c r="X14" s="349"/>
+      <c r="Y14" s="349"/>
+      <c r="Z14" s="349"/>
+      <c r="AA14" s="349"/>
+      <c r="AB14" s="349"/>
+      <c r="AC14" s="349"/>
+      <c r="AD14" s="349"/>
+      <c r="AE14" s="350"/>
+      <c r="AF14" s="345"/>
+      <c r="AG14" s="346"/>
+      <c r="AH14" s="346"/>
+      <c r="AI14" s="347"/>
     </row>
     <row r="15" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="23"/>
-      <c r="B15" s="282"/>
-      <c r="C15" s="283"/>
-      <c r="D15" s="284"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="286"/>
-      <c r="G15" s="282"/>
-      <c r="H15" s="287"/>
-      <c r="I15" s="283"/>
-      <c r="J15" s="288"/>
-      <c r="K15" s="289"/>
-      <c r="L15" s="289"/>
-      <c r="M15" s="289"/>
-      <c r="N15" s="289"/>
-      <c r="O15" s="289"/>
-      <c r="P15" s="290"/>
-      <c r="Q15" s="291"/>
-      <c r="R15" s="292"/>
-      <c r="S15" s="292"/>
-      <c r="T15" s="292"/>
-      <c r="U15" s="292"/>
-      <c r="V15" s="292"/>
-      <c r="W15" s="292"/>
-      <c r="X15" s="292"/>
-      <c r="Y15" s="292"/>
-      <c r="Z15" s="292"/>
-      <c r="AA15" s="292"/>
-      <c r="AB15" s="292"/>
-      <c r="AC15" s="292"/>
-      <c r="AD15" s="292"/>
-      <c r="AE15" s="293"/>
-      <c r="AF15" s="288"/>
-      <c r="AG15" s="289"/>
-      <c r="AH15" s="289"/>
-      <c r="AI15" s="290"/>
+      <c r="B15" s="339"/>
+      <c r="C15" s="340"/>
+      <c r="D15" s="341"/>
+      <c r="E15" s="342"/>
+      <c r="F15" s="343"/>
+      <c r="G15" s="339"/>
+      <c r="H15" s="344"/>
+      <c r="I15" s="340"/>
+      <c r="J15" s="345"/>
+      <c r="K15" s="346"/>
+      <c r="L15" s="346"/>
+      <c r="M15" s="346"/>
+      <c r="N15" s="346"/>
+      <c r="O15" s="346"/>
+      <c r="P15" s="347"/>
+      <c r="Q15" s="348"/>
+      <c r="R15" s="349"/>
+      <c r="S15" s="349"/>
+      <c r="T15" s="349"/>
+      <c r="U15" s="349"/>
+      <c r="V15" s="349"/>
+      <c r="W15" s="349"/>
+      <c r="X15" s="349"/>
+      <c r="Y15" s="349"/>
+      <c r="Z15" s="349"/>
+      <c r="AA15" s="349"/>
+      <c r="AB15" s="349"/>
+      <c r="AC15" s="349"/>
+      <c r="AD15" s="349"/>
+      <c r="AE15" s="350"/>
+      <c r="AF15" s="345"/>
+      <c r="AG15" s="346"/>
+      <c r="AH15" s="346"/>
+      <c r="AI15" s="347"/>
     </row>
     <row r="16" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="23"/>
-      <c r="B16" s="282"/>
-      <c r="C16" s="283"/>
-      <c r="D16" s="284"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="286"/>
-      <c r="G16" s="282"/>
-      <c r="H16" s="287"/>
-      <c r="I16" s="283"/>
-      <c r="J16" s="288"/>
-      <c r="K16" s="289"/>
-      <c r="L16" s="289"/>
-      <c r="M16" s="289"/>
-      <c r="N16" s="289"/>
-      <c r="O16" s="289"/>
-      <c r="P16" s="290"/>
-      <c r="Q16" s="291"/>
-      <c r="R16" s="292"/>
-      <c r="S16" s="292"/>
-      <c r="T16" s="292"/>
-      <c r="U16" s="292"/>
-      <c r="V16" s="292"/>
-      <c r="W16" s="292"/>
-      <c r="X16" s="292"/>
-      <c r="Y16" s="292"/>
-      <c r="Z16" s="292"/>
-      <c r="AA16" s="292"/>
-      <c r="AB16" s="292"/>
-      <c r="AC16" s="292"/>
-      <c r="AD16" s="292"/>
-      <c r="AE16" s="293"/>
-      <c r="AF16" s="288"/>
-      <c r="AG16" s="289"/>
-      <c r="AH16" s="289"/>
-      <c r="AI16" s="290"/>
+      <c r="B16" s="339"/>
+      <c r="C16" s="340"/>
+      <c r="D16" s="341"/>
+      <c r="E16" s="342"/>
+      <c r="F16" s="343"/>
+      <c r="G16" s="339"/>
+      <c r="H16" s="344"/>
+      <c r="I16" s="340"/>
+      <c r="J16" s="345"/>
+      <c r="K16" s="346"/>
+      <c r="L16" s="346"/>
+      <c r="M16" s="346"/>
+      <c r="N16" s="346"/>
+      <c r="O16" s="346"/>
+      <c r="P16" s="347"/>
+      <c r="Q16" s="348"/>
+      <c r="R16" s="349"/>
+      <c r="S16" s="349"/>
+      <c r="T16" s="349"/>
+      <c r="U16" s="349"/>
+      <c r="V16" s="349"/>
+      <c r="W16" s="349"/>
+      <c r="X16" s="349"/>
+      <c r="Y16" s="349"/>
+      <c r="Z16" s="349"/>
+      <c r="AA16" s="349"/>
+      <c r="AB16" s="349"/>
+      <c r="AC16" s="349"/>
+      <c r="AD16" s="349"/>
+      <c r="AE16" s="350"/>
+      <c r="AF16" s="345"/>
+      <c r="AG16" s="346"/>
+      <c r="AH16" s="346"/>
+      <c r="AI16" s="347"/>
     </row>
     <row r="17" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="23"/>
-      <c r="B17" s="282"/>
-      <c r="C17" s="283"/>
-      <c r="D17" s="284"/>
-      <c r="E17" s="285"/>
-      <c r="F17" s="286"/>
-      <c r="G17" s="282"/>
-      <c r="H17" s="287"/>
-      <c r="I17" s="283"/>
-      <c r="J17" s="288"/>
-      <c r="K17" s="289"/>
-      <c r="L17" s="289"/>
-      <c r="M17" s="289"/>
-      <c r="N17" s="289"/>
-      <c r="O17" s="289"/>
-      <c r="P17" s="290"/>
-      <c r="Q17" s="291"/>
-      <c r="R17" s="292"/>
-      <c r="S17" s="292"/>
-      <c r="T17" s="292"/>
-      <c r="U17" s="292"/>
-      <c r="V17" s="292"/>
-      <c r="W17" s="292"/>
-      <c r="X17" s="292"/>
-      <c r="Y17" s="292"/>
-      <c r="Z17" s="292"/>
-      <c r="AA17" s="292"/>
-      <c r="AB17" s="292"/>
-      <c r="AC17" s="292"/>
-      <c r="AD17" s="292"/>
-      <c r="AE17" s="293"/>
-      <c r="AF17" s="288"/>
-      <c r="AG17" s="289"/>
-      <c r="AH17" s="289"/>
-      <c r="AI17" s="290"/>
+      <c r="B17" s="339"/>
+      <c r="C17" s="340"/>
+      <c r="D17" s="341"/>
+      <c r="E17" s="342"/>
+      <c r="F17" s="343"/>
+      <c r="G17" s="339"/>
+      <c r="H17" s="344"/>
+      <c r="I17" s="340"/>
+      <c r="J17" s="345"/>
+      <c r="K17" s="346"/>
+      <c r="L17" s="346"/>
+      <c r="M17" s="346"/>
+      <c r="N17" s="346"/>
+      <c r="O17" s="346"/>
+      <c r="P17" s="347"/>
+      <c r="Q17" s="348"/>
+      <c r="R17" s="349"/>
+      <c r="S17" s="349"/>
+      <c r="T17" s="349"/>
+      <c r="U17" s="349"/>
+      <c r="V17" s="349"/>
+      <c r="W17" s="349"/>
+      <c r="X17" s="349"/>
+      <c r="Y17" s="349"/>
+      <c r="Z17" s="349"/>
+      <c r="AA17" s="349"/>
+      <c r="AB17" s="349"/>
+      <c r="AC17" s="349"/>
+      <c r="AD17" s="349"/>
+      <c r="AE17" s="350"/>
+      <c r="AF17" s="345"/>
+      <c r="AG17" s="346"/>
+      <c r="AH17" s="346"/>
+      <c r="AI17" s="347"/>
     </row>
     <row r="18" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="23"/>
-      <c r="B18" s="282"/>
-      <c r="C18" s="283"/>
-      <c r="D18" s="284"/>
-      <c r="E18" s="285"/>
-      <c r="F18" s="286"/>
-      <c r="G18" s="282"/>
-      <c r="H18" s="287"/>
-      <c r="I18" s="283"/>
-      <c r="J18" s="288"/>
-      <c r="K18" s="289"/>
-      <c r="L18" s="289"/>
-      <c r="M18" s="289"/>
-      <c r="N18" s="289"/>
-      <c r="O18" s="289"/>
-      <c r="P18" s="290"/>
-      <c r="Q18" s="291"/>
-      <c r="R18" s="292"/>
-      <c r="S18" s="292"/>
-      <c r="T18" s="292"/>
-      <c r="U18" s="292"/>
-      <c r="V18" s="292"/>
-      <c r="W18" s="292"/>
-      <c r="X18" s="292"/>
-      <c r="Y18" s="292"/>
-      <c r="Z18" s="292"/>
-      <c r="AA18" s="292"/>
-      <c r="AB18" s="292"/>
-      <c r="AC18" s="292"/>
-      <c r="AD18" s="292"/>
-      <c r="AE18" s="293"/>
-      <c r="AF18" s="288"/>
-      <c r="AG18" s="289"/>
-      <c r="AH18" s="289"/>
-      <c r="AI18" s="290"/>
+      <c r="B18" s="339"/>
+      <c r="C18" s="340"/>
+      <c r="D18" s="341"/>
+      <c r="E18" s="342"/>
+      <c r="F18" s="343"/>
+      <c r="G18" s="339"/>
+      <c r="H18" s="344"/>
+      <c r="I18" s="340"/>
+      <c r="J18" s="345"/>
+      <c r="K18" s="346"/>
+      <c r="L18" s="346"/>
+      <c r="M18" s="346"/>
+      <c r="N18" s="346"/>
+      <c r="O18" s="346"/>
+      <c r="P18" s="347"/>
+      <c r="Q18" s="348"/>
+      <c r="R18" s="349"/>
+      <c r="S18" s="349"/>
+      <c r="T18" s="349"/>
+      <c r="U18" s="349"/>
+      <c r="V18" s="349"/>
+      <c r="W18" s="349"/>
+      <c r="X18" s="349"/>
+      <c r="Y18" s="349"/>
+      <c r="Z18" s="349"/>
+      <c r="AA18" s="349"/>
+      <c r="AB18" s="349"/>
+      <c r="AC18" s="349"/>
+      <c r="AD18" s="349"/>
+      <c r="AE18" s="350"/>
+      <c r="AF18" s="345"/>
+      <c r="AG18" s="346"/>
+      <c r="AH18" s="346"/>
+      <c r="AI18" s="347"/>
     </row>
     <row r="19" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="23"/>
-      <c r="B19" s="282"/>
-      <c r="C19" s="283"/>
-      <c r="D19" s="284"/>
-      <c r="E19" s="285"/>
-      <c r="F19" s="286"/>
-      <c r="G19" s="282"/>
-      <c r="H19" s="287"/>
-      <c r="I19" s="283"/>
-      <c r="J19" s="288"/>
-      <c r="K19" s="289"/>
-      <c r="L19" s="289"/>
-      <c r="M19" s="289"/>
-      <c r="N19" s="289"/>
-      <c r="O19" s="289"/>
-      <c r="P19" s="290"/>
-      <c r="Q19" s="291"/>
-      <c r="R19" s="292"/>
-      <c r="S19" s="292"/>
-      <c r="T19" s="292"/>
-      <c r="U19" s="292"/>
-      <c r="V19" s="292"/>
-      <c r="W19" s="292"/>
-      <c r="X19" s="292"/>
-      <c r="Y19" s="292"/>
-      <c r="Z19" s="292"/>
-      <c r="AA19" s="292"/>
-      <c r="AB19" s="292"/>
-      <c r="AC19" s="292"/>
-      <c r="AD19" s="292"/>
-      <c r="AE19" s="293"/>
-      <c r="AF19" s="288"/>
-      <c r="AG19" s="289"/>
-      <c r="AH19" s="289"/>
-      <c r="AI19" s="290"/>
+      <c r="B19" s="339"/>
+      <c r="C19" s="340"/>
+      <c r="D19" s="341"/>
+      <c r="E19" s="342"/>
+      <c r="F19" s="343"/>
+      <c r="G19" s="339"/>
+      <c r="H19" s="344"/>
+      <c r="I19" s="340"/>
+      <c r="J19" s="345"/>
+      <c r="K19" s="346"/>
+      <c r="L19" s="346"/>
+      <c r="M19" s="346"/>
+      <c r="N19" s="346"/>
+      <c r="O19" s="346"/>
+      <c r="P19" s="347"/>
+      <c r="Q19" s="348"/>
+      <c r="R19" s="349"/>
+      <c r="S19" s="349"/>
+      <c r="T19" s="349"/>
+      <c r="U19" s="349"/>
+      <c r="V19" s="349"/>
+      <c r="W19" s="349"/>
+      <c r="X19" s="349"/>
+      <c r="Y19" s="349"/>
+      <c r="Z19" s="349"/>
+      <c r="AA19" s="349"/>
+      <c r="AB19" s="349"/>
+      <c r="AC19" s="349"/>
+      <c r="AD19" s="349"/>
+      <c r="AE19" s="350"/>
+      <c r="AF19" s="345"/>
+      <c r="AG19" s="346"/>
+      <c r="AH19" s="346"/>
+      <c r="AI19" s="347"/>
     </row>
     <row r="20" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="23"/>
-      <c r="B20" s="282"/>
-      <c r="C20" s="283"/>
-      <c r="D20" s="284"/>
-      <c r="E20" s="285"/>
-      <c r="F20" s="286"/>
-      <c r="G20" s="282"/>
-      <c r="H20" s="287"/>
-      <c r="I20" s="283"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="289"/>
-      <c r="L20" s="289"/>
-      <c r="M20" s="289"/>
-      <c r="N20" s="289"/>
-      <c r="O20" s="289"/>
-      <c r="P20" s="290"/>
-      <c r="Q20" s="291"/>
-      <c r="R20" s="292"/>
-      <c r="S20" s="292"/>
-      <c r="T20" s="292"/>
-      <c r="U20" s="292"/>
-      <c r="V20" s="292"/>
-      <c r="W20" s="292"/>
-      <c r="X20" s="292"/>
-      <c r="Y20" s="292"/>
-      <c r="Z20" s="292"/>
-      <c r="AA20" s="292"/>
-      <c r="AB20" s="292"/>
-      <c r="AC20" s="292"/>
-      <c r="AD20" s="292"/>
-      <c r="AE20" s="293"/>
-      <c r="AF20" s="288"/>
-      <c r="AG20" s="289"/>
-      <c r="AH20" s="289"/>
-      <c r="AI20" s="290"/>
+      <c r="B20" s="339"/>
+      <c r="C20" s="340"/>
+      <c r="D20" s="341"/>
+      <c r="E20" s="342"/>
+      <c r="F20" s="343"/>
+      <c r="G20" s="339"/>
+      <c r="H20" s="344"/>
+      <c r="I20" s="340"/>
+      <c r="J20" s="345"/>
+      <c r="K20" s="346"/>
+      <c r="L20" s="346"/>
+      <c r="M20" s="346"/>
+      <c r="N20" s="346"/>
+      <c r="O20" s="346"/>
+      <c r="P20" s="347"/>
+      <c r="Q20" s="348"/>
+      <c r="R20" s="349"/>
+      <c r="S20" s="349"/>
+      <c r="T20" s="349"/>
+      <c r="U20" s="349"/>
+      <c r="V20" s="349"/>
+      <c r="W20" s="349"/>
+      <c r="X20" s="349"/>
+      <c r="Y20" s="349"/>
+      <c r="Z20" s="349"/>
+      <c r="AA20" s="349"/>
+      <c r="AB20" s="349"/>
+      <c r="AC20" s="349"/>
+      <c r="AD20" s="349"/>
+      <c r="AE20" s="350"/>
+      <c r="AF20" s="345"/>
+      <c r="AG20" s="346"/>
+      <c r="AH20" s="346"/>
+      <c r="AI20" s="347"/>
     </row>
     <row r="21" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="23"/>
-      <c r="B21" s="282"/>
-      <c r="C21" s="283"/>
-      <c r="D21" s="284"/>
-      <c r="E21" s="285"/>
-      <c r="F21" s="286"/>
-      <c r="G21" s="282"/>
-      <c r="H21" s="287"/>
-      <c r="I21" s="283"/>
-      <c r="J21" s="288"/>
-      <c r="K21" s="289"/>
-      <c r="L21" s="289"/>
-      <c r="M21" s="289"/>
-      <c r="N21" s="289"/>
-      <c r="O21" s="289"/>
-      <c r="P21" s="290"/>
-      <c r="Q21" s="291"/>
-      <c r="R21" s="292"/>
-      <c r="S21" s="292"/>
-      <c r="T21" s="292"/>
-      <c r="U21" s="292"/>
-      <c r="V21" s="292"/>
-      <c r="W21" s="292"/>
-      <c r="X21" s="292"/>
-      <c r="Y21" s="292"/>
-      <c r="Z21" s="292"/>
-      <c r="AA21" s="292"/>
-      <c r="AB21" s="292"/>
-      <c r="AC21" s="292"/>
-      <c r="AD21" s="292"/>
-      <c r="AE21" s="293"/>
-      <c r="AF21" s="288"/>
-      <c r="AG21" s="289"/>
-      <c r="AH21" s="289"/>
-      <c r="AI21" s="290"/>
+      <c r="B21" s="339"/>
+      <c r="C21" s="340"/>
+      <c r="D21" s="341"/>
+      <c r="E21" s="342"/>
+      <c r="F21" s="343"/>
+      <c r="G21" s="339"/>
+      <c r="H21" s="344"/>
+      <c r="I21" s="340"/>
+      <c r="J21" s="345"/>
+      <c r="K21" s="346"/>
+      <c r="L21" s="346"/>
+      <c r="M21" s="346"/>
+      <c r="N21" s="346"/>
+      <c r="O21" s="346"/>
+      <c r="P21" s="347"/>
+      <c r="Q21" s="348"/>
+      <c r="R21" s="349"/>
+      <c r="S21" s="349"/>
+      <c r="T21" s="349"/>
+      <c r="U21" s="349"/>
+      <c r="V21" s="349"/>
+      <c r="W21" s="349"/>
+      <c r="X21" s="349"/>
+      <c r="Y21" s="349"/>
+      <c r="Z21" s="349"/>
+      <c r="AA21" s="349"/>
+      <c r="AB21" s="349"/>
+      <c r="AC21" s="349"/>
+      <c r="AD21" s="349"/>
+      <c r="AE21" s="350"/>
+      <c r="AF21" s="345"/>
+      <c r="AG21" s="346"/>
+      <c r="AH21" s="346"/>
+      <c r="AI21" s="347"/>
     </row>
     <row r="22" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="23"/>
-      <c r="B22" s="282"/>
-      <c r="C22" s="283"/>
-      <c r="D22" s="284"/>
-      <c r="E22" s="285"/>
-      <c r="F22" s="286"/>
-      <c r="G22" s="282"/>
-      <c r="H22" s="287"/>
-      <c r="I22" s="283"/>
-      <c r="J22" s="288"/>
-      <c r="K22" s="289"/>
-      <c r="L22" s="289"/>
-      <c r="M22" s="289"/>
-      <c r="N22" s="289"/>
-      <c r="O22" s="289"/>
-      <c r="P22" s="290"/>
-      <c r="Q22" s="291"/>
-      <c r="R22" s="292"/>
-      <c r="S22" s="292"/>
-      <c r="T22" s="292"/>
-      <c r="U22" s="292"/>
-      <c r="V22" s="292"/>
-      <c r="W22" s="292"/>
-      <c r="X22" s="292"/>
-      <c r="Y22" s="292"/>
-      <c r="Z22" s="292"/>
-      <c r="AA22" s="292"/>
-      <c r="AB22" s="292"/>
-      <c r="AC22" s="292"/>
-      <c r="AD22" s="292"/>
-      <c r="AE22" s="293"/>
-      <c r="AF22" s="288"/>
-      <c r="AG22" s="289"/>
-      <c r="AH22" s="289"/>
-      <c r="AI22" s="290"/>
+      <c r="B22" s="339"/>
+      <c r="C22" s="340"/>
+      <c r="D22" s="341"/>
+      <c r="E22" s="342"/>
+      <c r="F22" s="343"/>
+      <c r="G22" s="339"/>
+      <c r="H22" s="344"/>
+      <c r="I22" s="340"/>
+      <c r="J22" s="345"/>
+      <c r="K22" s="346"/>
+      <c r="L22" s="346"/>
+      <c r="M22" s="346"/>
+      <c r="N22" s="346"/>
+      <c r="O22" s="346"/>
+      <c r="P22" s="347"/>
+      <c r="Q22" s="348"/>
+      <c r="R22" s="349"/>
+      <c r="S22" s="349"/>
+      <c r="T22" s="349"/>
+      <c r="U22" s="349"/>
+      <c r="V22" s="349"/>
+      <c r="W22" s="349"/>
+      <c r="X22" s="349"/>
+      <c r="Y22" s="349"/>
+      <c r="Z22" s="349"/>
+      <c r="AA22" s="349"/>
+      <c r="AB22" s="349"/>
+      <c r="AC22" s="349"/>
+      <c r="AD22" s="349"/>
+      <c r="AE22" s="350"/>
+      <c r="AF22" s="345"/>
+      <c r="AG22" s="346"/>
+      <c r="AH22" s="346"/>
+      <c r="AI22" s="347"/>
     </row>
     <row r="23" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="23"/>
-      <c r="B23" s="282"/>
-      <c r="C23" s="283"/>
-      <c r="D23" s="284"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="286"/>
-      <c r="G23" s="282"/>
-      <c r="H23" s="287"/>
-      <c r="I23" s="283"/>
-      <c r="J23" s="288"/>
-      <c r="K23" s="289"/>
-      <c r="L23" s="289"/>
-      <c r="M23" s="289"/>
-      <c r="N23" s="289"/>
-      <c r="O23" s="289"/>
-      <c r="P23" s="290"/>
-      <c r="Q23" s="291"/>
-      <c r="R23" s="292"/>
-      <c r="S23" s="292"/>
-      <c r="T23" s="292"/>
-      <c r="U23" s="292"/>
-      <c r="V23" s="292"/>
-      <c r="W23" s="292"/>
-      <c r="X23" s="292"/>
-      <c r="Y23" s="292"/>
-      <c r="Z23" s="292"/>
-      <c r="AA23" s="292"/>
-      <c r="AB23" s="292"/>
-      <c r="AC23" s="292"/>
-      <c r="AD23" s="292"/>
-      <c r="AE23" s="293"/>
-      <c r="AF23" s="288"/>
-      <c r="AG23" s="289"/>
-      <c r="AH23" s="289"/>
-      <c r="AI23" s="290"/>
+      <c r="B23" s="339"/>
+      <c r="C23" s="340"/>
+      <c r="D23" s="341"/>
+      <c r="E23" s="342"/>
+      <c r="F23" s="343"/>
+      <c r="G23" s="339"/>
+      <c r="H23" s="344"/>
+      <c r="I23" s="340"/>
+      <c r="J23" s="345"/>
+      <c r="K23" s="346"/>
+      <c r="L23" s="346"/>
+      <c r="M23" s="346"/>
+      <c r="N23" s="346"/>
+      <c r="O23" s="346"/>
+      <c r="P23" s="347"/>
+      <c r="Q23" s="348"/>
+      <c r="R23" s="349"/>
+      <c r="S23" s="349"/>
+      <c r="T23" s="349"/>
+      <c r="U23" s="349"/>
+      <c r="V23" s="349"/>
+      <c r="W23" s="349"/>
+      <c r="X23" s="349"/>
+      <c r="Y23" s="349"/>
+      <c r="Z23" s="349"/>
+      <c r="AA23" s="349"/>
+      <c r="AB23" s="349"/>
+      <c r="AC23" s="349"/>
+      <c r="AD23" s="349"/>
+      <c r="AE23" s="350"/>
+      <c r="AF23" s="345"/>
+      <c r="AG23" s="346"/>
+      <c r="AH23" s="346"/>
+      <c r="AI23" s="347"/>
     </row>
     <row r="24" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="B24" s="282"/>
-      <c r="C24" s="283"/>
-      <c r="D24" s="284"/>
-      <c r="E24" s="285"/>
-      <c r="F24" s="286"/>
-      <c r="G24" s="282"/>
-      <c r="H24" s="287"/>
-      <c r="I24" s="283"/>
-      <c r="J24" s="288"/>
-      <c r="K24" s="289"/>
-      <c r="L24" s="289"/>
-      <c r="M24" s="289"/>
-      <c r="N24" s="289"/>
-      <c r="O24" s="289"/>
-      <c r="P24" s="290"/>
-      <c r="Q24" s="291"/>
-      <c r="R24" s="292"/>
-      <c r="S24" s="292"/>
-      <c r="T24" s="292"/>
-      <c r="U24" s="292"/>
-      <c r="V24" s="292"/>
-      <c r="W24" s="292"/>
-      <c r="X24" s="292"/>
-      <c r="Y24" s="292"/>
-      <c r="Z24" s="292"/>
-      <c r="AA24" s="292"/>
-      <c r="AB24" s="292"/>
-      <c r="AC24" s="292"/>
-      <c r="AD24" s="292"/>
-      <c r="AE24" s="293"/>
-      <c r="AF24" s="288"/>
-      <c r="AG24" s="289"/>
-      <c r="AH24" s="289"/>
-      <c r="AI24" s="290"/>
+      <c r="B24" s="339"/>
+      <c r="C24" s="340"/>
+      <c r="D24" s="341"/>
+      <c r="E24" s="342"/>
+      <c r="F24" s="343"/>
+      <c r="G24" s="339"/>
+      <c r="H24" s="344"/>
+      <c r="I24" s="340"/>
+      <c r="J24" s="345"/>
+      <c r="K24" s="346"/>
+      <c r="L24" s="346"/>
+      <c r="M24" s="346"/>
+      <c r="N24" s="346"/>
+      <c r="O24" s="346"/>
+      <c r="P24" s="347"/>
+      <c r="Q24" s="348"/>
+      <c r="R24" s="349"/>
+      <c r="S24" s="349"/>
+      <c r="T24" s="349"/>
+      <c r="U24" s="349"/>
+      <c r="V24" s="349"/>
+      <c r="W24" s="349"/>
+      <c r="X24" s="349"/>
+      <c r="Y24" s="349"/>
+      <c r="Z24" s="349"/>
+      <c r="AA24" s="349"/>
+      <c r="AB24" s="349"/>
+      <c r="AC24" s="349"/>
+      <c r="AD24" s="349"/>
+      <c r="AE24" s="350"/>
+      <c r="AF24" s="345"/>
+      <c r="AG24" s="346"/>
+      <c r="AH24" s="346"/>
+      <c r="AI24" s="347"/>
     </row>
     <row r="25" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="23"/>
-      <c r="B25" s="282"/>
-      <c r="C25" s="283"/>
-      <c r="D25" s="284"/>
-      <c r="E25" s="285"/>
-      <c r="F25" s="286"/>
-      <c r="G25" s="282"/>
-      <c r="H25" s="287"/>
-      <c r="I25" s="283"/>
-      <c r="J25" s="288"/>
-      <c r="K25" s="289"/>
-      <c r="L25" s="289"/>
-      <c r="M25" s="289"/>
-      <c r="N25" s="289"/>
-      <c r="O25" s="289"/>
-      <c r="P25" s="290"/>
-      <c r="Q25" s="291"/>
-      <c r="R25" s="292"/>
-      <c r="S25" s="292"/>
-      <c r="T25" s="292"/>
-      <c r="U25" s="292"/>
-      <c r="V25" s="292"/>
-      <c r="W25" s="292"/>
-      <c r="X25" s="292"/>
-      <c r="Y25" s="292"/>
-      <c r="Z25" s="292"/>
-      <c r="AA25" s="292"/>
-      <c r="AB25" s="292"/>
-      <c r="AC25" s="292"/>
-      <c r="AD25" s="292"/>
-      <c r="AE25" s="293"/>
-      <c r="AF25" s="288"/>
-      <c r="AG25" s="289"/>
-      <c r="AH25" s="289"/>
-      <c r="AI25" s="290"/>
+      <c r="B25" s="339"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="343"/>
+      <c r="G25" s="339"/>
+      <c r="H25" s="344"/>
+      <c r="I25" s="340"/>
+      <c r="J25" s="345"/>
+      <c r="K25" s="346"/>
+      <c r="L25" s="346"/>
+      <c r="M25" s="346"/>
+      <c r="N25" s="346"/>
+      <c r="O25" s="346"/>
+      <c r="P25" s="347"/>
+      <c r="Q25" s="348"/>
+      <c r="R25" s="349"/>
+      <c r="S25" s="349"/>
+      <c r="T25" s="349"/>
+      <c r="U25" s="349"/>
+      <c r="V25" s="349"/>
+      <c r="W25" s="349"/>
+      <c r="X25" s="349"/>
+      <c r="Y25" s="349"/>
+      <c r="Z25" s="349"/>
+      <c r="AA25" s="349"/>
+      <c r="AB25" s="349"/>
+      <c r="AC25" s="349"/>
+      <c r="AD25" s="349"/>
+      <c r="AE25" s="350"/>
+      <c r="AF25" s="345"/>
+      <c r="AG25" s="346"/>
+      <c r="AH25" s="346"/>
+      <c r="AI25" s="347"/>
     </row>
     <row r="26" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="23"/>
-      <c r="B26" s="282"/>
-      <c r="C26" s="283"/>
-      <c r="D26" s="284"/>
-      <c r="E26" s="285"/>
-      <c r="F26" s="286"/>
-      <c r="G26" s="282"/>
-      <c r="H26" s="287"/>
-      <c r="I26" s="283"/>
-      <c r="J26" s="288"/>
-      <c r="K26" s="289"/>
-      <c r="L26" s="289"/>
-      <c r="M26" s="289"/>
-      <c r="N26" s="289"/>
-      <c r="O26" s="289"/>
-      <c r="P26" s="290"/>
-      <c r="Q26" s="291"/>
-      <c r="R26" s="292"/>
-      <c r="S26" s="292"/>
-      <c r="T26" s="292"/>
-      <c r="U26" s="292"/>
-      <c r="V26" s="292"/>
-      <c r="W26" s="292"/>
-      <c r="X26" s="292"/>
-      <c r="Y26" s="292"/>
-      <c r="Z26" s="292"/>
-      <c r="AA26" s="292"/>
-      <c r="AB26" s="292"/>
-      <c r="AC26" s="292"/>
-      <c r="AD26" s="292"/>
-      <c r="AE26" s="293"/>
-      <c r="AF26" s="288"/>
-      <c r="AG26" s="289"/>
-      <c r="AH26" s="289"/>
-      <c r="AI26" s="290"/>
+      <c r="B26" s="339"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="343"/>
+      <c r="G26" s="339"/>
+      <c r="H26" s="344"/>
+      <c r="I26" s="340"/>
+      <c r="J26" s="345"/>
+      <c r="K26" s="346"/>
+      <c r="L26" s="346"/>
+      <c r="M26" s="346"/>
+      <c r="N26" s="346"/>
+      <c r="O26" s="346"/>
+      <c r="P26" s="347"/>
+      <c r="Q26" s="348"/>
+      <c r="R26" s="349"/>
+      <c r="S26" s="349"/>
+      <c r="T26" s="349"/>
+      <c r="U26" s="349"/>
+      <c r="V26" s="349"/>
+      <c r="W26" s="349"/>
+      <c r="X26" s="349"/>
+      <c r="Y26" s="349"/>
+      <c r="Z26" s="349"/>
+      <c r="AA26" s="349"/>
+      <c r="AB26" s="349"/>
+      <c r="AC26" s="349"/>
+      <c r="AD26" s="349"/>
+      <c r="AE26" s="350"/>
+      <c r="AF26" s="345"/>
+      <c r="AG26" s="346"/>
+      <c r="AH26" s="346"/>
+      <c r="AI26" s="347"/>
     </row>
     <row r="27" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="23"/>
-      <c r="B27" s="282"/>
-      <c r="C27" s="283"/>
-      <c r="D27" s="284"/>
-      <c r="E27" s="285"/>
-      <c r="F27" s="286"/>
-      <c r="G27" s="282"/>
-      <c r="H27" s="287"/>
-      <c r="I27" s="283"/>
-      <c r="J27" s="288"/>
-      <c r="K27" s="289"/>
-      <c r="L27" s="289"/>
-      <c r="M27" s="289"/>
-      <c r="N27" s="289"/>
-      <c r="O27" s="289"/>
-      <c r="P27" s="290"/>
-      <c r="Q27" s="291"/>
-      <c r="R27" s="292"/>
-      <c r="S27" s="292"/>
-      <c r="T27" s="292"/>
-      <c r="U27" s="292"/>
-      <c r="V27" s="292"/>
-      <c r="W27" s="292"/>
-      <c r="X27" s="292"/>
-      <c r="Y27" s="292"/>
-      <c r="Z27" s="292"/>
-      <c r="AA27" s="292"/>
-      <c r="AB27" s="292"/>
-      <c r="AC27" s="292"/>
-      <c r="AD27" s="292"/>
-      <c r="AE27" s="293"/>
-      <c r="AF27" s="288"/>
-      <c r="AG27" s="289"/>
-      <c r="AH27" s="289"/>
-      <c r="AI27" s="290"/>
+      <c r="B27" s="339"/>
+      <c r="C27" s="340"/>
+      <c r="D27" s="341"/>
+      <c r="E27" s="342"/>
+      <c r="F27" s="343"/>
+      <c r="G27" s="339"/>
+      <c r="H27" s="344"/>
+      <c r="I27" s="340"/>
+      <c r="J27" s="345"/>
+      <c r="K27" s="346"/>
+      <c r="L27" s="346"/>
+      <c r="M27" s="346"/>
+      <c r="N27" s="346"/>
+      <c r="O27" s="346"/>
+      <c r="P27" s="347"/>
+      <c r="Q27" s="348"/>
+      <c r="R27" s="349"/>
+      <c r="S27" s="349"/>
+      <c r="T27" s="349"/>
+      <c r="U27" s="349"/>
+      <c r="V27" s="349"/>
+      <c r="W27" s="349"/>
+      <c r="X27" s="349"/>
+      <c r="Y27" s="349"/>
+      <c r="Z27" s="349"/>
+      <c r="AA27" s="349"/>
+      <c r="AB27" s="349"/>
+      <c r="AC27" s="349"/>
+      <c r="AD27" s="349"/>
+      <c r="AE27" s="350"/>
+      <c r="AF27" s="345"/>
+      <c r="AG27" s="346"/>
+      <c r="AH27" s="346"/>
+      <c r="AI27" s="347"/>
     </row>
     <row r="28" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="23"/>
-      <c r="B28" s="282"/>
-      <c r="C28" s="283"/>
-      <c r="D28" s="284"/>
-      <c r="E28" s="285"/>
-      <c r="F28" s="286"/>
-      <c r="G28" s="282"/>
-      <c r="H28" s="287"/>
-      <c r="I28" s="283"/>
-      <c r="J28" s="288"/>
-      <c r="K28" s="289"/>
-      <c r="L28" s="289"/>
-      <c r="M28" s="289"/>
-      <c r="N28" s="289"/>
-      <c r="O28" s="289"/>
-      <c r="P28" s="290"/>
-      <c r="Q28" s="291"/>
-      <c r="R28" s="292"/>
-      <c r="S28" s="292"/>
-      <c r="T28" s="292"/>
-      <c r="U28" s="292"/>
-      <c r="V28" s="292"/>
-      <c r="W28" s="292"/>
-      <c r="X28" s="292"/>
-      <c r="Y28" s="292"/>
-      <c r="Z28" s="292"/>
-      <c r="AA28" s="292"/>
-      <c r="AB28" s="292"/>
-      <c r="AC28" s="292"/>
-      <c r="AD28" s="292"/>
-      <c r="AE28" s="293"/>
-      <c r="AF28" s="288"/>
-      <c r="AG28" s="289"/>
-      <c r="AH28" s="289"/>
-      <c r="AI28" s="290"/>
+      <c r="B28" s="339"/>
+      <c r="C28" s="340"/>
+      <c r="D28" s="341"/>
+      <c r="E28" s="342"/>
+      <c r="F28" s="343"/>
+      <c r="G28" s="339"/>
+      <c r="H28" s="344"/>
+      <c r="I28" s="340"/>
+      <c r="J28" s="345"/>
+      <c r="K28" s="346"/>
+      <c r="L28" s="346"/>
+      <c r="M28" s="346"/>
+      <c r="N28" s="346"/>
+      <c r="O28" s="346"/>
+      <c r="P28" s="347"/>
+      <c r="Q28" s="348"/>
+      <c r="R28" s="349"/>
+      <c r="S28" s="349"/>
+      <c r="T28" s="349"/>
+      <c r="U28" s="349"/>
+      <c r="V28" s="349"/>
+      <c r="W28" s="349"/>
+      <c r="X28" s="349"/>
+      <c r="Y28" s="349"/>
+      <c r="Z28" s="349"/>
+      <c r="AA28" s="349"/>
+      <c r="AB28" s="349"/>
+      <c r="AC28" s="349"/>
+      <c r="AD28" s="349"/>
+      <c r="AE28" s="350"/>
+      <c r="AF28" s="345"/>
+      <c r="AG28" s="346"/>
+      <c r="AH28" s="346"/>
+      <c r="AI28" s="347"/>
     </row>
     <row r="29" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="23"/>
-      <c r="B29" s="282"/>
-      <c r="C29" s="283"/>
-      <c r="D29" s="284"/>
-      <c r="E29" s="285"/>
-      <c r="F29" s="286"/>
-      <c r="G29" s="282"/>
-      <c r="H29" s="287"/>
-      <c r="I29" s="283"/>
-      <c r="J29" s="288"/>
-      <c r="K29" s="289"/>
-      <c r="L29" s="289"/>
-      <c r="M29" s="289"/>
-      <c r="N29" s="289"/>
-      <c r="O29" s="289"/>
-      <c r="P29" s="290"/>
-      <c r="Q29" s="291"/>
-      <c r="R29" s="292"/>
-      <c r="S29" s="292"/>
-      <c r="T29" s="292"/>
-      <c r="U29" s="292"/>
-      <c r="V29" s="292"/>
-      <c r="W29" s="292"/>
-      <c r="X29" s="292"/>
-      <c r="Y29" s="292"/>
-      <c r="Z29" s="292"/>
-      <c r="AA29" s="292"/>
-      <c r="AB29" s="292"/>
-      <c r="AC29" s="292"/>
-      <c r="AD29" s="292"/>
-      <c r="AE29" s="293"/>
-      <c r="AF29" s="288"/>
-      <c r="AG29" s="289"/>
-      <c r="AH29" s="289"/>
-      <c r="AI29" s="290"/>
+      <c r="B29" s="339"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="343"/>
+      <c r="G29" s="339"/>
+      <c r="H29" s="344"/>
+      <c r="I29" s="340"/>
+      <c r="J29" s="345"/>
+      <c r="K29" s="346"/>
+      <c r="L29" s="346"/>
+      <c r="M29" s="346"/>
+      <c r="N29" s="346"/>
+      <c r="O29" s="346"/>
+      <c r="P29" s="347"/>
+      <c r="Q29" s="348"/>
+      <c r="R29" s="349"/>
+      <c r="S29" s="349"/>
+      <c r="T29" s="349"/>
+      <c r="U29" s="349"/>
+      <c r="V29" s="349"/>
+      <c r="W29" s="349"/>
+      <c r="X29" s="349"/>
+      <c r="Y29" s="349"/>
+      <c r="Z29" s="349"/>
+      <c r="AA29" s="349"/>
+      <c r="AB29" s="349"/>
+      <c r="AC29" s="349"/>
+      <c r="AD29" s="349"/>
+      <c r="AE29" s="350"/>
+      <c r="AF29" s="345"/>
+      <c r="AG29" s="346"/>
+      <c r="AH29" s="346"/>
+      <c r="AI29" s="347"/>
     </row>
     <row r="30" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="23"/>
-      <c r="B30" s="282"/>
-      <c r="C30" s="283"/>
-      <c r="D30" s="284"/>
-      <c r="E30" s="285"/>
-      <c r="F30" s="286"/>
-      <c r="G30" s="282"/>
-      <c r="H30" s="287"/>
-      <c r="I30" s="283"/>
-      <c r="J30" s="288"/>
-      <c r="K30" s="289"/>
-      <c r="L30" s="289"/>
-      <c r="M30" s="289"/>
-      <c r="N30" s="289"/>
-      <c r="O30" s="289"/>
-      <c r="P30" s="290"/>
-      <c r="Q30" s="291"/>
-      <c r="R30" s="292"/>
-      <c r="S30" s="292"/>
-      <c r="T30" s="292"/>
-      <c r="U30" s="292"/>
-      <c r="V30" s="292"/>
-      <c r="W30" s="292"/>
-      <c r="X30" s="292"/>
-      <c r="Y30" s="292"/>
-      <c r="Z30" s="292"/>
-      <c r="AA30" s="292"/>
-      <c r="AB30" s="292"/>
-      <c r="AC30" s="292"/>
-      <c r="AD30" s="292"/>
-      <c r="AE30" s="293"/>
-      <c r="AF30" s="288"/>
-      <c r="AG30" s="289"/>
-      <c r="AH30" s="289"/>
-      <c r="AI30" s="290"/>
+      <c r="B30" s="339"/>
+      <c r="C30" s="340"/>
+      <c r="D30" s="341"/>
+      <c r="E30" s="342"/>
+      <c r="F30" s="343"/>
+      <c r="G30" s="339"/>
+      <c r="H30" s="344"/>
+      <c r="I30" s="340"/>
+      <c r="J30" s="345"/>
+      <c r="K30" s="346"/>
+      <c r="L30" s="346"/>
+      <c r="M30" s="346"/>
+      <c r="N30" s="346"/>
+      <c r="O30" s="346"/>
+      <c r="P30" s="347"/>
+      <c r="Q30" s="348"/>
+      <c r="R30" s="349"/>
+      <c r="S30" s="349"/>
+      <c r="T30" s="349"/>
+      <c r="U30" s="349"/>
+      <c r="V30" s="349"/>
+      <c r="W30" s="349"/>
+      <c r="X30" s="349"/>
+      <c r="Y30" s="349"/>
+      <c r="Z30" s="349"/>
+      <c r="AA30" s="349"/>
+      <c r="AB30" s="349"/>
+      <c r="AC30" s="349"/>
+      <c r="AD30" s="349"/>
+      <c r="AE30" s="350"/>
+      <c r="AF30" s="345"/>
+      <c r="AG30" s="346"/>
+      <c r="AH30" s="346"/>
+      <c r="AI30" s="347"/>
     </row>
     <row r="31" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="23"/>
-      <c r="B31" s="282"/>
-      <c r="C31" s="283"/>
-      <c r="D31" s="284"/>
-      <c r="E31" s="285"/>
-      <c r="F31" s="286"/>
-      <c r="G31" s="282"/>
-      <c r="H31" s="287"/>
-      <c r="I31" s="283"/>
-      <c r="J31" s="288"/>
-      <c r="K31" s="289"/>
-      <c r="L31" s="289"/>
-      <c r="M31" s="289"/>
-      <c r="N31" s="289"/>
-      <c r="O31" s="289"/>
-      <c r="P31" s="290"/>
-      <c r="Q31" s="291"/>
-      <c r="R31" s="292"/>
-      <c r="S31" s="292"/>
-      <c r="T31" s="292"/>
-      <c r="U31" s="292"/>
-      <c r="V31" s="292"/>
-      <c r="W31" s="292"/>
-      <c r="X31" s="292"/>
-      <c r="Y31" s="292"/>
-      <c r="Z31" s="292"/>
-      <c r="AA31" s="292"/>
-      <c r="AB31" s="292"/>
-      <c r="AC31" s="292"/>
-      <c r="AD31" s="292"/>
-      <c r="AE31" s="293"/>
-      <c r="AF31" s="288"/>
-      <c r="AG31" s="289"/>
-      <c r="AH31" s="289"/>
-      <c r="AI31" s="290"/>
+      <c r="B31" s="339"/>
+      <c r="C31" s="340"/>
+      <c r="D31" s="341"/>
+      <c r="E31" s="342"/>
+      <c r="F31" s="343"/>
+      <c r="G31" s="339"/>
+      <c r="H31" s="344"/>
+      <c r="I31" s="340"/>
+      <c r="J31" s="345"/>
+      <c r="K31" s="346"/>
+      <c r="L31" s="346"/>
+      <c r="M31" s="346"/>
+      <c r="N31" s="346"/>
+      <c r="O31" s="346"/>
+      <c r="P31" s="347"/>
+      <c r="Q31" s="348"/>
+      <c r="R31" s="349"/>
+      <c r="S31" s="349"/>
+      <c r="T31" s="349"/>
+      <c r="U31" s="349"/>
+      <c r="V31" s="349"/>
+      <c r="W31" s="349"/>
+      <c r="X31" s="349"/>
+      <c r="Y31" s="349"/>
+      <c r="Z31" s="349"/>
+      <c r="AA31" s="349"/>
+      <c r="AB31" s="349"/>
+      <c r="AC31" s="349"/>
+      <c r="AD31" s="349"/>
+      <c r="AE31" s="350"/>
+      <c r="AF31" s="345"/>
+      <c r="AG31" s="346"/>
+      <c r="AH31" s="346"/>
+      <c r="AI31" s="347"/>
     </row>
     <row r="32" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="23"/>
-      <c r="B32" s="282"/>
-      <c r="C32" s="283"/>
-      <c r="D32" s="284"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="286"/>
-      <c r="G32" s="282"/>
-      <c r="H32" s="287"/>
-      <c r="I32" s="283"/>
-      <c r="J32" s="288"/>
-      <c r="K32" s="294"/>
-      <c r="L32" s="289"/>
-      <c r="M32" s="289"/>
-      <c r="N32" s="289"/>
-      <c r="O32" s="289"/>
-      <c r="P32" s="290"/>
-      <c r="Q32" s="291"/>
-      <c r="R32" s="292"/>
-      <c r="S32" s="292"/>
-      <c r="T32" s="292"/>
-      <c r="U32" s="292"/>
-      <c r="V32" s="292"/>
-      <c r="W32" s="292"/>
-      <c r="X32" s="292"/>
-      <c r="Y32" s="292"/>
-      <c r="Z32" s="292"/>
-      <c r="AA32" s="292"/>
-      <c r="AB32" s="292"/>
-      <c r="AC32" s="292"/>
-      <c r="AD32" s="292"/>
-      <c r="AE32" s="293"/>
-      <c r="AF32" s="288"/>
-      <c r="AG32" s="289"/>
-      <c r="AH32" s="289"/>
-      <c r="AI32" s="290"/>
+      <c r="B32" s="339"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="343"/>
+      <c r="G32" s="339"/>
+      <c r="H32" s="344"/>
+      <c r="I32" s="340"/>
+      <c r="J32" s="345"/>
+      <c r="K32" s="351"/>
+      <c r="L32" s="346"/>
+      <c r="M32" s="346"/>
+      <c r="N32" s="346"/>
+      <c r="O32" s="346"/>
+      <c r="P32" s="347"/>
+      <c r="Q32" s="348"/>
+      <c r="R32" s="349"/>
+      <c r="S32" s="349"/>
+      <c r="T32" s="349"/>
+      <c r="U32" s="349"/>
+      <c r="V32" s="349"/>
+      <c r="W32" s="349"/>
+      <c r="X32" s="349"/>
+      <c r="Y32" s="349"/>
+      <c r="Z32" s="349"/>
+      <c r="AA32" s="349"/>
+      <c r="AB32" s="349"/>
+      <c r="AC32" s="349"/>
+      <c r="AD32" s="349"/>
+      <c r="AE32" s="350"/>
+      <c r="AF32" s="345"/>
+      <c r="AG32" s="346"/>
+      <c r="AH32" s="346"/>
+      <c r="AI32" s="347"/>
     </row>
     <row r="33" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="23"/>
-      <c r="B33" s="282"/>
-      <c r="C33" s="283"/>
-      <c r="D33" s="284"/>
-      <c r="E33" s="285"/>
-      <c r="F33" s="286"/>
-      <c r="G33" s="282"/>
-      <c r="H33" s="287"/>
-      <c r="I33" s="283"/>
-      <c r="J33" s="288"/>
-      <c r="K33" s="289"/>
-      <c r="L33" s="289"/>
-      <c r="M33" s="289"/>
-      <c r="N33" s="289"/>
-      <c r="O33" s="289"/>
-      <c r="P33" s="290"/>
-      <c r="Q33" s="291"/>
-      <c r="R33" s="292"/>
-      <c r="S33" s="292"/>
-      <c r="T33" s="292"/>
-      <c r="U33" s="292"/>
-      <c r="V33" s="292"/>
-      <c r="W33" s="292"/>
-      <c r="X33" s="292"/>
-      <c r="Y33" s="292"/>
-      <c r="Z33" s="292"/>
-      <c r="AA33" s="292"/>
-      <c r="AB33" s="292"/>
-      <c r="AC33" s="292"/>
-      <c r="AD33" s="292"/>
-      <c r="AE33" s="293"/>
-      <c r="AF33" s="288"/>
-      <c r="AG33" s="289"/>
-      <c r="AH33" s="289"/>
-      <c r="AI33" s="290"/>
+      <c r="B33" s="339"/>
+      <c r="C33" s="340"/>
+      <c r="D33" s="341"/>
+      <c r="E33" s="342"/>
+      <c r="F33" s="343"/>
+      <c r="G33" s="339"/>
+      <c r="H33" s="344"/>
+      <c r="I33" s="340"/>
+      <c r="J33" s="345"/>
+      <c r="K33" s="346"/>
+      <c r="L33" s="346"/>
+      <c r="M33" s="346"/>
+      <c r="N33" s="346"/>
+      <c r="O33" s="346"/>
+      <c r="P33" s="347"/>
+      <c r="Q33" s="348"/>
+      <c r="R33" s="349"/>
+      <c r="S33" s="349"/>
+      <c r="T33" s="349"/>
+      <c r="U33" s="349"/>
+      <c r="V33" s="349"/>
+      <c r="W33" s="349"/>
+      <c r="X33" s="349"/>
+      <c r="Y33" s="349"/>
+      <c r="Z33" s="349"/>
+      <c r="AA33" s="349"/>
+      <c r="AB33" s="349"/>
+      <c r="AC33" s="349"/>
+      <c r="AD33" s="349"/>
+      <c r="AE33" s="350"/>
+      <c r="AF33" s="345"/>
+      <c r="AG33" s="346"/>
+      <c r="AH33" s="346"/>
+      <c r="AI33" s="347"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -18554,161 +18713,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -30136,7 +30140,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="30" t="s">
-        <v>751</v>
+        <v>852</v>
       </c>
       <c r="O7" s="30" t="s">
         <v>18</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A9CFA6-F764-420F-ACBF-27F9848C6623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6CDEAD-8577-4575-8270-2664C446AA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11314,7 +11314,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>リクエストID：RWxxxxxxxx</t>
+    <t>テストターゲット名：RWxxxxxxxx</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -12825,108 +12828,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -13033,6 +12934,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -17211,57 +17214,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="285" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="321"/>
-      <c r="E1" s="322" t="s">
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="287"/>
+      <c r="E1" s="288" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="323"/>
-      <c r="G1" s="323"/>
-      <c r="H1" s="323"/>
-      <c r="I1" s="323"/>
-      <c r="J1" s="323"/>
-      <c r="K1" s="323"/>
-      <c r="L1" s="323"/>
-      <c r="M1" s="323"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="328" t="s">
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
+      <c r="M1" s="289"/>
+      <c r="N1" s="290"/>
+      <c r="O1" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="329"/>
-      <c r="Q1" s="329"/>
-      <c r="R1" s="330"/>
-      <c r="S1" s="337" t="s">
+      <c r="P1" s="295"/>
+      <c r="Q1" s="295"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="303" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="338"/>
-      <c r="U1" s="338"/>
-      <c r="V1" s="338"/>
-      <c r="W1" s="338"/>
-      <c r="X1" s="338"/>
-      <c r="Y1" s="338"/>
-      <c r="Z1" s="339"/>
-      <c r="AA1" s="319" t="s">
+      <c r="T1" s="304"/>
+      <c r="U1" s="304"/>
+      <c r="V1" s="304"/>
+      <c r="W1" s="304"/>
+      <c r="X1" s="304"/>
+      <c r="Y1" s="304"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="AB1" s="321"/>
-      <c r="AC1" s="346" t="str">
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="312" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="347"/>
-      <c r="AE1" s="347"/>
-      <c r="AF1" s="348"/>
-      <c r="AG1" s="313">
+      <c r="AD1" s="313"/>
+      <c r="AE1" s="313"/>
+      <c r="AF1" s="314"/>
+      <c r="AG1" s="279">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="314"/>
-      <c r="AI1" s="315"/>
+      <c r="AH1" s="280"/>
+      <c r="AI1" s="281"/>
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
       <c r="AL1" s="13"/>
@@ -17269,53 +17272,53 @@
       <c r="AN1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="319" t="s">
+      <c r="A2" s="285" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="320"/>
-      <c r="D2" s="321"/>
-      <c r="E2" s="322" t="s">
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="288" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="323"/>
-      <c r="G2" s="323"/>
-      <c r="H2" s="323"/>
-      <c r="I2" s="323"/>
-      <c r="J2" s="323"/>
-      <c r="K2" s="323"/>
-      <c r="L2" s="323"/>
-      <c r="M2" s="323"/>
-      <c r="N2" s="324"/>
-      <c r="O2" s="331"/>
-      <c r="P2" s="332"/>
-      <c r="Q2" s="332"/>
-      <c r="R2" s="333"/>
-      <c r="S2" s="340"/>
-      <c r="T2" s="341"/>
-      <c r="U2" s="341"/>
-      <c r="V2" s="341"/>
-      <c r="W2" s="341"/>
-      <c r="X2" s="341"/>
-      <c r="Y2" s="341"/>
-      <c r="Z2" s="342"/>
-      <c r="AA2" s="319" t="s">
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="289"/>
+      <c r="I2" s="289"/>
+      <c r="J2" s="289"/>
+      <c r="K2" s="289"/>
+      <c r="L2" s="289"/>
+      <c r="M2" s="289"/>
+      <c r="N2" s="290"/>
+      <c r="O2" s="297"/>
+      <c r="P2" s="298"/>
+      <c r="Q2" s="298"/>
+      <c r="R2" s="299"/>
+      <c r="S2" s="306"/>
+      <c r="T2" s="307"/>
+      <c r="U2" s="307"/>
+      <c r="V2" s="307"/>
+      <c r="W2" s="307"/>
+      <c r="X2" s="307"/>
+      <c r="Y2" s="307"/>
+      <c r="Z2" s="308"/>
+      <c r="AA2" s="285" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="321"/>
-      <c r="AC2" s="325" t="str">
+      <c r="AB2" s="287"/>
+      <c r="AC2" s="291" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="326"/>
-      <c r="AE2" s="326"/>
-      <c r="AF2" s="327"/>
-      <c r="AG2" s="313">
+      <c r="AD2" s="292"/>
+      <c r="AE2" s="292"/>
+      <c r="AF2" s="293"/>
+      <c r="AG2" s="279">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="314"/>
-      <c r="AI2" s="315"/>
+      <c r="AH2" s="280"/>
+      <c r="AI2" s="281"/>
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
       <c r="AL2" s="13"/>
@@ -17323,45 +17326,45 @@
       <c r="AN2" s="13"/>
     </row>
     <row r="3" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="319" t="s">
+      <c r="A3" s="285" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="320"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="322" t="s">
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="287"/>
+      <c r="E3" s="288" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="323"/>
-      <c r="G3" s="323"/>
-      <c r="H3" s="323"/>
-      <c r="I3" s="323"/>
-      <c r="J3" s="323"/>
-      <c r="K3" s="323"/>
-      <c r="L3" s="323"/>
-      <c r="M3" s="323"/>
-      <c r="N3" s="324"/>
-      <c r="O3" s="334"/>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="343"/>
-      <c r="T3" s="344"/>
-      <c r="U3" s="344"/>
-      <c r="V3" s="344"/>
-      <c r="W3" s="344"/>
-      <c r="X3" s="344"/>
-      <c r="Y3" s="344"/>
-      <c r="Z3" s="345"/>
-      <c r="AA3" s="319"/>
-      <c r="AB3" s="321"/>
-      <c r="AC3" s="346"/>
-      <c r="AD3" s="347"/>
-      <c r="AE3" s="347"/>
-      <c r="AF3" s="348"/>
-      <c r="AG3" s="313"/>
-      <c r="AH3" s="314"/>
-      <c r="AI3" s="315"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="289"/>
+      <c r="I3" s="289"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
+      <c r="M3" s="289"/>
+      <c r="N3" s="290"/>
+      <c r="O3" s="300"/>
+      <c r="P3" s="301"/>
+      <c r="Q3" s="301"/>
+      <c r="R3" s="302"/>
+      <c r="S3" s="309"/>
+      <c r="T3" s="310"/>
+      <c r="U3" s="310"/>
+      <c r="V3" s="310"/>
+      <c r="W3" s="310"/>
+      <c r="X3" s="310"/>
+      <c r="Y3" s="310"/>
+      <c r="Z3" s="311"/>
+      <c r="AA3" s="285"/>
+      <c r="AB3" s="287"/>
+      <c r="AC3" s="312"/>
+      <c r="AD3" s="313"/>
+      <c r="AE3" s="313"/>
+      <c r="AF3" s="314"/>
+      <c r="AG3" s="279"/>
+      <c r="AH3" s="280"/>
+      <c r="AI3" s="281"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
@@ -17398,97 +17401,97 @@
       <c r="A7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="316" t="s">
+      <c r="B7" s="282" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="317"/>
-      <c r="D7" s="316" t="s">
+      <c r="C7" s="283"/>
+      <c r="D7" s="282" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="318"/>
-      <c r="F7" s="317"/>
-      <c r="G7" s="316" t="s">
+      <c r="E7" s="284"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="282" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="318"/>
-      <c r="I7" s="317"/>
-      <c r="J7" s="316" t="s">
+      <c r="H7" s="284"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="282" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="318"/>
-      <c r="L7" s="318"/>
-      <c r="M7" s="318"/>
-      <c r="N7" s="318"/>
-      <c r="O7" s="318"/>
-      <c r="P7" s="317"/>
-      <c r="Q7" s="316" t="s">
+      <c r="K7" s="284"/>
+      <c r="L7" s="284"/>
+      <c r="M7" s="284"/>
+      <c r="N7" s="284"/>
+      <c r="O7" s="284"/>
+      <c r="P7" s="283"/>
+      <c r="Q7" s="282" t="s">
         <v>69</v>
       </c>
-      <c r="R7" s="318"/>
-      <c r="S7" s="318"/>
-      <c r="T7" s="318"/>
-      <c r="U7" s="318"/>
-      <c r="V7" s="318"/>
-      <c r="W7" s="318"/>
-      <c r="X7" s="318"/>
-      <c r="Y7" s="318"/>
-      <c r="Z7" s="318"/>
-      <c r="AA7" s="318"/>
-      <c r="AB7" s="318"/>
-      <c r="AC7" s="318"/>
-      <c r="AD7" s="318"/>
-      <c r="AE7" s="317"/>
-      <c r="AF7" s="316" t="s">
+      <c r="R7" s="284"/>
+      <c r="S7" s="284"/>
+      <c r="T7" s="284"/>
+      <c r="U7" s="284"/>
+      <c r="V7" s="284"/>
+      <c r="W7" s="284"/>
+      <c r="X7" s="284"/>
+      <c r="Y7" s="284"/>
+      <c r="Z7" s="284"/>
+      <c r="AA7" s="284"/>
+      <c r="AB7" s="284"/>
+      <c r="AC7" s="284"/>
+      <c r="AD7" s="284"/>
+      <c r="AE7" s="283"/>
+      <c r="AF7" s="282" t="s">
         <v>70</v>
       </c>
-      <c r="AG7" s="318"/>
-      <c r="AH7" s="318"/>
-      <c r="AI7" s="317"/>
+      <c r="AG7" s="284"/>
+      <c r="AH7" s="284"/>
+      <c r="AI7" s="283"/>
     </row>
     <row r="8" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="26">
         <v>1</v>
       </c>
-      <c r="B8" s="304" t="s">
+      <c r="B8" s="327" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="305"/>
-      <c r="D8" s="306">
+      <c r="C8" s="328"/>
+      <c r="D8" s="329">
         <v>43336</v>
       </c>
-      <c r="E8" s="307"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="304" t="s">
+      <c r="E8" s="330"/>
+      <c r="F8" s="331"/>
+      <c r="G8" s="327" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="309"/>
-      <c r="I8" s="305"/>
-      <c r="J8" s="310" t="s">
+      <c r="H8" s="332"/>
+      <c r="I8" s="328"/>
+      <c r="J8" s="333" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="311"/>
-      <c r="L8" s="311"/>
-      <c r="M8" s="311"/>
-      <c r="N8" s="311"/>
-      <c r="O8" s="311"/>
-      <c r="P8" s="312"/>
-      <c r="Q8" s="310" t="s">
+      <c r="K8" s="334"/>
+      <c r="L8" s="334"/>
+      <c r="M8" s="334"/>
+      <c r="N8" s="334"/>
+      <c r="O8" s="334"/>
+      <c r="P8" s="335"/>
+      <c r="Q8" s="333" t="s">
         <v>78</v>
       </c>
-      <c r="R8" s="311"/>
-      <c r="S8" s="311"/>
-      <c r="T8" s="311"/>
-      <c r="U8" s="311"/>
-      <c r="V8" s="311"/>
-      <c r="W8" s="311"/>
-      <c r="X8" s="311"/>
-      <c r="Y8" s="311"/>
-      <c r="Z8" s="311"/>
-      <c r="AA8" s="311"/>
-      <c r="AB8" s="311"/>
-      <c r="AC8" s="311"/>
-      <c r="AD8" s="311"/>
-      <c r="AE8" s="312"/>
+      <c r="R8" s="334"/>
+      <c r="S8" s="334"/>
+      <c r="T8" s="334"/>
+      <c r="U8" s="334"/>
+      <c r="V8" s="334"/>
+      <c r="W8" s="334"/>
+      <c r="X8" s="334"/>
+      <c r="Y8" s="334"/>
+      <c r="Z8" s="334"/>
+      <c r="AA8" s="334"/>
+      <c r="AB8" s="334"/>
+      <c r="AC8" s="334"/>
+      <c r="AD8" s="334"/>
+      <c r="AE8" s="335"/>
       <c r="AF8" s="27" t="s">
         <v>79</v>
       </c>
@@ -17500,946 +17503,1101 @@
       <c r="A9" s="26">
         <v>2</v>
       </c>
-      <c r="B9" s="292" t="s">
+      <c r="B9" s="315" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="293"/>
-      <c r="D9" s="294">
+      <c r="C9" s="316"/>
+      <c r="D9" s="317">
         <v>44852</v>
       </c>
-      <c r="E9" s="295"/>
-      <c r="F9" s="296"/>
-      <c r="G9" s="294" t="s">
+      <c r="E9" s="318"/>
+      <c r="F9" s="319"/>
+      <c r="G9" s="317" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="297"/>
-      <c r="I9" s="293"/>
-      <c r="J9" s="298" t="s">
+      <c r="H9" s="320"/>
+      <c r="I9" s="316"/>
+      <c r="J9" s="321" t="s">
         <v>741</v>
       </c>
-      <c r="K9" s="299"/>
-      <c r="L9" s="299"/>
-      <c r="M9" s="299"/>
-      <c r="N9" s="299"/>
-      <c r="O9" s="299"/>
-      <c r="P9" s="300"/>
-      <c r="Q9" s="298" t="s">
+      <c r="K9" s="322"/>
+      <c r="L9" s="322"/>
+      <c r="M9" s="322"/>
+      <c r="N9" s="322"/>
+      <c r="O9" s="322"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="321" t="s">
         <v>742</v>
       </c>
-      <c r="R9" s="301"/>
-      <c r="S9" s="301"/>
-      <c r="T9" s="301"/>
-      <c r="U9" s="301"/>
-      <c r="V9" s="301"/>
-      <c r="W9" s="301"/>
-      <c r="X9" s="301"/>
-      <c r="Y9" s="301"/>
-      <c r="Z9" s="301"/>
-      <c r="AA9" s="301"/>
-      <c r="AB9" s="301"/>
-      <c r="AC9" s="301"/>
-      <c r="AD9" s="301"/>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="303" t="s">
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="324"/>
+      <c r="V9" s="324"/>
+      <c r="W9" s="324"/>
+      <c r="X9" s="324"/>
+      <c r="Y9" s="324"/>
+      <c r="Z9" s="324"/>
+      <c r="AA9" s="324"/>
+      <c r="AB9" s="324"/>
+      <c r="AC9" s="324"/>
+      <c r="AD9" s="324"/>
+      <c r="AE9" s="325"/>
+      <c r="AF9" s="326" t="s">
         <v>79</v>
       </c>
-      <c r="AG9" s="299"/>
-      <c r="AH9" s="299"/>
-      <c r="AI9" s="300"/>
+      <c r="AG9" s="322"/>
+      <c r="AH9" s="322"/>
+      <c r="AI9" s="323"/>
     </row>
     <row r="10" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="279"/>
-      <c r="C10" s="280"/>
-      <c r="D10" s="281"/>
-      <c r="E10" s="282"/>
-      <c r="F10" s="283"/>
-      <c r="G10" s="279"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="285"/>
-      <c r="K10" s="286"/>
-      <c r="L10" s="286"/>
-      <c r="M10" s="286"/>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="287"/>
-      <c r="Q10" s="288"/>
-      <c r="R10" s="289"/>
-      <c r="S10" s="289"/>
-      <c r="T10" s="289"/>
-      <c r="U10" s="289"/>
-      <c r="V10" s="289"/>
-      <c r="W10" s="289"/>
-      <c r="X10" s="289"/>
-      <c r="Y10" s="289"/>
-      <c r="Z10" s="289"/>
-      <c r="AA10" s="289"/>
-      <c r="AB10" s="289"/>
-      <c r="AC10" s="289"/>
-      <c r="AD10" s="289"/>
-      <c r="AE10" s="290"/>
-      <c r="AF10" s="285"/>
-      <c r="AG10" s="286"/>
-      <c r="AH10" s="286"/>
-      <c r="AI10" s="287"/>
+      <c r="B10" s="336"/>
+      <c r="C10" s="337"/>
+      <c r="D10" s="338"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="340"/>
+      <c r="G10" s="336"/>
+      <c r="H10" s="341"/>
+      <c r="I10" s="337"/>
+      <c r="J10" s="342"/>
+      <c r="K10" s="343"/>
+      <c r="L10" s="343"/>
+      <c r="M10" s="343"/>
+      <c r="N10" s="343"/>
+      <c r="O10" s="343"/>
+      <c r="P10" s="344"/>
+      <c r="Q10" s="345"/>
+      <c r="R10" s="346"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="346"/>
+      <c r="U10" s="346"/>
+      <c r="V10" s="346"/>
+      <c r="W10" s="346"/>
+      <c r="X10" s="346"/>
+      <c r="Y10" s="346"/>
+      <c r="Z10" s="346"/>
+      <c r="AA10" s="346"/>
+      <c r="AB10" s="346"/>
+      <c r="AC10" s="346"/>
+      <c r="AD10" s="346"/>
+      <c r="AE10" s="347"/>
+      <c r="AF10" s="342"/>
+      <c r="AG10" s="343"/>
+      <c r="AH10" s="343"/>
+      <c r="AI10" s="344"/>
     </row>
     <row r="11" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="23"/>
-      <c r="B11" s="279"/>
-      <c r="C11" s="280"/>
-      <c r="D11" s="281"/>
-      <c r="E11" s="282"/>
-      <c r="F11" s="283"/>
-      <c r="G11" s="279"/>
-      <c r="H11" s="284"/>
-      <c r="I11" s="280"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="287"/>
-      <c r="Q11" s="288"/>
-      <c r="R11" s="289"/>
-      <c r="S11" s="289"/>
-      <c r="T11" s="289"/>
-      <c r="U11" s="289"/>
-      <c r="V11" s="289"/>
-      <c r="W11" s="289"/>
-      <c r="X11" s="289"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="289"/>
-      <c r="AD11" s="289"/>
-      <c r="AE11" s="290"/>
-      <c r="AF11" s="285"/>
-      <c r="AG11" s="286"/>
-      <c r="AH11" s="286"/>
-      <c r="AI11" s="287"/>
+      <c r="B11" s="336"/>
+      <c r="C11" s="337"/>
+      <c r="D11" s="338"/>
+      <c r="E11" s="339"/>
+      <c r="F11" s="340"/>
+      <c r="G11" s="336"/>
+      <c r="H11" s="341"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="343"/>
+      <c r="L11" s="343"/>
+      <c r="M11" s="343"/>
+      <c r="N11" s="343"/>
+      <c r="O11" s="343"/>
+      <c r="P11" s="344"/>
+      <c r="Q11" s="345"/>
+      <c r="R11" s="346"/>
+      <c r="S11" s="346"/>
+      <c r="T11" s="346"/>
+      <c r="U11" s="346"/>
+      <c r="V11" s="346"/>
+      <c r="W11" s="346"/>
+      <c r="X11" s="346"/>
+      <c r="Y11" s="346"/>
+      <c r="Z11" s="346"/>
+      <c r="AA11" s="346"/>
+      <c r="AB11" s="346"/>
+      <c r="AC11" s="346"/>
+      <c r="AD11" s="346"/>
+      <c r="AE11" s="347"/>
+      <c r="AF11" s="342"/>
+      <c r="AG11" s="343"/>
+      <c r="AH11" s="343"/>
+      <c r="AI11" s="344"/>
     </row>
     <row r="12" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="23"/>
-      <c r="B12" s="279"/>
-      <c r="C12" s="280"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="282"/>
-      <c r="F12" s="283"/>
-      <c r="G12" s="279"/>
-      <c r="H12" s="284"/>
-      <c r="I12" s="280"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="286"/>
-      <c r="L12" s="286"/>
-      <c r="M12" s="286"/>
-      <c r="N12" s="286"/>
-      <c r="O12" s="286"/>
-      <c r="P12" s="287"/>
-      <c r="Q12" s="288"/>
-      <c r="R12" s="289"/>
-      <c r="S12" s="289"/>
-      <c r="T12" s="289"/>
-      <c r="U12" s="289"/>
-      <c r="V12" s="289"/>
-      <c r="W12" s="289"/>
-      <c r="X12" s="289"/>
-      <c r="Y12" s="289"/>
-      <c r="Z12" s="289"/>
-      <c r="AA12" s="289"/>
-      <c r="AB12" s="289"/>
-      <c r="AC12" s="289"/>
-      <c r="AD12" s="289"/>
-      <c r="AE12" s="290"/>
-      <c r="AF12" s="285"/>
-      <c r="AG12" s="286"/>
-      <c r="AH12" s="286"/>
-      <c r="AI12" s="287"/>
+      <c r="B12" s="336"/>
+      <c r="C12" s="337"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="340"/>
+      <c r="G12" s="336"/>
+      <c r="H12" s="341"/>
+      <c r="I12" s="337"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="343"/>
+      <c r="L12" s="343"/>
+      <c r="M12" s="343"/>
+      <c r="N12" s="343"/>
+      <c r="O12" s="343"/>
+      <c r="P12" s="344"/>
+      <c r="Q12" s="345"/>
+      <c r="R12" s="346"/>
+      <c r="S12" s="346"/>
+      <c r="T12" s="346"/>
+      <c r="U12" s="346"/>
+      <c r="V12" s="346"/>
+      <c r="W12" s="346"/>
+      <c r="X12" s="346"/>
+      <c r="Y12" s="346"/>
+      <c r="Z12" s="346"/>
+      <c r="AA12" s="346"/>
+      <c r="AB12" s="346"/>
+      <c r="AC12" s="346"/>
+      <c r="AD12" s="346"/>
+      <c r="AE12" s="347"/>
+      <c r="AF12" s="342"/>
+      <c r="AG12" s="343"/>
+      <c r="AH12" s="343"/>
+      <c r="AI12" s="344"/>
     </row>
     <row r="13" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="23"/>
-      <c r="B13" s="279"/>
-      <c r="C13" s="280"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="282"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="279"/>
-      <c r="H13" s="284"/>
-      <c r="I13" s="280"/>
-      <c r="J13" s="285"/>
-      <c r="K13" s="286"/>
-      <c r="L13" s="286"/>
-      <c r="M13" s="286"/>
-      <c r="N13" s="286"/>
-      <c r="O13" s="286"/>
-      <c r="P13" s="287"/>
-      <c r="Q13" s="288"/>
-      <c r="R13" s="289"/>
-      <c r="S13" s="289"/>
-      <c r="T13" s="289"/>
-      <c r="U13" s="289"/>
-      <c r="V13" s="289"/>
-      <c r="W13" s="289"/>
-      <c r="X13" s="289"/>
-      <c r="Y13" s="289"/>
-      <c r="Z13" s="289"/>
-      <c r="AA13" s="289"/>
-      <c r="AB13" s="289"/>
-      <c r="AC13" s="289"/>
-      <c r="AD13" s="289"/>
-      <c r="AE13" s="290"/>
-      <c r="AF13" s="285"/>
-      <c r="AG13" s="286"/>
-      <c r="AH13" s="286"/>
-      <c r="AI13" s="287"/>
+      <c r="B13" s="336"/>
+      <c r="C13" s="337"/>
+      <c r="D13" s="338"/>
+      <c r="E13" s="339"/>
+      <c r="F13" s="340"/>
+      <c r="G13" s="336"/>
+      <c r="H13" s="341"/>
+      <c r="I13" s="337"/>
+      <c r="J13" s="342"/>
+      <c r="K13" s="343"/>
+      <c r="L13" s="343"/>
+      <c r="M13" s="343"/>
+      <c r="N13" s="343"/>
+      <c r="O13" s="343"/>
+      <c r="P13" s="344"/>
+      <c r="Q13" s="345"/>
+      <c r="R13" s="346"/>
+      <c r="S13" s="346"/>
+      <c r="T13" s="346"/>
+      <c r="U13" s="346"/>
+      <c r="V13" s="346"/>
+      <c r="W13" s="346"/>
+      <c r="X13" s="346"/>
+      <c r="Y13" s="346"/>
+      <c r="Z13" s="346"/>
+      <c r="AA13" s="346"/>
+      <c r="AB13" s="346"/>
+      <c r="AC13" s="346"/>
+      <c r="AD13" s="346"/>
+      <c r="AE13" s="347"/>
+      <c r="AF13" s="342"/>
+      <c r="AG13" s="343"/>
+      <c r="AH13" s="343"/>
+      <c r="AI13" s="344"/>
     </row>
     <row r="14" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="23"/>
-      <c r="B14" s="279"/>
-      <c r="C14" s="280"/>
-      <c r="D14" s="281"/>
-      <c r="E14" s="282"/>
-      <c r="F14" s="283"/>
-      <c r="G14" s="279"/>
-      <c r="H14" s="284"/>
-      <c r="I14" s="280"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="286"/>
-      <c r="L14" s="286"/>
-      <c r="M14" s="286"/>
-      <c r="N14" s="286"/>
-      <c r="O14" s="286"/>
-      <c r="P14" s="287"/>
-      <c r="Q14" s="288"/>
-      <c r="R14" s="289"/>
-      <c r="S14" s="289"/>
-      <c r="T14" s="289"/>
-      <c r="U14" s="289"/>
-      <c r="V14" s="289"/>
-      <c r="W14" s="289"/>
-      <c r="X14" s="289"/>
-      <c r="Y14" s="289"/>
-      <c r="Z14" s="289"/>
-      <c r="AA14" s="289"/>
-      <c r="AB14" s="289"/>
-      <c r="AC14" s="289"/>
-      <c r="AD14" s="289"/>
-      <c r="AE14" s="290"/>
-      <c r="AF14" s="285"/>
-      <c r="AG14" s="286"/>
-      <c r="AH14" s="286"/>
-      <c r="AI14" s="287"/>
+      <c r="B14" s="336"/>
+      <c r="C14" s="337"/>
+      <c r="D14" s="338"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="340"/>
+      <c r="G14" s="336"/>
+      <c r="H14" s="341"/>
+      <c r="I14" s="337"/>
+      <c r="J14" s="342"/>
+      <c r="K14" s="343"/>
+      <c r="L14" s="343"/>
+      <c r="M14" s="343"/>
+      <c r="N14" s="343"/>
+      <c r="O14" s="343"/>
+      <c r="P14" s="344"/>
+      <c r="Q14" s="345"/>
+      <c r="R14" s="346"/>
+      <c r="S14" s="346"/>
+      <c r="T14" s="346"/>
+      <c r="U14" s="346"/>
+      <c r="V14" s="346"/>
+      <c r="W14" s="346"/>
+      <c r="X14" s="346"/>
+      <c r="Y14" s="346"/>
+      <c r="Z14" s="346"/>
+      <c r="AA14" s="346"/>
+      <c r="AB14" s="346"/>
+      <c r="AC14" s="346"/>
+      <c r="AD14" s="346"/>
+      <c r="AE14" s="347"/>
+      <c r="AF14" s="342"/>
+      <c r="AG14" s="343"/>
+      <c r="AH14" s="343"/>
+      <c r="AI14" s="344"/>
     </row>
     <row r="15" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="23"/>
-      <c r="B15" s="279"/>
-      <c r="C15" s="280"/>
-      <c r="D15" s="281"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="283"/>
-      <c r="G15" s="279"/>
-      <c r="H15" s="284"/>
-      <c r="I15" s="280"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="286"/>
-      <c r="L15" s="286"/>
-      <c r="M15" s="286"/>
-      <c r="N15" s="286"/>
-      <c r="O15" s="286"/>
-      <c r="P15" s="287"/>
-      <c r="Q15" s="288"/>
-      <c r="R15" s="289"/>
-      <c r="S15" s="289"/>
-      <c r="T15" s="289"/>
-      <c r="U15" s="289"/>
-      <c r="V15" s="289"/>
-      <c r="W15" s="289"/>
-      <c r="X15" s="289"/>
-      <c r="Y15" s="289"/>
-      <c r="Z15" s="289"/>
-      <c r="AA15" s="289"/>
-      <c r="AB15" s="289"/>
-      <c r="AC15" s="289"/>
-      <c r="AD15" s="289"/>
-      <c r="AE15" s="290"/>
-      <c r="AF15" s="285"/>
-      <c r="AG15" s="286"/>
-      <c r="AH15" s="286"/>
-      <c r="AI15" s="287"/>
+      <c r="B15" s="336"/>
+      <c r="C15" s="337"/>
+      <c r="D15" s="338"/>
+      <c r="E15" s="339"/>
+      <c r="F15" s="340"/>
+      <c r="G15" s="336"/>
+      <c r="H15" s="341"/>
+      <c r="I15" s="337"/>
+      <c r="J15" s="342"/>
+      <c r="K15" s="343"/>
+      <c r="L15" s="343"/>
+      <c r="M15" s="343"/>
+      <c r="N15" s="343"/>
+      <c r="O15" s="343"/>
+      <c r="P15" s="344"/>
+      <c r="Q15" s="345"/>
+      <c r="R15" s="346"/>
+      <c r="S15" s="346"/>
+      <c r="T15" s="346"/>
+      <c r="U15" s="346"/>
+      <c r="V15" s="346"/>
+      <c r="W15" s="346"/>
+      <c r="X15" s="346"/>
+      <c r="Y15" s="346"/>
+      <c r="Z15" s="346"/>
+      <c r="AA15" s="346"/>
+      <c r="AB15" s="346"/>
+      <c r="AC15" s="346"/>
+      <c r="AD15" s="346"/>
+      <c r="AE15" s="347"/>
+      <c r="AF15" s="342"/>
+      <c r="AG15" s="343"/>
+      <c r="AH15" s="343"/>
+      <c r="AI15" s="344"/>
     </row>
     <row r="16" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="23"/>
-      <c r="B16" s="279"/>
-      <c r="C16" s="280"/>
-      <c r="D16" s="281"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="283"/>
-      <c r="G16" s="279"/>
-      <c r="H16" s="284"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="286"/>
-      <c r="L16" s="286"/>
-      <c r="M16" s="286"/>
-      <c r="N16" s="286"/>
-      <c r="O16" s="286"/>
-      <c r="P16" s="287"/>
-      <c r="Q16" s="288"/>
-      <c r="R16" s="289"/>
-      <c r="S16" s="289"/>
-      <c r="T16" s="289"/>
-      <c r="U16" s="289"/>
-      <c r="V16" s="289"/>
-      <c r="W16" s="289"/>
-      <c r="X16" s="289"/>
-      <c r="Y16" s="289"/>
-      <c r="Z16" s="289"/>
-      <c r="AA16" s="289"/>
-      <c r="AB16" s="289"/>
-      <c r="AC16" s="289"/>
-      <c r="AD16" s="289"/>
-      <c r="AE16" s="290"/>
-      <c r="AF16" s="285"/>
-      <c r="AG16" s="286"/>
-      <c r="AH16" s="286"/>
-      <c r="AI16" s="287"/>
+      <c r="B16" s="336"/>
+      <c r="C16" s="337"/>
+      <c r="D16" s="338"/>
+      <c r="E16" s="339"/>
+      <c r="F16" s="340"/>
+      <c r="G16" s="336"/>
+      <c r="H16" s="341"/>
+      <c r="I16" s="337"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="343"/>
+      <c r="L16" s="343"/>
+      <c r="M16" s="343"/>
+      <c r="N16" s="343"/>
+      <c r="O16" s="343"/>
+      <c r="P16" s="344"/>
+      <c r="Q16" s="345"/>
+      <c r="R16" s="346"/>
+      <c r="S16" s="346"/>
+      <c r="T16" s="346"/>
+      <c r="U16" s="346"/>
+      <c r="V16" s="346"/>
+      <c r="W16" s="346"/>
+      <c r="X16" s="346"/>
+      <c r="Y16" s="346"/>
+      <c r="Z16" s="346"/>
+      <c r="AA16" s="346"/>
+      <c r="AB16" s="346"/>
+      <c r="AC16" s="346"/>
+      <c r="AD16" s="346"/>
+      <c r="AE16" s="347"/>
+      <c r="AF16" s="342"/>
+      <c r="AG16" s="343"/>
+      <c r="AH16" s="343"/>
+      <c r="AI16" s="344"/>
     </row>
     <row r="17" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="23"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
-      <c r="D17" s="281"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="283"/>
-      <c r="G17" s="279"/>
-      <c r="H17" s="284"/>
-      <c r="I17" s="280"/>
-      <c r="J17" s="285"/>
-      <c r="K17" s="286"/>
-      <c r="L17" s="286"/>
-      <c r="M17" s="286"/>
-      <c r="N17" s="286"/>
-      <c r="O17" s="286"/>
-      <c r="P17" s="287"/>
-      <c r="Q17" s="288"/>
-      <c r="R17" s="289"/>
-      <c r="S17" s="289"/>
-      <c r="T17" s="289"/>
-      <c r="U17" s="289"/>
-      <c r="V17" s="289"/>
-      <c r="W17" s="289"/>
-      <c r="X17" s="289"/>
-      <c r="Y17" s="289"/>
-      <c r="Z17" s="289"/>
-      <c r="AA17" s="289"/>
-      <c r="AB17" s="289"/>
-      <c r="AC17" s="289"/>
-      <c r="AD17" s="289"/>
-      <c r="AE17" s="290"/>
-      <c r="AF17" s="285"/>
-      <c r="AG17" s="286"/>
-      <c r="AH17" s="286"/>
-      <c r="AI17" s="287"/>
+      <c r="B17" s="336"/>
+      <c r="C17" s="337"/>
+      <c r="D17" s="338"/>
+      <c r="E17" s="339"/>
+      <c r="F17" s="340"/>
+      <c r="G17" s="336"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="337"/>
+      <c r="J17" s="342"/>
+      <c r="K17" s="343"/>
+      <c r="L17" s="343"/>
+      <c r="M17" s="343"/>
+      <c r="N17" s="343"/>
+      <c r="O17" s="343"/>
+      <c r="P17" s="344"/>
+      <c r="Q17" s="345"/>
+      <c r="R17" s="346"/>
+      <c r="S17" s="346"/>
+      <c r="T17" s="346"/>
+      <c r="U17" s="346"/>
+      <c r="V17" s="346"/>
+      <c r="W17" s="346"/>
+      <c r="X17" s="346"/>
+      <c r="Y17" s="346"/>
+      <c r="Z17" s="346"/>
+      <c r="AA17" s="346"/>
+      <c r="AB17" s="346"/>
+      <c r="AC17" s="346"/>
+      <c r="AD17" s="346"/>
+      <c r="AE17" s="347"/>
+      <c r="AF17" s="342"/>
+      <c r="AG17" s="343"/>
+      <c r="AH17" s="343"/>
+      <c r="AI17" s="344"/>
     </row>
     <row r="18" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="23"/>
-      <c r="B18" s="279"/>
-      <c r="C18" s="280"/>
-      <c r="D18" s="281"/>
-      <c r="E18" s="282"/>
-      <c r="F18" s="283"/>
-      <c r="G18" s="279"/>
-      <c r="H18" s="284"/>
-      <c r="I18" s="280"/>
-      <c r="J18" s="285"/>
-      <c r="K18" s="286"/>
-      <c r="L18" s="286"/>
-      <c r="M18" s="286"/>
-      <c r="N18" s="286"/>
-      <c r="O18" s="286"/>
-      <c r="P18" s="287"/>
-      <c r="Q18" s="288"/>
-      <c r="R18" s="289"/>
-      <c r="S18" s="289"/>
-      <c r="T18" s="289"/>
-      <c r="U18" s="289"/>
-      <c r="V18" s="289"/>
-      <c r="W18" s="289"/>
-      <c r="X18" s="289"/>
-      <c r="Y18" s="289"/>
-      <c r="Z18" s="289"/>
-      <c r="AA18" s="289"/>
-      <c r="AB18" s="289"/>
-      <c r="AC18" s="289"/>
-      <c r="AD18" s="289"/>
-      <c r="AE18" s="290"/>
-      <c r="AF18" s="285"/>
-      <c r="AG18" s="286"/>
-      <c r="AH18" s="286"/>
-      <c r="AI18" s="287"/>
+      <c r="B18" s="336"/>
+      <c r="C18" s="337"/>
+      <c r="D18" s="338"/>
+      <c r="E18" s="339"/>
+      <c r="F18" s="340"/>
+      <c r="G18" s="336"/>
+      <c r="H18" s="341"/>
+      <c r="I18" s="337"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="343"/>
+      <c r="L18" s="343"/>
+      <c r="M18" s="343"/>
+      <c r="N18" s="343"/>
+      <c r="O18" s="343"/>
+      <c r="P18" s="344"/>
+      <c r="Q18" s="345"/>
+      <c r="R18" s="346"/>
+      <c r="S18" s="346"/>
+      <c r="T18" s="346"/>
+      <c r="U18" s="346"/>
+      <c r="V18" s="346"/>
+      <c r="W18" s="346"/>
+      <c r="X18" s="346"/>
+      <c r="Y18" s="346"/>
+      <c r="Z18" s="346"/>
+      <c r="AA18" s="346"/>
+      <c r="AB18" s="346"/>
+      <c r="AC18" s="346"/>
+      <c r="AD18" s="346"/>
+      <c r="AE18" s="347"/>
+      <c r="AF18" s="342"/>
+      <c r="AG18" s="343"/>
+      <c r="AH18" s="343"/>
+      <c r="AI18" s="344"/>
     </row>
     <row r="19" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="23"/>
-      <c r="B19" s="279"/>
-      <c r="C19" s="280"/>
-      <c r="D19" s="281"/>
-      <c r="E19" s="282"/>
-      <c r="F19" s="283"/>
-      <c r="G19" s="279"/>
-      <c r="H19" s="284"/>
-      <c r="I19" s="280"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="286"/>
-      <c r="M19" s="286"/>
-      <c r="N19" s="286"/>
-      <c r="O19" s="286"/>
-      <c r="P19" s="287"/>
-      <c r="Q19" s="288"/>
-      <c r="R19" s="289"/>
-      <c r="S19" s="289"/>
-      <c r="T19" s="289"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
-      <c r="W19" s="289"/>
-      <c r="X19" s="289"/>
-      <c r="Y19" s="289"/>
-      <c r="Z19" s="289"/>
-      <c r="AA19" s="289"/>
-      <c r="AB19" s="289"/>
-      <c r="AC19" s="289"/>
-      <c r="AD19" s="289"/>
-      <c r="AE19" s="290"/>
-      <c r="AF19" s="285"/>
-      <c r="AG19" s="286"/>
-      <c r="AH19" s="286"/>
-      <c r="AI19" s="287"/>
+      <c r="B19" s="336"/>
+      <c r="C19" s="337"/>
+      <c r="D19" s="338"/>
+      <c r="E19" s="339"/>
+      <c r="F19" s="340"/>
+      <c r="G19" s="336"/>
+      <c r="H19" s="341"/>
+      <c r="I19" s="337"/>
+      <c r="J19" s="342"/>
+      <c r="K19" s="343"/>
+      <c r="L19" s="343"/>
+      <c r="M19" s="343"/>
+      <c r="N19" s="343"/>
+      <c r="O19" s="343"/>
+      <c r="P19" s="344"/>
+      <c r="Q19" s="345"/>
+      <c r="R19" s="346"/>
+      <c r="S19" s="346"/>
+      <c r="T19" s="346"/>
+      <c r="U19" s="346"/>
+      <c r="V19" s="346"/>
+      <c r="W19" s="346"/>
+      <c r="X19" s="346"/>
+      <c r="Y19" s="346"/>
+      <c r="Z19" s="346"/>
+      <c r="AA19" s="346"/>
+      <c r="AB19" s="346"/>
+      <c r="AC19" s="346"/>
+      <c r="AD19" s="346"/>
+      <c r="AE19" s="347"/>
+      <c r="AF19" s="342"/>
+      <c r="AG19" s="343"/>
+      <c r="AH19" s="343"/>
+      <c r="AI19" s="344"/>
     </row>
     <row r="20" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="23"/>
-      <c r="B20" s="279"/>
-      <c r="C20" s="280"/>
-      <c r="D20" s="281"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="279"/>
-      <c r="H20" s="284"/>
-      <c r="I20" s="280"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="286"/>
-      <c r="L20" s="286"/>
-      <c r="M20" s="286"/>
-      <c r="N20" s="286"/>
-      <c r="O20" s="286"/>
-      <c r="P20" s="287"/>
-      <c r="Q20" s="288"/>
-      <c r="R20" s="289"/>
-      <c r="S20" s="289"/>
-      <c r="T20" s="289"/>
-      <c r="U20" s="289"/>
-      <c r="V20" s="289"/>
-      <c r="W20" s="289"/>
-      <c r="X20" s="289"/>
-      <c r="Y20" s="289"/>
-      <c r="Z20" s="289"/>
-      <c r="AA20" s="289"/>
-      <c r="AB20" s="289"/>
-      <c r="AC20" s="289"/>
-      <c r="AD20" s="289"/>
-      <c r="AE20" s="290"/>
-      <c r="AF20" s="285"/>
-      <c r="AG20" s="286"/>
-      <c r="AH20" s="286"/>
-      <c r="AI20" s="287"/>
+      <c r="B20" s="336"/>
+      <c r="C20" s="337"/>
+      <c r="D20" s="338"/>
+      <c r="E20" s="339"/>
+      <c r="F20" s="340"/>
+      <c r="G20" s="336"/>
+      <c r="H20" s="341"/>
+      <c r="I20" s="337"/>
+      <c r="J20" s="342"/>
+      <c r="K20" s="343"/>
+      <c r="L20" s="343"/>
+      <c r="M20" s="343"/>
+      <c r="N20" s="343"/>
+      <c r="O20" s="343"/>
+      <c r="P20" s="344"/>
+      <c r="Q20" s="345"/>
+      <c r="R20" s="346"/>
+      <c r="S20" s="346"/>
+      <c r="T20" s="346"/>
+      <c r="U20" s="346"/>
+      <c r="V20" s="346"/>
+      <c r="W20" s="346"/>
+      <c r="X20" s="346"/>
+      <c r="Y20" s="346"/>
+      <c r="Z20" s="346"/>
+      <c r="AA20" s="346"/>
+      <c r="AB20" s="346"/>
+      <c r="AC20" s="346"/>
+      <c r="AD20" s="346"/>
+      <c r="AE20" s="347"/>
+      <c r="AF20" s="342"/>
+      <c r="AG20" s="343"/>
+      <c r="AH20" s="343"/>
+      <c r="AI20" s="344"/>
     </row>
     <row r="21" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="23"/>
-      <c r="B21" s="279"/>
-      <c r="C21" s="280"/>
-      <c r="D21" s="281"/>
-      <c r="E21" s="282"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="279"/>
-      <c r="H21" s="284"/>
-      <c r="I21" s="280"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="286"/>
-      <c r="M21" s="286"/>
-      <c r="N21" s="286"/>
-      <c r="O21" s="286"/>
-      <c r="P21" s="287"/>
-      <c r="Q21" s="288"/>
-      <c r="R21" s="289"/>
-      <c r="S21" s="289"/>
-      <c r="T21" s="289"/>
-      <c r="U21" s="289"/>
-      <c r="V21" s="289"/>
-      <c r="W21" s="289"/>
-      <c r="X21" s="289"/>
-      <c r="Y21" s="289"/>
-      <c r="Z21" s="289"/>
-      <c r="AA21" s="289"/>
-      <c r="AB21" s="289"/>
-      <c r="AC21" s="289"/>
-      <c r="AD21" s="289"/>
-      <c r="AE21" s="290"/>
-      <c r="AF21" s="285"/>
-      <c r="AG21" s="286"/>
-      <c r="AH21" s="286"/>
-      <c r="AI21" s="287"/>
+      <c r="B21" s="336"/>
+      <c r="C21" s="337"/>
+      <c r="D21" s="338"/>
+      <c r="E21" s="339"/>
+      <c r="F21" s="340"/>
+      <c r="G21" s="336"/>
+      <c r="H21" s="341"/>
+      <c r="I21" s="337"/>
+      <c r="J21" s="342"/>
+      <c r="K21" s="343"/>
+      <c r="L21" s="343"/>
+      <c r="M21" s="343"/>
+      <c r="N21" s="343"/>
+      <c r="O21" s="343"/>
+      <c r="P21" s="344"/>
+      <c r="Q21" s="345"/>
+      <c r="R21" s="346"/>
+      <c r="S21" s="346"/>
+      <c r="T21" s="346"/>
+      <c r="U21" s="346"/>
+      <c r="V21" s="346"/>
+      <c r="W21" s="346"/>
+      <c r="X21" s="346"/>
+      <c r="Y21" s="346"/>
+      <c r="Z21" s="346"/>
+      <c r="AA21" s="346"/>
+      <c r="AB21" s="346"/>
+      <c r="AC21" s="346"/>
+      <c r="AD21" s="346"/>
+      <c r="AE21" s="347"/>
+      <c r="AF21" s="342"/>
+      <c r="AG21" s="343"/>
+      <c r="AH21" s="343"/>
+      <c r="AI21" s="344"/>
     </row>
     <row r="22" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="23"/>
-      <c r="B22" s="279"/>
-      <c r="C22" s="280"/>
-      <c r="D22" s="281"/>
-      <c r="E22" s="282"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="284"/>
-      <c r="I22" s="280"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="286"/>
-      <c r="L22" s="286"/>
-      <c r="M22" s="286"/>
-      <c r="N22" s="286"/>
-      <c r="O22" s="286"/>
-      <c r="P22" s="287"/>
-      <c r="Q22" s="288"/>
-      <c r="R22" s="289"/>
-      <c r="S22" s="289"/>
-      <c r="T22" s="289"/>
-      <c r="U22" s="289"/>
-      <c r="V22" s="289"/>
-      <c r="W22" s="289"/>
-      <c r="X22" s="289"/>
-      <c r="Y22" s="289"/>
-      <c r="Z22" s="289"/>
-      <c r="AA22" s="289"/>
-      <c r="AB22" s="289"/>
-      <c r="AC22" s="289"/>
-      <c r="AD22" s="289"/>
-      <c r="AE22" s="290"/>
-      <c r="AF22" s="285"/>
-      <c r="AG22" s="286"/>
-      <c r="AH22" s="286"/>
-      <c r="AI22" s="287"/>
+      <c r="B22" s="336"/>
+      <c r="C22" s="337"/>
+      <c r="D22" s="338"/>
+      <c r="E22" s="339"/>
+      <c r="F22" s="340"/>
+      <c r="G22" s="336"/>
+      <c r="H22" s="341"/>
+      <c r="I22" s="337"/>
+      <c r="J22" s="342"/>
+      <c r="K22" s="343"/>
+      <c r="L22" s="343"/>
+      <c r="M22" s="343"/>
+      <c r="N22" s="343"/>
+      <c r="O22" s="343"/>
+      <c r="P22" s="344"/>
+      <c r="Q22" s="345"/>
+      <c r="R22" s="346"/>
+      <c r="S22" s="346"/>
+      <c r="T22" s="346"/>
+      <c r="U22" s="346"/>
+      <c r="V22" s="346"/>
+      <c r="W22" s="346"/>
+      <c r="X22" s="346"/>
+      <c r="Y22" s="346"/>
+      <c r="Z22" s="346"/>
+      <c r="AA22" s="346"/>
+      <c r="AB22" s="346"/>
+      <c r="AC22" s="346"/>
+      <c r="AD22" s="346"/>
+      <c r="AE22" s="347"/>
+      <c r="AF22" s="342"/>
+      <c r="AG22" s="343"/>
+      <c r="AH22" s="343"/>
+      <c r="AI22" s="344"/>
     </row>
     <row r="23" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="23"/>
-      <c r="B23" s="279"/>
-      <c r="C23" s="280"/>
-      <c r="D23" s="281"/>
-      <c r="E23" s="282"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="279"/>
-      <c r="H23" s="284"/>
-      <c r="I23" s="280"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="286"/>
-      <c r="M23" s="286"/>
-      <c r="N23" s="286"/>
-      <c r="O23" s="286"/>
-      <c r="P23" s="287"/>
-      <c r="Q23" s="288"/>
-      <c r="R23" s="289"/>
-      <c r="S23" s="289"/>
-      <c r="T23" s="289"/>
-      <c r="U23" s="289"/>
-      <c r="V23" s="289"/>
-      <c r="W23" s="289"/>
-      <c r="X23" s="289"/>
-      <c r="Y23" s="289"/>
-      <c r="Z23" s="289"/>
-      <c r="AA23" s="289"/>
-      <c r="AB23" s="289"/>
-      <c r="AC23" s="289"/>
-      <c r="AD23" s="289"/>
-      <c r="AE23" s="290"/>
-      <c r="AF23" s="285"/>
-      <c r="AG23" s="286"/>
-      <c r="AH23" s="286"/>
-      <c r="AI23" s="287"/>
+      <c r="B23" s="336"/>
+      <c r="C23" s="337"/>
+      <c r="D23" s="338"/>
+      <c r="E23" s="339"/>
+      <c r="F23" s="340"/>
+      <c r="G23" s="336"/>
+      <c r="H23" s="341"/>
+      <c r="I23" s="337"/>
+      <c r="J23" s="342"/>
+      <c r="K23" s="343"/>
+      <c r="L23" s="343"/>
+      <c r="M23" s="343"/>
+      <c r="N23" s="343"/>
+      <c r="O23" s="343"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="345"/>
+      <c r="R23" s="346"/>
+      <c r="S23" s="346"/>
+      <c r="T23" s="346"/>
+      <c r="U23" s="346"/>
+      <c r="V23" s="346"/>
+      <c r="W23" s="346"/>
+      <c r="X23" s="346"/>
+      <c r="Y23" s="346"/>
+      <c r="Z23" s="346"/>
+      <c r="AA23" s="346"/>
+      <c r="AB23" s="346"/>
+      <c r="AC23" s="346"/>
+      <c r="AD23" s="346"/>
+      <c r="AE23" s="347"/>
+      <c r="AF23" s="342"/>
+      <c r="AG23" s="343"/>
+      <c r="AH23" s="343"/>
+      <c r="AI23" s="344"/>
     </row>
     <row r="24" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="B24" s="279"/>
-      <c r="C24" s="280"/>
-      <c r="D24" s="281"/>
-      <c r="E24" s="282"/>
-      <c r="F24" s="283"/>
-      <c r="G24" s="279"/>
-      <c r="H24" s="284"/>
-      <c r="I24" s="280"/>
-      <c r="J24" s="285"/>
-      <c r="K24" s="286"/>
-      <c r="L24" s="286"/>
-      <c r="M24" s="286"/>
-      <c r="N24" s="286"/>
-      <c r="O24" s="286"/>
-      <c r="P24" s="287"/>
-      <c r="Q24" s="288"/>
-      <c r="R24" s="289"/>
-      <c r="S24" s="289"/>
-      <c r="T24" s="289"/>
-      <c r="U24" s="289"/>
-      <c r="V24" s="289"/>
-      <c r="W24" s="289"/>
-      <c r="X24" s="289"/>
-      <c r="Y24" s="289"/>
-      <c r="Z24" s="289"/>
-      <c r="AA24" s="289"/>
-      <c r="AB24" s="289"/>
-      <c r="AC24" s="289"/>
-      <c r="AD24" s="289"/>
-      <c r="AE24" s="290"/>
-      <c r="AF24" s="285"/>
-      <c r="AG24" s="286"/>
-      <c r="AH24" s="286"/>
-      <c r="AI24" s="287"/>
+      <c r="B24" s="336"/>
+      <c r="C24" s="337"/>
+      <c r="D24" s="338"/>
+      <c r="E24" s="339"/>
+      <c r="F24" s="340"/>
+      <c r="G24" s="336"/>
+      <c r="H24" s="341"/>
+      <c r="I24" s="337"/>
+      <c r="J24" s="342"/>
+      <c r="K24" s="343"/>
+      <c r="L24" s="343"/>
+      <c r="M24" s="343"/>
+      <c r="N24" s="343"/>
+      <c r="O24" s="343"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="345"/>
+      <c r="R24" s="346"/>
+      <c r="S24" s="346"/>
+      <c r="T24" s="346"/>
+      <c r="U24" s="346"/>
+      <c r="V24" s="346"/>
+      <c r="W24" s="346"/>
+      <c r="X24" s="346"/>
+      <c r="Y24" s="346"/>
+      <c r="Z24" s="346"/>
+      <c r="AA24" s="346"/>
+      <c r="AB24" s="346"/>
+      <c r="AC24" s="346"/>
+      <c r="AD24" s="346"/>
+      <c r="AE24" s="347"/>
+      <c r="AF24" s="342"/>
+      <c r="AG24" s="343"/>
+      <c r="AH24" s="343"/>
+      <c r="AI24" s="344"/>
     </row>
     <row r="25" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="23"/>
-      <c r="B25" s="279"/>
-      <c r="C25" s="280"/>
-      <c r="D25" s="281"/>
-      <c r="E25" s="282"/>
-      <c r="F25" s="283"/>
-      <c r="G25" s="279"/>
-      <c r="H25" s="284"/>
-      <c r="I25" s="280"/>
-      <c r="J25" s="285"/>
-      <c r="K25" s="286"/>
-      <c r="L25" s="286"/>
-      <c r="M25" s="286"/>
-      <c r="N25" s="286"/>
-      <c r="O25" s="286"/>
-      <c r="P25" s="287"/>
-      <c r="Q25" s="288"/>
-      <c r="R25" s="289"/>
-      <c r="S25" s="289"/>
-      <c r="T25" s="289"/>
-      <c r="U25" s="289"/>
-      <c r="V25" s="289"/>
-      <c r="W25" s="289"/>
-      <c r="X25" s="289"/>
-      <c r="Y25" s="289"/>
-      <c r="Z25" s="289"/>
-      <c r="AA25" s="289"/>
-      <c r="AB25" s="289"/>
-      <c r="AC25" s="289"/>
-      <c r="AD25" s="289"/>
-      <c r="AE25" s="290"/>
-      <c r="AF25" s="285"/>
-      <c r="AG25" s="286"/>
-      <c r="AH25" s="286"/>
-      <c r="AI25" s="287"/>
+      <c r="B25" s="336"/>
+      <c r="C25" s="337"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="340"/>
+      <c r="G25" s="336"/>
+      <c r="H25" s="341"/>
+      <c r="I25" s="337"/>
+      <c r="J25" s="342"/>
+      <c r="K25" s="343"/>
+      <c r="L25" s="343"/>
+      <c r="M25" s="343"/>
+      <c r="N25" s="343"/>
+      <c r="O25" s="343"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="345"/>
+      <c r="R25" s="346"/>
+      <c r="S25" s="346"/>
+      <c r="T25" s="346"/>
+      <c r="U25" s="346"/>
+      <c r="V25" s="346"/>
+      <c r="W25" s="346"/>
+      <c r="X25" s="346"/>
+      <c r="Y25" s="346"/>
+      <c r="Z25" s="346"/>
+      <c r="AA25" s="346"/>
+      <c r="AB25" s="346"/>
+      <c r="AC25" s="346"/>
+      <c r="AD25" s="346"/>
+      <c r="AE25" s="347"/>
+      <c r="AF25" s="342"/>
+      <c r="AG25" s="343"/>
+      <c r="AH25" s="343"/>
+      <c r="AI25" s="344"/>
     </row>
     <row r="26" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="23"/>
-      <c r="B26" s="279"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="281"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="283"/>
-      <c r="G26" s="279"/>
-      <c r="H26" s="284"/>
-      <c r="I26" s="280"/>
-      <c r="J26" s="285"/>
-      <c r="K26" s="286"/>
-      <c r="L26" s="286"/>
-      <c r="M26" s="286"/>
-      <c r="N26" s="286"/>
-      <c r="O26" s="286"/>
-      <c r="P26" s="287"/>
-      <c r="Q26" s="288"/>
-      <c r="R26" s="289"/>
-      <c r="S26" s="289"/>
-      <c r="T26" s="289"/>
-      <c r="U26" s="289"/>
-      <c r="V26" s="289"/>
-      <c r="W26" s="289"/>
-      <c r="X26" s="289"/>
-      <c r="Y26" s="289"/>
-      <c r="Z26" s="289"/>
-      <c r="AA26" s="289"/>
-      <c r="AB26" s="289"/>
-      <c r="AC26" s="289"/>
-      <c r="AD26" s="289"/>
-      <c r="AE26" s="290"/>
-      <c r="AF26" s="285"/>
-      <c r="AG26" s="286"/>
-      <c r="AH26" s="286"/>
-      <c r="AI26" s="287"/>
+      <c r="B26" s="336"/>
+      <c r="C26" s="337"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="340"/>
+      <c r="G26" s="336"/>
+      <c r="H26" s="341"/>
+      <c r="I26" s="337"/>
+      <c r="J26" s="342"/>
+      <c r="K26" s="343"/>
+      <c r="L26" s="343"/>
+      <c r="M26" s="343"/>
+      <c r="N26" s="343"/>
+      <c r="O26" s="343"/>
+      <c r="P26" s="344"/>
+      <c r="Q26" s="345"/>
+      <c r="R26" s="346"/>
+      <c r="S26" s="346"/>
+      <c r="T26" s="346"/>
+      <c r="U26" s="346"/>
+      <c r="V26" s="346"/>
+      <c r="W26" s="346"/>
+      <c r="X26" s="346"/>
+      <c r="Y26" s="346"/>
+      <c r="Z26" s="346"/>
+      <c r="AA26" s="346"/>
+      <c r="AB26" s="346"/>
+      <c r="AC26" s="346"/>
+      <c r="AD26" s="346"/>
+      <c r="AE26" s="347"/>
+      <c r="AF26" s="342"/>
+      <c r="AG26" s="343"/>
+      <c r="AH26" s="343"/>
+      <c r="AI26" s="344"/>
     </row>
     <row r="27" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="23"/>
-      <c r="B27" s="279"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="281"/>
-      <c r="E27" s="282"/>
-      <c r="F27" s="283"/>
-      <c r="G27" s="279"/>
-      <c r="H27" s="284"/>
-      <c r="I27" s="280"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="286"/>
-      <c r="L27" s="286"/>
-      <c r="M27" s="286"/>
-      <c r="N27" s="286"/>
-      <c r="O27" s="286"/>
-      <c r="P27" s="287"/>
-      <c r="Q27" s="288"/>
-      <c r="R27" s="289"/>
-      <c r="S27" s="289"/>
-      <c r="T27" s="289"/>
-      <c r="U27" s="289"/>
-      <c r="V27" s="289"/>
-      <c r="W27" s="289"/>
-      <c r="X27" s="289"/>
-      <c r="Y27" s="289"/>
-      <c r="Z27" s="289"/>
-      <c r="AA27" s="289"/>
-      <c r="AB27" s="289"/>
-      <c r="AC27" s="289"/>
-      <c r="AD27" s="289"/>
-      <c r="AE27" s="290"/>
-      <c r="AF27" s="285"/>
-      <c r="AG27" s="286"/>
-      <c r="AH27" s="286"/>
-      <c r="AI27" s="287"/>
+      <c r="B27" s="336"/>
+      <c r="C27" s="337"/>
+      <c r="D27" s="338"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="340"/>
+      <c r="G27" s="336"/>
+      <c r="H27" s="341"/>
+      <c r="I27" s="337"/>
+      <c r="J27" s="342"/>
+      <c r="K27" s="343"/>
+      <c r="L27" s="343"/>
+      <c r="M27" s="343"/>
+      <c r="N27" s="343"/>
+      <c r="O27" s="343"/>
+      <c r="P27" s="344"/>
+      <c r="Q27" s="345"/>
+      <c r="R27" s="346"/>
+      <c r="S27" s="346"/>
+      <c r="T27" s="346"/>
+      <c r="U27" s="346"/>
+      <c r="V27" s="346"/>
+      <c r="W27" s="346"/>
+      <c r="X27" s="346"/>
+      <c r="Y27" s="346"/>
+      <c r="Z27" s="346"/>
+      <c r="AA27" s="346"/>
+      <c r="AB27" s="346"/>
+      <c r="AC27" s="346"/>
+      <c r="AD27" s="346"/>
+      <c r="AE27" s="347"/>
+      <c r="AF27" s="342"/>
+      <c r="AG27" s="343"/>
+      <c r="AH27" s="343"/>
+      <c r="AI27" s="344"/>
     </row>
     <row r="28" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="23"/>
-      <c r="B28" s="279"/>
-      <c r="C28" s="280"/>
-      <c r="D28" s="281"/>
-      <c r="E28" s="282"/>
-      <c r="F28" s="283"/>
-      <c r="G28" s="279"/>
-      <c r="H28" s="284"/>
-      <c r="I28" s="280"/>
-      <c r="J28" s="285"/>
-      <c r="K28" s="286"/>
-      <c r="L28" s="286"/>
-      <c r="M28" s="286"/>
-      <c r="N28" s="286"/>
-      <c r="O28" s="286"/>
-      <c r="P28" s="287"/>
-      <c r="Q28" s="288"/>
-      <c r="R28" s="289"/>
-      <c r="S28" s="289"/>
-      <c r="T28" s="289"/>
-      <c r="U28" s="289"/>
-      <c r="V28" s="289"/>
-      <c r="W28" s="289"/>
-      <c r="X28" s="289"/>
-      <c r="Y28" s="289"/>
-      <c r="Z28" s="289"/>
-      <c r="AA28" s="289"/>
-      <c r="AB28" s="289"/>
-      <c r="AC28" s="289"/>
-      <c r="AD28" s="289"/>
-      <c r="AE28" s="290"/>
-      <c r="AF28" s="285"/>
-      <c r="AG28" s="286"/>
-      <c r="AH28" s="286"/>
-      <c r="AI28" s="287"/>
+      <c r="B28" s="336"/>
+      <c r="C28" s="337"/>
+      <c r="D28" s="338"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="340"/>
+      <c r="G28" s="336"/>
+      <c r="H28" s="341"/>
+      <c r="I28" s="337"/>
+      <c r="J28" s="342"/>
+      <c r="K28" s="343"/>
+      <c r="L28" s="343"/>
+      <c r="M28" s="343"/>
+      <c r="N28" s="343"/>
+      <c r="O28" s="343"/>
+      <c r="P28" s="344"/>
+      <c r="Q28" s="345"/>
+      <c r="R28" s="346"/>
+      <c r="S28" s="346"/>
+      <c r="T28" s="346"/>
+      <c r="U28" s="346"/>
+      <c r="V28" s="346"/>
+      <c r="W28" s="346"/>
+      <c r="X28" s="346"/>
+      <c r="Y28" s="346"/>
+      <c r="Z28" s="346"/>
+      <c r="AA28" s="346"/>
+      <c r="AB28" s="346"/>
+      <c r="AC28" s="346"/>
+      <c r="AD28" s="346"/>
+      <c r="AE28" s="347"/>
+      <c r="AF28" s="342"/>
+      <c r="AG28" s="343"/>
+      <c r="AH28" s="343"/>
+      <c r="AI28" s="344"/>
     </row>
     <row r="29" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="23"/>
-      <c r="B29" s="279"/>
-      <c r="C29" s="280"/>
-      <c r="D29" s="281"/>
-      <c r="E29" s="282"/>
-      <c r="F29" s="283"/>
-      <c r="G29" s="279"/>
-      <c r="H29" s="284"/>
-      <c r="I29" s="280"/>
-      <c r="J29" s="285"/>
-      <c r="K29" s="286"/>
-      <c r="L29" s="286"/>
-      <c r="M29" s="286"/>
-      <c r="N29" s="286"/>
-      <c r="O29" s="286"/>
-      <c r="P29" s="287"/>
-      <c r="Q29" s="288"/>
-      <c r="R29" s="289"/>
-      <c r="S29" s="289"/>
-      <c r="T29" s="289"/>
-      <c r="U29" s="289"/>
-      <c r="V29" s="289"/>
-      <c r="W29" s="289"/>
-      <c r="X29" s="289"/>
-      <c r="Y29" s="289"/>
-      <c r="Z29" s="289"/>
-      <c r="AA29" s="289"/>
-      <c r="AB29" s="289"/>
-      <c r="AC29" s="289"/>
-      <c r="AD29" s="289"/>
-      <c r="AE29" s="290"/>
-      <c r="AF29" s="285"/>
-      <c r="AG29" s="286"/>
-      <c r="AH29" s="286"/>
-      <c r="AI29" s="287"/>
+      <c r="B29" s="336"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="340"/>
+      <c r="G29" s="336"/>
+      <c r="H29" s="341"/>
+      <c r="I29" s="337"/>
+      <c r="J29" s="342"/>
+      <c r="K29" s="343"/>
+      <c r="L29" s="343"/>
+      <c r="M29" s="343"/>
+      <c r="N29" s="343"/>
+      <c r="O29" s="343"/>
+      <c r="P29" s="344"/>
+      <c r="Q29" s="345"/>
+      <c r="R29" s="346"/>
+      <c r="S29" s="346"/>
+      <c r="T29" s="346"/>
+      <c r="U29" s="346"/>
+      <c r="V29" s="346"/>
+      <c r="W29" s="346"/>
+      <c r="X29" s="346"/>
+      <c r="Y29" s="346"/>
+      <c r="Z29" s="346"/>
+      <c r="AA29" s="346"/>
+      <c r="AB29" s="346"/>
+      <c r="AC29" s="346"/>
+      <c r="AD29" s="346"/>
+      <c r="AE29" s="347"/>
+      <c r="AF29" s="342"/>
+      <c r="AG29" s="343"/>
+      <c r="AH29" s="343"/>
+      <c r="AI29" s="344"/>
     </row>
     <row r="30" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="23"/>
-      <c r="B30" s="279"/>
-      <c r="C30" s="280"/>
-      <c r="D30" s="281"/>
-      <c r="E30" s="282"/>
-      <c r="F30" s="283"/>
-      <c r="G30" s="279"/>
-      <c r="H30" s="284"/>
-      <c r="I30" s="280"/>
-      <c r="J30" s="285"/>
-      <c r="K30" s="286"/>
-      <c r="L30" s="286"/>
-      <c r="M30" s="286"/>
-      <c r="N30" s="286"/>
-      <c r="O30" s="286"/>
-      <c r="P30" s="287"/>
-      <c r="Q30" s="288"/>
-      <c r="R30" s="289"/>
-      <c r="S30" s="289"/>
-      <c r="T30" s="289"/>
-      <c r="U30" s="289"/>
-      <c r="V30" s="289"/>
-      <c r="W30" s="289"/>
-      <c r="X30" s="289"/>
-      <c r="Y30" s="289"/>
-      <c r="Z30" s="289"/>
-      <c r="AA30" s="289"/>
-      <c r="AB30" s="289"/>
-      <c r="AC30" s="289"/>
-      <c r="AD30" s="289"/>
-      <c r="AE30" s="290"/>
-      <c r="AF30" s="285"/>
-      <c r="AG30" s="286"/>
-      <c r="AH30" s="286"/>
-      <c r="AI30" s="287"/>
+      <c r="B30" s="336"/>
+      <c r="C30" s="337"/>
+      <c r="D30" s="338"/>
+      <c r="E30" s="339"/>
+      <c r="F30" s="340"/>
+      <c r="G30" s="336"/>
+      <c r="H30" s="341"/>
+      <c r="I30" s="337"/>
+      <c r="J30" s="342"/>
+      <c r="K30" s="343"/>
+      <c r="L30" s="343"/>
+      <c r="M30" s="343"/>
+      <c r="N30" s="343"/>
+      <c r="O30" s="343"/>
+      <c r="P30" s="344"/>
+      <c r="Q30" s="345"/>
+      <c r="R30" s="346"/>
+      <c r="S30" s="346"/>
+      <c r="T30" s="346"/>
+      <c r="U30" s="346"/>
+      <c r="V30" s="346"/>
+      <c r="W30" s="346"/>
+      <c r="X30" s="346"/>
+      <c r="Y30" s="346"/>
+      <c r="Z30" s="346"/>
+      <c r="AA30" s="346"/>
+      <c r="AB30" s="346"/>
+      <c r="AC30" s="346"/>
+      <c r="AD30" s="346"/>
+      <c r="AE30" s="347"/>
+      <c r="AF30" s="342"/>
+      <c r="AG30" s="343"/>
+      <c r="AH30" s="343"/>
+      <c r="AI30" s="344"/>
     </row>
     <row r="31" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="23"/>
-      <c r="B31" s="279"/>
-      <c r="C31" s="280"/>
-      <c r="D31" s="281"/>
-      <c r="E31" s="282"/>
-      <c r="F31" s="283"/>
-      <c r="G31" s="279"/>
-      <c r="H31" s="284"/>
-      <c r="I31" s="280"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="286"/>
-      <c r="L31" s="286"/>
-      <c r="M31" s="286"/>
-      <c r="N31" s="286"/>
-      <c r="O31" s="286"/>
-      <c r="P31" s="287"/>
-      <c r="Q31" s="288"/>
-      <c r="R31" s="289"/>
-      <c r="S31" s="289"/>
-      <c r="T31" s="289"/>
-      <c r="U31" s="289"/>
-      <c r="V31" s="289"/>
-      <c r="W31" s="289"/>
-      <c r="X31" s="289"/>
-      <c r="Y31" s="289"/>
-      <c r="Z31" s="289"/>
-      <c r="AA31" s="289"/>
-      <c r="AB31" s="289"/>
-      <c r="AC31" s="289"/>
-      <c r="AD31" s="289"/>
-      <c r="AE31" s="290"/>
-      <c r="AF31" s="285"/>
-      <c r="AG31" s="286"/>
-      <c r="AH31" s="286"/>
-      <c r="AI31" s="287"/>
+      <c r="B31" s="336"/>
+      <c r="C31" s="337"/>
+      <c r="D31" s="338"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="340"/>
+      <c r="G31" s="336"/>
+      <c r="H31" s="341"/>
+      <c r="I31" s="337"/>
+      <c r="J31" s="342"/>
+      <c r="K31" s="343"/>
+      <c r="L31" s="343"/>
+      <c r="M31" s="343"/>
+      <c r="N31" s="343"/>
+      <c r="O31" s="343"/>
+      <c r="P31" s="344"/>
+      <c r="Q31" s="345"/>
+      <c r="R31" s="346"/>
+      <c r="S31" s="346"/>
+      <c r="T31" s="346"/>
+      <c r="U31" s="346"/>
+      <c r="V31" s="346"/>
+      <c r="W31" s="346"/>
+      <c r="X31" s="346"/>
+      <c r="Y31" s="346"/>
+      <c r="Z31" s="346"/>
+      <c r="AA31" s="346"/>
+      <c r="AB31" s="346"/>
+      <c r="AC31" s="346"/>
+      <c r="AD31" s="346"/>
+      <c r="AE31" s="347"/>
+      <c r="AF31" s="342"/>
+      <c r="AG31" s="343"/>
+      <c r="AH31" s="343"/>
+      <c r="AI31" s="344"/>
     </row>
     <row r="32" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="23"/>
-      <c r="B32" s="279"/>
-      <c r="C32" s="280"/>
-      <c r="D32" s="281"/>
-      <c r="E32" s="282"/>
-      <c r="F32" s="283"/>
-      <c r="G32" s="279"/>
-      <c r="H32" s="284"/>
-      <c r="I32" s="280"/>
-      <c r="J32" s="285"/>
-      <c r="K32" s="291"/>
-      <c r="L32" s="286"/>
-      <c r="M32" s="286"/>
-      <c r="N32" s="286"/>
-      <c r="O32" s="286"/>
-      <c r="P32" s="287"/>
-      <c r="Q32" s="288"/>
-      <c r="R32" s="289"/>
-      <c r="S32" s="289"/>
-      <c r="T32" s="289"/>
-      <c r="U32" s="289"/>
-      <c r="V32" s="289"/>
-      <c r="W32" s="289"/>
-      <c r="X32" s="289"/>
-      <c r="Y32" s="289"/>
-      <c r="Z32" s="289"/>
-      <c r="AA32" s="289"/>
-      <c r="AB32" s="289"/>
-      <c r="AC32" s="289"/>
-      <c r="AD32" s="289"/>
-      <c r="AE32" s="290"/>
-      <c r="AF32" s="285"/>
-      <c r="AG32" s="286"/>
-      <c r="AH32" s="286"/>
-      <c r="AI32" s="287"/>
+      <c r="B32" s="336"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="340"/>
+      <c r="G32" s="336"/>
+      <c r="H32" s="341"/>
+      <c r="I32" s="337"/>
+      <c r="J32" s="342"/>
+      <c r="K32" s="348"/>
+      <c r="L32" s="343"/>
+      <c r="M32" s="343"/>
+      <c r="N32" s="343"/>
+      <c r="O32" s="343"/>
+      <c r="P32" s="344"/>
+      <c r="Q32" s="345"/>
+      <c r="R32" s="346"/>
+      <c r="S32" s="346"/>
+      <c r="T32" s="346"/>
+      <c r="U32" s="346"/>
+      <c r="V32" s="346"/>
+      <c r="W32" s="346"/>
+      <c r="X32" s="346"/>
+      <c r="Y32" s="346"/>
+      <c r="Z32" s="346"/>
+      <c r="AA32" s="346"/>
+      <c r="AB32" s="346"/>
+      <c r="AC32" s="346"/>
+      <c r="AD32" s="346"/>
+      <c r="AE32" s="347"/>
+      <c r="AF32" s="342"/>
+      <c r="AG32" s="343"/>
+      <c r="AH32" s="343"/>
+      <c r="AI32" s="344"/>
     </row>
     <row r="33" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="23"/>
-      <c r="B33" s="279"/>
-      <c r="C33" s="280"/>
-      <c r="D33" s="281"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="283"/>
-      <c r="G33" s="279"/>
-      <c r="H33" s="284"/>
-      <c r="I33" s="280"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="286"/>
-      <c r="L33" s="286"/>
-      <c r="M33" s="286"/>
-      <c r="N33" s="286"/>
-      <c r="O33" s="286"/>
-      <c r="P33" s="287"/>
-      <c r="Q33" s="288"/>
-      <c r="R33" s="289"/>
-      <c r="S33" s="289"/>
-      <c r="T33" s="289"/>
-      <c r="U33" s="289"/>
-      <c r="V33" s="289"/>
-      <c r="W33" s="289"/>
-      <c r="X33" s="289"/>
-      <c r="Y33" s="289"/>
-      <c r="Z33" s="289"/>
-      <c r="AA33" s="289"/>
-      <c r="AB33" s="289"/>
-      <c r="AC33" s="289"/>
-      <c r="AD33" s="289"/>
-      <c r="AE33" s="290"/>
-      <c r="AF33" s="285"/>
-      <c r="AG33" s="286"/>
-      <c r="AH33" s="286"/>
-      <c r="AI33" s="287"/>
+      <c r="B33" s="336"/>
+      <c r="C33" s="337"/>
+      <c r="D33" s="338"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="340"/>
+      <c r="G33" s="336"/>
+      <c r="H33" s="341"/>
+      <c r="I33" s="337"/>
+      <c r="J33" s="342"/>
+      <c r="K33" s="343"/>
+      <c r="L33" s="343"/>
+      <c r="M33" s="343"/>
+      <c r="N33" s="343"/>
+      <c r="O33" s="343"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="345"/>
+      <c r="R33" s="346"/>
+      <c r="S33" s="346"/>
+      <c r="T33" s="346"/>
+      <c r="U33" s="346"/>
+      <c r="V33" s="346"/>
+      <c r="W33" s="346"/>
+      <c r="X33" s="346"/>
+      <c r="Y33" s="346"/>
+      <c r="Z33" s="346"/>
+      <c r="AA33" s="346"/>
+      <c r="AB33" s="346"/>
+      <c r="AC33" s="346"/>
+      <c r="AD33" s="346"/>
+      <c r="AE33" s="347"/>
+      <c r="AF33" s="342"/>
+      <c r="AG33" s="343"/>
+      <c r="AH33" s="343"/>
+      <c r="AI33" s="344"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -18463,161 +18621,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926A583D-0B4D-4C85-9D2C-C288893404A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE1025E-AC5D-4389-8E8D-1E470504FDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12800,108 +12800,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -13008,6 +12906,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -17186,57 +17186,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="285" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="321"/>
-      <c r="E1" s="322" t="s">
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="287"/>
+      <c r="E1" s="288" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="323"/>
-      <c r="G1" s="323"/>
-      <c r="H1" s="323"/>
-      <c r="I1" s="323"/>
-      <c r="J1" s="323"/>
-      <c r="K1" s="323"/>
-      <c r="L1" s="323"/>
-      <c r="M1" s="323"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="328" t="s">
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
+      <c r="M1" s="289"/>
+      <c r="N1" s="290"/>
+      <c r="O1" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="329"/>
-      <c r="Q1" s="329"/>
-      <c r="R1" s="330"/>
-      <c r="S1" s="337" t="s">
+      <c r="P1" s="295"/>
+      <c r="Q1" s="295"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="303" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="338"/>
-      <c r="U1" s="338"/>
-      <c r="V1" s="338"/>
-      <c r="W1" s="338"/>
-      <c r="X1" s="338"/>
-      <c r="Y1" s="338"/>
-      <c r="Z1" s="339"/>
-      <c r="AA1" s="319" t="s">
+      <c r="T1" s="304"/>
+      <c r="U1" s="304"/>
+      <c r="V1" s="304"/>
+      <c r="W1" s="304"/>
+      <c r="X1" s="304"/>
+      <c r="Y1" s="304"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="AB1" s="321"/>
-      <c r="AC1" s="346" t="str">
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="312" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="347"/>
-      <c r="AE1" s="347"/>
-      <c r="AF1" s="348"/>
-      <c r="AG1" s="313">
+      <c r="AD1" s="313"/>
+      <c r="AE1" s="313"/>
+      <c r="AF1" s="314"/>
+      <c r="AG1" s="279">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="314"/>
-      <c r="AI1" s="315"/>
+      <c r="AH1" s="280"/>
+      <c r="AI1" s="281"/>
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
       <c r="AL1" s="13"/>
@@ -17244,53 +17244,53 @@
       <c r="AN1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="319" t="s">
+      <c r="A2" s="285" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="320"/>
-      <c r="C2" s="320"/>
-      <c r="D2" s="321"/>
-      <c r="E2" s="322" t="s">
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="288" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="323"/>
-      <c r="G2" s="323"/>
-      <c r="H2" s="323"/>
-      <c r="I2" s="323"/>
-      <c r="J2" s="323"/>
-      <c r="K2" s="323"/>
-      <c r="L2" s="323"/>
-      <c r="M2" s="323"/>
-      <c r="N2" s="324"/>
-      <c r="O2" s="331"/>
-      <c r="P2" s="332"/>
-      <c r="Q2" s="332"/>
-      <c r="R2" s="333"/>
-      <c r="S2" s="340"/>
-      <c r="T2" s="341"/>
-      <c r="U2" s="341"/>
-      <c r="V2" s="341"/>
-      <c r="W2" s="341"/>
-      <c r="X2" s="341"/>
-      <c r="Y2" s="341"/>
-      <c r="Z2" s="342"/>
-      <c r="AA2" s="319" t="s">
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="289"/>
+      <c r="I2" s="289"/>
+      <c r="J2" s="289"/>
+      <c r="K2" s="289"/>
+      <c r="L2" s="289"/>
+      <c r="M2" s="289"/>
+      <c r="N2" s="290"/>
+      <c r="O2" s="297"/>
+      <c r="P2" s="298"/>
+      <c r="Q2" s="298"/>
+      <c r="R2" s="299"/>
+      <c r="S2" s="306"/>
+      <c r="T2" s="307"/>
+      <c r="U2" s="307"/>
+      <c r="V2" s="307"/>
+      <c r="W2" s="307"/>
+      <c r="X2" s="307"/>
+      <c r="Y2" s="307"/>
+      <c r="Z2" s="308"/>
+      <c r="AA2" s="285" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="321"/>
-      <c r="AC2" s="325" t="str">
+      <c r="AB2" s="287"/>
+      <c r="AC2" s="291" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="326"/>
-      <c r="AE2" s="326"/>
-      <c r="AF2" s="327"/>
-      <c r="AG2" s="313">
+      <c r="AD2" s="292"/>
+      <c r="AE2" s="292"/>
+      <c r="AF2" s="293"/>
+      <c r="AG2" s="279">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="314"/>
-      <c r="AI2" s="315"/>
+      <c r="AH2" s="280"/>
+      <c r="AI2" s="281"/>
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
       <c r="AL2" s="13"/>
@@ -17298,45 +17298,45 @@
       <c r="AN2" s="13"/>
     </row>
     <row r="3" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="319" t="s">
+      <c r="A3" s="285" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="320"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="322" t="s">
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="287"/>
+      <c r="E3" s="288" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="323"/>
-      <c r="G3" s="323"/>
-      <c r="H3" s="323"/>
-      <c r="I3" s="323"/>
-      <c r="J3" s="323"/>
-      <c r="K3" s="323"/>
-      <c r="L3" s="323"/>
-      <c r="M3" s="323"/>
-      <c r="N3" s="324"/>
-      <c r="O3" s="334"/>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="343"/>
-      <c r="T3" s="344"/>
-      <c r="U3" s="344"/>
-      <c r="V3" s="344"/>
-      <c r="W3" s="344"/>
-      <c r="X3" s="344"/>
-      <c r="Y3" s="344"/>
-      <c r="Z3" s="345"/>
-      <c r="AA3" s="319"/>
-      <c r="AB3" s="321"/>
-      <c r="AC3" s="346"/>
-      <c r="AD3" s="347"/>
-      <c r="AE3" s="347"/>
-      <c r="AF3" s="348"/>
-      <c r="AG3" s="313"/>
-      <c r="AH3" s="314"/>
-      <c r="AI3" s="315"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="289"/>
+      <c r="I3" s="289"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
+      <c r="M3" s="289"/>
+      <c r="N3" s="290"/>
+      <c r="O3" s="300"/>
+      <c r="P3" s="301"/>
+      <c r="Q3" s="301"/>
+      <c r="R3" s="302"/>
+      <c r="S3" s="309"/>
+      <c r="T3" s="310"/>
+      <c r="U3" s="310"/>
+      <c r="V3" s="310"/>
+      <c r="W3" s="310"/>
+      <c r="X3" s="310"/>
+      <c r="Y3" s="310"/>
+      <c r="Z3" s="311"/>
+      <c r="AA3" s="285"/>
+      <c r="AB3" s="287"/>
+      <c r="AC3" s="312"/>
+      <c r="AD3" s="313"/>
+      <c r="AE3" s="313"/>
+      <c r="AF3" s="314"/>
+      <c r="AG3" s="279"/>
+      <c r="AH3" s="280"/>
+      <c r="AI3" s="281"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
@@ -17373,97 +17373,97 @@
       <c r="A7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="316" t="s">
+      <c r="B7" s="282" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="317"/>
-      <c r="D7" s="316" t="s">
+      <c r="C7" s="283"/>
+      <c r="D7" s="282" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="318"/>
-      <c r="F7" s="317"/>
-      <c r="G7" s="316" t="s">
+      <c r="E7" s="284"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="282" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="318"/>
-      <c r="I7" s="317"/>
-      <c r="J7" s="316" t="s">
+      <c r="H7" s="284"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="282" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="318"/>
-      <c r="L7" s="318"/>
-      <c r="M7" s="318"/>
-      <c r="N7" s="318"/>
-      <c r="O7" s="318"/>
-      <c r="P7" s="317"/>
-      <c r="Q7" s="316" t="s">
+      <c r="K7" s="284"/>
+      <c r="L7" s="284"/>
+      <c r="M7" s="284"/>
+      <c r="N7" s="284"/>
+      <c r="O7" s="284"/>
+      <c r="P7" s="283"/>
+      <c r="Q7" s="282" t="s">
         <v>69</v>
       </c>
-      <c r="R7" s="318"/>
-      <c r="S7" s="318"/>
-      <c r="T7" s="318"/>
-      <c r="U7" s="318"/>
-      <c r="V7" s="318"/>
-      <c r="W7" s="318"/>
-      <c r="X7" s="318"/>
-      <c r="Y7" s="318"/>
-      <c r="Z7" s="318"/>
-      <c r="AA7" s="318"/>
-      <c r="AB7" s="318"/>
-      <c r="AC7" s="318"/>
-      <c r="AD7" s="318"/>
-      <c r="AE7" s="317"/>
-      <c r="AF7" s="316" t="s">
+      <c r="R7" s="284"/>
+      <c r="S7" s="284"/>
+      <c r="T7" s="284"/>
+      <c r="U7" s="284"/>
+      <c r="V7" s="284"/>
+      <c r="W7" s="284"/>
+      <c r="X7" s="284"/>
+      <c r="Y7" s="284"/>
+      <c r="Z7" s="284"/>
+      <c r="AA7" s="284"/>
+      <c r="AB7" s="284"/>
+      <c r="AC7" s="284"/>
+      <c r="AD7" s="284"/>
+      <c r="AE7" s="283"/>
+      <c r="AF7" s="282" t="s">
         <v>70</v>
       </c>
-      <c r="AG7" s="318"/>
-      <c r="AH7" s="318"/>
-      <c r="AI7" s="317"/>
+      <c r="AG7" s="284"/>
+      <c r="AH7" s="284"/>
+      <c r="AI7" s="283"/>
     </row>
     <row r="8" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="26">
         <v>1</v>
       </c>
-      <c r="B8" s="304" t="s">
+      <c r="B8" s="327" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="305"/>
-      <c r="D8" s="306">
+      <c r="C8" s="328"/>
+      <c r="D8" s="329">
         <v>43336</v>
       </c>
-      <c r="E8" s="307"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="304" t="s">
+      <c r="E8" s="330"/>
+      <c r="F8" s="331"/>
+      <c r="G8" s="327" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="309"/>
-      <c r="I8" s="305"/>
-      <c r="J8" s="310" t="s">
+      <c r="H8" s="332"/>
+      <c r="I8" s="328"/>
+      <c r="J8" s="333" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="311"/>
-      <c r="L8" s="311"/>
-      <c r="M8" s="311"/>
-      <c r="N8" s="311"/>
-      <c r="O8" s="311"/>
-      <c r="P8" s="312"/>
-      <c r="Q8" s="310" t="s">
+      <c r="K8" s="334"/>
+      <c r="L8" s="334"/>
+      <c r="M8" s="334"/>
+      <c r="N8" s="334"/>
+      <c r="O8" s="334"/>
+      <c r="P8" s="335"/>
+      <c r="Q8" s="333" t="s">
         <v>78</v>
       </c>
-      <c r="R8" s="311"/>
-      <c r="S8" s="311"/>
-      <c r="T8" s="311"/>
-      <c r="U8" s="311"/>
-      <c r="V8" s="311"/>
-      <c r="W8" s="311"/>
-      <c r="X8" s="311"/>
-      <c r="Y8" s="311"/>
-      <c r="Z8" s="311"/>
-      <c r="AA8" s="311"/>
-      <c r="AB8" s="311"/>
-      <c r="AC8" s="311"/>
-      <c r="AD8" s="311"/>
-      <c r="AE8" s="312"/>
+      <c r="R8" s="334"/>
+      <c r="S8" s="334"/>
+      <c r="T8" s="334"/>
+      <c r="U8" s="334"/>
+      <c r="V8" s="334"/>
+      <c r="W8" s="334"/>
+      <c r="X8" s="334"/>
+      <c r="Y8" s="334"/>
+      <c r="Z8" s="334"/>
+      <c r="AA8" s="334"/>
+      <c r="AB8" s="334"/>
+      <c r="AC8" s="334"/>
+      <c r="AD8" s="334"/>
+      <c r="AE8" s="335"/>
       <c r="AF8" s="27" t="s">
         <v>79</v>
       </c>
@@ -17475,946 +17475,1101 @@
       <c r="A9" s="26">
         <v>2</v>
       </c>
-      <c r="B9" s="292" t="s">
+      <c r="B9" s="315" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="293"/>
-      <c r="D9" s="294">
+      <c r="C9" s="316"/>
+      <c r="D9" s="317">
         <v>44852</v>
       </c>
-      <c r="E9" s="295"/>
-      <c r="F9" s="296"/>
-      <c r="G9" s="294" t="s">
+      <c r="E9" s="318"/>
+      <c r="F9" s="319"/>
+      <c r="G9" s="317" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="297"/>
-      <c r="I9" s="293"/>
-      <c r="J9" s="298" t="s">
+      <c r="H9" s="320"/>
+      <c r="I9" s="316"/>
+      <c r="J9" s="321" t="s">
         <v>740</v>
       </c>
-      <c r="K9" s="299"/>
-      <c r="L9" s="299"/>
-      <c r="M9" s="299"/>
-      <c r="N9" s="299"/>
-      <c r="O9" s="299"/>
-      <c r="P9" s="300"/>
-      <c r="Q9" s="298" t="s">
+      <c r="K9" s="322"/>
+      <c r="L9" s="322"/>
+      <c r="M9" s="322"/>
+      <c r="N9" s="322"/>
+      <c r="O9" s="322"/>
+      <c r="P9" s="323"/>
+      <c r="Q9" s="321" t="s">
         <v>741</v>
       </c>
-      <c r="R9" s="301"/>
-      <c r="S9" s="301"/>
-      <c r="T9" s="301"/>
-      <c r="U9" s="301"/>
-      <c r="V9" s="301"/>
-      <c r="W9" s="301"/>
-      <c r="X9" s="301"/>
-      <c r="Y9" s="301"/>
-      <c r="Z9" s="301"/>
-      <c r="AA9" s="301"/>
-      <c r="AB9" s="301"/>
-      <c r="AC9" s="301"/>
-      <c r="AD9" s="301"/>
-      <c r="AE9" s="302"/>
-      <c r="AF9" s="303" t="s">
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="324"/>
+      <c r="V9" s="324"/>
+      <c r="W9" s="324"/>
+      <c r="X9" s="324"/>
+      <c r="Y9" s="324"/>
+      <c r="Z9" s="324"/>
+      <c r="AA9" s="324"/>
+      <c r="AB9" s="324"/>
+      <c r="AC9" s="324"/>
+      <c r="AD9" s="324"/>
+      <c r="AE9" s="325"/>
+      <c r="AF9" s="326" t="s">
         <v>79</v>
       </c>
-      <c r="AG9" s="299"/>
-      <c r="AH9" s="299"/>
-      <c r="AI9" s="300"/>
+      <c r="AG9" s="322"/>
+      <c r="AH9" s="322"/>
+      <c r="AI9" s="323"/>
     </row>
     <row r="10" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="279"/>
-      <c r="C10" s="280"/>
-      <c r="D10" s="281"/>
-      <c r="E10" s="282"/>
-      <c r="F10" s="283"/>
-      <c r="G10" s="279"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="285"/>
-      <c r="K10" s="286"/>
-      <c r="L10" s="286"/>
-      <c r="M10" s="286"/>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="287"/>
-      <c r="Q10" s="288"/>
-      <c r="R10" s="289"/>
-      <c r="S10" s="289"/>
-      <c r="T10" s="289"/>
-      <c r="U10" s="289"/>
-      <c r="V10" s="289"/>
-      <c r="W10" s="289"/>
-      <c r="X10" s="289"/>
-      <c r="Y10" s="289"/>
-      <c r="Z10" s="289"/>
-      <c r="AA10" s="289"/>
-      <c r="AB10" s="289"/>
-      <c r="AC10" s="289"/>
-      <c r="AD10" s="289"/>
-      <c r="AE10" s="290"/>
-      <c r="AF10" s="285"/>
-      <c r="AG10" s="286"/>
-      <c r="AH10" s="286"/>
-      <c r="AI10" s="287"/>
+      <c r="B10" s="336"/>
+      <c r="C10" s="337"/>
+      <c r="D10" s="338"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="340"/>
+      <c r="G10" s="336"/>
+      <c r="H10" s="341"/>
+      <c r="I10" s="337"/>
+      <c r="J10" s="342"/>
+      <c r="K10" s="343"/>
+      <c r="L10" s="343"/>
+      <c r="M10" s="343"/>
+      <c r="N10" s="343"/>
+      <c r="O10" s="343"/>
+      <c r="P10" s="344"/>
+      <c r="Q10" s="345"/>
+      <c r="R10" s="346"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="346"/>
+      <c r="U10" s="346"/>
+      <c r="V10" s="346"/>
+      <c r="W10" s="346"/>
+      <c r="X10" s="346"/>
+      <c r="Y10" s="346"/>
+      <c r="Z10" s="346"/>
+      <c r="AA10" s="346"/>
+      <c r="AB10" s="346"/>
+      <c r="AC10" s="346"/>
+      <c r="AD10" s="346"/>
+      <c r="AE10" s="347"/>
+      <c r="AF10" s="342"/>
+      <c r="AG10" s="343"/>
+      <c r="AH10" s="343"/>
+      <c r="AI10" s="344"/>
     </row>
     <row r="11" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="23"/>
-      <c r="B11" s="279"/>
-      <c r="C11" s="280"/>
-      <c r="D11" s="281"/>
-      <c r="E11" s="282"/>
-      <c r="F11" s="283"/>
-      <c r="G11" s="279"/>
-      <c r="H11" s="284"/>
-      <c r="I11" s="280"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="287"/>
-      <c r="Q11" s="288"/>
-      <c r="R11" s="289"/>
-      <c r="S11" s="289"/>
-      <c r="T11" s="289"/>
-      <c r="U11" s="289"/>
-      <c r="V11" s="289"/>
-      <c r="W11" s="289"/>
-      <c r="X11" s="289"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="289"/>
-      <c r="AD11" s="289"/>
-      <c r="AE11" s="290"/>
-      <c r="AF11" s="285"/>
-      <c r="AG11" s="286"/>
-      <c r="AH11" s="286"/>
-      <c r="AI11" s="287"/>
+      <c r="B11" s="336"/>
+      <c r="C11" s="337"/>
+      <c r="D11" s="338"/>
+      <c r="E11" s="339"/>
+      <c r="F11" s="340"/>
+      <c r="G11" s="336"/>
+      <c r="H11" s="341"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="343"/>
+      <c r="L11" s="343"/>
+      <c r="M11" s="343"/>
+      <c r="N11" s="343"/>
+      <c r="O11" s="343"/>
+      <c r="P11" s="344"/>
+      <c r="Q11" s="345"/>
+      <c r="R11" s="346"/>
+      <c r="S11" s="346"/>
+      <c r="T11" s="346"/>
+      <c r="U11" s="346"/>
+      <c r="V11" s="346"/>
+      <c r="W11" s="346"/>
+      <c r="X11" s="346"/>
+      <c r="Y11" s="346"/>
+      <c r="Z11" s="346"/>
+      <c r="AA11" s="346"/>
+      <c r="AB11" s="346"/>
+      <c r="AC11" s="346"/>
+      <c r="AD11" s="346"/>
+      <c r="AE11" s="347"/>
+      <c r="AF11" s="342"/>
+      <c r="AG11" s="343"/>
+      <c r="AH11" s="343"/>
+      <c r="AI11" s="344"/>
     </row>
     <row r="12" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="23"/>
-      <c r="B12" s="279"/>
-      <c r="C12" s="280"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="282"/>
-      <c r="F12" s="283"/>
-      <c r="G12" s="279"/>
-      <c r="H12" s="284"/>
-      <c r="I12" s="280"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="286"/>
-      <c r="L12" s="286"/>
-      <c r="M12" s="286"/>
-      <c r="N12" s="286"/>
-      <c r="O12" s="286"/>
-      <c r="P12" s="287"/>
-      <c r="Q12" s="288"/>
-      <c r="R12" s="289"/>
-      <c r="S12" s="289"/>
-      <c r="T12" s="289"/>
-      <c r="U12" s="289"/>
-      <c r="V12" s="289"/>
-      <c r="W12" s="289"/>
-      <c r="X12" s="289"/>
-      <c r="Y12" s="289"/>
-      <c r="Z12" s="289"/>
-      <c r="AA12" s="289"/>
-      <c r="AB12" s="289"/>
-      <c r="AC12" s="289"/>
-      <c r="AD12" s="289"/>
-      <c r="AE12" s="290"/>
-      <c r="AF12" s="285"/>
-      <c r="AG12" s="286"/>
-      <c r="AH12" s="286"/>
-      <c r="AI12" s="287"/>
+      <c r="B12" s="336"/>
+      <c r="C12" s="337"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="340"/>
+      <c r="G12" s="336"/>
+      <c r="H12" s="341"/>
+      <c r="I12" s="337"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="343"/>
+      <c r="L12" s="343"/>
+      <c r="M12" s="343"/>
+      <c r="N12" s="343"/>
+      <c r="O12" s="343"/>
+      <c r="P12" s="344"/>
+      <c r="Q12" s="345"/>
+      <c r="R12" s="346"/>
+      <c r="S12" s="346"/>
+      <c r="T12" s="346"/>
+      <c r="U12" s="346"/>
+      <c r="V12" s="346"/>
+      <c r="W12" s="346"/>
+      <c r="X12" s="346"/>
+      <c r="Y12" s="346"/>
+      <c r="Z12" s="346"/>
+      <c r="AA12" s="346"/>
+      <c r="AB12" s="346"/>
+      <c r="AC12" s="346"/>
+      <c r="AD12" s="346"/>
+      <c r="AE12" s="347"/>
+      <c r="AF12" s="342"/>
+      <c r="AG12" s="343"/>
+      <c r="AH12" s="343"/>
+      <c r="AI12" s="344"/>
     </row>
     <row r="13" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="23"/>
-      <c r="B13" s="279"/>
-      <c r="C13" s="280"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="282"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="279"/>
-      <c r="H13" s="284"/>
-      <c r="I13" s="280"/>
-      <c r="J13" s="285"/>
-      <c r="K13" s="286"/>
-      <c r="L13" s="286"/>
-      <c r="M13" s="286"/>
-      <c r="N13" s="286"/>
-      <c r="O13" s="286"/>
-      <c r="P13" s="287"/>
-      <c r="Q13" s="288"/>
-      <c r="R13" s="289"/>
-      <c r="S13" s="289"/>
-      <c r="T13" s="289"/>
-      <c r="U13" s="289"/>
-      <c r="V13" s="289"/>
-      <c r="W13" s="289"/>
-      <c r="X13" s="289"/>
-      <c r="Y13" s="289"/>
-      <c r="Z13" s="289"/>
-      <c r="AA13" s="289"/>
-      <c r="AB13" s="289"/>
-      <c r="AC13" s="289"/>
-      <c r="AD13" s="289"/>
-      <c r="AE13" s="290"/>
-      <c r="AF13" s="285"/>
-      <c r="AG13" s="286"/>
-      <c r="AH13" s="286"/>
-      <c r="AI13" s="287"/>
+      <c r="B13" s="336"/>
+      <c r="C13" s="337"/>
+      <c r="D13" s="338"/>
+      <c r="E13" s="339"/>
+      <c r="F13" s="340"/>
+      <c r="G13" s="336"/>
+      <c r="H13" s="341"/>
+      <c r="I13" s="337"/>
+      <c r="J13" s="342"/>
+      <c r="K13" s="343"/>
+      <c r="L13" s="343"/>
+      <c r="M13" s="343"/>
+      <c r="N13" s="343"/>
+      <c r="O13" s="343"/>
+      <c r="P13" s="344"/>
+      <c r="Q13" s="345"/>
+      <c r="R13" s="346"/>
+      <c r="S13" s="346"/>
+      <c r="T13" s="346"/>
+      <c r="U13" s="346"/>
+      <c r="V13" s="346"/>
+      <c r="W13" s="346"/>
+      <c r="X13" s="346"/>
+      <c r="Y13" s="346"/>
+      <c r="Z13" s="346"/>
+      <c r="AA13" s="346"/>
+      <c r="AB13" s="346"/>
+      <c r="AC13" s="346"/>
+      <c r="AD13" s="346"/>
+      <c r="AE13" s="347"/>
+      <c r="AF13" s="342"/>
+      <c r="AG13" s="343"/>
+      <c r="AH13" s="343"/>
+      <c r="AI13" s="344"/>
     </row>
     <row r="14" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="23"/>
-      <c r="B14" s="279"/>
-      <c r="C14" s="280"/>
-      <c r="D14" s="281"/>
-      <c r="E14" s="282"/>
-      <c r="F14" s="283"/>
-      <c r="G14" s="279"/>
-      <c r="H14" s="284"/>
-      <c r="I14" s="280"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="286"/>
-      <c r="L14" s="286"/>
-      <c r="M14" s="286"/>
-      <c r="N14" s="286"/>
-      <c r="O14" s="286"/>
-      <c r="P14" s="287"/>
-      <c r="Q14" s="288"/>
-      <c r="R14" s="289"/>
-      <c r="S14" s="289"/>
-      <c r="T14" s="289"/>
-      <c r="U14" s="289"/>
-      <c r="V14" s="289"/>
-      <c r="W14" s="289"/>
-      <c r="X14" s="289"/>
-      <c r="Y14" s="289"/>
-      <c r="Z14" s="289"/>
-      <c r="AA14" s="289"/>
-      <c r="AB14" s="289"/>
-      <c r="AC14" s="289"/>
-      <c r="AD14" s="289"/>
-      <c r="AE14" s="290"/>
-      <c r="AF14" s="285"/>
-      <c r="AG14" s="286"/>
-      <c r="AH14" s="286"/>
-      <c r="AI14" s="287"/>
+      <c r="B14" s="336"/>
+      <c r="C14" s="337"/>
+      <c r="D14" s="338"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="340"/>
+      <c r="G14" s="336"/>
+      <c r="H14" s="341"/>
+      <c r="I14" s="337"/>
+      <c r="J14" s="342"/>
+      <c r="K14" s="343"/>
+      <c r="L14" s="343"/>
+      <c r="M14" s="343"/>
+      <c r="N14" s="343"/>
+      <c r="O14" s="343"/>
+      <c r="P14" s="344"/>
+      <c r="Q14" s="345"/>
+      <c r="R14" s="346"/>
+      <c r="S14" s="346"/>
+      <c r="T14" s="346"/>
+      <c r="U14" s="346"/>
+      <c r="V14" s="346"/>
+      <c r="W14" s="346"/>
+      <c r="X14" s="346"/>
+      <c r="Y14" s="346"/>
+      <c r="Z14" s="346"/>
+      <c r="AA14" s="346"/>
+      <c r="AB14" s="346"/>
+      <c r="AC14" s="346"/>
+      <c r="AD14" s="346"/>
+      <c r="AE14" s="347"/>
+      <c r="AF14" s="342"/>
+      <c r="AG14" s="343"/>
+      <c r="AH14" s="343"/>
+      <c r="AI14" s="344"/>
     </row>
     <row r="15" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="23"/>
-      <c r="B15" s="279"/>
-      <c r="C15" s="280"/>
-      <c r="D15" s="281"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="283"/>
-      <c r="G15" s="279"/>
-      <c r="H15" s="284"/>
-      <c r="I15" s="280"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="286"/>
-      <c r="L15" s="286"/>
-      <c r="M15" s="286"/>
-      <c r="N15" s="286"/>
-      <c r="O15" s="286"/>
-      <c r="P15" s="287"/>
-      <c r="Q15" s="288"/>
-      <c r="R15" s="289"/>
-      <c r="S15" s="289"/>
-      <c r="T15" s="289"/>
-      <c r="U15" s="289"/>
-      <c r="V15" s="289"/>
-      <c r="W15" s="289"/>
-      <c r="X15" s="289"/>
-      <c r="Y15" s="289"/>
-      <c r="Z15" s="289"/>
-      <c r="AA15" s="289"/>
-      <c r="AB15" s="289"/>
-      <c r="AC15" s="289"/>
-      <c r="AD15" s="289"/>
-      <c r="AE15" s="290"/>
-      <c r="AF15" s="285"/>
-      <c r="AG15" s="286"/>
-      <c r="AH15" s="286"/>
-      <c r="AI15" s="287"/>
+      <c r="B15" s="336"/>
+      <c r="C15" s="337"/>
+      <c r="D15" s="338"/>
+      <c r="E15" s="339"/>
+      <c r="F15" s="340"/>
+      <c r="G15" s="336"/>
+      <c r="H15" s="341"/>
+      <c r="I15" s="337"/>
+      <c r="J15" s="342"/>
+      <c r="K15" s="343"/>
+      <c r="L15" s="343"/>
+      <c r="M15" s="343"/>
+      <c r="N15" s="343"/>
+      <c r="O15" s="343"/>
+      <c r="P15" s="344"/>
+      <c r="Q15" s="345"/>
+      <c r="R15" s="346"/>
+      <c r="S15" s="346"/>
+      <c r="T15" s="346"/>
+      <c r="U15" s="346"/>
+      <c r="V15" s="346"/>
+      <c r="W15" s="346"/>
+      <c r="X15" s="346"/>
+      <c r="Y15" s="346"/>
+      <c r="Z15" s="346"/>
+      <c r="AA15" s="346"/>
+      <c r="AB15" s="346"/>
+      <c r="AC15" s="346"/>
+      <c r="AD15" s="346"/>
+      <c r="AE15" s="347"/>
+      <c r="AF15" s="342"/>
+      <c r="AG15" s="343"/>
+      <c r="AH15" s="343"/>
+      <c r="AI15" s="344"/>
     </row>
     <row r="16" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="23"/>
-      <c r="B16" s="279"/>
-      <c r="C16" s="280"/>
-      <c r="D16" s="281"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="283"/>
-      <c r="G16" s="279"/>
-      <c r="H16" s="284"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="286"/>
-      <c r="L16" s="286"/>
-      <c r="M16" s="286"/>
-      <c r="N16" s="286"/>
-      <c r="O16" s="286"/>
-      <c r="P16" s="287"/>
-      <c r="Q16" s="288"/>
-      <c r="R16" s="289"/>
-      <c r="S16" s="289"/>
-      <c r="T16" s="289"/>
-      <c r="U16" s="289"/>
-      <c r="V16" s="289"/>
-      <c r="W16" s="289"/>
-      <c r="X16" s="289"/>
-      <c r="Y16" s="289"/>
-      <c r="Z16" s="289"/>
-      <c r="AA16" s="289"/>
-      <c r="AB16" s="289"/>
-      <c r="AC16" s="289"/>
-      <c r="AD16" s="289"/>
-      <c r="AE16" s="290"/>
-      <c r="AF16" s="285"/>
-      <c r="AG16" s="286"/>
-      <c r="AH16" s="286"/>
-      <c r="AI16" s="287"/>
+      <c r="B16" s="336"/>
+      <c r="C16" s="337"/>
+      <c r="D16" s="338"/>
+      <c r="E16" s="339"/>
+      <c r="F16" s="340"/>
+      <c r="G16" s="336"/>
+      <c r="H16" s="341"/>
+      <c r="I16" s="337"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="343"/>
+      <c r="L16" s="343"/>
+      <c r="M16" s="343"/>
+      <c r="N16" s="343"/>
+      <c r="O16" s="343"/>
+      <c r="P16" s="344"/>
+      <c r="Q16" s="345"/>
+      <c r="R16" s="346"/>
+      <c r="S16" s="346"/>
+      <c r="T16" s="346"/>
+      <c r="U16" s="346"/>
+      <c r="V16" s="346"/>
+      <c r="W16" s="346"/>
+      <c r="X16" s="346"/>
+      <c r="Y16" s="346"/>
+      <c r="Z16" s="346"/>
+      <c r="AA16" s="346"/>
+      <c r="AB16" s="346"/>
+      <c r="AC16" s="346"/>
+      <c r="AD16" s="346"/>
+      <c r="AE16" s="347"/>
+      <c r="AF16" s="342"/>
+      <c r="AG16" s="343"/>
+      <c r="AH16" s="343"/>
+      <c r="AI16" s="344"/>
     </row>
     <row r="17" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="23"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
-      <c r="D17" s="281"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="283"/>
-      <c r="G17" s="279"/>
-      <c r="H17" s="284"/>
-      <c r="I17" s="280"/>
-      <c r="J17" s="285"/>
-      <c r="K17" s="286"/>
-      <c r="L17" s="286"/>
-      <c r="M17" s="286"/>
-      <c r="N17" s="286"/>
-      <c r="O17" s="286"/>
-      <c r="P17" s="287"/>
-      <c r="Q17" s="288"/>
-      <c r="R17" s="289"/>
-      <c r="S17" s="289"/>
-      <c r="T17" s="289"/>
-      <c r="U17" s="289"/>
-      <c r="V17" s="289"/>
-      <c r="W17" s="289"/>
-      <c r="X17" s="289"/>
-      <c r="Y17" s="289"/>
-      <c r="Z17" s="289"/>
-      <c r="AA17" s="289"/>
-      <c r="AB17" s="289"/>
-      <c r="AC17" s="289"/>
-      <c r="AD17" s="289"/>
-      <c r="AE17" s="290"/>
-      <c r="AF17" s="285"/>
-      <c r="AG17" s="286"/>
-      <c r="AH17" s="286"/>
-      <c r="AI17" s="287"/>
+      <c r="B17" s="336"/>
+      <c r="C17" s="337"/>
+      <c r="D17" s="338"/>
+      <c r="E17" s="339"/>
+      <c r="F17" s="340"/>
+      <c r="G17" s="336"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="337"/>
+      <c r="J17" s="342"/>
+      <c r="K17" s="343"/>
+      <c r="L17" s="343"/>
+      <c r="M17" s="343"/>
+      <c r="N17" s="343"/>
+      <c r="O17" s="343"/>
+      <c r="P17" s="344"/>
+      <c r="Q17" s="345"/>
+      <c r="R17" s="346"/>
+      <c r="S17" s="346"/>
+      <c r="T17" s="346"/>
+      <c r="U17" s="346"/>
+      <c r="V17" s="346"/>
+      <c r="W17" s="346"/>
+      <c r="X17" s="346"/>
+      <c r="Y17" s="346"/>
+      <c r="Z17" s="346"/>
+      <c r="AA17" s="346"/>
+      <c r="AB17" s="346"/>
+      <c r="AC17" s="346"/>
+      <c r="AD17" s="346"/>
+      <c r="AE17" s="347"/>
+      <c r="AF17" s="342"/>
+      <c r="AG17" s="343"/>
+      <c r="AH17" s="343"/>
+      <c r="AI17" s="344"/>
     </row>
     <row r="18" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="23"/>
-      <c r="B18" s="279"/>
-      <c r="C18" s="280"/>
-      <c r="D18" s="281"/>
-      <c r="E18" s="282"/>
-      <c r="F18" s="283"/>
-      <c r="G18" s="279"/>
-      <c r="H18" s="284"/>
-      <c r="I18" s="280"/>
-      <c r="J18" s="285"/>
-      <c r="K18" s="286"/>
-      <c r="L18" s="286"/>
-      <c r="M18" s="286"/>
-      <c r="N18" s="286"/>
-      <c r="O18" s="286"/>
-      <c r="P18" s="287"/>
-      <c r="Q18" s="288"/>
-      <c r="R18" s="289"/>
-      <c r="S18" s="289"/>
-      <c r="T18" s="289"/>
-      <c r="U18" s="289"/>
-      <c r="V18" s="289"/>
-      <c r="W18" s="289"/>
-      <c r="X18" s="289"/>
-      <c r="Y18" s="289"/>
-      <c r="Z18" s="289"/>
-      <c r="AA18" s="289"/>
-      <c r="AB18" s="289"/>
-      <c r="AC18" s="289"/>
-      <c r="AD18" s="289"/>
-      <c r="AE18" s="290"/>
-      <c r="AF18" s="285"/>
-      <c r="AG18" s="286"/>
-      <c r="AH18" s="286"/>
-      <c r="AI18" s="287"/>
+      <c r="B18" s="336"/>
+      <c r="C18" s="337"/>
+      <c r="D18" s="338"/>
+      <c r="E18" s="339"/>
+      <c r="F18" s="340"/>
+      <c r="G18" s="336"/>
+      <c r="H18" s="341"/>
+      <c r="I18" s="337"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="343"/>
+      <c r="L18" s="343"/>
+      <c r="M18" s="343"/>
+      <c r="N18" s="343"/>
+      <c r="O18" s="343"/>
+      <c r="P18" s="344"/>
+      <c r="Q18" s="345"/>
+      <c r="R18" s="346"/>
+      <c r="S18" s="346"/>
+      <c r="T18" s="346"/>
+      <c r="U18" s="346"/>
+      <c r="V18" s="346"/>
+      <c r="W18" s="346"/>
+      <c r="X18" s="346"/>
+      <c r="Y18" s="346"/>
+      <c r="Z18" s="346"/>
+      <c r="AA18" s="346"/>
+      <c r="AB18" s="346"/>
+      <c r="AC18" s="346"/>
+      <c r="AD18" s="346"/>
+      <c r="AE18" s="347"/>
+      <c r="AF18" s="342"/>
+      <c r="AG18" s="343"/>
+      <c r="AH18" s="343"/>
+      <c r="AI18" s="344"/>
     </row>
     <row r="19" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="23"/>
-      <c r="B19" s="279"/>
-      <c r="C19" s="280"/>
-      <c r="D19" s="281"/>
-      <c r="E19" s="282"/>
-      <c r="F19" s="283"/>
-      <c r="G19" s="279"/>
-      <c r="H19" s="284"/>
-      <c r="I19" s="280"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="286"/>
-      <c r="M19" s="286"/>
-      <c r="N19" s="286"/>
-      <c r="O19" s="286"/>
-      <c r="P19" s="287"/>
-      <c r="Q19" s="288"/>
-      <c r="R19" s="289"/>
-      <c r="S19" s="289"/>
-      <c r="T19" s="289"/>
-      <c r="U19" s="289"/>
-      <c r="V19" s="289"/>
-      <c r="W19" s="289"/>
-      <c r="X19" s="289"/>
-      <c r="Y19" s="289"/>
-      <c r="Z19" s="289"/>
-      <c r="AA19" s="289"/>
-      <c r="AB19" s="289"/>
-      <c r="AC19" s="289"/>
-      <c r="AD19" s="289"/>
-      <c r="AE19" s="290"/>
-      <c r="AF19" s="285"/>
-      <c r="AG19" s="286"/>
-      <c r="AH19" s="286"/>
-      <c r="AI19" s="287"/>
+      <c r="B19" s="336"/>
+      <c r="C19" s="337"/>
+      <c r="D19" s="338"/>
+      <c r="E19" s="339"/>
+      <c r="F19" s="340"/>
+      <c r="G19" s="336"/>
+      <c r="H19" s="341"/>
+      <c r="I19" s="337"/>
+      <c r="J19" s="342"/>
+      <c r="K19" s="343"/>
+      <c r="L19" s="343"/>
+      <c r="M19" s="343"/>
+      <c r="N19" s="343"/>
+      <c r="O19" s="343"/>
+      <c r="P19" s="344"/>
+      <c r="Q19" s="345"/>
+      <c r="R19" s="346"/>
+      <c r="S19" s="346"/>
+      <c r="T19" s="346"/>
+      <c r="U19" s="346"/>
+      <c r="V19" s="346"/>
+      <c r="W19" s="346"/>
+      <c r="X19" s="346"/>
+      <c r="Y19" s="346"/>
+      <c r="Z19" s="346"/>
+      <c r="AA19" s="346"/>
+      <c r="AB19" s="346"/>
+      <c r="AC19" s="346"/>
+      <c r="AD19" s="346"/>
+      <c r="AE19" s="347"/>
+      <c r="AF19" s="342"/>
+      <c r="AG19" s="343"/>
+      <c r="AH19" s="343"/>
+      <c r="AI19" s="344"/>
     </row>
     <row r="20" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="23"/>
-      <c r="B20" s="279"/>
-      <c r="C20" s="280"/>
-      <c r="D20" s="281"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="279"/>
-      <c r="H20" s="284"/>
-      <c r="I20" s="280"/>
-      <c r="J20" s="285"/>
-      <c r="K20" s="286"/>
-      <c r="L20" s="286"/>
-      <c r="M20" s="286"/>
-      <c r="N20" s="286"/>
-      <c r="O20" s="286"/>
-      <c r="P20" s="287"/>
-      <c r="Q20" s="288"/>
-      <c r="R20" s="289"/>
-      <c r="S20" s="289"/>
-      <c r="T20" s="289"/>
-      <c r="U20" s="289"/>
-      <c r="V20" s="289"/>
-      <c r="W20" s="289"/>
-      <c r="X20" s="289"/>
-      <c r="Y20" s="289"/>
-      <c r="Z20" s="289"/>
-      <c r="AA20" s="289"/>
-      <c r="AB20" s="289"/>
-      <c r="AC20" s="289"/>
-      <c r="AD20" s="289"/>
-      <c r="AE20" s="290"/>
-      <c r="AF20" s="285"/>
-      <c r="AG20" s="286"/>
-      <c r="AH20" s="286"/>
-      <c r="AI20" s="287"/>
+      <c r="B20" s="336"/>
+      <c r="C20" s="337"/>
+      <c r="D20" s="338"/>
+      <c r="E20" s="339"/>
+      <c r="F20" s="340"/>
+      <c r="G20" s="336"/>
+      <c r="H20" s="341"/>
+      <c r="I20" s="337"/>
+      <c r="J20" s="342"/>
+      <c r="K20" s="343"/>
+      <c r="L20" s="343"/>
+      <c r="M20" s="343"/>
+      <c r="N20" s="343"/>
+      <c r="O20" s="343"/>
+      <c r="P20" s="344"/>
+      <c r="Q20" s="345"/>
+      <c r="R20" s="346"/>
+      <c r="S20" s="346"/>
+      <c r="T20" s="346"/>
+      <c r="U20" s="346"/>
+      <c r="V20" s="346"/>
+      <c r="W20" s="346"/>
+      <c r="X20" s="346"/>
+      <c r="Y20" s="346"/>
+      <c r="Z20" s="346"/>
+      <c r="AA20" s="346"/>
+      <c r="AB20" s="346"/>
+      <c r="AC20" s="346"/>
+      <c r="AD20" s="346"/>
+      <c r="AE20" s="347"/>
+      <c r="AF20" s="342"/>
+      <c r="AG20" s="343"/>
+      <c r="AH20" s="343"/>
+      <c r="AI20" s="344"/>
     </row>
     <row r="21" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="23"/>
-      <c r="B21" s="279"/>
-      <c r="C21" s="280"/>
-      <c r="D21" s="281"/>
-      <c r="E21" s="282"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="279"/>
-      <c r="H21" s="284"/>
-      <c r="I21" s="280"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="286"/>
-      <c r="M21" s="286"/>
-      <c r="N21" s="286"/>
-      <c r="O21" s="286"/>
-      <c r="P21" s="287"/>
-      <c r="Q21" s="288"/>
-      <c r="R21" s="289"/>
-      <c r="S21" s="289"/>
-      <c r="T21" s="289"/>
-      <c r="U21" s="289"/>
-      <c r="V21" s="289"/>
-      <c r="W21" s="289"/>
-      <c r="X21" s="289"/>
-      <c r="Y21" s="289"/>
-      <c r="Z21" s="289"/>
-      <c r="AA21" s="289"/>
-      <c r="AB21" s="289"/>
-      <c r="AC21" s="289"/>
-      <c r="AD21" s="289"/>
-      <c r="AE21" s="290"/>
-      <c r="AF21" s="285"/>
-      <c r="AG21" s="286"/>
-      <c r="AH21" s="286"/>
-      <c r="AI21" s="287"/>
+      <c r="B21" s="336"/>
+      <c r="C21" s="337"/>
+      <c r="D21" s="338"/>
+      <c r="E21" s="339"/>
+      <c r="F21" s="340"/>
+      <c r="G21" s="336"/>
+      <c r="H21" s="341"/>
+      <c r="I21" s="337"/>
+      <c r="J21" s="342"/>
+      <c r="K21" s="343"/>
+      <c r="L21" s="343"/>
+      <c r="M21" s="343"/>
+      <c r="N21" s="343"/>
+      <c r="O21" s="343"/>
+      <c r="P21" s="344"/>
+      <c r="Q21" s="345"/>
+      <c r="R21" s="346"/>
+      <c r="S21" s="346"/>
+      <c r="T21" s="346"/>
+      <c r="U21" s="346"/>
+      <c r="V21" s="346"/>
+      <c r="W21" s="346"/>
+      <c r="X21" s="346"/>
+      <c r="Y21" s="346"/>
+      <c r="Z21" s="346"/>
+      <c r="AA21" s="346"/>
+      <c r="AB21" s="346"/>
+      <c r="AC21" s="346"/>
+      <c r="AD21" s="346"/>
+      <c r="AE21" s="347"/>
+      <c r="AF21" s="342"/>
+      <c r="AG21" s="343"/>
+      <c r="AH21" s="343"/>
+      <c r="AI21" s="344"/>
     </row>
     <row r="22" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="23"/>
-      <c r="B22" s="279"/>
-      <c r="C22" s="280"/>
-      <c r="D22" s="281"/>
-      <c r="E22" s="282"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="284"/>
-      <c r="I22" s="280"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="286"/>
-      <c r="L22" s="286"/>
-      <c r="M22" s="286"/>
-      <c r="N22" s="286"/>
-      <c r="O22" s="286"/>
-      <c r="P22" s="287"/>
-      <c r="Q22" s="288"/>
-      <c r="R22" s="289"/>
-      <c r="S22" s="289"/>
-      <c r="T22" s="289"/>
-      <c r="U22" s="289"/>
-      <c r="V22" s="289"/>
-      <c r="W22" s="289"/>
-      <c r="X22" s="289"/>
-      <c r="Y22" s="289"/>
-      <c r="Z22" s="289"/>
-      <c r="AA22" s="289"/>
-      <c r="AB22" s="289"/>
-      <c r="AC22" s="289"/>
-      <c r="AD22" s="289"/>
-      <c r="AE22" s="290"/>
-      <c r="AF22" s="285"/>
-      <c r="AG22" s="286"/>
-      <c r="AH22" s="286"/>
-      <c r="AI22" s="287"/>
+      <c r="B22" s="336"/>
+      <c r="C22" s="337"/>
+      <c r="D22" s="338"/>
+      <c r="E22" s="339"/>
+      <c r="F22" s="340"/>
+      <c r="G22" s="336"/>
+      <c r="H22" s="341"/>
+      <c r="I22" s="337"/>
+      <c r="J22" s="342"/>
+      <c r="K22" s="343"/>
+      <c r="L22" s="343"/>
+      <c r="M22" s="343"/>
+      <c r="N22" s="343"/>
+      <c r="O22" s="343"/>
+      <c r="P22" s="344"/>
+      <c r="Q22" s="345"/>
+      <c r="R22" s="346"/>
+      <c r="S22" s="346"/>
+      <c r="T22" s="346"/>
+      <c r="U22" s="346"/>
+      <c r="V22" s="346"/>
+      <c r="W22" s="346"/>
+      <c r="X22" s="346"/>
+      <c r="Y22" s="346"/>
+      <c r="Z22" s="346"/>
+      <c r="AA22" s="346"/>
+      <c r="AB22" s="346"/>
+      <c r="AC22" s="346"/>
+      <c r="AD22" s="346"/>
+      <c r="AE22" s="347"/>
+      <c r="AF22" s="342"/>
+      <c r="AG22" s="343"/>
+      <c r="AH22" s="343"/>
+      <c r="AI22" s="344"/>
     </row>
     <row r="23" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="23"/>
-      <c r="B23" s="279"/>
-      <c r="C23" s="280"/>
-      <c r="D23" s="281"/>
-      <c r="E23" s="282"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="279"/>
-      <c r="H23" s="284"/>
-      <c r="I23" s="280"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="286"/>
-      <c r="M23" s="286"/>
-      <c r="N23" s="286"/>
-      <c r="O23" s="286"/>
-      <c r="P23" s="287"/>
-      <c r="Q23" s="288"/>
-      <c r="R23" s="289"/>
-      <c r="S23" s="289"/>
-      <c r="T23" s="289"/>
-      <c r="U23" s="289"/>
-      <c r="V23" s="289"/>
-      <c r="W23" s="289"/>
-      <c r="X23" s="289"/>
-      <c r="Y23" s="289"/>
-      <c r="Z23" s="289"/>
-      <c r="AA23" s="289"/>
-      <c r="AB23" s="289"/>
-      <c r="AC23" s="289"/>
-      <c r="AD23" s="289"/>
-      <c r="AE23" s="290"/>
-      <c r="AF23" s="285"/>
-      <c r="AG23" s="286"/>
-      <c r="AH23" s="286"/>
-      <c r="AI23" s="287"/>
+      <c r="B23" s="336"/>
+      <c r="C23" s="337"/>
+      <c r="D23" s="338"/>
+      <c r="E23" s="339"/>
+      <c r="F23" s="340"/>
+      <c r="G23" s="336"/>
+      <c r="H23" s="341"/>
+      <c r="I23" s="337"/>
+      <c r="J23" s="342"/>
+      <c r="K23" s="343"/>
+      <c r="L23" s="343"/>
+      <c r="M23" s="343"/>
+      <c r="N23" s="343"/>
+      <c r="O23" s="343"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="345"/>
+      <c r="R23" s="346"/>
+      <c r="S23" s="346"/>
+      <c r="T23" s="346"/>
+      <c r="U23" s="346"/>
+      <c r="V23" s="346"/>
+      <c r="W23" s="346"/>
+      <c r="X23" s="346"/>
+      <c r="Y23" s="346"/>
+      <c r="Z23" s="346"/>
+      <c r="AA23" s="346"/>
+      <c r="AB23" s="346"/>
+      <c r="AC23" s="346"/>
+      <c r="AD23" s="346"/>
+      <c r="AE23" s="347"/>
+      <c r="AF23" s="342"/>
+      <c r="AG23" s="343"/>
+      <c r="AH23" s="343"/>
+      <c r="AI23" s="344"/>
     </row>
     <row r="24" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="B24" s="279"/>
-      <c r="C24" s="280"/>
-      <c r="D24" s="281"/>
-      <c r="E24" s="282"/>
-      <c r="F24" s="283"/>
-      <c r="G24" s="279"/>
-      <c r="H24" s="284"/>
-      <c r="I24" s="280"/>
-      <c r="J24" s="285"/>
-      <c r="K24" s="286"/>
-      <c r="L24" s="286"/>
-      <c r="M24" s="286"/>
-      <c r="N24" s="286"/>
-      <c r="O24" s="286"/>
-      <c r="P24" s="287"/>
-      <c r="Q24" s="288"/>
-      <c r="R24" s="289"/>
-      <c r="S24" s="289"/>
-      <c r="T24" s="289"/>
-      <c r="U24" s="289"/>
-      <c r="V24" s="289"/>
-      <c r="W24" s="289"/>
-      <c r="X24" s="289"/>
-      <c r="Y24" s="289"/>
-      <c r="Z24" s="289"/>
-      <c r="AA24" s="289"/>
-      <c r="AB24" s="289"/>
-      <c r="AC24" s="289"/>
-      <c r="AD24" s="289"/>
-      <c r="AE24" s="290"/>
-      <c r="AF24" s="285"/>
-      <c r="AG24" s="286"/>
-      <c r="AH24" s="286"/>
-      <c r="AI24" s="287"/>
+      <c r="B24" s="336"/>
+      <c r="C24" s="337"/>
+      <c r="D24" s="338"/>
+      <c r="E24" s="339"/>
+      <c r="F24" s="340"/>
+      <c r="G24" s="336"/>
+      <c r="H24" s="341"/>
+      <c r="I24" s="337"/>
+      <c r="J24" s="342"/>
+      <c r="K24" s="343"/>
+      <c r="L24" s="343"/>
+      <c r="M24" s="343"/>
+      <c r="N24" s="343"/>
+      <c r="O24" s="343"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="345"/>
+      <c r="R24" s="346"/>
+      <c r="S24" s="346"/>
+      <c r="T24" s="346"/>
+      <c r="U24" s="346"/>
+      <c r="V24" s="346"/>
+      <c r="W24" s="346"/>
+      <c r="X24" s="346"/>
+      <c r="Y24" s="346"/>
+      <c r="Z24" s="346"/>
+      <c r="AA24" s="346"/>
+      <c r="AB24" s="346"/>
+      <c r="AC24" s="346"/>
+      <c r="AD24" s="346"/>
+      <c r="AE24" s="347"/>
+      <c r="AF24" s="342"/>
+      <c r="AG24" s="343"/>
+      <c r="AH24" s="343"/>
+      <c r="AI24" s="344"/>
     </row>
     <row r="25" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="23"/>
-      <c r="B25" s="279"/>
-      <c r="C25" s="280"/>
-      <c r="D25" s="281"/>
-      <c r="E25" s="282"/>
-      <c r="F25" s="283"/>
-      <c r="G25" s="279"/>
-      <c r="H25" s="284"/>
-      <c r="I25" s="280"/>
-      <c r="J25" s="285"/>
-      <c r="K25" s="286"/>
-      <c r="L25" s="286"/>
-      <c r="M25" s="286"/>
-      <c r="N25" s="286"/>
-      <c r="O25" s="286"/>
-      <c r="P25" s="287"/>
-      <c r="Q25" s="288"/>
-      <c r="R25" s="289"/>
-      <c r="S25" s="289"/>
-      <c r="T25" s="289"/>
-      <c r="U25" s="289"/>
-      <c r="V25" s="289"/>
-      <c r="W25" s="289"/>
-      <c r="X25" s="289"/>
-      <c r="Y25" s="289"/>
-      <c r="Z25" s="289"/>
-      <c r="AA25" s="289"/>
-      <c r="AB25" s="289"/>
-      <c r="AC25" s="289"/>
-      <c r="AD25" s="289"/>
-      <c r="AE25" s="290"/>
-      <c r="AF25" s="285"/>
-      <c r="AG25" s="286"/>
-      <c r="AH25" s="286"/>
-      <c r="AI25" s="287"/>
+      <c r="B25" s="336"/>
+      <c r="C25" s="337"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="340"/>
+      <c r="G25" s="336"/>
+      <c r="H25" s="341"/>
+      <c r="I25" s="337"/>
+      <c r="J25" s="342"/>
+      <c r="K25" s="343"/>
+      <c r="L25" s="343"/>
+      <c r="M25" s="343"/>
+      <c r="N25" s="343"/>
+      <c r="O25" s="343"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="345"/>
+      <c r="R25" s="346"/>
+      <c r="S25" s="346"/>
+      <c r="T25" s="346"/>
+      <c r="U25" s="346"/>
+      <c r="V25" s="346"/>
+      <c r="W25" s="346"/>
+      <c r="X25" s="346"/>
+      <c r="Y25" s="346"/>
+      <c r="Z25" s="346"/>
+      <c r="AA25" s="346"/>
+      <c r="AB25" s="346"/>
+      <c r="AC25" s="346"/>
+      <c r="AD25" s="346"/>
+      <c r="AE25" s="347"/>
+      <c r="AF25" s="342"/>
+      <c r="AG25" s="343"/>
+      <c r="AH25" s="343"/>
+      <c r="AI25" s="344"/>
     </row>
     <row r="26" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="23"/>
-      <c r="B26" s="279"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="281"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="283"/>
-      <c r="G26" s="279"/>
-      <c r="H26" s="284"/>
-      <c r="I26" s="280"/>
-      <c r="J26" s="285"/>
-      <c r="K26" s="286"/>
-      <c r="L26" s="286"/>
-      <c r="M26" s="286"/>
-      <c r="N26" s="286"/>
-      <c r="O26" s="286"/>
-      <c r="P26" s="287"/>
-      <c r="Q26" s="288"/>
-      <c r="R26" s="289"/>
-      <c r="S26" s="289"/>
-      <c r="T26" s="289"/>
-      <c r="U26" s="289"/>
-      <c r="V26" s="289"/>
-      <c r="W26" s="289"/>
-      <c r="X26" s="289"/>
-      <c r="Y26" s="289"/>
-      <c r="Z26" s="289"/>
-      <c r="AA26" s="289"/>
-      <c r="AB26" s="289"/>
-      <c r="AC26" s="289"/>
-      <c r="AD26" s="289"/>
-      <c r="AE26" s="290"/>
-      <c r="AF26" s="285"/>
-      <c r="AG26" s="286"/>
-      <c r="AH26" s="286"/>
-      <c r="AI26" s="287"/>
+      <c r="B26" s="336"/>
+      <c r="C26" s="337"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="340"/>
+      <c r="G26" s="336"/>
+      <c r="H26" s="341"/>
+      <c r="I26" s="337"/>
+      <c r="J26" s="342"/>
+      <c r="K26" s="343"/>
+      <c r="L26" s="343"/>
+      <c r="M26" s="343"/>
+      <c r="N26" s="343"/>
+      <c r="O26" s="343"/>
+      <c r="P26" s="344"/>
+      <c r="Q26" s="345"/>
+      <c r="R26" s="346"/>
+      <c r="S26" s="346"/>
+      <c r="T26" s="346"/>
+      <c r="U26" s="346"/>
+      <c r="V26" s="346"/>
+      <c r="W26" s="346"/>
+      <c r="X26" s="346"/>
+      <c r="Y26" s="346"/>
+      <c r="Z26" s="346"/>
+      <c r="AA26" s="346"/>
+      <c r="AB26" s="346"/>
+      <c r="AC26" s="346"/>
+      <c r="AD26" s="346"/>
+      <c r="AE26" s="347"/>
+      <c r="AF26" s="342"/>
+      <c r="AG26" s="343"/>
+      <c r="AH26" s="343"/>
+      <c r="AI26" s="344"/>
     </row>
     <row r="27" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="23"/>
-      <c r="B27" s="279"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="281"/>
-      <c r="E27" s="282"/>
-      <c r="F27" s="283"/>
-      <c r="G27" s="279"/>
-      <c r="H27" s="284"/>
-      <c r="I27" s="280"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="286"/>
-      <c r="L27" s="286"/>
-      <c r="M27" s="286"/>
-      <c r="N27" s="286"/>
-      <c r="O27" s="286"/>
-      <c r="P27" s="287"/>
-      <c r="Q27" s="288"/>
-      <c r="R27" s="289"/>
-      <c r="S27" s="289"/>
-      <c r="T27" s="289"/>
-      <c r="U27" s="289"/>
-      <c r="V27" s="289"/>
-      <c r="W27" s="289"/>
-      <c r="X27" s="289"/>
-      <c r="Y27" s="289"/>
-      <c r="Z27" s="289"/>
-      <c r="AA27" s="289"/>
-      <c r="AB27" s="289"/>
-      <c r="AC27" s="289"/>
-      <c r="AD27" s="289"/>
-      <c r="AE27" s="290"/>
-      <c r="AF27" s="285"/>
-      <c r="AG27" s="286"/>
-      <c r="AH27" s="286"/>
-      <c r="AI27" s="287"/>
+      <c r="B27" s="336"/>
+      <c r="C27" s="337"/>
+      <c r="D27" s="338"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="340"/>
+      <c r="G27" s="336"/>
+      <c r="H27" s="341"/>
+      <c r="I27" s="337"/>
+      <c r="J27" s="342"/>
+      <c r="K27" s="343"/>
+      <c r="L27" s="343"/>
+      <c r="M27" s="343"/>
+      <c r="N27" s="343"/>
+      <c r="O27" s="343"/>
+      <c r="P27" s="344"/>
+      <c r="Q27" s="345"/>
+      <c r="R27" s="346"/>
+      <c r="S27" s="346"/>
+      <c r="T27" s="346"/>
+      <c r="U27" s="346"/>
+      <c r="V27" s="346"/>
+      <c r="W27" s="346"/>
+      <c r="X27" s="346"/>
+      <c r="Y27" s="346"/>
+      <c r="Z27" s="346"/>
+      <c r="AA27" s="346"/>
+      <c r="AB27" s="346"/>
+      <c r="AC27" s="346"/>
+      <c r="AD27" s="346"/>
+      <c r="AE27" s="347"/>
+      <c r="AF27" s="342"/>
+      <c r="AG27" s="343"/>
+      <c r="AH27" s="343"/>
+      <c r="AI27" s="344"/>
     </row>
     <row r="28" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="23"/>
-      <c r="B28" s="279"/>
-      <c r="C28" s="280"/>
-      <c r="D28" s="281"/>
-      <c r="E28" s="282"/>
-      <c r="F28" s="283"/>
-      <c r="G28" s="279"/>
-      <c r="H28" s="284"/>
-      <c r="I28" s="280"/>
-      <c r="J28" s="285"/>
-      <c r="K28" s="286"/>
-      <c r="L28" s="286"/>
-      <c r="M28" s="286"/>
-      <c r="N28" s="286"/>
-      <c r="O28" s="286"/>
-      <c r="P28" s="287"/>
-      <c r="Q28" s="288"/>
-      <c r="R28" s="289"/>
-      <c r="S28" s="289"/>
-      <c r="T28" s="289"/>
-      <c r="U28" s="289"/>
-      <c r="V28" s="289"/>
-      <c r="W28" s="289"/>
-      <c r="X28" s="289"/>
-      <c r="Y28" s="289"/>
-      <c r="Z28" s="289"/>
-      <c r="AA28" s="289"/>
-      <c r="AB28" s="289"/>
-      <c r="AC28" s="289"/>
-      <c r="AD28" s="289"/>
-      <c r="AE28" s="290"/>
-      <c r="AF28" s="285"/>
-      <c r="AG28" s="286"/>
-      <c r="AH28" s="286"/>
-      <c r="AI28" s="287"/>
+      <c r="B28" s="336"/>
+      <c r="C28" s="337"/>
+      <c r="D28" s="338"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="340"/>
+      <c r="G28" s="336"/>
+      <c r="H28" s="341"/>
+      <c r="I28" s="337"/>
+      <c r="J28" s="342"/>
+      <c r="K28" s="343"/>
+      <c r="L28" s="343"/>
+      <c r="M28" s="343"/>
+      <c r="N28" s="343"/>
+      <c r="O28" s="343"/>
+      <c r="P28" s="344"/>
+      <c r="Q28" s="345"/>
+      <c r="R28" s="346"/>
+      <c r="S28" s="346"/>
+      <c r="T28" s="346"/>
+      <c r="U28" s="346"/>
+      <c r="V28" s="346"/>
+      <c r="W28" s="346"/>
+      <c r="X28" s="346"/>
+      <c r="Y28" s="346"/>
+      <c r="Z28" s="346"/>
+      <c r="AA28" s="346"/>
+      <c r="AB28" s="346"/>
+      <c r="AC28" s="346"/>
+      <c r="AD28" s="346"/>
+      <c r="AE28" s="347"/>
+      <c r="AF28" s="342"/>
+      <c r="AG28" s="343"/>
+      <c r="AH28" s="343"/>
+      <c r="AI28" s="344"/>
     </row>
     <row r="29" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="23"/>
-      <c r="B29" s="279"/>
-      <c r="C29" s="280"/>
-      <c r="D29" s="281"/>
-      <c r="E29" s="282"/>
-      <c r="F29" s="283"/>
-      <c r="G29" s="279"/>
-      <c r="H29" s="284"/>
-      <c r="I29" s="280"/>
-      <c r="J29" s="285"/>
-      <c r="K29" s="286"/>
-      <c r="L29" s="286"/>
-      <c r="M29" s="286"/>
-      <c r="N29" s="286"/>
-      <c r="O29" s="286"/>
-      <c r="P29" s="287"/>
-      <c r="Q29" s="288"/>
-      <c r="R29" s="289"/>
-      <c r="S29" s="289"/>
-      <c r="T29" s="289"/>
-      <c r="U29" s="289"/>
-      <c r="V29" s="289"/>
-      <c r="W29" s="289"/>
-      <c r="X29" s="289"/>
-      <c r="Y29" s="289"/>
-      <c r="Z29" s="289"/>
-      <c r="AA29" s="289"/>
-      <c r="AB29" s="289"/>
-      <c r="AC29" s="289"/>
-      <c r="AD29" s="289"/>
-      <c r="AE29" s="290"/>
-      <c r="AF29" s="285"/>
-      <c r="AG29" s="286"/>
-      <c r="AH29" s="286"/>
-      <c r="AI29" s="287"/>
+      <c r="B29" s="336"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="340"/>
+      <c r="G29" s="336"/>
+      <c r="H29" s="341"/>
+      <c r="I29" s="337"/>
+      <c r="J29" s="342"/>
+      <c r="K29" s="343"/>
+      <c r="L29" s="343"/>
+      <c r="M29" s="343"/>
+      <c r="N29" s="343"/>
+      <c r="O29" s="343"/>
+      <c r="P29" s="344"/>
+      <c r="Q29" s="345"/>
+      <c r="R29" s="346"/>
+      <c r="S29" s="346"/>
+      <c r="T29" s="346"/>
+      <c r="U29" s="346"/>
+      <c r="V29" s="346"/>
+      <c r="W29" s="346"/>
+      <c r="X29" s="346"/>
+      <c r="Y29" s="346"/>
+      <c r="Z29" s="346"/>
+      <c r="AA29" s="346"/>
+      <c r="AB29" s="346"/>
+      <c r="AC29" s="346"/>
+      <c r="AD29" s="346"/>
+      <c r="AE29" s="347"/>
+      <c r="AF29" s="342"/>
+      <c r="AG29" s="343"/>
+      <c r="AH29" s="343"/>
+      <c r="AI29" s="344"/>
     </row>
     <row r="30" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="23"/>
-      <c r="B30" s="279"/>
-      <c r="C30" s="280"/>
-      <c r="D30" s="281"/>
-      <c r="E30" s="282"/>
-      <c r="F30" s="283"/>
-      <c r="G30" s="279"/>
-      <c r="H30" s="284"/>
-      <c r="I30" s="280"/>
-      <c r="J30" s="285"/>
-      <c r="K30" s="286"/>
-      <c r="L30" s="286"/>
-      <c r="M30" s="286"/>
-      <c r="N30" s="286"/>
-      <c r="O30" s="286"/>
-      <c r="P30" s="287"/>
-      <c r="Q30" s="288"/>
-      <c r="R30" s="289"/>
-      <c r="S30" s="289"/>
-      <c r="T30" s="289"/>
-      <c r="U30" s="289"/>
-      <c r="V30" s="289"/>
-      <c r="W30" s="289"/>
-      <c r="X30" s="289"/>
-      <c r="Y30" s="289"/>
-      <c r="Z30" s="289"/>
-      <c r="AA30" s="289"/>
-      <c r="AB30" s="289"/>
-      <c r="AC30" s="289"/>
-      <c r="AD30" s="289"/>
-      <c r="AE30" s="290"/>
-      <c r="AF30" s="285"/>
-      <c r="AG30" s="286"/>
-      <c r="AH30" s="286"/>
-      <c r="AI30" s="287"/>
+      <c r="B30" s="336"/>
+      <c r="C30" s="337"/>
+      <c r="D30" s="338"/>
+      <c r="E30" s="339"/>
+      <c r="F30" s="340"/>
+      <c r="G30" s="336"/>
+      <c r="H30" s="341"/>
+      <c r="I30" s="337"/>
+      <c r="J30" s="342"/>
+      <c r="K30" s="343"/>
+      <c r="L30" s="343"/>
+      <c r="M30" s="343"/>
+      <c r="N30" s="343"/>
+      <c r="O30" s="343"/>
+      <c r="P30" s="344"/>
+      <c r="Q30" s="345"/>
+      <c r="R30" s="346"/>
+      <c r="S30" s="346"/>
+      <c r="T30" s="346"/>
+      <c r="U30" s="346"/>
+      <c r="V30" s="346"/>
+      <c r="W30" s="346"/>
+      <c r="X30" s="346"/>
+      <c r="Y30" s="346"/>
+      <c r="Z30" s="346"/>
+      <c r="AA30" s="346"/>
+      <c r="AB30" s="346"/>
+      <c r="AC30" s="346"/>
+      <c r="AD30" s="346"/>
+      <c r="AE30" s="347"/>
+      <c r="AF30" s="342"/>
+      <c r="AG30" s="343"/>
+      <c r="AH30" s="343"/>
+      <c r="AI30" s="344"/>
     </row>
     <row r="31" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="23"/>
-      <c r="B31" s="279"/>
-      <c r="C31" s="280"/>
-      <c r="D31" s="281"/>
-      <c r="E31" s="282"/>
-      <c r="F31" s="283"/>
-      <c r="G31" s="279"/>
-      <c r="H31" s="284"/>
-      <c r="I31" s="280"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="286"/>
-      <c r="L31" s="286"/>
-      <c r="M31" s="286"/>
-      <c r="N31" s="286"/>
-      <c r="O31" s="286"/>
-      <c r="P31" s="287"/>
-      <c r="Q31" s="288"/>
-      <c r="R31" s="289"/>
-      <c r="S31" s="289"/>
-      <c r="T31" s="289"/>
-      <c r="U31" s="289"/>
-      <c r="V31" s="289"/>
-      <c r="W31" s="289"/>
-      <c r="X31" s="289"/>
-      <c r="Y31" s="289"/>
-      <c r="Z31" s="289"/>
-      <c r="AA31" s="289"/>
-      <c r="AB31" s="289"/>
-      <c r="AC31" s="289"/>
-      <c r="AD31" s="289"/>
-      <c r="AE31" s="290"/>
-      <c r="AF31" s="285"/>
-      <c r="AG31" s="286"/>
-      <c r="AH31" s="286"/>
-      <c r="AI31" s="287"/>
+      <c r="B31" s="336"/>
+      <c r="C31" s="337"/>
+      <c r="D31" s="338"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="340"/>
+      <c r="G31" s="336"/>
+      <c r="H31" s="341"/>
+      <c r="I31" s="337"/>
+      <c r="J31" s="342"/>
+      <c r="K31" s="343"/>
+      <c r="L31" s="343"/>
+      <c r="M31" s="343"/>
+      <c r="N31" s="343"/>
+      <c r="O31" s="343"/>
+      <c r="P31" s="344"/>
+      <c r="Q31" s="345"/>
+      <c r="R31" s="346"/>
+      <c r="S31" s="346"/>
+      <c r="T31" s="346"/>
+      <c r="U31" s="346"/>
+      <c r="V31" s="346"/>
+      <c r="W31" s="346"/>
+      <c r="X31" s="346"/>
+      <c r="Y31" s="346"/>
+      <c r="Z31" s="346"/>
+      <c r="AA31" s="346"/>
+      <c r="AB31" s="346"/>
+      <c r="AC31" s="346"/>
+      <c r="AD31" s="346"/>
+      <c r="AE31" s="347"/>
+      <c r="AF31" s="342"/>
+      <c r="AG31" s="343"/>
+      <c r="AH31" s="343"/>
+      <c r="AI31" s="344"/>
     </row>
     <row r="32" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="23"/>
-      <c r="B32" s="279"/>
-      <c r="C32" s="280"/>
-      <c r="D32" s="281"/>
-      <c r="E32" s="282"/>
-      <c r="F32" s="283"/>
-      <c r="G32" s="279"/>
-      <c r="H32" s="284"/>
-      <c r="I32" s="280"/>
-      <c r="J32" s="285"/>
-      <c r="K32" s="291"/>
-      <c r="L32" s="286"/>
-      <c r="M32" s="286"/>
-      <c r="N32" s="286"/>
-      <c r="O32" s="286"/>
-      <c r="P32" s="287"/>
-      <c r="Q32" s="288"/>
-      <c r="R32" s="289"/>
-      <c r="S32" s="289"/>
-      <c r="T32" s="289"/>
-      <c r="U32" s="289"/>
-      <c r="V32" s="289"/>
-      <c r="W32" s="289"/>
-      <c r="X32" s="289"/>
-      <c r="Y32" s="289"/>
-      <c r="Z32" s="289"/>
-      <c r="AA32" s="289"/>
-      <c r="AB32" s="289"/>
-      <c r="AC32" s="289"/>
-      <c r="AD32" s="289"/>
-      <c r="AE32" s="290"/>
-      <c r="AF32" s="285"/>
-      <c r="AG32" s="286"/>
-      <c r="AH32" s="286"/>
-      <c r="AI32" s="287"/>
+      <c r="B32" s="336"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="340"/>
+      <c r="G32" s="336"/>
+      <c r="H32" s="341"/>
+      <c r="I32" s="337"/>
+      <c r="J32" s="342"/>
+      <c r="K32" s="348"/>
+      <c r="L32" s="343"/>
+      <c r="M32" s="343"/>
+      <c r="N32" s="343"/>
+      <c r="O32" s="343"/>
+      <c r="P32" s="344"/>
+      <c r="Q32" s="345"/>
+      <c r="R32" s="346"/>
+      <c r="S32" s="346"/>
+      <c r="T32" s="346"/>
+      <c r="U32" s="346"/>
+      <c r="V32" s="346"/>
+      <c r="W32" s="346"/>
+      <c r="X32" s="346"/>
+      <c r="Y32" s="346"/>
+      <c r="Z32" s="346"/>
+      <c r="AA32" s="346"/>
+      <c r="AB32" s="346"/>
+      <c r="AC32" s="346"/>
+      <c r="AD32" s="346"/>
+      <c r="AE32" s="347"/>
+      <c r="AF32" s="342"/>
+      <c r="AG32" s="343"/>
+      <c r="AH32" s="343"/>
+      <c r="AI32" s="344"/>
     </row>
     <row r="33" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="23"/>
-      <c r="B33" s="279"/>
-      <c r="C33" s="280"/>
-      <c r="D33" s="281"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="283"/>
-      <c r="G33" s="279"/>
-      <c r="H33" s="284"/>
-      <c r="I33" s="280"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="286"/>
-      <c r="L33" s="286"/>
-      <c r="M33" s="286"/>
-      <c r="N33" s="286"/>
-      <c r="O33" s="286"/>
-      <c r="P33" s="287"/>
-      <c r="Q33" s="288"/>
-      <c r="R33" s="289"/>
-      <c r="S33" s="289"/>
-      <c r="T33" s="289"/>
-      <c r="U33" s="289"/>
-      <c r="V33" s="289"/>
-      <c r="W33" s="289"/>
-      <c r="X33" s="289"/>
-      <c r="Y33" s="289"/>
-      <c r="Z33" s="289"/>
-      <c r="AA33" s="289"/>
-      <c r="AB33" s="289"/>
-      <c r="AC33" s="289"/>
-      <c r="AD33" s="289"/>
-      <c r="AE33" s="290"/>
-      <c r="AF33" s="285"/>
-      <c r="AG33" s="286"/>
-      <c r="AH33" s="286"/>
-      <c r="AI33" s="287"/>
+      <c r="B33" s="336"/>
+      <c r="C33" s="337"/>
+      <c r="D33" s="338"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="340"/>
+      <c r="G33" s="336"/>
+      <c r="H33" s="341"/>
+      <c r="I33" s="337"/>
+      <c r="J33" s="342"/>
+      <c r="K33" s="343"/>
+      <c r="L33" s="343"/>
+      <c r="M33" s="343"/>
+      <c r="N33" s="343"/>
+      <c r="O33" s="343"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="345"/>
+      <c r="R33" s="346"/>
+      <c r="S33" s="346"/>
+      <c r="T33" s="346"/>
+      <c r="U33" s="346"/>
+      <c r="V33" s="346"/>
+      <c r="W33" s="346"/>
+      <c r="X33" s="346"/>
+      <c r="Y33" s="346"/>
+      <c r="Z33" s="346"/>
+      <c r="AA33" s="346"/>
+      <c r="AB33" s="346"/>
+      <c r="AC33" s="346"/>
+      <c r="AD33" s="346"/>
+      <c r="AE33" s="347"/>
+      <c r="AF33" s="342"/>
+      <c r="AG33" s="343"/>
+      <c r="AH33" s="343"/>
+      <c r="AI33" s="344"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -18438,161 +18593,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -47000,7 +47000,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47045,12 +47045,12 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
 )</f>
-        <v>1-1-1</v>
+        <v>1-1-2</v>
       </c>
       <c r="B12" s="46"/>
       <c r="C12" s="46"/>
@@ -47080,7 +47080,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47121,12 +47121,12 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
 )</f>
-        <v>2-1-1</v>
+        <v>2-1-2</v>
       </c>
       <c r="B14" s="51"/>
       <c r="C14" s="51"/>
@@ -47156,7 +47156,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47191,7 +47191,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47232,7 +47232,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47275,7 +47275,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47310,7 +47310,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47351,7 +47351,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47386,7 +47386,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D21)&gt;0)*ROW($D$11:D21),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E21),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E21)&gt;0)*ROW($E$11:E21),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E21)&gt;0)*ROW($E$11:E21),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I21),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47421,7 +47421,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D22)&gt;0)*ROW($D$11:D22),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E22),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E22)&gt;0)*ROW($E$11:E22),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E22)&gt;0)*ROW($E$11:E22),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I22),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47458,7 +47458,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D23)&gt;0)*ROW($D$11:D23),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E23),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E23)&gt;0)*ROW($E$11:E23),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E23)&gt;0)*ROW($E$11:E23),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I23),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -47501,7 +47501,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D24)&gt;0)*ROW($D$11:D24),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E24),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E24)&gt;0)*ROW($E$11:E24),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E24)&gt;0)*ROW($E$11:E24),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I24),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE1025E-AC5D-4389-8E8D-1E470504FDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE276F4-F91F-4D61-A96E-B798AB814866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="RWxxxxxxxx_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="XxxAction_リクエスト単体" sheetId="26" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RWxxxxxxxx_リクエスト単体!$A$10:$R$450</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">RWxxxxxxxx_リクエスト単体!$A$1:$R$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$450</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$312</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$450</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">RWxxxxxxxx_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="838">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -11286,10 +11286,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>テストターゲット名：RWxxxxxxxx</t>
-    <rPh sb="8" eb="9">
-      <t>メイ</t>
-    </rPh>
+    <t>リクエストID：XXX</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -30020,7 +30017,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="30" t="s">
-        <v>837</v>
+        <v>742</v>
       </c>
       <c r="O7" s="30" t="s">
         <v>18</v>
@@ -30030,7 +30027,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="32"/>
+      <c r="A8" s="32" t="s">
+        <v>837</v>
+      </c>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
       <c r="D8" s="33"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE276F4-F91F-4D61-A96E-B798AB814866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87AD940-CAC6-46C5-B62E-925C6D05F199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="XxxAction_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="XXX_リクエスト単体" sheetId="26" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XXX_リクエスト単体!$A$10:$R$450</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$450</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XXX_リクエスト単体!$A$1:$R$450</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$312</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$450</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XXX_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -12797,6 +12797,108 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -12903,108 +13005,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -17183,57 +17183,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="285" t="s">
+      <c r="A1" s="319" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="288" t="s">
+      <c r="B1" s="320"/>
+      <c r="C1" s="320"/>
+      <c r="D1" s="321"/>
+      <c r="E1" s="322" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="289"/>
-      <c r="N1" s="290"/>
-      <c r="O1" s="294" t="s">
+      <c r="F1" s="323"/>
+      <c r="G1" s="323"/>
+      <c r="H1" s="323"/>
+      <c r="I1" s="323"/>
+      <c r="J1" s="323"/>
+      <c r="K1" s="323"/>
+      <c r="L1" s="323"/>
+      <c r="M1" s="323"/>
+      <c r="N1" s="324"/>
+      <c r="O1" s="328" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="295"/>
-      <c r="Q1" s="295"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="303" t="s">
+      <c r="P1" s="329"/>
+      <c r="Q1" s="329"/>
+      <c r="R1" s="330"/>
+      <c r="S1" s="337" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="304"/>
-      <c r="U1" s="304"/>
-      <c r="V1" s="304"/>
-      <c r="W1" s="304"/>
-      <c r="X1" s="304"/>
-      <c r="Y1" s="304"/>
-      <c r="Z1" s="305"/>
-      <c r="AA1" s="285" t="s">
+      <c r="T1" s="338"/>
+      <c r="U1" s="338"/>
+      <c r="V1" s="338"/>
+      <c r="W1" s="338"/>
+      <c r="X1" s="338"/>
+      <c r="Y1" s="338"/>
+      <c r="Z1" s="339"/>
+      <c r="AA1" s="319" t="s">
         <v>60</v>
       </c>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="312" t="str">
+      <c r="AB1" s="321"/>
+      <c r="AC1" s="346" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="313"/>
-      <c r="AE1" s="313"/>
-      <c r="AF1" s="314"/>
-      <c r="AG1" s="279">
+      <c r="AD1" s="347"/>
+      <c r="AE1" s="347"/>
+      <c r="AF1" s="348"/>
+      <c r="AG1" s="313">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="280"/>
-      <c r="AI1" s="281"/>
+      <c r="AH1" s="314"/>
+      <c r="AI1" s="315"/>
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
       <c r="AL1" s="13"/>
@@ -17241,53 +17241,53 @@
       <c r="AN1" s="14"/>
     </row>
     <row r="2" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="285" t="s">
+      <c r="A2" s="319" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="286"/>
-      <c r="C2" s="286"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="288" t="s">
+      <c r="B2" s="320"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="321"/>
+      <c r="E2" s="322" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="289"/>
-      <c r="G2" s="289"/>
-      <c r="H2" s="289"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="289"/>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="289"/>
-      <c r="N2" s="290"/>
-      <c r="O2" s="297"/>
-      <c r="P2" s="298"/>
-      <c r="Q2" s="298"/>
-      <c r="R2" s="299"/>
-      <c r="S2" s="306"/>
-      <c r="T2" s="307"/>
-      <c r="U2" s="307"/>
-      <c r="V2" s="307"/>
-      <c r="W2" s="307"/>
-      <c r="X2" s="307"/>
-      <c r="Y2" s="307"/>
-      <c r="Z2" s="308"/>
-      <c r="AA2" s="285" t="s">
+      <c r="F2" s="323"/>
+      <c r="G2" s="323"/>
+      <c r="H2" s="323"/>
+      <c r="I2" s="323"/>
+      <c r="J2" s="323"/>
+      <c r="K2" s="323"/>
+      <c r="L2" s="323"/>
+      <c r="M2" s="323"/>
+      <c r="N2" s="324"/>
+      <c r="O2" s="331"/>
+      <c r="P2" s="332"/>
+      <c r="Q2" s="332"/>
+      <c r="R2" s="333"/>
+      <c r="S2" s="340"/>
+      <c r="T2" s="341"/>
+      <c r="U2" s="341"/>
+      <c r="V2" s="341"/>
+      <c r="W2" s="341"/>
+      <c r="X2" s="341"/>
+      <c r="Y2" s="341"/>
+      <c r="Z2" s="342"/>
+      <c r="AA2" s="319" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="287"/>
-      <c r="AC2" s="291" t="str">
+      <c r="AB2" s="321"/>
+      <c r="AC2" s="325" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="292"/>
-      <c r="AE2" s="292"/>
-      <c r="AF2" s="293"/>
-      <c r="AG2" s="279">
+      <c r="AD2" s="326"/>
+      <c r="AE2" s="326"/>
+      <c r="AF2" s="327"/>
+      <c r="AG2" s="313">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="280"/>
-      <c r="AI2" s="281"/>
+      <c r="AH2" s="314"/>
+      <c r="AI2" s="315"/>
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
       <c r="AL2" s="13"/>
@@ -17295,45 +17295,45 @@
       <c r="AN2" s="13"/>
     </row>
     <row r="3" spans="1:40" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="285" t="s">
+      <c r="A3" s="319" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="286"/>
-      <c r="C3" s="286"/>
-      <c r="D3" s="287"/>
-      <c r="E3" s="288" t="s">
+      <c r="B3" s="320"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="322" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="289"/>
-      <c r="G3" s="289"/>
-      <c r="H3" s="289"/>
-      <c r="I3" s="289"/>
-      <c r="J3" s="289"/>
-      <c r="K3" s="289"/>
-      <c r="L3" s="289"/>
-      <c r="M3" s="289"/>
-      <c r="N3" s="290"/>
-      <c r="O3" s="300"/>
-      <c r="P3" s="301"/>
-      <c r="Q3" s="301"/>
-      <c r="R3" s="302"/>
-      <c r="S3" s="309"/>
-      <c r="T3" s="310"/>
-      <c r="U3" s="310"/>
-      <c r="V3" s="310"/>
-      <c r="W3" s="310"/>
-      <c r="X3" s="310"/>
-      <c r="Y3" s="310"/>
-      <c r="Z3" s="311"/>
-      <c r="AA3" s="285"/>
-      <c r="AB3" s="287"/>
-      <c r="AC3" s="312"/>
-      <c r="AD3" s="313"/>
-      <c r="AE3" s="313"/>
-      <c r="AF3" s="314"/>
-      <c r="AG3" s="279"/>
-      <c r="AH3" s="280"/>
-      <c r="AI3" s="281"/>
+      <c r="F3" s="323"/>
+      <c r="G3" s="323"/>
+      <c r="H3" s="323"/>
+      <c r="I3" s="323"/>
+      <c r="J3" s="323"/>
+      <c r="K3" s="323"/>
+      <c r="L3" s="323"/>
+      <c r="M3" s="323"/>
+      <c r="N3" s="324"/>
+      <c r="O3" s="334"/>
+      <c r="P3" s="335"/>
+      <c r="Q3" s="335"/>
+      <c r="R3" s="336"/>
+      <c r="S3" s="343"/>
+      <c r="T3" s="344"/>
+      <c r="U3" s="344"/>
+      <c r="V3" s="344"/>
+      <c r="W3" s="344"/>
+      <c r="X3" s="344"/>
+      <c r="Y3" s="344"/>
+      <c r="Z3" s="345"/>
+      <c r="AA3" s="319"/>
+      <c r="AB3" s="321"/>
+      <c r="AC3" s="346"/>
+      <c r="AD3" s="347"/>
+      <c r="AE3" s="347"/>
+      <c r="AF3" s="348"/>
+      <c r="AG3" s="313"/>
+      <c r="AH3" s="314"/>
+      <c r="AI3" s="315"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
@@ -17370,97 +17370,97 @@
       <c r="A7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="282" t="s">
+      <c r="B7" s="316" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="283"/>
-      <c r="D7" s="282" t="s">
+      <c r="C7" s="317"/>
+      <c r="D7" s="316" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="284"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="282" t="s">
+      <c r="E7" s="318"/>
+      <c r="F7" s="317"/>
+      <c r="G7" s="316" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="284"/>
-      <c r="I7" s="283"/>
-      <c r="J7" s="282" t="s">
+      <c r="H7" s="318"/>
+      <c r="I7" s="317"/>
+      <c r="J7" s="316" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="284"/>
-      <c r="L7" s="284"/>
-      <c r="M7" s="284"/>
-      <c r="N7" s="284"/>
-      <c r="O7" s="284"/>
-      <c r="P7" s="283"/>
-      <c r="Q7" s="282" t="s">
+      <c r="K7" s="318"/>
+      <c r="L7" s="318"/>
+      <c r="M7" s="318"/>
+      <c r="N7" s="318"/>
+      <c r="O7" s="318"/>
+      <c r="P7" s="317"/>
+      <c r="Q7" s="316" t="s">
         <v>69</v>
       </c>
-      <c r="R7" s="284"/>
-      <c r="S7" s="284"/>
-      <c r="T7" s="284"/>
-      <c r="U7" s="284"/>
-      <c r="V7" s="284"/>
-      <c r="W7" s="284"/>
-      <c r="X7" s="284"/>
-      <c r="Y7" s="284"/>
-      <c r="Z7" s="284"/>
-      <c r="AA7" s="284"/>
-      <c r="AB7" s="284"/>
-      <c r="AC7" s="284"/>
-      <c r="AD7" s="284"/>
-      <c r="AE7" s="283"/>
-      <c r="AF7" s="282" t="s">
+      <c r="R7" s="318"/>
+      <c r="S7" s="318"/>
+      <c r="T7" s="318"/>
+      <c r="U7" s="318"/>
+      <c r="V7" s="318"/>
+      <c r="W7" s="318"/>
+      <c r="X7" s="318"/>
+      <c r="Y7" s="318"/>
+      <c r="Z7" s="318"/>
+      <c r="AA7" s="318"/>
+      <c r="AB7" s="318"/>
+      <c r="AC7" s="318"/>
+      <c r="AD7" s="318"/>
+      <c r="AE7" s="317"/>
+      <c r="AF7" s="316" t="s">
         <v>70</v>
       </c>
-      <c r="AG7" s="284"/>
-      <c r="AH7" s="284"/>
-      <c r="AI7" s="283"/>
+      <c r="AG7" s="318"/>
+      <c r="AH7" s="318"/>
+      <c r="AI7" s="317"/>
     </row>
     <row r="8" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="26">
         <v>1</v>
       </c>
-      <c r="B8" s="327" t="s">
+      <c r="B8" s="304" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="328"/>
-      <c r="D8" s="329">
+      <c r="C8" s="305"/>
+      <c r="D8" s="306">
         <v>43336</v>
       </c>
-      <c r="E8" s="330"/>
-      <c r="F8" s="331"/>
-      <c r="G8" s="327" t="s">
+      <c r="E8" s="307"/>
+      <c r="F8" s="308"/>
+      <c r="G8" s="304" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="332"/>
-      <c r="I8" s="328"/>
-      <c r="J8" s="333" t="s">
+      <c r="H8" s="309"/>
+      <c r="I8" s="305"/>
+      <c r="J8" s="310" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
-      <c r="N8" s="334"/>
-      <c r="O8" s="334"/>
-      <c r="P8" s="335"/>
-      <c r="Q8" s="333" t="s">
+      <c r="K8" s="311"/>
+      <c r="L8" s="311"/>
+      <c r="M8" s="311"/>
+      <c r="N8" s="311"/>
+      <c r="O8" s="311"/>
+      <c r="P8" s="312"/>
+      <c r="Q8" s="310" t="s">
         <v>78</v>
       </c>
-      <c r="R8" s="334"/>
-      <c r="S8" s="334"/>
-      <c r="T8" s="334"/>
-      <c r="U8" s="334"/>
-      <c r="V8" s="334"/>
-      <c r="W8" s="334"/>
-      <c r="X8" s="334"/>
-      <c r="Y8" s="334"/>
-      <c r="Z8" s="334"/>
-      <c r="AA8" s="334"/>
-      <c r="AB8" s="334"/>
-      <c r="AC8" s="334"/>
-      <c r="AD8" s="334"/>
-      <c r="AE8" s="335"/>
+      <c r="R8" s="311"/>
+      <c r="S8" s="311"/>
+      <c r="T8" s="311"/>
+      <c r="U8" s="311"/>
+      <c r="V8" s="311"/>
+      <c r="W8" s="311"/>
+      <c r="X8" s="311"/>
+      <c r="Y8" s="311"/>
+      <c r="Z8" s="311"/>
+      <c r="AA8" s="311"/>
+      <c r="AB8" s="311"/>
+      <c r="AC8" s="311"/>
+      <c r="AD8" s="311"/>
+      <c r="AE8" s="312"/>
       <c r="AF8" s="27" t="s">
         <v>79</v>
       </c>
@@ -17472,1101 +17472,946 @@
       <c r="A9" s="26">
         <v>2</v>
       </c>
-      <c r="B9" s="315" t="s">
+      <c r="B9" s="292" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="316"/>
-      <c r="D9" s="317">
+      <c r="C9" s="293"/>
+      <c r="D9" s="294">
         <v>44852</v>
       </c>
-      <c r="E9" s="318"/>
-      <c r="F9" s="319"/>
-      <c r="G9" s="317" t="s">
+      <c r="E9" s="295"/>
+      <c r="F9" s="296"/>
+      <c r="G9" s="294" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="320"/>
-      <c r="I9" s="316"/>
-      <c r="J9" s="321" t="s">
+      <c r="H9" s="297"/>
+      <c r="I9" s="293"/>
+      <c r="J9" s="298" t="s">
         <v>740</v>
       </c>
-      <c r="K9" s="322"/>
-      <c r="L9" s="322"/>
-      <c r="M9" s="322"/>
-      <c r="N9" s="322"/>
-      <c r="O9" s="322"/>
-      <c r="P9" s="323"/>
-      <c r="Q9" s="321" t="s">
+      <c r="K9" s="299"/>
+      <c r="L9" s="299"/>
+      <c r="M9" s="299"/>
+      <c r="N9" s="299"/>
+      <c r="O9" s="299"/>
+      <c r="P9" s="300"/>
+      <c r="Q9" s="298" t="s">
         <v>741</v>
       </c>
-      <c r="R9" s="324"/>
-      <c r="S9" s="324"/>
-      <c r="T9" s="324"/>
-      <c r="U9" s="324"/>
-      <c r="V9" s="324"/>
-      <c r="W9" s="324"/>
-      <c r="X9" s="324"/>
-      <c r="Y9" s="324"/>
-      <c r="Z9" s="324"/>
-      <c r="AA9" s="324"/>
-      <c r="AB9" s="324"/>
-      <c r="AC9" s="324"/>
-      <c r="AD9" s="324"/>
-      <c r="AE9" s="325"/>
-      <c r="AF9" s="326" t="s">
+      <c r="R9" s="301"/>
+      <c r="S9" s="301"/>
+      <c r="T9" s="301"/>
+      <c r="U9" s="301"/>
+      <c r="V9" s="301"/>
+      <c r="W9" s="301"/>
+      <c r="X9" s="301"/>
+      <c r="Y9" s="301"/>
+      <c r="Z9" s="301"/>
+      <c r="AA9" s="301"/>
+      <c r="AB9" s="301"/>
+      <c r="AC9" s="301"/>
+      <c r="AD9" s="301"/>
+      <c r="AE9" s="302"/>
+      <c r="AF9" s="303" t="s">
         <v>79</v>
       </c>
-      <c r="AG9" s="322"/>
-      <c r="AH9" s="322"/>
-      <c r="AI9" s="323"/>
+      <c r="AG9" s="299"/>
+      <c r="AH9" s="299"/>
+      <c r="AI9" s="300"/>
     </row>
     <row r="10" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="B10" s="336"/>
-      <c r="C10" s="337"/>
-      <c r="D10" s="338"/>
-      <c r="E10" s="339"/>
-      <c r="F10" s="340"/>
-      <c r="G10" s="336"/>
-      <c r="H10" s="341"/>
-      <c r="I10" s="337"/>
-      <c r="J10" s="342"/>
-      <c r="K10" s="343"/>
-      <c r="L10" s="343"/>
-      <c r="M10" s="343"/>
-      <c r="N10" s="343"/>
-      <c r="O10" s="343"/>
-      <c r="P10" s="344"/>
-      <c r="Q10" s="345"/>
-      <c r="R10" s="346"/>
-      <c r="S10" s="346"/>
-      <c r="T10" s="346"/>
-      <c r="U10" s="346"/>
-      <c r="V10" s="346"/>
-      <c r="W10" s="346"/>
-      <c r="X10" s="346"/>
-      <c r="Y10" s="346"/>
-      <c r="Z10" s="346"/>
-      <c r="AA10" s="346"/>
-      <c r="AB10" s="346"/>
-      <c r="AC10" s="346"/>
-      <c r="AD10" s="346"/>
-      <c r="AE10" s="347"/>
-      <c r="AF10" s="342"/>
-      <c r="AG10" s="343"/>
-      <c r="AH10" s="343"/>
-      <c r="AI10" s="344"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="280"/>
+      <c r="D10" s="281"/>
+      <c r="E10" s="282"/>
+      <c r="F10" s="283"/>
+      <c r="G10" s="279"/>
+      <c r="H10" s="284"/>
+      <c r="I10" s="280"/>
+      <c r="J10" s="285"/>
+      <c r="K10" s="286"/>
+      <c r="L10" s="286"/>
+      <c r="M10" s="286"/>
+      <c r="N10" s="286"/>
+      <c r="O10" s="286"/>
+      <c r="P10" s="287"/>
+      <c r="Q10" s="288"/>
+      <c r="R10" s="289"/>
+      <c r="S10" s="289"/>
+      <c r="T10" s="289"/>
+      <c r="U10" s="289"/>
+      <c r="V10" s="289"/>
+      <c r="W10" s="289"/>
+      <c r="X10" s="289"/>
+      <c r="Y10" s="289"/>
+      <c r="Z10" s="289"/>
+      <c r="AA10" s="289"/>
+      <c r="AB10" s="289"/>
+      <c r="AC10" s="289"/>
+      <c r="AD10" s="289"/>
+      <c r="AE10" s="290"/>
+      <c r="AF10" s="285"/>
+      <c r="AG10" s="286"/>
+      <c r="AH10" s="286"/>
+      <c r="AI10" s="287"/>
     </row>
     <row r="11" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="23"/>
-      <c r="B11" s="336"/>
-      <c r="C11" s="337"/>
-      <c r="D11" s="338"/>
-      <c r="E11" s="339"/>
-      <c r="F11" s="340"/>
-      <c r="G11" s="336"/>
-      <c r="H11" s="341"/>
-      <c r="I11" s="337"/>
-      <c r="J11" s="342"/>
-      <c r="K11" s="343"/>
-      <c r="L11" s="343"/>
-      <c r="M11" s="343"/>
-      <c r="N11" s="343"/>
-      <c r="O11" s="343"/>
-      <c r="P11" s="344"/>
-      <c r="Q11" s="345"/>
-      <c r="R11" s="346"/>
-      <c r="S11" s="346"/>
-      <c r="T11" s="346"/>
-      <c r="U11" s="346"/>
-      <c r="V11" s="346"/>
-      <c r="W11" s="346"/>
-      <c r="X11" s="346"/>
-      <c r="Y11" s="346"/>
-      <c r="Z11" s="346"/>
-      <c r="AA11" s="346"/>
-      <c r="AB11" s="346"/>
-      <c r="AC11" s="346"/>
-      <c r="AD11" s="346"/>
-      <c r="AE11" s="347"/>
-      <c r="AF11" s="342"/>
-      <c r="AG11" s="343"/>
-      <c r="AH11" s="343"/>
-      <c r="AI11" s="344"/>
+      <c r="B11" s="279"/>
+      <c r="C11" s="280"/>
+      <c r="D11" s="281"/>
+      <c r="E11" s="282"/>
+      <c r="F11" s="283"/>
+      <c r="G11" s="279"/>
+      <c r="H11" s="284"/>
+      <c r="I11" s="280"/>
+      <c r="J11" s="285"/>
+      <c r="K11" s="286"/>
+      <c r="L11" s="286"/>
+      <c r="M11" s="286"/>
+      <c r="N11" s="286"/>
+      <c r="O11" s="286"/>
+      <c r="P11" s="287"/>
+      <c r="Q11" s="288"/>
+      <c r="R11" s="289"/>
+      <c r="S11" s="289"/>
+      <c r="T11" s="289"/>
+      <c r="U11" s="289"/>
+      <c r="V11" s="289"/>
+      <c r="W11" s="289"/>
+      <c r="X11" s="289"/>
+      <c r="Y11" s="289"/>
+      <c r="Z11" s="289"/>
+      <c r="AA11" s="289"/>
+      <c r="AB11" s="289"/>
+      <c r="AC11" s="289"/>
+      <c r="AD11" s="289"/>
+      <c r="AE11" s="290"/>
+      <c r="AF11" s="285"/>
+      <c r="AG11" s="286"/>
+      <c r="AH11" s="286"/>
+      <c r="AI11" s="287"/>
     </row>
     <row r="12" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="23"/>
-      <c r="B12" s="336"/>
-      <c r="C12" s="337"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="340"/>
-      <c r="G12" s="336"/>
-      <c r="H12" s="341"/>
-      <c r="I12" s="337"/>
-      <c r="J12" s="342"/>
-      <c r="K12" s="343"/>
-      <c r="L12" s="343"/>
-      <c r="M12" s="343"/>
-      <c r="N12" s="343"/>
-      <c r="O12" s="343"/>
-      <c r="P12" s="344"/>
-      <c r="Q12" s="345"/>
-      <c r="R12" s="346"/>
-      <c r="S12" s="346"/>
-      <c r="T12" s="346"/>
-      <c r="U12" s="346"/>
-      <c r="V12" s="346"/>
-      <c r="W12" s="346"/>
-      <c r="X12" s="346"/>
-      <c r="Y12" s="346"/>
-      <c r="Z12" s="346"/>
-      <c r="AA12" s="346"/>
-      <c r="AB12" s="346"/>
-      <c r="AC12" s="346"/>
-      <c r="AD12" s="346"/>
-      <c r="AE12" s="347"/>
-      <c r="AF12" s="342"/>
-      <c r="AG12" s="343"/>
-      <c r="AH12" s="343"/>
-      <c r="AI12" s="344"/>
+      <c r="B12" s="279"/>
+      <c r="C12" s="280"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="282"/>
+      <c r="F12" s="283"/>
+      <c r="G12" s="279"/>
+      <c r="H12" s="284"/>
+      <c r="I12" s="280"/>
+      <c r="J12" s="285"/>
+      <c r="K12" s="286"/>
+      <c r="L12" s="286"/>
+      <c r="M12" s="286"/>
+      <c r="N12" s="286"/>
+      <c r="O12" s="286"/>
+      <c r="P12" s="287"/>
+      <c r="Q12" s="288"/>
+      <c r="R12" s="289"/>
+      <c r="S12" s="289"/>
+      <c r="T12" s="289"/>
+      <c r="U12" s="289"/>
+      <c r="V12" s="289"/>
+      <c r="W12" s="289"/>
+      <c r="X12" s="289"/>
+      <c r="Y12" s="289"/>
+      <c r="Z12" s="289"/>
+      <c r="AA12" s="289"/>
+      <c r="AB12" s="289"/>
+      <c r="AC12" s="289"/>
+      <c r="AD12" s="289"/>
+      <c r="AE12" s="290"/>
+      <c r="AF12" s="285"/>
+      <c r="AG12" s="286"/>
+      <c r="AH12" s="286"/>
+      <c r="AI12" s="287"/>
     </row>
     <row r="13" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="23"/>
-      <c r="B13" s="336"/>
-      <c r="C13" s="337"/>
-      <c r="D13" s="338"/>
-      <c r="E13" s="339"/>
-      <c r="F13" s="340"/>
-      <c r="G13" s="336"/>
-      <c r="H13" s="341"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="342"/>
-      <c r="K13" s="343"/>
-      <c r="L13" s="343"/>
-      <c r="M13" s="343"/>
-      <c r="N13" s="343"/>
-      <c r="O13" s="343"/>
-      <c r="P13" s="344"/>
-      <c r="Q13" s="345"/>
-      <c r="R13" s="346"/>
-      <c r="S13" s="346"/>
-      <c r="T13" s="346"/>
-      <c r="U13" s="346"/>
-      <c r="V13" s="346"/>
-      <c r="W13" s="346"/>
-      <c r="X13" s="346"/>
-      <c r="Y13" s="346"/>
-      <c r="Z13" s="346"/>
-      <c r="AA13" s="346"/>
-      <c r="AB13" s="346"/>
-      <c r="AC13" s="346"/>
-      <c r="AD13" s="346"/>
-      <c r="AE13" s="347"/>
-      <c r="AF13" s="342"/>
-      <c r="AG13" s="343"/>
-      <c r="AH13" s="343"/>
-      <c r="AI13" s="344"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="280"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="282"/>
+      <c r="F13" s="283"/>
+      <c r="G13" s="279"/>
+      <c r="H13" s="284"/>
+      <c r="I13" s="280"/>
+      <c r="J13" s="285"/>
+      <c r="K13" s="286"/>
+      <c r="L13" s="286"/>
+      <c r="M13" s="286"/>
+      <c r="N13" s="286"/>
+      <c r="O13" s="286"/>
+      <c r="P13" s="287"/>
+      <c r="Q13" s="288"/>
+      <c r="R13" s="289"/>
+      <c r="S13" s="289"/>
+      <c r="T13" s="289"/>
+      <c r="U13" s="289"/>
+      <c r="V13" s="289"/>
+      <c r="W13" s="289"/>
+      <c r="X13" s="289"/>
+      <c r="Y13" s="289"/>
+      <c r="Z13" s="289"/>
+      <c r="AA13" s="289"/>
+      <c r="AB13" s="289"/>
+      <c r="AC13" s="289"/>
+      <c r="AD13" s="289"/>
+      <c r="AE13" s="290"/>
+      <c r="AF13" s="285"/>
+      <c r="AG13" s="286"/>
+      <c r="AH13" s="286"/>
+      <c r="AI13" s="287"/>
     </row>
     <row r="14" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="23"/>
-      <c r="B14" s="336"/>
-      <c r="C14" s="337"/>
-      <c r="D14" s="338"/>
-      <c r="E14" s="339"/>
-      <c r="F14" s="340"/>
-      <c r="G14" s="336"/>
-      <c r="H14" s="341"/>
-      <c r="I14" s="337"/>
-      <c r="J14" s="342"/>
-      <c r="K14" s="343"/>
-      <c r="L14" s="343"/>
-      <c r="M14" s="343"/>
-      <c r="N14" s="343"/>
-      <c r="O14" s="343"/>
-      <c r="P14" s="344"/>
-      <c r="Q14" s="345"/>
-      <c r="R14" s="346"/>
-      <c r="S14" s="346"/>
-      <c r="T14" s="346"/>
-      <c r="U14" s="346"/>
-      <c r="V14" s="346"/>
-      <c r="W14" s="346"/>
-      <c r="X14" s="346"/>
-      <c r="Y14" s="346"/>
-      <c r="Z14" s="346"/>
-      <c r="AA14" s="346"/>
-      <c r="AB14" s="346"/>
-      <c r="AC14" s="346"/>
-      <c r="AD14" s="346"/>
-      <c r="AE14" s="347"/>
-      <c r="AF14" s="342"/>
-      <c r="AG14" s="343"/>
-      <c r="AH14" s="343"/>
-      <c r="AI14" s="344"/>
+      <c r="B14" s="279"/>
+      <c r="C14" s="280"/>
+      <c r="D14" s="281"/>
+      <c r="E14" s="282"/>
+      <c r="F14" s="283"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="284"/>
+      <c r="I14" s="280"/>
+      <c r="J14" s="285"/>
+      <c r="K14" s="286"/>
+      <c r="L14" s="286"/>
+      <c r="M14" s="286"/>
+      <c r="N14" s="286"/>
+      <c r="O14" s="286"/>
+      <c r="P14" s="287"/>
+      <c r="Q14" s="288"/>
+      <c r="R14" s="289"/>
+      <c r="S14" s="289"/>
+      <c r="T14" s="289"/>
+      <c r="U14" s="289"/>
+      <c r="V14" s="289"/>
+      <c r="W14" s="289"/>
+      <c r="X14" s="289"/>
+      <c r="Y14" s="289"/>
+      <c r="Z14" s="289"/>
+      <c r="AA14" s="289"/>
+      <c r="AB14" s="289"/>
+      <c r="AC14" s="289"/>
+      <c r="AD14" s="289"/>
+      <c r="AE14" s="290"/>
+      <c r="AF14" s="285"/>
+      <c r="AG14" s="286"/>
+      <c r="AH14" s="286"/>
+      <c r="AI14" s="287"/>
     </row>
     <row r="15" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="23"/>
-      <c r="B15" s="336"/>
-      <c r="C15" s="337"/>
-      <c r="D15" s="338"/>
-      <c r="E15" s="339"/>
-      <c r="F15" s="340"/>
-      <c r="G15" s="336"/>
-      <c r="H15" s="341"/>
-      <c r="I15" s="337"/>
-      <c r="J15" s="342"/>
-      <c r="K15" s="343"/>
-      <c r="L15" s="343"/>
-      <c r="M15" s="343"/>
-      <c r="N15" s="343"/>
-      <c r="O15" s="343"/>
-      <c r="P15" s="344"/>
-      <c r="Q15" s="345"/>
-      <c r="R15" s="346"/>
-      <c r="S15" s="346"/>
-      <c r="T15" s="346"/>
-      <c r="U15" s="346"/>
-      <c r="V15" s="346"/>
-      <c r="W15" s="346"/>
-      <c r="X15" s="346"/>
-      <c r="Y15" s="346"/>
-      <c r="Z15" s="346"/>
-      <c r="AA15" s="346"/>
-      <c r="AB15" s="346"/>
-      <c r="AC15" s="346"/>
-      <c r="AD15" s="346"/>
-      <c r="AE15" s="347"/>
-      <c r="AF15" s="342"/>
-      <c r="AG15" s="343"/>
-      <c r="AH15" s="343"/>
-      <c r="AI15" s="344"/>
+      <c r="B15" s="279"/>
+      <c r="C15" s="280"/>
+      <c r="D15" s="281"/>
+      <c r="E15" s="282"/>
+      <c r="F15" s="283"/>
+      <c r="G15" s="279"/>
+      <c r="H15" s="284"/>
+      <c r="I15" s="280"/>
+      <c r="J15" s="285"/>
+      <c r="K15" s="286"/>
+      <c r="L15" s="286"/>
+      <c r="M15" s="286"/>
+      <c r="N15" s="286"/>
+      <c r="O15" s="286"/>
+      <c r="P15" s="287"/>
+      <c r="Q15" s="288"/>
+      <c r="R15" s="289"/>
+      <c r="S15" s="289"/>
+      <c r="T15" s="289"/>
+      <c r="U15" s="289"/>
+      <c r="V15" s="289"/>
+      <c r="W15" s="289"/>
+      <c r="X15" s="289"/>
+      <c r="Y15" s="289"/>
+      <c r="Z15" s="289"/>
+      <c r="AA15" s="289"/>
+      <c r="AB15" s="289"/>
+      <c r="AC15" s="289"/>
+      <c r="AD15" s="289"/>
+      <c r="AE15" s="290"/>
+      <c r="AF15" s="285"/>
+      <c r="AG15" s="286"/>
+      <c r="AH15" s="286"/>
+      <c r="AI15" s="287"/>
     </row>
     <row r="16" spans="1:40" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="23"/>
-      <c r="B16" s="336"/>
-      <c r="C16" s="337"/>
-      <c r="D16" s="338"/>
-      <c r="E16" s="339"/>
-      <c r="F16" s="340"/>
-      <c r="G16" s="336"/>
-      <c r="H16" s="341"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="342"/>
-      <c r="K16" s="343"/>
-      <c r="L16" s="343"/>
-      <c r="M16" s="343"/>
-      <c r="N16" s="343"/>
-      <c r="O16" s="343"/>
-      <c r="P16" s="344"/>
-      <c r="Q16" s="345"/>
-      <c r="R16" s="346"/>
-      <c r="S16" s="346"/>
-      <c r="T16" s="346"/>
-      <c r="U16" s="346"/>
-      <c r="V16" s="346"/>
-      <c r="W16" s="346"/>
-      <c r="X16" s="346"/>
-      <c r="Y16" s="346"/>
-      <c r="Z16" s="346"/>
-      <c r="AA16" s="346"/>
-      <c r="AB16" s="346"/>
-      <c r="AC16" s="346"/>
-      <c r="AD16" s="346"/>
-      <c r="AE16" s="347"/>
-      <c r="AF16" s="342"/>
-      <c r="AG16" s="343"/>
-      <c r="AH16" s="343"/>
-      <c r="AI16" s="344"/>
+      <c r="B16" s="279"/>
+      <c r="C16" s="280"/>
+      <c r="D16" s="281"/>
+      <c r="E16" s="282"/>
+      <c r="F16" s="283"/>
+      <c r="G16" s="279"/>
+      <c r="H16" s="284"/>
+      <c r="I16" s="280"/>
+      <c r="J16" s="285"/>
+      <c r="K16" s="286"/>
+      <c r="L16" s="286"/>
+      <c r="M16" s="286"/>
+      <c r="N16" s="286"/>
+      <c r="O16" s="286"/>
+      <c r="P16" s="287"/>
+      <c r="Q16" s="288"/>
+      <c r="R16" s="289"/>
+      <c r="S16" s="289"/>
+      <c r="T16" s="289"/>
+      <c r="U16" s="289"/>
+      <c r="V16" s="289"/>
+      <c r="W16" s="289"/>
+      <c r="X16" s="289"/>
+      <c r="Y16" s="289"/>
+      <c r="Z16" s="289"/>
+      <c r="AA16" s="289"/>
+      <c r="AB16" s="289"/>
+      <c r="AC16" s="289"/>
+      <c r="AD16" s="289"/>
+      <c r="AE16" s="290"/>
+      <c r="AF16" s="285"/>
+      <c r="AG16" s="286"/>
+      <c r="AH16" s="286"/>
+      <c r="AI16" s="287"/>
     </row>
     <row r="17" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="23"/>
-      <c r="B17" s="336"/>
-      <c r="C17" s="337"/>
-      <c r="D17" s="338"/>
-      <c r="E17" s="339"/>
-      <c r="F17" s="340"/>
-      <c r="G17" s="336"/>
-      <c r="H17" s="341"/>
-      <c r="I17" s="337"/>
-      <c r="J17" s="342"/>
-      <c r="K17" s="343"/>
-      <c r="L17" s="343"/>
-      <c r="M17" s="343"/>
-      <c r="N17" s="343"/>
-      <c r="O17" s="343"/>
-      <c r="P17" s="344"/>
-      <c r="Q17" s="345"/>
-      <c r="R17" s="346"/>
-      <c r="S17" s="346"/>
-      <c r="T17" s="346"/>
-      <c r="U17" s="346"/>
-      <c r="V17" s="346"/>
-      <c r="W17" s="346"/>
-      <c r="X17" s="346"/>
-      <c r="Y17" s="346"/>
-      <c r="Z17" s="346"/>
-      <c r="AA17" s="346"/>
-      <c r="AB17" s="346"/>
-      <c r="AC17" s="346"/>
-      <c r="AD17" s="346"/>
-      <c r="AE17" s="347"/>
-      <c r="AF17" s="342"/>
-      <c r="AG17" s="343"/>
-      <c r="AH17" s="343"/>
-      <c r="AI17" s="344"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="280"/>
+      <c r="D17" s="281"/>
+      <c r="E17" s="282"/>
+      <c r="F17" s="283"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="284"/>
+      <c r="I17" s="280"/>
+      <c r="J17" s="285"/>
+      <c r="K17" s="286"/>
+      <c r="L17" s="286"/>
+      <c r="M17" s="286"/>
+      <c r="N17" s="286"/>
+      <c r="O17" s="286"/>
+      <c r="P17" s="287"/>
+      <c r="Q17" s="288"/>
+      <c r="R17" s="289"/>
+      <c r="S17" s="289"/>
+      <c r="T17" s="289"/>
+      <c r="U17" s="289"/>
+      <c r="V17" s="289"/>
+      <c r="W17" s="289"/>
+      <c r="X17" s="289"/>
+      <c r="Y17" s="289"/>
+      <c r="Z17" s="289"/>
+      <c r="AA17" s="289"/>
+      <c r="AB17" s="289"/>
+      <c r="AC17" s="289"/>
+      <c r="AD17" s="289"/>
+      <c r="AE17" s="290"/>
+      <c r="AF17" s="285"/>
+      <c r="AG17" s="286"/>
+      <c r="AH17" s="286"/>
+      <c r="AI17" s="287"/>
     </row>
     <row r="18" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="23"/>
-      <c r="B18" s="336"/>
-      <c r="C18" s="337"/>
-      <c r="D18" s="338"/>
-      <c r="E18" s="339"/>
-      <c r="F18" s="340"/>
-      <c r="G18" s="336"/>
-      <c r="H18" s="341"/>
-      <c r="I18" s="337"/>
-      <c r="J18" s="342"/>
-      <c r="K18" s="343"/>
-      <c r="L18" s="343"/>
-      <c r="M18" s="343"/>
-      <c r="N18" s="343"/>
-      <c r="O18" s="343"/>
-      <c r="P18" s="344"/>
-      <c r="Q18" s="345"/>
-      <c r="R18" s="346"/>
-      <c r="S18" s="346"/>
-      <c r="T18" s="346"/>
-      <c r="U18" s="346"/>
-      <c r="V18" s="346"/>
-      <c r="W18" s="346"/>
-      <c r="X18" s="346"/>
-      <c r="Y18" s="346"/>
-      <c r="Z18" s="346"/>
-      <c r="AA18" s="346"/>
-      <c r="AB18" s="346"/>
-      <c r="AC18" s="346"/>
-      <c r="AD18" s="346"/>
-      <c r="AE18" s="347"/>
-      <c r="AF18" s="342"/>
-      <c r="AG18" s="343"/>
-      <c r="AH18" s="343"/>
-      <c r="AI18" s="344"/>
+      <c r="B18" s="279"/>
+      <c r="C18" s="280"/>
+      <c r="D18" s="281"/>
+      <c r="E18" s="282"/>
+      <c r="F18" s="283"/>
+      <c r="G18" s="279"/>
+      <c r="H18" s="284"/>
+      <c r="I18" s="280"/>
+      <c r="J18" s="285"/>
+      <c r="K18" s="286"/>
+      <c r="L18" s="286"/>
+      <c r="M18" s="286"/>
+      <c r="N18" s="286"/>
+      <c r="O18" s="286"/>
+      <c r="P18" s="287"/>
+      <c r="Q18" s="288"/>
+      <c r="R18" s="289"/>
+      <c r="S18" s="289"/>
+      <c r="T18" s="289"/>
+      <c r="U18" s="289"/>
+      <c r="V18" s="289"/>
+      <c r="W18" s="289"/>
+      <c r="X18" s="289"/>
+      <c r="Y18" s="289"/>
+      <c r="Z18" s="289"/>
+      <c r="AA18" s="289"/>
+      <c r="AB18" s="289"/>
+      <c r="AC18" s="289"/>
+      <c r="AD18" s="289"/>
+      <c r="AE18" s="290"/>
+      <c r="AF18" s="285"/>
+      <c r="AG18" s="286"/>
+      <c r="AH18" s="286"/>
+      <c r="AI18" s="287"/>
     </row>
     <row r="19" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="23"/>
-      <c r="B19" s="336"/>
-      <c r="C19" s="337"/>
-      <c r="D19" s="338"/>
-      <c r="E19" s="339"/>
-      <c r="F19" s="340"/>
-      <c r="G19" s="336"/>
-      <c r="H19" s="341"/>
-      <c r="I19" s="337"/>
-      <c r="J19" s="342"/>
-      <c r="K19" s="343"/>
-      <c r="L19" s="343"/>
-      <c r="M19" s="343"/>
-      <c r="N19" s="343"/>
-      <c r="O19" s="343"/>
-      <c r="P19" s="344"/>
-      <c r="Q19" s="345"/>
-      <c r="R19" s="346"/>
-      <c r="S19" s="346"/>
-      <c r="T19" s="346"/>
-      <c r="U19" s="346"/>
-      <c r="V19" s="346"/>
-      <c r="W19" s="346"/>
-      <c r="X19" s="346"/>
-      <c r="Y19" s="346"/>
-      <c r="Z19" s="346"/>
-      <c r="AA19" s="346"/>
-      <c r="AB19" s="346"/>
-      <c r="AC19" s="346"/>
-      <c r="AD19" s="346"/>
-      <c r="AE19" s="347"/>
-      <c r="AF19" s="342"/>
-      <c r="AG19" s="343"/>
-      <c r="AH19" s="343"/>
-      <c r="AI19" s="344"/>
+      <c r="B19" s="279"/>
+      <c r="C19" s="280"/>
+      <c r="D19" s="281"/>
+      <c r="E19" s="282"/>
+      <c r="F19" s="283"/>
+      <c r="G19" s="279"/>
+      <c r="H19" s="284"/>
+      <c r="I19" s="280"/>
+      <c r="J19" s="285"/>
+      <c r="K19" s="286"/>
+      <c r="L19" s="286"/>
+      <c r="M19" s="286"/>
+      <c r="N19" s="286"/>
+      <c r="O19" s="286"/>
+      <c r="P19" s="287"/>
+      <c r="Q19" s="288"/>
+      <c r="R19" s="289"/>
+      <c r="S19" s="289"/>
+      <c r="T19" s="289"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="289"/>
+      <c r="W19" s="289"/>
+      <c r="X19" s="289"/>
+      <c r="Y19" s="289"/>
+      <c r="Z19" s="289"/>
+      <c r="AA19" s="289"/>
+      <c r="AB19" s="289"/>
+      <c r="AC19" s="289"/>
+      <c r="AD19" s="289"/>
+      <c r="AE19" s="290"/>
+      <c r="AF19" s="285"/>
+      <c r="AG19" s="286"/>
+      <c r="AH19" s="286"/>
+      <c r="AI19" s="287"/>
     </row>
     <row r="20" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="23"/>
-      <c r="B20" s="336"/>
-      <c r="C20" s="337"/>
-      <c r="D20" s="338"/>
-      <c r="E20" s="339"/>
-      <c r="F20" s="340"/>
-      <c r="G20" s="336"/>
-      <c r="H20" s="341"/>
-      <c r="I20" s="337"/>
-      <c r="J20" s="342"/>
-      <c r="K20" s="343"/>
-      <c r="L20" s="343"/>
-      <c r="M20" s="343"/>
-      <c r="N20" s="343"/>
-      <c r="O20" s="343"/>
-      <c r="P20" s="344"/>
-      <c r="Q20" s="345"/>
-      <c r="R20" s="346"/>
-      <c r="S20" s="346"/>
-      <c r="T20" s="346"/>
-      <c r="U20" s="346"/>
-      <c r="V20" s="346"/>
-      <c r="W20" s="346"/>
-      <c r="X20" s="346"/>
-      <c r="Y20" s="346"/>
-      <c r="Z20" s="346"/>
-      <c r="AA20" s="346"/>
-      <c r="AB20" s="346"/>
-      <c r="AC20" s="346"/>
-      <c r="AD20" s="346"/>
-      <c r="AE20" s="347"/>
-      <c r="AF20" s="342"/>
-      <c r="AG20" s="343"/>
-      <c r="AH20" s="343"/>
-      <c r="AI20" s="344"/>
+      <c r="B20" s="279"/>
+      <c r="C20" s="280"/>
+      <c r="D20" s="281"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="283"/>
+      <c r="G20" s="279"/>
+      <c r="H20" s="284"/>
+      <c r="I20" s="280"/>
+      <c r="J20" s="285"/>
+      <c r="K20" s="286"/>
+      <c r="L20" s="286"/>
+      <c r="M20" s="286"/>
+      <c r="N20" s="286"/>
+      <c r="O20" s="286"/>
+      <c r="P20" s="287"/>
+      <c r="Q20" s="288"/>
+      <c r="R20" s="289"/>
+      <c r="S20" s="289"/>
+      <c r="T20" s="289"/>
+      <c r="U20" s="289"/>
+      <c r="V20" s="289"/>
+      <c r="W20" s="289"/>
+      <c r="X20" s="289"/>
+      <c r="Y20" s="289"/>
+      <c r="Z20" s="289"/>
+      <c r="AA20" s="289"/>
+      <c r="AB20" s="289"/>
+      <c r="AC20" s="289"/>
+      <c r="AD20" s="289"/>
+      <c r="AE20" s="290"/>
+      <c r="AF20" s="285"/>
+      <c r="AG20" s="286"/>
+      <c r="AH20" s="286"/>
+      <c r="AI20" s="287"/>
     </row>
     <row r="21" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="23"/>
-      <c r="B21" s="336"/>
-      <c r="C21" s="337"/>
-      <c r="D21" s="338"/>
-      <c r="E21" s="339"/>
-      <c r="F21" s="340"/>
-      <c r="G21" s="336"/>
-      <c r="H21" s="341"/>
-      <c r="I21" s="337"/>
-      <c r="J21" s="342"/>
-      <c r="K21" s="343"/>
-      <c r="L21" s="343"/>
-      <c r="M21" s="343"/>
-      <c r="N21" s="343"/>
-      <c r="O21" s="343"/>
-      <c r="P21" s="344"/>
-      <c r="Q21" s="345"/>
-      <c r="R21" s="346"/>
-      <c r="S21" s="346"/>
-      <c r="T21" s="346"/>
-      <c r="U21" s="346"/>
-      <c r="V21" s="346"/>
-      <c r="W21" s="346"/>
-      <c r="X21" s="346"/>
-      <c r="Y21" s="346"/>
-      <c r="Z21" s="346"/>
-      <c r="AA21" s="346"/>
-      <c r="AB21" s="346"/>
-      <c r="AC21" s="346"/>
-      <c r="AD21" s="346"/>
-      <c r="AE21" s="347"/>
-      <c r="AF21" s="342"/>
-      <c r="AG21" s="343"/>
-      <c r="AH21" s="343"/>
-      <c r="AI21" s="344"/>
+      <c r="B21" s="279"/>
+      <c r="C21" s="280"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="282"/>
+      <c r="F21" s="283"/>
+      <c r="G21" s="279"/>
+      <c r="H21" s="284"/>
+      <c r="I21" s="280"/>
+      <c r="J21" s="285"/>
+      <c r="K21" s="286"/>
+      <c r="L21" s="286"/>
+      <c r="M21" s="286"/>
+      <c r="N21" s="286"/>
+      <c r="O21" s="286"/>
+      <c r="P21" s="287"/>
+      <c r="Q21" s="288"/>
+      <c r="R21" s="289"/>
+      <c r="S21" s="289"/>
+      <c r="T21" s="289"/>
+      <c r="U21" s="289"/>
+      <c r="V21" s="289"/>
+      <c r="W21" s="289"/>
+      <c r="X21" s="289"/>
+      <c r="Y21" s="289"/>
+      <c r="Z21" s="289"/>
+      <c r="AA21" s="289"/>
+      <c r="AB21" s="289"/>
+      <c r="AC21" s="289"/>
+      <c r="AD21" s="289"/>
+      <c r="AE21" s="290"/>
+      <c r="AF21" s="285"/>
+      <c r="AG21" s="286"/>
+      <c r="AH21" s="286"/>
+      <c r="AI21" s="287"/>
     </row>
     <row r="22" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="23"/>
-      <c r="B22" s="336"/>
-      <c r="C22" s="337"/>
-      <c r="D22" s="338"/>
-      <c r="E22" s="339"/>
-      <c r="F22" s="340"/>
-      <c r="G22" s="336"/>
-      <c r="H22" s="341"/>
-      <c r="I22" s="337"/>
-      <c r="J22" s="342"/>
-      <c r="K22" s="343"/>
-      <c r="L22" s="343"/>
-      <c r="M22" s="343"/>
-      <c r="N22" s="343"/>
-      <c r="O22" s="343"/>
-      <c r="P22" s="344"/>
-      <c r="Q22" s="345"/>
-      <c r="R22" s="346"/>
-      <c r="S22" s="346"/>
-      <c r="T22" s="346"/>
-      <c r="U22" s="346"/>
-      <c r="V22" s="346"/>
-      <c r="W22" s="346"/>
-      <c r="X22" s="346"/>
-      <c r="Y22" s="346"/>
-      <c r="Z22" s="346"/>
-      <c r="AA22" s="346"/>
-      <c r="AB22" s="346"/>
-      <c r="AC22" s="346"/>
-      <c r="AD22" s="346"/>
-      <c r="AE22" s="347"/>
-      <c r="AF22" s="342"/>
-      <c r="AG22" s="343"/>
-      <c r="AH22" s="343"/>
-      <c r="AI22" s="344"/>
+      <c r="B22" s="279"/>
+      <c r="C22" s="280"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="282"/>
+      <c r="F22" s="283"/>
+      <c r="G22" s="279"/>
+      <c r="H22" s="284"/>
+      <c r="I22" s="280"/>
+      <c r="J22" s="285"/>
+      <c r="K22" s="286"/>
+      <c r="L22" s="286"/>
+      <c r="M22" s="286"/>
+      <c r="N22" s="286"/>
+      <c r="O22" s="286"/>
+      <c r="P22" s="287"/>
+      <c r="Q22" s="288"/>
+      <c r="R22" s="289"/>
+      <c r="S22" s="289"/>
+      <c r="T22" s="289"/>
+      <c r="U22" s="289"/>
+      <c r="V22" s="289"/>
+      <c r="W22" s="289"/>
+      <c r="X22" s="289"/>
+      <c r="Y22" s="289"/>
+      <c r="Z22" s="289"/>
+      <c r="AA22" s="289"/>
+      <c r="AB22" s="289"/>
+      <c r="AC22" s="289"/>
+      <c r="AD22" s="289"/>
+      <c r="AE22" s="290"/>
+      <c r="AF22" s="285"/>
+      <c r="AG22" s="286"/>
+      <c r="AH22" s="286"/>
+      <c r="AI22" s="287"/>
     </row>
     <row r="23" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="23"/>
-      <c r="B23" s="336"/>
-      <c r="C23" s="337"/>
-      <c r="D23" s="338"/>
-      <c r="E23" s="339"/>
-      <c r="F23" s="340"/>
-      <c r="G23" s="336"/>
-      <c r="H23" s="341"/>
-      <c r="I23" s="337"/>
-      <c r="J23" s="342"/>
-      <c r="K23" s="343"/>
-      <c r="L23" s="343"/>
-      <c r="M23" s="343"/>
-      <c r="N23" s="343"/>
-      <c r="O23" s="343"/>
-      <c r="P23" s="344"/>
-      <c r="Q23" s="345"/>
-      <c r="R23" s="346"/>
-      <c r="S23" s="346"/>
-      <c r="T23" s="346"/>
-      <c r="U23" s="346"/>
-      <c r="V23" s="346"/>
-      <c r="W23" s="346"/>
-      <c r="X23" s="346"/>
-      <c r="Y23" s="346"/>
-      <c r="Z23" s="346"/>
-      <c r="AA23" s="346"/>
-      <c r="AB23" s="346"/>
-      <c r="AC23" s="346"/>
-      <c r="AD23" s="346"/>
-      <c r="AE23" s="347"/>
-      <c r="AF23" s="342"/>
-      <c r="AG23" s="343"/>
-      <c r="AH23" s="343"/>
-      <c r="AI23" s="344"/>
+      <c r="B23" s="279"/>
+      <c r="C23" s="280"/>
+      <c r="D23" s="281"/>
+      <c r="E23" s="282"/>
+      <c r="F23" s="283"/>
+      <c r="G23" s="279"/>
+      <c r="H23" s="284"/>
+      <c r="I23" s="280"/>
+      <c r="J23" s="285"/>
+      <c r="K23" s="286"/>
+      <c r="L23" s="286"/>
+      <c r="M23" s="286"/>
+      <c r="N23" s="286"/>
+      <c r="O23" s="286"/>
+      <c r="P23" s="287"/>
+      <c r="Q23" s="288"/>
+      <c r="R23" s="289"/>
+      <c r="S23" s="289"/>
+      <c r="T23" s="289"/>
+      <c r="U23" s="289"/>
+      <c r="V23" s="289"/>
+      <c r="W23" s="289"/>
+      <c r="X23" s="289"/>
+      <c r="Y23" s="289"/>
+      <c r="Z23" s="289"/>
+      <c r="AA23" s="289"/>
+      <c r="AB23" s="289"/>
+      <c r="AC23" s="289"/>
+      <c r="AD23" s="289"/>
+      <c r="AE23" s="290"/>
+      <c r="AF23" s="285"/>
+      <c r="AG23" s="286"/>
+      <c r="AH23" s="286"/>
+      <c r="AI23" s="287"/>
     </row>
     <row r="24" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="B24" s="336"/>
-      <c r="C24" s="337"/>
-      <c r="D24" s="338"/>
-      <c r="E24" s="339"/>
-      <c r="F24" s="340"/>
-      <c r="G24" s="336"/>
-      <c r="H24" s="341"/>
-      <c r="I24" s="337"/>
-      <c r="J24" s="342"/>
-      <c r="K24" s="343"/>
-      <c r="L24" s="343"/>
-      <c r="M24" s="343"/>
-      <c r="N24" s="343"/>
-      <c r="O24" s="343"/>
-      <c r="P24" s="344"/>
-      <c r="Q24" s="345"/>
-      <c r="R24" s="346"/>
-      <c r="S24" s="346"/>
-      <c r="T24" s="346"/>
-      <c r="U24" s="346"/>
-      <c r="V24" s="346"/>
-      <c r="W24" s="346"/>
-      <c r="X24" s="346"/>
-      <c r="Y24" s="346"/>
-      <c r="Z24" s="346"/>
-      <c r="AA24" s="346"/>
-      <c r="AB24" s="346"/>
-      <c r="AC24" s="346"/>
-      <c r="AD24" s="346"/>
-      <c r="AE24" s="347"/>
-      <c r="AF24" s="342"/>
-      <c r="AG24" s="343"/>
-      <c r="AH24" s="343"/>
-      <c r="AI24" s="344"/>
+      <c r="B24" s="279"/>
+      <c r="C24" s="280"/>
+      <c r="D24" s="281"/>
+      <c r="E24" s="282"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="279"/>
+      <c r="H24" s="284"/>
+      <c r="I24" s="280"/>
+      <c r="J24" s="285"/>
+      <c r="K24" s="286"/>
+      <c r="L24" s="286"/>
+      <c r="M24" s="286"/>
+      <c r="N24" s="286"/>
+      <c r="O24" s="286"/>
+      <c r="P24" s="287"/>
+      <c r="Q24" s="288"/>
+      <c r="R24" s="289"/>
+      <c r="S24" s="289"/>
+      <c r="T24" s="289"/>
+      <c r="U24" s="289"/>
+      <c r="V24" s="289"/>
+      <c r="W24" s="289"/>
+      <c r="X24" s="289"/>
+      <c r="Y24" s="289"/>
+      <c r="Z24" s="289"/>
+      <c r="AA24" s="289"/>
+      <c r="AB24" s="289"/>
+      <c r="AC24" s="289"/>
+      <c r="AD24" s="289"/>
+      <c r="AE24" s="290"/>
+      <c r="AF24" s="285"/>
+      <c r="AG24" s="286"/>
+      <c r="AH24" s="286"/>
+      <c r="AI24" s="287"/>
     </row>
     <row r="25" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="23"/>
-      <c r="B25" s="336"/>
-      <c r="C25" s="337"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="340"/>
-      <c r="G25" s="336"/>
-      <c r="H25" s="341"/>
-      <c r="I25" s="337"/>
-      <c r="J25" s="342"/>
-      <c r="K25" s="343"/>
-      <c r="L25" s="343"/>
-      <c r="M25" s="343"/>
-      <c r="N25" s="343"/>
-      <c r="O25" s="343"/>
-      <c r="P25" s="344"/>
-      <c r="Q25" s="345"/>
-      <c r="R25" s="346"/>
-      <c r="S25" s="346"/>
-      <c r="T25" s="346"/>
-      <c r="U25" s="346"/>
-      <c r="V25" s="346"/>
-      <c r="W25" s="346"/>
-      <c r="X25" s="346"/>
-      <c r="Y25" s="346"/>
-      <c r="Z25" s="346"/>
-      <c r="AA25" s="346"/>
-      <c r="AB25" s="346"/>
-      <c r="AC25" s="346"/>
-      <c r="AD25" s="346"/>
-      <c r="AE25" s="347"/>
-      <c r="AF25" s="342"/>
-      <c r="AG25" s="343"/>
-      <c r="AH25" s="343"/>
-      <c r="AI25" s="344"/>
+      <c r="B25" s="279"/>
+      <c r="C25" s="280"/>
+      <c r="D25" s="281"/>
+      <c r="E25" s="282"/>
+      <c r="F25" s="283"/>
+      <c r="G25" s="279"/>
+      <c r="H25" s="284"/>
+      <c r="I25" s="280"/>
+      <c r="J25" s="285"/>
+      <c r="K25" s="286"/>
+      <c r="L25" s="286"/>
+      <c r="M25" s="286"/>
+      <c r="N25" s="286"/>
+      <c r="O25" s="286"/>
+      <c r="P25" s="287"/>
+      <c r="Q25" s="288"/>
+      <c r="R25" s="289"/>
+      <c r="S25" s="289"/>
+      <c r="T25" s="289"/>
+      <c r="U25" s="289"/>
+      <c r="V25" s="289"/>
+      <c r="W25" s="289"/>
+      <c r="X25" s="289"/>
+      <c r="Y25" s="289"/>
+      <c r="Z25" s="289"/>
+      <c r="AA25" s="289"/>
+      <c r="AB25" s="289"/>
+      <c r="AC25" s="289"/>
+      <c r="AD25" s="289"/>
+      <c r="AE25" s="290"/>
+      <c r="AF25" s="285"/>
+      <c r="AG25" s="286"/>
+      <c r="AH25" s="286"/>
+      <c r="AI25" s="287"/>
     </row>
     <row r="26" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="23"/>
-      <c r="B26" s="336"/>
-      <c r="C26" s="337"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="340"/>
-      <c r="G26" s="336"/>
-      <c r="H26" s="341"/>
-      <c r="I26" s="337"/>
-      <c r="J26" s="342"/>
-      <c r="K26" s="343"/>
-      <c r="L26" s="343"/>
-      <c r="M26" s="343"/>
-      <c r="N26" s="343"/>
-      <c r="O26" s="343"/>
-      <c r="P26" s="344"/>
-      <c r="Q26" s="345"/>
-      <c r="R26" s="346"/>
-      <c r="S26" s="346"/>
-      <c r="T26" s="346"/>
-      <c r="U26" s="346"/>
-      <c r="V26" s="346"/>
-      <c r="W26" s="346"/>
-      <c r="X26" s="346"/>
-      <c r="Y26" s="346"/>
-      <c r="Z26" s="346"/>
-      <c r="AA26" s="346"/>
-      <c r="AB26" s="346"/>
-      <c r="AC26" s="346"/>
-      <c r="AD26" s="346"/>
-      <c r="AE26" s="347"/>
-      <c r="AF26" s="342"/>
-      <c r="AG26" s="343"/>
-      <c r="AH26" s="343"/>
-      <c r="AI26" s="344"/>
+      <c r="B26" s="279"/>
+      <c r="C26" s="280"/>
+      <c r="D26" s="281"/>
+      <c r="E26" s="282"/>
+      <c r="F26" s="283"/>
+      <c r="G26" s="279"/>
+      <c r="H26" s="284"/>
+      <c r="I26" s="280"/>
+      <c r="J26" s="285"/>
+      <c r="K26" s="286"/>
+      <c r="L26" s="286"/>
+      <c r="M26" s="286"/>
+      <c r="N26" s="286"/>
+      <c r="O26" s="286"/>
+      <c r="P26" s="287"/>
+      <c r="Q26" s="288"/>
+      <c r="R26" s="289"/>
+      <c r="S26" s="289"/>
+      <c r="T26" s="289"/>
+      <c r="U26" s="289"/>
+      <c r="V26" s="289"/>
+      <c r="W26" s="289"/>
+      <c r="X26" s="289"/>
+      <c r="Y26" s="289"/>
+      <c r="Z26" s="289"/>
+      <c r="AA26" s="289"/>
+      <c r="AB26" s="289"/>
+      <c r="AC26" s="289"/>
+      <c r="AD26" s="289"/>
+      <c r="AE26" s="290"/>
+      <c r="AF26" s="285"/>
+      <c r="AG26" s="286"/>
+      <c r="AH26" s="286"/>
+      <c r="AI26" s="287"/>
     </row>
     <row r="27" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="23"/>
-      <c r="B27" s="336"/>
-      <c r="C27" s="337"/>
-      <c r="D27" s="338"/>
-      <c r="E27" s="339"/>
-      <c r="F27" s="340"/>
-      <c r="G27" s="336"/>
-      <c r="H27" s="341"/>
-      <c r="I27" s="337"/>
-      <c r="J27" s="342"/>
-      <c r="K27" s="343"/>
-      <c r="L27" s="343"/>
-      <c r="M27" s="343"/>
-      <c r="N27" s="343"/>
-      <c r="O27" s="343"/>
-      <c r="P27" s="344"/>
-      <c r="Q27" s="345"/>
-      <c r="R27" s="346"/>
-      <c r="S27" s="346"/>
-      <c r="T27" s="346"/>
-      <c r="U27" s="346"/>
-      <c r="V27" s="346"/>
-      <c r="W27" s="346"/>
-      <c r="X27" s="346"/>
-      <c r="Y27" s="346"/>
-      <c r="Z27" s="346"/>
-      <c r="AA27" s="346"/>
-      <c r="AB27" s="346"/>
-      <c r="AC27" s="346"/>
-      <c r="AD27" s="346"/>
-      <c r="AE27" s="347"/>
-      <c r="AF27" s="342"/>
-      <c r="AG27" s="343"/>
-      <c r="AH27" s="343"/>
-      <c r="AI27" s="344"/>
+      <c r="B27" s="279"/>
+      <c r="C27" s="280"/>
+      <c r="D27" s="281"/>
+      <c r="E27" s="282"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="284"/>
+      <c r="I27" s="280"/>
+      <c r="J27" s="285"/>
+      <c r="K27" s="286"/>
+      <c r="L27" s="286"/>
+      <c r="M27" s="286"/>
+      <c r="N27" s="286"/>
+      <c r="O27" s="286"/>
+      <c r="P27" s="287"/>
+      <c r="Q27" s="288"/>
+      <c r="R27" s="289"/>
+      <c r="S27" s="289"/>
+      <c r="T27" s="289"/>
+      <c r="U27" s="289"/>
+      <c r="V27" s="289"/>
+      <c r="W27" s="289"/>
+      <c r="X27" s="289"/>
+      <c r="Y27" s="289"/>
+      <c r="Z27" s="289"/>
+      <c r="AA27" s="289"/>
+      <c r="AB27" s="289"/>
+      <c r="AC27" s="289"/>
+      <c r="AD27" s="289"/>
+      <c r="AE27" s="290"/>
+      <c r="AF27" s="285"/>
+      <c r="AG27" s="286"/>
+      <c r="AH27" s="286"/>
+      <c r="AI27" s="287"/>
     </row>
     <row r="28" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="23"/>
-      <c r="B28" s="336"/>
-      <c r="C28" s="337"/>
-      <c r="D28" s="338"/>
-      <c r="E28" s="339"/>
-      <c r="F28" s="340"/>
-      <c r="G28" s="336"/>
-      <c r="H28" s="341"/>
-      <c r="I28" s="337"/>
-      <c r="J28" s="342"/>
-      <c r="K28" s="343"/>
-      <c r="L28" s="343"/>
-      <c r="M28" s="343"/>
-      <c r="N28" s="343"/>
-      <c r="O28" s="343"/>
-      <c r="P28" s="344"/>
-      <c r="Q28" s="345"/>
-      <c r="R28" s="346"/>
-      <c r="S28" s="346"/>
-      <c r="T28" s="346"/>
-      <c r="U28" s="346"/>
-      <c r="V28" s="346"/>
-      <c r="W28" s="346"/>
-      <c r="X28" s="346"/>
-      <c r="Y28" s="346"/>
-      <c r="Z28" s="346"/>
-      <c r="AA28" s="346"/>
-      <c r="AB28" s="346"/>
-      <c r="AC28" s="346"/>
-      <c r="AD28" s="346"/>
-      <c r="AE28" s="347"/>
-      <c r="AF28" s="342"/>
-      <c r="AG28" s="343"/>
-      <c r="AH28" s="343"/>
-      <c r="AI28" s="344"/>
+      <c r="B28" s="279"/>
+      <c r="C28" s="280"/>
+      <c r="D28" s="281"/>
+      <c r="E28" s="282"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="284"/>
+      <c r="I28" s="280"/>
+      <c r="J28" s="285"/>
+      <c r="K28" s="286"/>
+      <c r="L28" s="286"/>
+      <c r="M28" s="286"/>
+      <c r="N28" s="286"/>
+      <c r="O28" s="286"/>
+      <c r="P28" s="287"/>
+      <c r="Q28" s="288"/>
+      <c r="R28" s="289"/>
+      <c r="S28" s="289"/>
+      <c r="T28" s="289"/>
+      <c r="U28" s="289"/>
+      <c r="V28" s="289"/>
+      <c r="W28" s="289"/>
+      <c r="X28" s="289"/>
+      <c r="Y28" s="289"/>
+      <c r="Z28" s="289"/>
+      <c r="AA28" s="289"/>
+      <c r="AB28" s="289"/>
+      <c r="AC28" s="289"/>
+      <c r="AD28" s="289"/>
+      <c r="AE28" s="290"/>
+      <c r="AF28" s="285"/>
+      <c r="AG28" s="286"/>
+      <c r="AH28" s="286"/>
+      <c r="AI28" s="287"/>
     </row>
     <row r="29" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="23"/>
-      <c r="B29" s="336"/>
-      <c r="C29" s="337"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="340"/>
-      <c r="G29" s="336"/>
-      <c r="H29" s="341"/>
-      <c r="I29" s="337"/>
-      <c r="J29" s="342"/>
-      <c r="K29" s="343"/>
-      <c r="L29" s="343"/>
-      <c r="M29" s="343"/>
-      <c r="N29" s="343"/>
-      <c r="O29" s="343"/>
-      <c r="P29" s="344"/>
-      <c r="Q29" s="345"/>
-      <c r="R29" s="346"/>
-      <c r="S29" s="346"/>
-      <c r="T29" s="346"/>
-      <c r="U29" s="346"/>
-      <c r="V29" s="346"/>
-      <c r="W29" s="346"/>
-      <c r="X29" s="346"/>
-      <c r="Y29" s="346"/>
-      <c r="Z29" s="346"/>
-      <c r="AA29" s="346"/>
-      <c r="AB29" s="346"/>
-      <c r="AC29" s="346"/>
-      <c r="AD29" s="346"/>
-      <c r="AE29" s="347"/>
-      <c r="AF29" s="342"/>
-      <c r="AG29" s="343"/>
-      <c r="AH29" s="343"/>
-      <c r="AI29" s="344"/>
+      <c r="B29" s="279"/>
+      <c r="C29" s="280"/>
+      <c r="D29" s="281"/>
+      <c r="E29" s="282"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="279"/>
+      <c r="H29" s="284"/>
+      <c r="I29" s="280"/>
+      <c r="J29" s="285"/>
+      <c r="K29" s="286"/>
+      <c r="L29" s="286"/>
+      <c r="M29" s="286"/>
+      <c r="N29" s="286"/>
+      <c r="O29" s="286"/>
+      <c r="P29" s="287"/>
+      <c r="Q29" s="288"/>
+      <c r="R29" s="289"/>
+      <c r="S29" s="289"/>
+      <c r="T29" s="289"/>
+      <c r="U29" s="289"/>
+      <c r="V29" s="289"/>
+      <c r="W29" s="289"/>
+      <c r="X29" s="289"/>
+      <c r="Y29" s="289"/>
+      <c r="Z29" s="289"/>
+      <c r="AA29" s="289"/>
+      <c r="AB29" s="289"/>
+      <c r="AC29" s="289"/>
+      <c r="AD29" s="289"/>
+      <c r="AE29" s="290"/>
+      <c r="AF29" s="285"/>
+      <c r="AG29" s="286"/>
+      <c r="AH29" s="286"/>
+      <c r="AI29" s="287"/>
     </row>
     <row r="30" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="23"/>
-      <c r="B30" s="336"/>
-      <c r="C30" s="337"/>
-      <c r="D30" s="338"/>
-      <c r="E30" s="339"/>
-      <c r="F30" s="340"/>
-      <c r="G30" s="336"/>
-      <c r="H30" s="341"/>
-      <c r="I30" s="337"/>
-      <c r="J30" s="342"/>
-      <c r="K30" s="343"/>
-      <c r="L30" s="343"/>
-      <c r="M30" s="343"/>
-      <c r="N30" s="343"/>
-      <c r="O30" s="343"/>
-      <c r="P30" s="344"/>
-      <c r="Q30" s="345"/>
-      <c r="R30" s="346"/>
-      <c r="S30" s="346"/>
-      <c r="T30" s="346"/>
-      <c r="U30" s="346"/>
-      <c r="V30" s="346"/>
-      <c r="W30" s="346"/>
-      <c r="X30" s="346"/>
-      <c r="Y30" s="346"/>
-      <c r="Z30" s="346"/>
-      <c r="AA30" s="346"/>
-      <c r="AB30" s="346"/>
-      <c r="AC30" s="346"/>
-      <c r="AD30" s="346"/>
-      <c r="AE30" s="347"/>
-      <c r="AF30" s="342"/>
-      <c r="AG30" s="343"/>
-      <c r="AH30" s="343"/>
-      <c r="AI30" s="344"/>
+      <c r="B30" s="279"/>
+      <c r="C30" s="280"/>
+      <c r="D30" s="281"/>
+      <c r="E30" s="282"/>
+      <c r="F30" s="283"/>
+      <c r="G30" s="279"/>
+      <c r="H30" s="284"/>
+      <c r="I30" s="280"/>
+      <c r="J30" s="285"/>
+      <c r="K30" s="286"/>
+      <c r="L30" s="286"/>
+      <c r="M30" s="286"/>
+      <c r="N30" s="286"/>
+      <c r="O30" s="286"/>
+      <c r="P30" s="287"/>
+      <c r="Q30" s="288"/>
+      <c r="R30" s="289"/>
+      <c r="S30" s="289"/>
+      <c r="T30" s="289"/>
+      <c r="U30" s="289"/>
+      <c r="V30" s="289"/>
+      <c r="W30" s="289"/>
+      <c r="X30" s="289"/>
+      <c r="Y30" s="289"/>
+      <c r="Z30" s="289"/>
+      <c r="AA30" s="289"/>
+      <c r="AB30" s="289"/>
+      <c r="AC30" s="289"/>
+      <c r="AD30" s="289"/>
+      <c r="AE30" s="290"/>
+      <c r="AF30" s="285"/>
+      <c r="AG30" s="286"/>
+      <c r="AH30" s="286"/>
+      <c r="AI30" s="287"/>
     </row>
     <row r="31" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="23"/>
-      <c r="B31" s="336"/>
-      <c r="C31" s="337"/>
-      <c r="D31" s="338"/>
-      <c r="E31" s="339"/>
-      <c r="F31" s="340"/>
-      <c r="G31" s="336"/>
-      <c r="H31" s="341"/>
-      <c r="I31" s="337"/>
-      <c r="J31" s="342"/>
-      <c r="K31" s="343"/>
-      <c r="L31" s="343"/>
-      <c r="M31" s="343"/>
-      <c r="N31" s="343"/>
-      <c r="O31" s="343"/>
-      <c r="P31" s="344"/>
-      <c r="Q31" s="345"/>
-      <c r="R31" s="346"/>
-      <c r="S31" s="346"/>
-      <c r="T31" s="346"/>
-      <c r="U31" s="346"/>
-      <c r="V31" s="346"/>
-      <c r="W31" s="346"/>
-      <c r="X31" s="346"/>
-      <c r="Y31" s="346"/>
-      <c r="Z31" s="346"/>
-      <c r="AA31" s="346"/>
-      <c r="AB31" s="346"/>
-      <c r="AC31" s="346"/>
-      <c r="AD31" s="346"/>
-      <c r="AE31" s="347"/>
-      <c r="AF31" s="342"/>
-      <c r="AG31" s="343"/>
-      <c r="AH31" s="343"/>
-      <c r="AI31" s="344"/>
+      <c r="B31" s="279"/>
+      <c r="C31" s="280"/>
+      <c r="D31" s="281"/>
+      <c r="E31" s="282"/>
+      <c r="F31" s="283"/>
+      <c r="G31" s="279"/>
+      <c r="H31" s="284"/>
+      <c r="I31" s="280"/>
+      <c r="J31" s="285"/>
+      <c r="K31" s="286"/>
+      <c r="L31" s="286"/>
+      <c r="M31" s="286"/>
+      <c r="N31" s="286"/>
+      <c r="O31" s="286"/>
+      <c r="P31" s="287"/>
+      <c r="Q31" s="288"/>
+      <c r="R31" s="289"/>
+      <c r="S31" s="289"/>
+      <c r="T31" s="289"/>
+      <c r="U31" s="289"/>
+      <c r="V31" s="289"/>
+      <c r="W31" s="289"/>
+      <c r="X31" s="289"/>
+      <c r="Y31" s="289"/>
+      <c r="Z31" s="289"/>
+      <c r="AA31" s="289"/>
+      <c r="AB31" s="289"/>
+      <c r="AC31" s="289"/>
+      <c r="AD31" s="289"/>
+      <c r="AE31" s="290"/>
+      <c r="AF31" s="285"/>
+      <c r="AG31" s="286"/>
+      <c r="AH31" s="286"/>
+      <c r="AI31" s="287"/>
     </row>
     <row r="32" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="23"/>
-      <c r="B32" s="336"/>
-      <c r="C32" s="337"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="340"/>
-      <c r="G32" s="336"/>
-      <c r="H32" s="341"/>
-      <c r="I32" s="337"/>
-      <c r="J32" s="342"/>
-      <c r="K32" s="348"/>
-      <c r="L32" s="343"/>
-      <c r="M32" s="343"/>
-      <c r="N32" s="343"/>
-      <c r="O32" s="343"/>
-      <c r="P32" s="344"/>
-      <c r="Q32" s="345"/>
-      <c r="R32" s="346"/>
-      <c r="S32" s="346"/>
-      <c r="T32" s="346"/>
-      <c r="U32" s="346"/>
-      <c r="V32" s="346"/>
-      <c r="W32" s="346"/>
-      <c r="X32" s="346"/>
-      <c r="Y32" s="346"/>
-      <c r="Z32" s="346"/>
-      <c r="AA32" s="346"/>
-      <c r="AB32" s="346"/>
-      <c r="AC32" s="346"/>
-      <c r="AD32" s="346"/>
-      <c r="AE32" s="347"/>
-      <c r="AF32" s="342"/>
-      <c r="AG32" s="343"/>
-      <c r="AH32" s="343"/>
-      <c r="AI32" s="344"/>
+      <c r="B32" s="279"/>
+      <c r="C32" s="280"/>
+      <c r="D32" s="281"/>
+      <c r="E32" s="282"/>
+      <c r="F32" s="283"/>
+      <c r="G32" s="279"/>
+      <c r="H32" s="284"/>
+      <c r="I32" s="280"/>
+      <c r="J32" s="285"/>
+      <c r="K32" s="291"/>
+      <c r="L32" s="286"/>
+      <c r="M32" s="286"/>
+      <c r="N32" s="286"/>
+      <c r="O32" s="286"/>
+      <c r="P32" s="287"/>
+      <c r="Q32" s="288"/>
+      <c r="R32" s="289"/>
+      <c r="S32" s="289"/>
+      <c r="T32" s="289"/>
+      <c r="U32" s="289"/>
+      <c r="V32" s="289"/>
+      <c r="W32" s="289"/>
+      <c r="X32" s="289"/>
+      <c r="Y32" s="289"/>
+      <c r="Z32" s="289"/>
+      <c r="AA32" s="289"/>
+      <c r="AB32" s="289"/>
+      <c r="AC32" s="289"/>
+      <c r="AD32" s="289"/>
+      <c r="AE32" s="290"/>
+      <c r="AF32" s="285"/>
+      <c r="AG32" s="286"/>
+      <c r="AH32" s="286"/>
+      <c r="AI32" s="287"/>
     </row>
     <row r="33" spans="1:35" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="23"/>
-      <c r="B33" s="336"/>
-      <c r="C33" s="337"/>
-      <c r="D33" s="338"/>
-      <c r="E33" s="339"/>
-      <c r="F33" s="340"/>
-      <c r="G33" s="336"/>
-      <c r="H33" s="341"/>
-      <c r="I33" s="337"/>
-      <c r="J33" s="342"/>
-      <c r="K33" s="343"/>
-      <c r="L33" s="343"/>
-      <c r="M33" s="343"/>
-      <c r="N33" s="343"/>
-      <c r="O33" s="343"/>
-      <c r="P33" s="344"/>
-      <c r="Q33" s="345"/>
-      <c r="R33" s="346"/>
-      <c r="S33" s="346"/>
-      <c r="T33" s="346"/>
-      <c r="U33" s="346"/>
-      <c r="V33" s="346"/>
-      <c r="W33" s="346"/>
-      <c r="X33" s="346"/>
-      <c r="Y33" s="346"/>
-      <c r="Z33" s="346"/>
-      <c r="AA33" s="346"/>
-      <c r="AB33" s="346"/>
-      <c r="AC33" s="346"/>
-      <c r="AD33" s="346"/>
-      <c r="AE33" s="347"/>
-      <c r="AF33" s="342"/>
-      <c r="AG33" s="343"/>
-      <c r="AH33" s="343"/>
-      <c r="AI33" s="344"/>
+      <c r="B33" s="279"/>
+      <c r="C33" s="280"/>
+      <c r="D33" s="281"/>
+      <c r="E33" s="282"/>
+      <c r="F33" s="283"/>
+      <c r="G33" s="279"/>
+      <c r="H33" s="284"/>
+      <c r="I33" s="280"/>
+      <c r="J33" s="285"/>
+      <c r="K33" s="286"/>
+      <c r="L33" s="286"/>
+      <c r="M33" s="286"/>
+      <c r="N33" s="286"/>
+      <c r="O33" s="286"/>
+      <c r="P33" s="287"/>
+      <c r="Q33" s="288"/>
+      <c r="R33" s="289"/>
+      <c r="S33" s="289"/>
+      <c r="T33" s="289"/>
+      <c r="U33" s="289"/>
+      <c r="V33" s="289"/>
+      <c r="W33" s="289"/>
+      <c r="X33" s="289"/>
+      <c r="Y33" s="289"/>
+      <c r="Z33" s="289"/>
+      <c r="AA33" s="289"/>
+      <c r="AB33" s="289"/>
+      <c r="AC33" s="289"/>
+      <c r="AD33" s="289"/>
+      <c r="AE33" s="290"/>
+      <c r="AF33" s="285"/>
+      <c r="AG33" s="286"/>
+      <c r="AH33" s="286"/>
+      <c r="AI33" s="287"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -18590,6 +18435,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(画面)_サンプル.xlsx
@@ -18748,8 +18748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -18791,8 +18791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -18828,8 +18828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -18867,8 +18867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -18902,8 +18902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -18937,8 +18937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -18972,8 +18972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -19007,8 +19007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -19046,8 +19046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -19081,8 +19081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -19116,8 +19116,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -19153,8 +19153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -19188,8 +19188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -19223,8 +19223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -19258,8 +19258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -19297,8 +19297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -19332,8 +19332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -19371,8 +19371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -19406,8 +19406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -19443,8 +19443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -19478,8 +19478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -19513,8 +19513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -19548,8 +19548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -19585,8 +19585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -19620,8 +19620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -19657,8 +19657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -19698,8 +19698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -19733,8 +19733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -19768,8 +19768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -19803,8 +19803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -19842,8 +19842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -19877,8 +19877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -19930,8 +19930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -19975,8 +19975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -20010,8 +20010,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -20047,8 +20047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -20082,8 +20082,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -20117,8 +20117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -20164,8 +20164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -20209,8 +20209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -20246,8 +20246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -20281,8 +20281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -20316,8 +20316,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -20351,8 +20351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -20386,8 +20386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -20421,8 +20421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -20458,8 +20458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -20495,8 +20495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -20532,8 +20532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -20571,8 +20571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -20616,8 +20616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -20651,8 +20651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -20686,8 +20686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -20721,8 +20721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -20758,8 +20758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -20793,8 +20793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -20828,8 +20828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -20863,8 +20863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -20898,8 +20898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -20933,8 +20933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -20968,8 +20968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -21003,8 +21003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -21050,8 +21050,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-2</v>
       </c>
@@ -21093,8 +21093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-3</v>
       </c>
@@ -21136,8 +21136,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-4</v>
       </c>
@@ -21179,8 +21179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-5</v>
       </c>
@@ -21222,8 +21222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-6</v>
       </c>
@@ -21265,8 +21265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-7</v>
       </c>
@@ -21308,8 +21308,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-8</v>
       </c>
@@ -21351,8 +21351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-9</v>
       </c>
@@ -21394,8 +21394,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -21441,8 +21441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-2</v>
       </c>
@@ -21484,8 +21484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-3</v>
       </c>
@@ -21527,8 +21527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-4</v>
       </c>
@@ -21570,8 +21570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-5</v>
       </c>
@@ -21613,8 +21613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-6</v>
       </c>
@@ -21656,8 +21656,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-7</v>
       </c>
@@ -21699,8 +21699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-8</v>
       </c>
@@ -21742,8 +21742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-9</v>
       </c>
@@ -21785,8 +21785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -21822,8 +21822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -21857,8 +21857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -21892,8 +21892,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -21927,8 +21927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -21968,8 +21968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -22003,8 +22003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -22040,8 +22040,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -22077,8 +22077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -22112,8 +22112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -22149,8 +22149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -22186,8 +22186,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -22237,8 +22237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -22284,8 +22284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -22321,8 +22321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -22372,8 +22372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-2</v>
       </c>
@@ -22415,8 +22415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -22450,8 +22450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -22497,8 +22497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -22534,8 +22534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -22569,8 +22569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -22606,8 +22606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -22647,8 +22647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -22682,8 +22682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -22717,8 +22717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -22752,8 +22752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -22787,8 +22787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -22834,8 +22834,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -22869,8 +22869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -22914,8 +22914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -22949,8 +22949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -22984,8 +22984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -23021,8 +23021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -23064,8 +23064,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -23105,8 +23105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -23140,8 +23140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -23181,8 +23181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -23222,8 +23222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -23257,8 +23257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -23300,8 +23300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -23337,8 +23337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -23372,8 +23372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -23407,8 +23407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -23444,8 +23444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -23479,8 +23479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -23514,8 +23514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -23549,8 +23549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -23584,8 +23584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -23621,8 +23621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -23656,8 +23656,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -23691,8 +23691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -23726,8 +23726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -23761,8 +23761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -23798,8 +23798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -23837,8 +23837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -23878,8 +23878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -23915,8 +23915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -23950,8 +23950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -23985,8 +23985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -24028,8 +24028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -24065,8 +24065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -24100,8 +24100,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -24135,8 +24135,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -24172,8 +24172,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -24207,8 +24207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -24246,8 +24246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -24287,8 +24287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -24324,8 +24324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -24361,8 +24361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -24398,8 +24398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -24435,8 +24435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -24472,8 +24472,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -24507,8 +24507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -24542,8 +24542,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -24577,8 +24577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -24612,8 +24612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -24647,8 +24647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -24686,8 +24686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -24721,8 +24721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -24758,8 +24758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -24793,8 +24793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -24828,8 +24828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -24863,8 +24863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -24898,8 +24898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -24933,8 +24933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -24968,8 +24968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -25003,8 +25003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -25038,8 +25038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -25073,8 +25073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -25108,8 +25108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -25145,8 +25145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -25180,8 +25180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -25215,8 +25215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -25250,8 +25250,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -25285,8 +25285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -25320,8 +25320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -25355,8 +25355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -25392,8 +25392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -25427,8 +25427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -25462,8 +25462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -25497,8 +25497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -25532,8 +25532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -25567,8 +25567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -25602,8 +25602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -25637,8 +25637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -25672,8 +25672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -25709,8 +25709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -25746,8 +25746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -25789,8 +25789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -25828,8 +25828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -25867,8 +25867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -25910,8 +25910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -25947,8 +25947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -25982,8 +25982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -26019,8 +26019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -26054,8 +26054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -26093,8 +26093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -26134,8 +26134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -26169,8 +26169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -26204,8 +26204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -26239,8 +26239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -26274,8 +26274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -26309,8 +26309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -26344,8 +26344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -26381,8 +26381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -26420,8 +26420,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -26455,8 +26455,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -26490,8 +26490,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -26525,8 +26525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -26560,8 +26560,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -26595,8 +26595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -26630,8 +26630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -26665,8 +26665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -26700,8 +26700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -26735,8 +26735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -26770,8 +26770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -26805,8 +26805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -26840,8 +26840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -26879,8 +26879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -26914,8 +26914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -26949,8 +26949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -26984,8 +26984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -27019,8 +27019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -27054,8 +27054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -27089,8 +27089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -27124,8 +27124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -27159,8 +27159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -27194,8 +27194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -27229,8 +27229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -27264,8 +27264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -27299,8 +27299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -27334,8 +27334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -27369,8 +27369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -27406,8 +27406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -27441,8 +27441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -27476,8 +27476,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -27513,8 +27513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -27550,8 +27550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -27593,8 +27593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -27630,8 +27630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -27665,8 +27665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -27700,8 +27700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -27735,8 +27735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -27770,8 +27770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -27807,8 +27807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -27842,8 +27842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -27877,8 +27877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -27912,8 +27912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -27947,8 +27947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -27984,8 +27984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -28025,8 +28025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -28068,8 +28068,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -28103,8 +28103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -28142,8 +28142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -28177,8 +28177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -28218,8 +28218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -28255,8 +28255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -28292,8 +28292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -28329,8 +28329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -28368,8 +28368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -28403,8 +28403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -28440,8 +28440,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -28475,8 +28475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -28510,8 +28510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -28545,8 +28545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -28580,8 +28580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -28615,8 +28615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -28650,8 +28650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -28685,8 +28685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -28720,8 +28720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -28755,8 +28755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -28790,8 +28790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -28827,8 +28827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -28862,8 +28862,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -28897,8 +28897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -28932,8 +28932,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -28967,8 +28967,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -29002,8 +29002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -29039,8 +29039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -29074,8 +29074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -29109,8 +29109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -29144,8 +29144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -29179,8 +29179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -29214,8 +29214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -29249,8 +29249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -29284,8 +29284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -29321,8 +29321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -29364,8 +29364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -29399,8 +29399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -29434,8 +29434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -29469,8 +29469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -29510,8 +29510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -29547,8 +29547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -29584,8 +29584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -29621,8 +29621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -29660,8 +29660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -29695,8 +29695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -29730,8 +29730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -29765,8 +29765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -29800,8 +29800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -29835,8 +29835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -29870,8 +29870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -29905,8 +29905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -30113,8 +30113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -30156,8 +30156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -30193,8 +30193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -30232,8 +30232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -30267,8 +30267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -30302,8 +30302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -30337,8 +30337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -30372,8 +30372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -30411,8 +30411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -30446,8 +30446,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -30481,8 +30481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -30518,8 +30518,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -30553,8 +30553,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -30588,8 +30588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -30623,8 +30623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -30662,8 +30662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -30697,8 +30697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -30736,8 +30736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -30771,8 +30771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -30808,8 +30808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -30843,8 +30843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -30878,8 +30878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -30913,8 +30913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -30950,8 +30950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -30985,8 +30985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -31022,8 +31022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -31063,8 +31063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -31098,8 +31098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -31133,8 +31133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -31168,8 +31168,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -31207,8 +31207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -31242,8 +31242,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -31285,8 +31285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -31320,8 +31320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -31355,8 +31355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -31392,8 +31392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -31427,8 +31427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -31462,8 +31462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -31499,8 +31499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -31534,8 +31534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -31571,8 +31571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -31606,8 +31606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -31641,8 +31641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -31676,8 +31676,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -31711,8 +31711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -31746,8 +31746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -31783,8 +31783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -31820,8 +31820,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -31857,8 +31857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -31896,8 +31896,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -31931,8 +31931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -31966,8 +31966,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -32001,8 +32001,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -32036,8 +32036,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -32073,8 +32073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -32108,8 +32108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -32143,8 +32143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -32178,8 +32178,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -32213,8 +32213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -32248,8 +32248,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -32283,8 +32283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -32318,8 +32318,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -32355,8 +32355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -32392,8 +32392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -32427,8 +32427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -32462,8 +32462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -32497,8 +32497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -32532,8 +32532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -32573,8 +32573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -32608,8 +32608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -32645,8 +32645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -32682,8 +32682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -32717,8 +32717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -32754,8 +32754,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -32791,8 +32791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -32832,8 +32832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -32869,8 +32869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -32906,8 +32906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -32947,8 +32947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -32982,8 +32982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -33019,8 +33019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -33056,8 +33056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -33091,8 +33091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -33128,8 +33128,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -33169,8 +33169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -33204,8 +33204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -33239,8 +33239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -33274,8 +33274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -33309,8 +33309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -33346,8 +33346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -33381,8 +33381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -33416,8 +33416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -33451,8 +33451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -33486,8 +33486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -33523,8 +33523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -33566,8 +33566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -33607,8 +33607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -33642,8 +33642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -33683,8 +33683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -33724,8 +33724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -33759,8 +33759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -33802,8 +33802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -33839,8 +33839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -33874,8 +33874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -33909,8 +33909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -33946,8 +33946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -33981,8 +33981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -34016,8 +34016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -34051,8 +34051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -34086,8 +34086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -34123,8 +34123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -34158,8 +34158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -34193,8 +34193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -34228,8 +34228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -34263,8 +34263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -34300,8 +34300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -34339,8 +34339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -34380,8 +34380,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -34417,8 +34417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -34452,8 +34452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -34487,8 +34487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -34530,8 +34530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -34567,8 +34567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -34602,8 +34602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -34637,8 +34637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -34674,8 +34674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -34709,8 +34709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -34748,8 +34748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -34789,8 +34789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -34826,8 +34826,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -34863,8 +34863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -34900,8 +34900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -34937,8 +34937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -34974,8 +34974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -35009,8 +35009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -35044,8 +35044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -35079,8 +35079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -35114,8 +35114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -35149,8 +35149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -35188,8 +35188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -35223,8 +35223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -35260,8 +35260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -35295,8 +35295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -35330,8 +35330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -35365,8 +35365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -35400,8 +35400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -35435,8 +35435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -35470,8 +35470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -35505,8 +35505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -35540,8 +35540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -35575,8 +35575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -35610,8 +35610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -35647,8 +35647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -35682,8 +35682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -35717,8 +35717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -35752,8 +35752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -35787,8 +35787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -35822,8 +35822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -35857,8 +35857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -35894,8 +35894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -35929,8 +35929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -35964,8 +35964,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -35999,8 +35999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -36034,8 +36034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -36069,8 +36069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -36104,8 +36104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -36139,8 +36139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -36174,8 +36174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -36211,8 +36211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -36248,8 +36248,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -36291,8 +36291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -36330,8 +36330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -36369,8 +36369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -36412,8 +36412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -36449,8 +36449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -36484,8 +36484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -36521,8 +36521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -36556,8 +36556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -36595,8 +36595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -36636,8 +36636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -36671,8 +36671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -36706,8 +36706,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -36741,8 +36741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -36776,8 +36776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -36811,8 +36811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -36846,8 +36846,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -36883,8 +36883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -36922,8 +36922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -36957,8 +36957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -36992,8 +36992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -37027,8 +37027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -37062,8 +37062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -37097,8 +37097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -37132,8 +37132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -37167,8 +37167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -37202,8 +37202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -37237,8 +37237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -37272,8 +37272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -37307,8 +37307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -37342,8 +37342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -37381,8 +37381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -37416,8 +37416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -37451,8 +37451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -37486,8 +37486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -37521,8 +37521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -37556,8 +37556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -37591,8 +37591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -37626,8 +37626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -37661,8 +37661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -37696,8 +37696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -37731,8 +37731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -37766,8 +37766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -37801,8 +37801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -37836,8 +37836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -37871,8 +37871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -37908,8 +37908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -37943,8 +37943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -37978,8 +37978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -38015,8 +38015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -38052,8 +38052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -38095,8 +38095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -38132,8 +38132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -38167,8 +38167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -38202,8 +38202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -38237,8 +38237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -38272,8 +38272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -38309,8 +38309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -38344,8 +38344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -38379,8 +38379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -38414,8 +38414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -38449,8 +38449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -38486,8 +38486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -38527,8 +38527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -38570,8 +38570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -38605,8 +38605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -38644,8 +38644,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -38679,8 +38679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -38720,8 +38720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -38757,8 +38757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -38794,8 +38794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -38831,8 +38831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -38870,8 +38870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -38905,8 +38905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -38942,8 +38942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -38977,8 +38977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -39012,8 +39012,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -39047,8 +39047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -39082,8 +39082,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -39117,8 +39117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -39152,8 +39152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -39187,8 +39187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -39222,8 +39222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -39257,8 +39257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -39292,8 +39292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -39329,8 +39329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -39364,8 +39364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -39399,8 +39399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -39434,8 +39434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -39469,8 +39469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -39504,8 +39504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -39541,8 +39541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -39576,8 +39576,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -39611,8 +39611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -39646,8 +39646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -39681,8 +39681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -39716,8 +39716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -39751,8 +39751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -39786,8 +39786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -39823,8 +39823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -39866,8 +39866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -39901,8 +39901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -39936,8 +39936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -39971,8 +39971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -40012,8 +40012,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -40049,8 +40049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -40086,8 +40086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -40123,8 +40123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -40162,8 +40162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -40197,8 +40197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -40232,8 +40232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -40267,8 +40267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -40302,8 +40302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -40337,8 +40337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -40372,8 +40372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -40407,8 +40407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -40442,8 +40442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -40485,8 +40485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -40520,8 +40520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -40565,8 +40565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -40610,8 +40610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-5-1</v>
       </c>
@@ -40655,8 +40655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-6-1</v>
       </c>
@@ -40700,8 +40700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-7-1</v>
       </c>
@@ -40743,8 +40743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-8-1</v>
       </c>
@@ -40786,8 +40786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-9-1</v>
       </c>
@@ -40831,8 +40831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-10-1</v>
       </c>
@@ -40876,8 +40876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-11-1</v>
       </c>
@@ -40921,8 +40921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-12-1</v>
       </c>
@@ -40966,8 +40966,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-13-1</v>
       </c>
@@ -41011,8 +41011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-1</v>
       </c>
@@ -41056,8 +41056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-2</v>
       </c>
@@ -41099,8 +41099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-3</v>
       </c>
@@ -41142,8 +41142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-4</v>
       </c>
@@ -41185,8 +41185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-5</v>
       </c>
@@ -41228,8 +41228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-6</v>
       </c>
@@ -41271,8 +41271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-7</v>
       </c>
@@ -41314,8 +41314,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-8</v>
       </c>
@@ -41357,8 +41357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-9</v>
       </c>
@@ -41400,8 +41400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-10</v>
       </c>
@@ -41443,8 +41443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-15-1</v>
       </c>
@@ -41488,8 +41488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-16-1</v>
       </c>
@@ -41525,8 +41525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-1</v>
       </c>
@@ -41570,8 +41570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-2</v>
       </c>
@@ -41613,8 +41613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-3</v>
       </c>
@@ -41656,8 +41656,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-4</v>
       </c>
@@ -41699,8 +41699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-5</v>
       </c>
@@ -41742,8 +41742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-6</v>
       </c>
@@ -41785,8 +41785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-7</v>
       </c>
@@ -41828,8 +41828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F328),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F328)&gt;0)*ROW($F$11:F328),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J328),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-8</v>
       </c>
@@ -41871,8 +41871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F329),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F329)&gt;0)*ROW($F$11:F329),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J329),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-9</v>
       </c>
@@ -41914,8 +41914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F330),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F330)&gt;0)*ROW($F$11:F330),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J330),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-10</v>
       </c>
@@ -41957,8 +41957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F331),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F331)&gt;0)*ROW($F$11:F331),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J331),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-1</v>
       </c>
@@ -42002,8 +42002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F332),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F332)&gt;0)*ROW($F$11:F332),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J332),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-2</v>
       </c>
@@ -42045,8 +42045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F333),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F333)&gt;0)*ROW($F$11:F333),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J333),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-3</v>
       </c>
@@ -42088,8 +42088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F334),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F334)&gt;0)*ROW($F$11:F334),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J334),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-4</v>
       </c>
@@ -42131,8 +42131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F335),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F335)&gt;0)*ROW($F$11:F335),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J335),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-5</v>
       </c>
@@ -42174,8 +42174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F336),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F336)&gt;0)*ROW($F$11:F336),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J336),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-6</v>
       </c>
@@ -42217,8 +42217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F337),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F337)&gt;0)*ROW($F$11:F337),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J337),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-7</v>
       </c>
@@ -42260,8 +42260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F338),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F338)&gt;0)*ROW($F$11:F338),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J338),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-8</v>
       </c>
@@ -42303,8 +42303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F339),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F339)&gt;0)*ROW($F$11:F339),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J339),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-9</v>
       </c>
@@ -42346,8 +42346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F340),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F340)&gt;0)*ROW($F$11:F340),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J340),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-10</v>
       </c>
@@ -42389,8 +42389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F341),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F341)&gt;0)*ROW($F$11:F341),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J341),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-1</v>
       </c>
@@ -42434,8 +42434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F342),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F342)&gt;0)*ROW($F$11:F342),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J342),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-2</v>
       </c>
@@ -42477,8 +42477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F343),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F343)&gt;0)*ROW($F$11:F343),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J343),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-3</v>
       </c>
@@ -42520,8 +42520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F344),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F344)&gt;0)*ROW($F$11:F344),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J344),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-4</v>
       </c>
@@ -42563,8 +42563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F345),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F345)&gt;0)*ROW($F$11:F345),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J345),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-5</v>
       </c>
@@ -42606,8 +42606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F346),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F346)&gt;0)*ROW($F$11:F346),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J346),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-6</v>
       </c>
@@ -42649,8 +42649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F347),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F347)&gt;0)*ROW($F$11:F347),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J347),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-7</v>
       </c>
@@ -42692,8 +42692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F348),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F348)&gt;0)*ROW($F$11:F348),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J348),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-8</v>
       </c>
@@ -42735,8 +42735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F349),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F349)&gt;0)*ROW($F$11:F349),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J349),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-9</v>
       </c>
@@ -42778,8 +42778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F350),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F350)&gt;0)*ROW($F$11:F350),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J350),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-10</v>
       </c>
@@ -42821,8 +42821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F351),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F351)&gt;0)*ROW($F$11:F351),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J351),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-20-1</v>
       </c>
@@ -42856,8 +42856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F352),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F352)&gt;0)*ROW($F$11:F352),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J352),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-21-1</v>
       </c>
@@ -42891,8 +42891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F353),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F353)&gt;0)*ROW($F$11:F353),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J353),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -42928,8 +42928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F354),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F354)&gt;0)*ROW($F$11:F354),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J354),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -42963,8 +42963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F355),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F355)&gt;0)*ROW($F$11:F355),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J355),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -43000,8 +43000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F356),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F356)&gt;0)*ROW($F$11:F356),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J356),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-1</v>
       </c>
@@ -43035,8 +43035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F357),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F357)&gt;0)*ROW($F$11:F357),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J357),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -43072,8 +43072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F358),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F358)&gt;0)*ROW($F$11:F358),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J358),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -43121,8 +43121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F359),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F359)&gt;0)*ROW($F$11:F359),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J359),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-2</v>
       </c>
@@ -43164,8 +43164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F360),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F360)&gt;0)*ROW($F$11:F360),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J360),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -43199,8 +43199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F361),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F361)&gt;0)*ROW($F$11:F361),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J361),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -43244,8 +43244,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F362),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F362)&gt;0)*ROW($F$11:F362),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J362),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -43279,8 +43279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F363),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F363)&gt;0)*ROW($F$11:F363),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J363),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -43314,8 +43314,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F364),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F364)&gt;0)*ROW($F$11:F364),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J364),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -43349,8 +43349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F365),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F365)&gt;0)*ROW($F$11:F365),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J365),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -43384,8 +43384,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F366),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F366)&gt;0)*ROW($F$11:F366),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J366),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -43419,8 +43419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F367),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F367)&gt;0)*ROW($F$11:F367),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J367),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -43462,8 +43462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F368),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F368)&gt;0)*ROW($F$11:F368),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J368),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -43499,8 +43499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F369),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F369)&gt;0)*ROW($F$11:F369),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J369),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -43544,8 +43544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F370),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F370)&gt;0)*ROW($F$11:F370),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J370),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -43593,8 +43593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F371),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F371)&gt;0)*ROW($F$11:F371),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J371),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-2</v>
       </c>
@@ -43636,8 +43636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F372),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F372)&gt;0)*ROW($F$11:F372),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J372),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-3</v>
       </c>
@@ -43679,8 +43679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F373),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F373)&gt;0)*ROW($F$11:F373),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J373),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-4</v>
       </c>
@@ -43722,8 +43722,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F374),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F374)&gt;0)*ROW($F$11:F374),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J374),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-5</v>
       </c>
@@ -43765,8 +43765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F375),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F375)&gt;0)*ROW($F$11:F375),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J375),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-6</v>
       </c>
@@ -43808,8 +43808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F376),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F376)&gt;0)*ROW($F$11:F376),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J376),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-7</v>
       </c>
@@ -43851,8 +43851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F377),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F377)&gt;0)*ROW($F$11:F377),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J377),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-8</v>
       </c>
@@ -43894,8 +43894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F378),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F378)&gt;0)*ROW($F$11:F378),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J378),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-9</v>
       </c>
@@ -43937,8 +43937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F379),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F379)&gt;0)*ROW($F$11:F379),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J379),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-10</v>
       </c>
@@ -43980,8 +43980,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F380),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F380)&gt;0)*ROW($F$11:F380),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J380),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -44017,8 +44017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F381),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F381)&gt;0)*ROW($F$11:F381),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J381),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-2-1</v>
       </c>
@@ -44062,8 +44062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F382),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F382)&gt;0)*ROW($F$11:F382),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J382),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-3-1</v>
       </c>
@@ -44107,8 +44107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F383),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F383)&gt;0)*ROW($F$11:F383),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J383),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-4-1</v>
       </c>
@@ -44152,8 +44152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F384),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F384)&gt;0)*ROW($F$11:F384),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J384),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -44191,8 +44191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F385),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F385)&gt;0)*ROW($F$11:F385),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J385),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-2-1</v>
       </c>
@@ -44226,8 +44226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F386),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F386)&gt;0)*ROW($F$11:F386),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J386),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-3-1</v>
       </c>
@@ -44261,8 +44261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F387),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F387)&gt;0)*ROW($F$11:F387),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J387),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-1</v>
       </c>
@@ -44310,8 +44310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F388),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F388)&gt;0)*ROW($F$11:F388),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J388),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-2</v>
       </c>
@@ -44353,8 +44353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F389),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F389)&gt;0)*ROW($F$11:F389),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J389),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-3</v>
       </c>
@@ -44396,8 +44396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F390),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F390)&gt;0)*ROW($F$11:F390),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J390),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-4</v>
       </c>
@@ -44439,8 +44439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F391),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F391)&gt;0)*ROW($F$11:F391),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J391),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-5</v>
       </c>
@@ -44482,8 +44482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F392),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F392)&gt;0)*ROW($F$11:F392),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J392),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-6</v>
       </c>
@@ -44525,8 +44525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F393),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F393)&gt;0)*ROW($F$11:F393),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J393),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-7</v>
       </c>
@@ -44568,8 +44568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F394),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F394)&gt;0)*ROW($F$11:F394),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J394),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-8</v>
       </c>
@@ -44611,8 +44611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F395),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F395)&gt;0)*ROW($F$11:F395),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J395),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-9</v>
       </c>
@@ -44654,8 +44654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F396),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F396)&gt;0)*ROW($F$11:F396),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J396),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-10</v>
       </c>
@@ -44697,8 +44697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F397),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F397)&gt;0)*ROW($F$11:F397),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J397),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-1</v>
       </c>
@@ -44742,8 +44742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F398),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F398)&gt;0)*ROW($F$11:F398),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J398),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-2</v>
       </c>
@@ -44785,8 +44785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F399),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F399)&gt;0)*ROW($F$11:F399),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J399),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-3</v>
       </c>
@@ -44828,8 +44828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F400),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F400)&gt;0)*ROW($F$11:F400),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J400),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-4</v>
       </c>
@@ -44871,8 +44871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F401),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F401)&gt;0)*ROW($F$11:F401),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J401),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-5</v>
       </c>
@@ -44914,8 +44914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F402),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F402)&gt;0)*ROW($F$11:F402),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J402),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-6</v>
       </c>
@@ -44957,8 +44957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F403),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F403)&gt;0)*ROW($F$11:F403),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J403),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-7</v>
       </c>
@@ -45000,8 +45000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F404),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F404)&gt;0)*ROW($F$11:F404),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J404),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-1</v>
       </c>
@@ -45045,8 +45045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F405),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F405)&gt;0)*ROW($F$11:F405),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J405),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-2</v>
       </c>
@@ -45088,8 +45088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F406),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F406)&gt;0)*ROW($F$11:F406),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J406),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-3</v>
       </c>
@@ -45131,8 +45131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F407),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F407)&gt;0)*ROW($F$11:F407),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J407),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-4</v>
       </c>
@@ -45174,8 +45174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F408),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F408)&gt;0)*ROW($F$11:F408),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J408),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-5</v>
       </c>
@@ -45217,8 +45217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F409),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F409)&gt;0)*ROW($F$11:F409),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J409),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-6</v>
       </c>
@@ -45260,8 +45260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F410),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F410)&gt;0)*ROW($F$11:F410),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J410),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-7</v>
       </c>
@@ -45303,8 +45303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F411),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F411)&gt;0)*ROW($F$11:F411),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J411),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-4-1</v>
       </c>
@@ -45338,8 +45338,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F412),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F412)&gt;0)*ROW($F$11:F412),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J412),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-5-1</v>
       </c>
@@ -45373,8 +45373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F413),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F413)&gt;0)*ROW($F$11:F413),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J413),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-6-1</v>
       </c>
@@ -45408,8 +45408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F414),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F414)&gt;0)*ROW($F$11:F414),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J414),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-7-1</v>
       </c>
@@ -45443,8 +45443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F415),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F415)&gt;0)*ROW($F$11:F415),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J415),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-8-1</v>
       </c>
@@ -45478,8 +45478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F416),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F416)&gt;0)*ROW($F$11:F416),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J416),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-9-1</v>
       </c>
@@ -45513,8 +45513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F417),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F417)&gt;0)*ROW($F$11:F417),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J417),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-10-1</v>
       </c>
@@ -45548,8 +45548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F418),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F418)&gt;0)*ROW($F$11:F418),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J418),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-11-1</v>
       </c>
@@ -45593,8 +45593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F419),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F419)&gt;0)*ROW($F$11:F419),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J419),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-12-1</v>
       </c>
@@ -45628,8 +45628,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F420),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F420)&gt;0)*ROW($F$11:F420),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J420),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-13-1</v>
       </c>
@@ -45663,8 +45663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F421),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F421)&gt;0)*ROW($F$11:F421),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J421),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-14-1</v>
       </c>
@@ -45698,8 +45698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F422),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F422)&gt;0)*ROW($F$11:F422),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J422),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-1-1</v>
       </c>
@@ -45745,8 +45745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F423),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F423)&gt;0)*ROW($F$11:F423),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J423),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-2-1</v>
       </c>
@@ -45780,8 +45780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F424),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F424)&gt;0)*ROW($F$11:F424),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J424),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-3-1</v>
       </c>
@@ -45815,8 +45815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F425),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F425)&gt;0)*ROW($F$11:F425),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J425),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-4-1</v>
       </c>
@@ -45850,8 +45850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F426),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F426)&gt;0)*ROW($F$11:F426),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J426),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-5-1</v>
       </c>
@@ -45885,8 +45885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F427),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F427)&gt;0)*ROW($F$11:F427),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J427),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-6-1</v>
       </c>
@@ -45920,8 +45920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F428),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F428)&gt;0)*ROW($F$11:F428),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J428),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-7-1</v>
       </c>
@@ -45955,8 +45955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F429),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F429)&gt;0)*ROW($F$11:F429),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J429),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-1-1</v>
       </c>
@@ -45998,8 +45998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F430),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F430)&gt;0)*ROW($F$11:F430),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J430),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-2-1</v>
       </c>
@@ -46033,8 +46033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F431),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F431)&gt;0)*ROW($F$11:F431),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J431),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-3-1</v>
       </c>
@@ -46068,8 +46068,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F432),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F432)&gt;0)*ROW($F$11:F432),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J432),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-4-1</v>
       </c>
@@ -46103,8 +46103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F433),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F433)&gt;0)*ROW($F$11:F433),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J433),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-5-1</v>
       </c>
@@ -46138,8 +46138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F434),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F434)&gt;0)*ROW($F$11:F434),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J434),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-1-1</v>
       </c>
@@ -46177,8 +46177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F435),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F435)&gt;0)*ROW($F$11:F435),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J435),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-2-1</v>
       </c>
@@ -46212,8 +46212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F436),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F436)&gt;0)*ROW($F$11:F436),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J436),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-3-1</v>
       </c>
@@ -46247,8 +46247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F437),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F437)&gt;0)*ROW($F$11:F437),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J437),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-4-1</v>
       </c>
@@ -46282,8 +46282,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F438),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F438)&gt;0)*ROW($F$11:F438),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J438),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-5-1</v>
       </c>
@@ -46317,8 +46317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F439),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F439)&gt;0)*ROW($F$11:F439),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J439),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-1</v>
       </c>
@@ -46368,8 +46368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F440),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F440)&gt;0)*ROW($F$11:F440),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J440),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-2-1</v>
       </c>
@@ -46403,8 +46403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F441),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F441)&gt;0)*ROW($F$11:F441),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J441),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-1</v>
       </c>
@@ -46448,8 +46448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F442),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F442)&gt;0)*ROW($F$11:F442),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J442),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-4-1</v>
       </c>
@@ -46483,8 +46483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F443),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F443)&gt;0)*ROW($F$11:F443),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J443),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-5-1</v>
       </c>
@@ -46518,8 +46518,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F444),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F444)&gt;0)*ROW($F$11:F444),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J444),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-6-1</v>
       </c>
@@ -46563,8 +46563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F445),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F445)&gt;0)*ROW($F$11:F445),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J445),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>116-1-1</v>
       </c>
@@ -46610,8 +46610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F446),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F446)&gt;0)*ROW($F$11:F446),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J446),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-1</v>
       </c>
@@ -46659,8 +46659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F447),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F447)&gt;0)*ROW($F$11:F447),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J447),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-2</v>
       </c>
@@ -46702,8 +46702,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F448),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F448)&gt;0)*ROW($F$11:F448),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J448),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>118-1-1</v>
       </c>
@@ -46749,8 +46749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F449),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F449)&gt;0)*ROW($F$11:F449),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J449),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-1-1</v>
       </c>
@@ -46792,8 +46792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F450),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F450)&gt;0)*ROW($F$11:F450),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J450),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-2-1</v>
       </c>
@@ -46998,11 +46998,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D11),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -47043,11 +47043,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D12),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-2</v>
       </c>
@@ -47078,11 +47078,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D13),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -47119,11 +47119,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D14),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-2</v>
       </c>
@@ -47154,11 +47154,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D15),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -47189,11 +47189,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D16),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -47230,11 +47230,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D17),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -47273,11 +47273,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D18),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -47308,11 +47308,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D19),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -47349,11 +47349,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D20),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-2</v>
       </c>
@@ -47384,11 +47384,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D21),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D21)&gt;0)*ROW($D$11:D21),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E21),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E21)&gt;0)*ROW($E$11:E21),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -47419,11 +47419,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D22),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D22)&gt;0)*ROW($D$11:D22),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E22),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E22)&gt;0)*ROW($E$11:E22),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -47456,11 +47456,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D23),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D23)&gt;0)*ROW($D$11:D23),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E23),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E23)&gt;0)*ROW($E$11:E23),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -47499,11 +47499,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D24),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D24)&gt;0)*ROW($D$11:D24),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E24),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E24)&gt;0)*ROW($E$11:E24),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-2</v>
       </c>
